--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -433,7 +433,7 @@
         <v>吊墜</v>
       </c>
       <c r="D2" t="str">
-        <v>丝带</v>
+        <v>絲帶</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -525,7 +525,7 @@
         <v>珍珠</v>
       </c>
       <c r="D6" t="str">
-        <v>圆珍珠</v>
+        <v>圓珍珠</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -548,7 +548,7 @@
         <v>珍珠</v>
       </c>
       <c r="D7" t="str">
-        <v>圆珍珠</v>
+        <v>圓珍珠</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -571,7 +571,7 @@
         <v>珍珠</v>
       </c>
       <c r="D8" t="str">
-        <v>圆珍珠</v>
+        <v>圓珍珠</v>
       </c>
       <c r="E8">
         <v>10</v>
@@ -594,7 +594,7 @@
         <v>隔珠</v>
       </c>
       <c r="D9" t="str">
-        <v>镂空钻蕾丝</v>
+        <v>鏤空鑽蕾絲</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -617,7 +617,7 @@
         <v>吊墜</v>
       </c>
       <c r="D10" t="str">
-        <v>满镶星星</v>
+        <v>滿鑲星星</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -640,7 +640,7 @@
         <v>吊墜</v>
       </c>
       <c r="D11" t="str">
-        <v>霹雳</v>
+        <v>霹靂</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -663,7 +663,7 @@
         <v>吊墜</v>
       </c>
       <c r="D12" t="str">
-        <v>镂空小猫</v>
+        <v>鏤空小貓</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -686,7 +686,7 @@
         <v>吊墜</v>
       </c>
       <c r="D13" t="str">
-        <v>爱心曲别针</v>
+        <v>愛心曲別針</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -709,7 +709,7 @@
         <v>隔珠</v>
       </c>
       <c r="D14" t="str">
-        <v>锆石魔盒钻</v>
+        <v>鋯石魔盒鑽</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -824,7 +824,7 @@
         <v>吊墜</v>
       </c>
       <c r="D19" t="str">
-        <v>银色满镶月亮</v>
+        <v>銀色滿鑲月亮</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -847,7 +847,7 @@
         <v>隔珠</v>
       </c>
       <c r="D20" t="str">
-        <v>锆石方钻</v>
+        <v>鋯石方鑽</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -939,7 +939,7 @@
         <v>吊墜</v>
       </c>
       <c r="D24" t="str">
-        <v>镂空金福</v>
+        <v>鏤空金福</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -1376,7 +1376,7 @@
         <v>隔珠</v>
       </c>
       <c r="D43" t="str">
-        <v>五棱银钻</v>
+        <v>五稜銀鑽</v>
       </c>
       <c r="E43">
         <v>5</v>
@@ -1399,7 +1399,7 @@
         <v>吊墜</v>
       </c>
       <c r="D44" t="str">
-        <v>锆石星星</v>
+        <v>鋯石星星</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -1422,7 +1422,7 @@
         <v>吊墜</v>
       </c>
       <c r="D45" t="str">
-        <v>寻心钥匙</v>
+        <v>尋心鑰匙</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -1445,7 +1445,7 @@
         <v>吊墜</v>
       </c>
       <c r="D46" t="str">
-        <v>白水鱼尾</v>
+        <v>白水魚尾</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -1468,7 +1468,7 @@
         <v>隔珠</v>
       </c>
       <c r="D47" t="str">
-        <v>转运柄</v>
+        <v>轉運柄</v>
       </c>
       <c r="E47">
         <v>8</v>
@@ -1491,7 +1491,7 @@
         <v>隔珠</v>
       </c>
       <c r="D48" t="str">
-        <v>恶魔之眼</v>
+        <v>惡魔之眼</v>
       </c>
       <c r="E48">
         <v>6</v>
@@ -1514,7 +1514,7 @@
         <v>隔珠</v>
       </c>
       <c r="D49" t="str">
-        <v>扭纹小环</v>
+        <v>扭紋小環</v>
       </c>
       <c r="E49">
         <v>5</v>
@@ -1537,7 +1537,7 @@
         <v>吊墜</v>
       </c>
       <c r="D50" t="str">
-        <v>星星奖章</v>
+        <v>星星獎章</v>
       </c>
       <c r="E50">
         <v>2</v>
@@ -1560,7 +1560,7 @@
         <v>隔珠</v>
       </c>
       <c r="D51" t="str">
-        <v>粉樱花</v>
+        <v>粉櫻花</v>
       </c>
       <c r="E51">
         <v>6</v>
@@ -1583,7 +1583,7 @@
         <v>隔珠</v>
       </c>
       <c r="D52" t="str">
-        <v>锆石花形钻</v>
+        <v>鋯石花形鑽</v>
       </c>
       <c r="E52">
         <v>6</v>
@@ -1675,7 +1675,7 @@
         <v>隔珠</v>
       </c>
       <c r="D56" t="str">
-        <v>锆石切割</v>
+        <v>鋯石切割</v>
       </c>
       <c r="E56">
         <v>5</v>
@@ -1698,7 +1698,7 @@
         <v>隔珠</v>
       </c>
       <c r="D57" t="str">
-        <v>交织戒</v>
+        <v>交織戒</v>
       </c>
       <c r="E57">
         <v>6</v>
@@ -1721,7 +1721,7 @@
         <v>吊墜</v>
       </c>
       <c r="D58" t="str">
-        <v>锆石晨星</v>
+        <v>鋯石晨星</v>
       </c>
       <c r="E58">
         <v>2</v>
@@ -1744,7 +1744,7 @@
         <v>隔珠</v>
       </c>
       <c r="D59" t="str">
-        <v>藏银十字架</v>
+        <v>藏銀十字架</v>
       </c>
       <c r="E59">
         <v>8</v>
@@ -1767,7 +1767,7 @@
         <v>隔珠</v>
       </c>
       <c r="D60" t="str">
-        <v>锆石切割双层</v>
+        <v>鋯石切割雙層</v>
       </c>
       <c r="E60">
         <v>6</v>
@@ -1790,7 +1790,7 @@
         <v>隔珠</v>
       </c>
       <c r="D61" t="str">
-        <v>银色小环</v>
+        <v>銀色小環</v>
       </c>
       <c r="E61">
         <v>5</v>
@@ -2020,7 +2020,7 @@
         <v>吊墜</v>
       </c>
       <c r="D71" t="str">
-        <v>满钻蝴蝶</v>
+        <v>滿鑽蝴蝶</v>
       </c>
       <c r="E71">
         <v>2</v>
@@ -2066,7 +2066,7 @@
         <v>隔珠</v>
       </c>
       <c r="D73" t="str">
-        <v>镂空金蕾丝</v>
+        <v>鏤空金蕾絲</v>
       </c>
       <c r="E73">
         <v>6</v>
@@ -2250,7 +2250,7 @@
         <v>隔珠</v>
       </c>
       <c r="D81" t="str">
-        <v>复古雕花</v>
+        <v>復古雕花</v>
       </c>
       <c r="E81">
         <v>8</v>
@@ -2342,7 +2342,7 @@
         <v>隔珠</v>
       </c>
       <c r="D85" t="str">
-        <v>小祥云</v>
+        <v>小祥雲</v>
       </c>
       <c r="E85">
         <v>5</v>
@@ -2365,7 +2365,7 @@
         <v>隔珠</v>
       </c>
       <c r="D86" t="str">
-        <v>大祥云</v>
+        <v>大祥雲</v>
       </c>
       <c r="E86">
         <v>5</v>
@@ -2595,7 +2595,7 @@
         <v>隔珠</v>
       </c>
       <c r="D96" t="str">
-        <v>锆石猫咪</v>
+        <v>鋯石貓咪</v>
       </c>
       <c r="E96">
         <v>8</v>
@@ -2687,7 +2687,7 @@
         <v>隔珠</v>
       </c>
       <c r="D100" t="str">
-        <v>五棱金钻</v>
+        <v>五稜金鑽</v>
       </c>
       <c r="E100">
         <v>5</v>
@@ -2825,7 +2825,7 @@
         <v>吊墜</v>
       </c>
       <c r="D106" t="str">
-        <v>葫芦成双</v>
+        <v>葫蘆成雙</v>
       </c>
       <c r="E106">
         <v>2</v>
@@ -2917,7 +2917,7 @@
         <v>隔珠</v>
       </c>
       <c r="D110" t="str">
-        <v>锆石螺旋</v>
+        <v>鋯石螺旋</v>
       </c>
       <c r="E110">
         <v>6</v>
@@ -2940,7 +2940,7 @@
         <v>吊墜</v>
       </c>
       <c r="D111" t="str">
-        <v>闪跃月亮</v>
+        <v>閃躍月亮</v>
       </c>
       <c r="E111">
         <v>2</v>
@@ -2963,7 +2963,7 @@
         <v>隔珠</v>
       </c>
       <c r="D112" t="str">
-        <v>锆石钻闪</v>
+        <v>鋯石鑽閃</v>
       </c>
       <c r="E112">
         <v>5</v>
@@ -2986,7 +2986,7 @@
         <v>吊墜</v>
       </c>
       <c r="D113" t="str">
-        <v>小年兽</v>
+        <v>小年獸</v>
       </c>
       <c r="E113">
         <v>2</v>
@@ -3009,7 +3009,7 @@
         <v>隔珠</v>
       </c>
       <c r="D114" t="str">
-        <v>金色小环</v>
+        <v>金色小環</v>
       </c>
       <c r="E114">
         <v>5</v>
@@ -3032,7 +3032,7 @@
         <v>吊墜</v>
       </c>
       <c r="D115" t="str">
-        <v>北极星</v>
+        <v>北極星</v>
       </c>
       <c r="E115">
         <v>2</v>
@@ -3055,7 +3055,7 @@
         <v>隔珠</v>
       </c>
       <c r="D116" t="str">
-        <v>彩锆轮</v>
+        <v>彩鋯輪</v>
       </c>
       <c r="E116">
         <v>6</v>
@@ -3147,7 +3147,7 @@
         <v>隔珠</v>
       </c>
       <c r="D120" t="str">
-        <v>醒狮</v>
+        <v>醒獅</v>
       </c>
       <c r="E120">
         <v>8</v>
@@ -3308,7 +3308,7 @@
         <v>吊墜</v>
       </c>
       <c r="D127" t="str">
-        <v>锆石彩虹</v>
+        <v>鋯石彩虹</v>
       </c>
       <c r="E127">
         <v>2</v>
@@ -3331,7 +3331,7 @@
         <v>隔珠</v>
       </c>
       <c r="D128" t="str">
-        <v>小锆石钻闪</v>
+        <v>小鋯石鑽閃</v>
       </c>
       <c r="E128">
         <v>5</v>
@@ -3515,7 +3515,7 @@
         <v>隔珠</v>
       </c>
       <c r="D136" t="str">
-        <v>银色小珠</v>
+        <v>銀色小珠</v>
       </c>
       <c r="E136">
         <v>6</v>
@@ -3607,7 +3607,7 @@
         <v>吊墜</v>
       </c>
       <c r="D140" t="str">
-        <v>金色满镶月亮</v>
+        <v>金色滿鑲月亮</v>
       </c>
       <c r="E140">
         <v>2</v>
@@ -3630,7 +3630,7 @@
         <v>隔珠</v>
       </c>
       <c r="D141" t="str">
-        <v>花边轨道</v>
+        <v>花邊軌道</v>
       </c>
       <c r="E141">
         <v>6</v>
@@ -3722,7 +3722,7 @@
         <v>隔珠</v>
       </c>
       <c r="D145" t="str">
-        <v>回财纹</v>
+        <v>回財紋</v>
       </c>
       <c r="E145">
         <v>5</v>
@@ -3745,7 +3745,7 @@
         <v>隔珠</v>
       </c>
       <c r="D146" t="str">
-        <v>藏银卷草</v>
+        <v>藏銀卷草</v>
       </c>
       <c r="E146">
         <v>6</v>
@@ -3791,7 +3791,7 @@
         <v>隔珠</v>
       </c>
       <c r="D148" t="str">
-        <v>藏银十字花</v>
+        <v>藏銀十字花</v>
       </c>
       <c r="E148">
         <v>8</v>
@@ -3883,7 +3883,7 @@
         <v>吊墜</v>
       </c>
       <c r="D152" t="str">
-        <v>藏银羽毛</v>
+        <v>藏銀羽毛</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -3975,7 +3975,7 @@
         <v>隔珠</v>
       </c>
       <c r="D156" t="str">
-        <v>藏银树叶</v>
+        <v>藏銀樹葉</v>
       </c>
       <c r="E156">
         <v>6</v>
@@ -4021,7 +4021,7 @@
         <v>隔珠</v>
       </c>
       <c r="D158" t="str">
-        <v>锆石钻闪双层</v>
+        <v>鋯石鑽閃雙層</v>
       </c>
       <c r="E158">
         <v>6</v>
@@ -4044,7 +4044,7 @@
         <v>隔珠</v>
       </c>
       <c r="D159" t="str">
-        <v>藏银瓦片</v>
+        <v>藏銀瓦片</v>
       </c>
       <c r="E159">
         <v>8</v>
@@ -4067,7 +4067,7 @@
         <v>吊墜</v>
       </c>
       <c r="D160" t="str">
-        <v>四叶草</v>
+        <v>四葉草</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -4228,7 +4228,7 @@
         <v>隔珠</v>
       </c>
       <c r="D167" t="str">
-        <v>银色六字真言</v>
+        <v>銀色六字真言</v>
       </c>
       <c r="E167">
         <v>8</v>
@@ -4251,7 +4251,7 @@
         <v>隔珠</v>
       </c>
       <c r="D168" t="str">
-        <v>凯尔特结</v>
+        <v>凱爾特結</v>
       </c>
       <c r="E168">
         <v>6</v>
@@ -4274,7 +4274,7 @@
         <v>隔珠</v>
       </c>
       <c r="D169" t="str">
-        <v>银色绣球</v>
+        <v>銀色繡球</v>
       </c>
       <c r="E169">
         <v>8</v>
@@ -4366,7 +4366,7 @@
         <v>吊墜</v>
       </c>
       <c r="D173" t="str">
-        <v>王国之泪</v>
+        <v>王國之淚</v>
       </c>
       <c r="E173">
         <v>2</v>
@@ -4964,7 +4964,7 @@
         <v>吊墜</v>
       </c>
       <c r="D199" t="str">
-        <v>藏银蝴蝶流苏</v>
+        <v>藏銀蝴蝶流蘇</v>
       </c>
       <c r="E199">
         <v>2</v>
@@ -4987,7 +4987,7 @@
         <v>隔珠</v>
       </c>
       <c r="D200" t="str">
-        <v>玫瑰花环</v>
+        <v>玫瑰花環</v>
       </c>
       <c r="E200">
         <v>6</v>
@@ -5010,7 +5010,7 @@
         <v>隔珠</v>
       </c>
       <c r="D201" t="str">
-        <v>白玛瑙魔盒</v>
+        <v>白瑪瑙魔盒</v>
       </c>
       <c r="E201">
         <v>8</v>
@@ -5033,7 +5033,7 @@
         <v>隔珠</v>
       </c>
       <c r="D202" t="str">
-        <v>藏银回纹</v>
+        <v>藏銀回紋</v>
       </c>
       <c r="E202">
         <v>5</v>
@@ -5125,7 +5125,7 @@
         <v>隔珠</v>
       </c>
       <c r="D206" t="str">
-        <v>朱砂魔盒</v>
+        <v>硃砂魔盒</v>
       </c>
       <c r="E206">
         <v>8</v>
@@ -5148,7 +5148,7 @@
         <v>吊墜</v>
       </c>
       <c r="D207" t="str">
-        <v>藏银十字吊坠</v>
+        <v>藏銀十字吊墜</v>
       </c>
       <c r="E207">
         <v>2</v>
@@ -5171,7 +5171,7 @@
         <v>吊墜</v>
       </c>
       <c r="D208" t="str">
-        <v>藏银叶丛</v>
+        <v>藏銀葉叢</v>
       </c>
       <c r="E208">
         <v>2</v>
@@ -5194,7 +5194,7 @@
         <v>隔珠</v>
       </c>
       <c r="D209" t="str">
-        <v>藏银小花立方</v>
+        <v>藏銀小花立方</v>
       </c>
       <c r="E209">
         <v>8</v>
@@ -5217,7 +5217,7 @@
         <v>隔珠</v>
       </c>
       <c r="D210" t="str">
-        <v>藏银大花立方</v>
+        <v>藏銀大花立方</v>
       </c>
       <c r="E210">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>隔珠</v>
       </c>
       <c r="D214" t="str">
-        <v>景泰蓝福球</v>
+        <v>景泰藍福球</v>
       </c>
       <c r="E214">
         <v>8</v>
@@ -5884,7 +5884,7 @@
         <v>吊墜</v>
       </c>
       <c r="D239" t="str">
-        <v>捕梦网</v>
+        <v>捕夢網</v>
       </c>
       <c r="E239">
         <v>2</v>

--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G281"/>
+  <dimension ref="A1:G195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,30 +424,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>sd_pnd_2</v>
+        <v>xhyl_cysl_6</v>
       </c>
       <c r="B2" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C2" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D2" t="str">
-        <v>絲帶</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G2" t="str">
-        <v>丝带.png</v>
+        <v>雪花幽灵.png</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>nbj_cysl_6</v>
+        <v>xhyl_cysl_8</v>
       </c>
       <c r="B3" t="str">
         <v>珠子</v>
@@ -456,21 +456,21 @@
         <v>水晶</v>
       </c>
       <c r="D3" t="str">
-        <v>奶白晶</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G3" t="str">
-        <v>奶白晶.png</v>
+        <v>雪花幽灵.png</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>nbj_cysl_8</v>
+        <v>xhyl_cysl_10</v>
       </c>
       <c r="B4" t="str">
         <v>珠子</v>
@@ -479,21 +479,21 @@
         <v>水晶</v>
       </c>
       <c r="D4" t="str">
-        <v>奶白晶</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="G4" t="str">
-        <v>奶白晶.png</v>
+        <v>雪花幽灵.png</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>nbj_cysl_10</v>
+        <v>bsj_cysl_6</v>
       </c>
       <c r="B5" t="str">
         <v>珠子</v>
@@ -502,228 +502,228 @@
         <v>水晶</v>
       </c>
       <c r="D5" t="str">
-        <v>奶白晶</v>
+        <v>白水晶</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G5" t="str">
-        <v>奶白晶.png</v>
+        <v>白水晶.png</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>dszz_prl_6</v>
+        <v>bsj_cysl_8</v>
       </c>
       <c r="B6" t="str">
         <v>珠子</v>
       </c>
       <c r="C6" t="str">
-        <v>珍珠</v>
+        <v>水晶</v>
       </c>
       <c r="D6" t="str">
-        <v>圓珍珠</v>
+        <v>白水晶</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G6" t="str">
-        <v>圆珍珠.png</v>
+        <v>白水晶.png</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>dszz_prl_8</v>
+        <v>bsj_cysl_10</v>
       </c>
       <c r="B7" t="str">
         <v>珠子</v>
       </c>
       <c r="C7" t="str">
-        <v>珍珠</v>
+        <v>水晶</v>
       </c>
       <c r="D7" t="str">
-        <v>圓珍珠</v>
+        <v>白水晶</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>199</v>
+        <v>89</v>
       </c>
       <c r="G7" t="str">
-        <v>圆珍珠.png</v>
+        <v>白水晶.png</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>dszz_prl_10</v>
+        <v>byl_cysl_8</v>
       </c>
       <c r="B8" t="str">
         <v>珠子</v>
       </c>
       <c r="C8" t="str">
-        <v>珍珠</v>
+        <v>水晶</v>
       </c>
       <c r="D8" t="str">
-        <v>圓珍珠</v>
+        <v>白幽靈</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="G8" t="str">
-        <v>圆珍珠.png</v>
+        <v>白幽灵.png</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>lkzls_spc_6</v>
+        <v>sd_pnd_2</v>
       </c>
       <c r="B9" t="str">
         <v>配件</v>
       </c>
       <c r="C9" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D9" t="str">
-        <v>鏤空鑽蕾絲</v>
+        <v>絲帶</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G9" t="str">
-        <v>镂空钻蕾丝.png</v>
+        <v>丝带.png</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>mxxx_pnd_2</v>
+        <v>lfj_cysl_8</v>
       </c>
       <c r="B10" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C10" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D10" t="str">
-        <v>滿鑲星星</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>99</v>
       </c>
       <c r="G10" t="str">
-        <v>满镶星星.png</v>
+        <v>绿发晶.png</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>pl_pnd_2</v>
+        <v>lfj_cysl_10</v>
       </c>
       <c r="B11" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C11" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D11" t="str">
-        <v>霹靂</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="G11" t="str">
-        <v>霹雳.png</v>
+        <v>绿发晶.png</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>lkxm_pnd_2</v>
+        <v>dszzhu_prl_6</v>
       </c>
       <c r="B12" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C12" t="str">
-        <v>吊墜</v>
+        <v>珍珠</v>
       </c>
       <c r="D12" t="str">
-        <v>鏤空小貓</v>
+        <v>淡水珍珠</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>99</v>
       </c>
       <c r="G12" t="str">
-        <v>镂空小猫.png</v>
+        <v>淡水珍珠.png</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>axqbz_pnd_2</v>
+        <v>dszzhu_prl_8</v>
       </c>
       <c r="B13" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C13" t="str">
-        <v>吊墜</v>
+        <v>珍珠</v>
       </c>
       <c r="D13" t="str">
-        <v>愛心曲別針</v>
+        <v>淡水珍珠</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="G13" t="str">
-        <v>爱心曲别针.png</v>
+        <v>淡水珍珠.png</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>gsmhz_spc_8</v>
+        <v>dszzhu_prl_10</v>
       </c>
       <c r="B14" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C14" t="str">
-        <v>隔珠</v>
+        <v>珍珠</v>
       </c>
       <c r="D14" t="str">
-        <v>鋯石魔盒鑽</v>
+        <v>淡水珍珠</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="G14" t="str">
-        <v>锆石魔盒钻.png</v>
+        <v>淡水珍珠.png</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>xgfj_cysl_6</v>
+        <v>hfj_cysl_6</v>
       </c>
       <c r="B15" t="str">
         <v>珠子</v>
@@ -732,21 +732,21 @@
         <v>水晶</v>
       </c>
       <c r="D15" t="str">
-        <v>星光粉晶</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E15">
         <v>6</v>
       </c>
       <c r="F15">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G15" t="str">
-        <v>星光粉晶.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>xgfj_cysl_8</v>
+        <v>hfj_cysl_8</v>
       </c>
       <c r="B16" t="str">
         <v>珠子</v>
@@ -755,21 +755,21 @@
         <v>水晶</v>
       </c>
       <c r="D16" t="str">
-        <v>星光粉晶</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E16">
         <v>8</v>
       </c>
       <c r="F16">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G16" t="str">
-        <v>星光粉晶.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>xgfj_cysl_10</v>
+        <v>hfj_cysl_10</v>
       </c>
       <c r="B17" t="str">
         <v>珠子</v>
@@ -778,159 +778,159 @@
         <v>水晶</v>
       </c>
       <c r="D17" t="str">
-        <v>星光粉晶</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E17">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="G17" t="str">
-        <v>星光粉晶.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>lglf_spc_8</v>
+        <v>pts_stn_6</v>
       </c>
       <c r="B18" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C18" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D18" t="str">
-        <v>菱格立方</v>
+        <v>葡萄石</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G18" t="str">
-        <v>菱格立方.png</v>
+        <v>葡萄石.png</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ysmxyl_pnd_2</v>
+        <v>pts_stn_10</v>
       </c>
       <c r="B19" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C19" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D19" t="str">
-        <v>銀色滿鑲月亮</v>
+        <v>葡萄石</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F19">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G19" t="str">
-        <v>银色满镶月亮.png</v>
+        <v>葡萄石.png</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>gsfz_spc_6</v>
+        <v>lys_stn_6</v>
       </c>
       <c r="B20" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C20" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D20" t="str">
-        <v>鋯石方鑽</v>
+        <v>綠螢石</v>
       </c>
       <c r="E20">
         <v>6</v>
       </c>
       <c r="F20">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G20" t="str">
-        <v>锆石方钻.png</v>
+        <v>绿萤石.png</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>by_agt_6</v>
+        <v>lys_stn_8</v>
       </c>
       <c r="B21" t="str">
         <v>珠子</v>
       </c>
       <c r="C21" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D21" t="str">
-        <v>白玉髓</v>
+        <v>綠螢石</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G21" t="str">
-        <v>白玉髓.png</v>
+        <v>绿萤石.png</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>by_agt_8</v>
+        <v>lkzls_spc_6</v>
       </c>
       <c r="B22" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C22" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D22" t="str">
-        <v>白玉髓</v>
+        <v>鏤空鑽蕾絲</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G22" t="str">
-        <v>白玉髓.png</v>
+        <v>镂空钻蕾丝.png</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>by_agt_10</v>
+        <v>mxxx_pnd_2</v>
       </c>
       <c r="B23" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C23" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D23" t="str">
-        <v>白玉髓</v>
+        <v>滿鑲星星</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>99</v>
       </c>
       <c r="G23" t="str">
-        <v>白玉髓.png</v>
+        <v>满镶星星.png</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lkjf_pnd_2</v>
+        <v>pl_pnd_2</v>
       </c>
       <c r="B24" t="str">
         <v>配件</v>
@@ -939,7 +939,7 @@
         <v>吊墜</v>
       </c>
       <c r="D24" t="str">
-        <v>鏤空金福</v>
+        <v>霹靂</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -948,173 +948,173 @@
         <v>99</v>
       </c>
       <c r="G24" t="str">
-        <v>镂空金福.png</v>
+        <v>霹雳.png</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>bsy_cysl_6</v>
+        <v>lkxm_pnd_2</v>
       </c>
       <c r="B25" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C25" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D25" t="str">
-        <v>白石英</v>
+        <v>鏤空小貓</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G25" t="str">
-        <v>白石英.png</v>
+        <v>镂空小猫.png</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>bsy_cysl_8</v>
+        <v>axqbz_pnd_2</v>
       </c>
       <c r="B26" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C26" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D26" t="str">
-        <v>白石英</v>
+        <v>愛心曲別針</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G26" t="str">
-        <v>白石英.png</v>
+        <v>爱心曲别针.png</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>bsy_cysl_10</v>
+        <v>gsmhz_spc_8</v>
       </c>
       <c r="B27" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C27" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D27" t="str">
-        <v>白石英</v>
+        <v>鋯石魔盒鑽</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G27" t="str">
-        <v>白石英.png</v>
+        <v>锆石魔盒钻.png</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>nyl_stn_6</v>
+        <v>by_agt_6</v>
       </c>
       <c r="B28" t="str">
         <v>珠子</v>
       </c>
       <c r="C28" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D28" t="str">
-        <v>奶油藍</v>
+        <v>白玉髓</v>
       </c>
       <c r="E28">
         <v>6</v>
       </c>
       <c r="F28">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G28" t="str">
-        <v>奶油藍.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>nyl_stn_8</v>
+        <v>by_agt_8</v>
       </c>
       <c r="B29" t="str">
         <v>珠子</v>
       </c>
       <c r="C29" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D29" t="str">
-        <v>奶油藍</v>
+        <v>白玉髓</v>
       </c>
       <c r="E29">
         <v>8</v>
       </c>
       <c r="F29">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G29" t="str">
-        <v>奶油藍.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>nyl_stn_10</v>
+        <v>by_agt_10</v>
       </c>
       <c r="B30" t="str">
         <v>珠子</v>
       </c>
       <c r="C30" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D30" t="str">
-        <v>奶油藍</v>
+        <v>白玉髓</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G30" t="str">
-        <v>奶油藍.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>mtfj_cysl_6</v>
+        <v>lglf_spc_8</v>
       </c>
       <c r="B31" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C31" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D31" t="str">
-        <v>蜜桃粉晶</v>
+        <v>菱格立方</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G31" t="str">
-        <v>蜜桃粉晶.png</v>
+        <v>菱格立方.png</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>mtfj_cysl_8</v>
+        <v>zlh_cysl_6</v>
       </c>
       <c r="B32" t="str">
         <v>珠子</v>
@@ -1123,21 +1123,21 @@
         <v>水晶</v>
       </c>
       <c r="D32" t="str">
-        <v>蜜桃粉晶</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32">
         <v>89</v>
       </c>
       <c r="G32" t="str">
-        <v>蜜桃粉晶.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>mtfj_cysl_10</v>
+        <v>zlh_cysl_8</v>
       </c>
       <c r="B33" t="str">
         <v>珠子</v>
@@ -1146,214 +1146,214 @@
         <v>水晶</v>
       </c>
       <c r="D33" t="str">
-        <v>蜜桃粉晶</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="G33" t="str">
-        <v>蜜桃粉晶.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lpts_stn_6</v>
+        <v>zlh_cysl_10</v>
       </c>
       <c r="B34" t="str">
         <v>珠子</v>
       </c>
       <c r="C34" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D34" t="str">
-        <v>綠葡萄石</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="G34" t="str">
-        <v>綠葡萄石.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lpts_stn_8</v>
+        <v>fsj_cysl_6</v>
       </c>
       <c r="B35" t="str">
         <v>珠子</v>
       </c>
       <c r="C35" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D35" t="str">
-        <v>綠葡萄石</v>
+        <v>粉水晶</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G35" t="str">
-        <v>綠葡萄石.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>lpts_stn_10</v>
+        <v>fsj_cysl_8</v>
       </c>
       <c r="B36" t="str">
         <v>珠子</v>
       </c>
       <c r="C36" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D36" t="str">
-        <v>綠葡萄石</v>
+        <v>粉水晶</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G36" t="str">
-        <v>綠葡萄石.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>lyg_stn_6</v>
+        <v>fsj_cysl_10</v>
       </c>
       <c r="B37" t="str">
         <v>珠子</v>
       </c>
       <c r="C37" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D37" t="str">
-        <v>藍月光</v>
+        <v>粉水晶</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F37">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G37" t="str">
-        <v>藍月光.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>lyg_stn_8</v>
+        <v>ysmxyl_pnd_2</v>
       </c>
       <c r="B38" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C38" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D38" t="str">
-        <v>藍月光</v>
+        <v>銀色滿鑲月亮</v>
       </c>
       <c r="E38">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G38" t="str">
-        <v>藍月光.png</v>
+        <v>银色满镶月亮.png</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>lyg_stn_10</v>
+        <v>gsfz_spc_6</v>
       </c>
       <c r="B39" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C39" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D39" t="str">
-        <v>藍月光</v>
+        <v>鋯石方鑽</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G39" t="str">
-        <v>藍月光.png</v>
+        <v>锆石方钻.png</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>sbs_stn_6</v>
+        <v>lkjf_pnd_2</v>
       </c>
       <c r="B40" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C40" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D40" t="str">
-        <v>閃白石</v>
+        <v>鏤空金福</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G40" t="str">
-        <v>閃白石.png</v>
+        <v>镂空金福.png</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>sbs_stn_8</v>
+        <v>bas_cysl_8</v>
       </c>
       <c r="B41" t="str">
         <v>珠子</v>
       </c>
       <c r="C41" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D41" t="str">
-        <v>閃白石</v>
+        <v>白阿塞</v>
       </c>
       <c r="E41">
         <v>8</v>
       </c>
       <c r="F41">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G41" t="str">
-        <v>閃白石.png</v>
+        <v>白阿塞.png</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>sbs_stn_10</v>
+        <v>bas_cysl_10</v>
       </c>
       <c r="B42" t="str">
         <v>珠子</v>
       </c>
       <c r="C42" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D42" t="str">
-        <v>閃白石</v>
+        <v>白阿塞</v>
       </c>
       <c r="E42">
         <v>10</v>
@@ -1362,113 +1362,113 @@
         <v>99</v>
       </c>
       <c r="G42" t="str">
-        <v>閃白石.png</v>
+        <v>白阿塞.png</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>wlyz_spc_5</v>
+        <v>hws_stn_6</v>
       </c>
       <c r="B43" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C43" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D43" t="str">
-        <v>五稜銀鑽</v>
+        <v>海紋石</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G43" t="str">
-        <v>五棱银钻.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>gsxx_pnd_2</v>
+        <v>hws_stn_8</v>
       </c>
       <c r="B44" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C44" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D44" t="str">
-        <v>鋯石星星</v>
+        <v>海紋石</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F44">
         <v>99</v>
       </c>
       <c r="G44" t="str">
-        <v>锆石星星.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>xxys_pnd_2</v>
+        <v>hws_stn_10</v>
       </c>
       <c r="B45" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C45" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D45" t="str">
-        <v>尋心鑰匙</v>
+        <v>海紋石</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F45">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="G45" t="str">
-        <v>寻心钥匙.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>bsyw_pnd_2</v>
+        <v>zys_agt_6</v>
       </c>
       <c r="B46" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C46" t="str">
-        <v>吊墜</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D46" t="str">
-        <v>白水魚尾</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F46">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G46" t="str">
-        <v>白水鱼尾.png</v>
+        <v>紫玉髓.png</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>zyb_spc_8</v>
+        <v>zys_agt_8</v>
       </c>
       <c r="B47" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C47" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D47" t="str">
-        <v>轉運柄</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E47">
         <v>8</v>
@@ -1477,81 +1477,81 @@
         <v>59</v>
       </c>
       <c r="G47" t="str">
-        <v>转运柄.png</v>
+        <v>紫玉髓.png</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>emzy_spc_6</v>
+        <v>jfj_cysl_6</v>
       </c>
       <c r="B48" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C48" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D48" t="str">
-        <v>惡魔之眼</v>
+        <v>金髮晶</v>
       </c>
       <c r="E48">
         <v>6</v>
       </c>
       <c r="F48">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G48" t="str">
-        <v>恶魔之眼.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>nwxh_spc_5</v>
+        <v>jfj_cysl_8</v>
       </c>
       <c r="B49" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C49" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D49" t="str">
-        <v>扭紋小環</v>
+        <v>金髮晶</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F49">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G49" t="str">
-        <v>扭纹小环.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>xxjz_pnd_2</v>
+        <v>jfj_cysl_10</v>
       </c>
       <c r="B50" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C50" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D50" t="str">
-        <v>星星獎章</v>
+        <v>金髮晶</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F50">
         <v>99</v>
       </c>
       <c r="G50" t="str">
-        <v>星星奖章.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>fyh_spc_6</v>
+        <v>wlyz_spc_5</v>
       </c>
       <c r="B51" t="str">
         <v>配件</v>
@@ -1560,113 +1560,113 @@
         <v>隔珠</v>
       </c>
       <c r="D51" t="str">
-        <v>粉櫻花</v>
+        <v>五稜銀鑽</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F51">
         <v>59</v>
       </c>
       <c r="G51" t="str">
-        <v>粉樱花.png</v>
+        <v>五棱银钻.png</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>gshxz_spc_6</v>
+        <v>gsxx_pnd_2</v>
       </c>
       <c r="B52" t="str">
         <v>配件</v>
       </c>
       <c r="C52" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D52" t="str">
-        <v>鋯石花形鑽</v>
+        <v>鋯石星星</v>
       </c>
       <c r="E52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G52" t="str">
-        <v>锆石花形钻.png</v>
+        <v>锆石星星.png</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lwmn_agt_6</v>
+        <v>xxys_pnd_2</v>
       </c>
       <c r="B53" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C53" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D53" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>尋心鑰匙</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G53" t="str">
-        <v>藍紋瑪瑙.png</v>
+        <v>寻心钥匙.png</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lwmn_agt_8</v>
+        <v>bsyw_pnd_2</v>
       </c>
       <c r="B54" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C54" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D54" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>白水魚尾</v>
       </c>
       <c r="E54">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G54" t="str">
-        <v>藍紋瑪瑙.png</v>
+        <v>白水鱼尾.png</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lwmn_agt_10</v>
+        <v>zyb_spc_8</v>
       </c>
       <c r="B55" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C55" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D55" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>轉運柄</v>
       </c>
       <c r="E55">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F55">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G55" t="str">
-        <v>藍紋瑪瑙.png</v>
+        <v>转运柄.png</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>gsqg_spc_5</v>
+        <v>emzy_spc_6</v>
       </c>
       <c r="B56" t="str">
         <v>配件</v>
@@ -1675,90 +1675,90 @@
         <v>隔珠</v>
       </c>
       <c r="D56" t="str">
-        <v>鋯石切割</v>
+        <v>惡魔之眼</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56">
         <v>59</v>
       </c>
       <c r="G56" t="str">
-        <v>锆石切割.png</v>
+        <v>恶魔之眼.png</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>jzj_spc_6</v>
+        <v>lwmn_agt_6</v>
       </c>
       <c r="B57" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C57" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D57" t="str">
-        <v>交織戒</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E57">
         <v>6</v>
       </c>
       <c r="F57">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G57" t="str">
-        <v>交织戒.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>gscx_pnd_2</v>
+        <v>lwmn_agt_8</v>
       </c>
       <c r="B58" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C58" t="str">
-        <v>吊墜</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D58" t="str">
-        <v>鋯石晨星</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F58">
         <v>99</v>
       </c>
       <c r="G58" t="str">
-        <v>锆石晨星.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>cyszj_spc_8</v>
+        <v>lwmn_agt_10</v>
       </c>
       <c r="B59" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C59" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D59" t="str">
-        <v>藏銀十字架</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E59">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F59">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="G59" t="str">
-        <v>藏银十字架.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>gsqgsc_spc_6</v>
+        <v>nwxh_spc_5</v>
       </c>
       <c r="B60" t="str">
         <v>配件</v>
@@ -1767,44 +1767,44 @@
         <v>隔珠</v>
       </c>
       <c r="D60" t="str">
-        <v>鋯石切割雙層</v>
+        <v>扭紋小環</v>
       </c>
       <c r="E60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F60">
         <v>59</v>
       </c>
       <c r="G60" t="str">
-        <v>锆石切割双层.png</v>
+        <v>扭纹小环.png</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ysxh_spc_5</v>
+        <v>xyc_cysl_8</v>
       </c>
       <c r="B61" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C61" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D61" t="str">
-        <v>銀色小環</v>
+        <v>薰衣草</v>
       </c>
       <c r="E61">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F61">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G61" t="str">
-        <v>银色小环.png</v>
+        <v>薰衣草.png</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>hsj_cysl_6</v>
+        <v>xyc_cysl_10</v>
       </c>
       <c r="B62" t="str">
         <v>珠子</v>
@@ -1813,136 +1813,136 @@
         <v>水晶</v>
       </c>
       <c r="D62" t="str">
-        <v>黃水晶</v>
+        <v>薰衣草</v>
       </c>
       <c r="E62">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F62">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="G62" t="str">
-        <v>黃水晶.png</v>
+        <v>薰衣草.png</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>hsj_cysl_8</v>
+        <v>xxjz_pnd_2</v>
       </c>
       <c r="B63" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C63" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D63" t="str">
-        <v>黃水晶</v>
+        <v>星星獎章</v>
       </c>
       <c r="E63">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G63" t="str">
-        <v>黃水晶.png</v>
+        <v>星星奖章.png</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>hsj_cysl_10</v>
+        <v>fyh_spc_6</v>
       </c>
       <c r="B64" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C64" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D64" t="str">
-        <v>黃水晶</v>
+        <v>粉櫻花</v>
       </c>
       <c r="E64">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F64">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G64" t="str">
-        <v>黃水晶.png</v>
+        <v>粉樱花.png</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>hm_agt_6</v>
+        <v>gshxz_spc_6</v>
       </c>
       <c r="B65" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C65" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D65" t="str">
-        <v>黃瑪瑙</v>
+        <v>鋯石花形鑽</v>
       </c>
       <c r="E65">
         <v>6</v>
       </c>
       <c r="F65">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G65" t="str">
-        <v>黃瑪瑙.png</v>
+        <v>锆石花形钻.png</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>hm_agt_8</v>
+        <v>yys_stn_6</v>
       </c>
       <c r="B66" t="str">
         <v>珠子</v>
       </c>
       <c r="C66" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D66" t="str">
-        <v>黃瑪瑙</v>
+        <v>銀曜石</v>
       </c>
       <c r="E66">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F66">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G66" t="str">
-        <v>黃瑪瑙.png</v>
+        <v>银曜石.png</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>hm_agt_10</v>
+        <v>yys_stn_8</v>
       </c>
       <c r="B67" t="str">
         <v>珠子</v>
       </c>
       <c r="C67" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D67" t="str">
-        <v>黃瑪瑙</v>
+        <v>銀曜石</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F67">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G67" t="str">
-        <v>黃瑪瑙.png</v>
+        <v>银曜石.png</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ml_stn_6</v>
+        <v>yys_stn_10</v>
       </c>
       <c r="B68" t="str">
         <v>珠子</v>
@@ -1951,113 +1951,113 @@
         <v>礦石</v>
       </c>
       <c r="D68" t="str">
-        <v>蜜蠟</v>
+        <v>銀曜石</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F68">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G68" t="str">
-        <v>蜜蠟.png</v>
+        <v>银曜石.png</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ml_stn_8</v>
+        <v>hsj_cysl_6</v>
       </c>
       <c r="B69" t="str">
         <v>珠子</v>
       </c>
       <c r="C69" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D69" t="str">
-        <v>蜜蠟</v>
+        <v>黃水晶</v>
       </c>
       <c r="E69">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F69">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G69" t="str">
-        <v>蜜蠟.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ml_stn_10</v>
+        <v>hsj_cysl_8</v>
       </c>
       <c r="B70" t="str">
         <v>珠子</v>
       </c>
       <c r="C70" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D70" t="str">
-        <v>蜜蠟</v>
+        <v>黃水晶</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F70">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G70" t="str">
-        <v>蜜蠟.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>mzhd_pnd_2</v>
+        <v>hsj_cysl_10</v>
       </c>
       <c r="B71" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C71" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D71" t="str">
-        <v>滿鑽蝴蝶</v>
+        <v>黃水晶</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F71">
         <v>99</v>
       </c>
       <c r="G71" t="str">
-        <v>满钻蝴蝶.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>jd_pnd_2</v>
+        <v>gsqg_spc_5</v>
       </c>
       <c r="B72" t="str">
         <v>配件</v>
       </c>
       <c r="C72" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D72" t="str">
-        <v>晶蝶</v>
+        <v>鋯石切割</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F72">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G72" t="str">
-        <v>晶蝶.png</v>
+        <v>锆石切割.png</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>lkjls_spc_6</v>
+        <v>jzj_spc_6</v>
       </c>
       <c r="B73" t="str">
         <v>配件</v>
@@ -2066,7 +2066,7 @@
         <v>隔珠</v>
       </c>
       <c r="D73" t="str">
-        <v>鏤空金蕾絲</v>
+        <v>交織戒</v>
       </c>
       <c r="E73">
         <v>6</v>
@@ -2075,196 +2075,196 @@
         <v>59</v>
       </c>
       <c r="G73" t="str">
-        <v>镂空金蕾丝.png</v>
+        <v>交织戒.png</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>hws_stn_6</v>
+        <v>gscx_pnd_2</v>
       </c>
       <c r="B74" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C74" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D74" t="str">
-        <v>海紋石</v>
+        <v>鋯石晨星</v>
       </c>
       <c r="E74">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G74" t="str">
-        <v>海紋石.png</v>
+        <v>锆石晨星.png</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>hws_stn_8</v>
+        <v>cyszj_spc_8</v>
       </c>
       <c r="B75" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C75" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D75" t="str">
-        <v>海紋石</v>
+        <v>藏銀十字架</v>
       </c>
       <c r="E75">
         <v>8</v>
       </c>
       <c r="F75">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G75" t="str">
-        <v>海紋石.png</v>
+        <v>藏银十字架.png</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>hws_stn_10</v>
+        <v>gsqgsc_spc_6</v>
       </c>
       <c r="B76" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C76" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D76" t="str">
-        <v>海紋石</v>
+        <v>鋯石切割雙層</v>
       </c>
       <c r="E76">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F76">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G76" t="str">
-        <v>海紋石.png</v>
+        <v>锆石切割双层.png</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>pts_stn_6</v>
+        <v>ysxh_spc_5</v>
       </c>
       <c r="B77" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C77" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D77" t="str">
-        <v>葡萄石</v>
+        <v>銀色小環</v>
       </c>
       <c r="E77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F77">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G77" t="str">
-        <v>葡萄石.png</v>
+        <v>银色小环.png</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>pts_stn_8</v>
+        <v>hm_agt_6</v>
       </c>
       <c r="B78" t="str">
         <v>珠子</v>
       </c>
       <c r="C78" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D78" t="str">
-        <v>葡萄石</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E78">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F78">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G78" t="str">
-        <v>葡萄石.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>pts_stn_10</v>
+        <v>hm_agt_8</v>
       </c>
       <c r="B79" t="str">
         <v>珠子</v>
       </c>
       <c r="C79" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D79" t="str">
-        <v>葡萄石</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E79">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F79">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G79" t="str">
-        <v>葡萄石.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>jf_pnd_2</v>
+        <v>hm_agt_10</v>
       </c>
       <c r="B80" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C80" t="str">
-        <v>吊墜</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D80" t="str">
-        <v>金福</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F80">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G80" t="str">
-        <v>金福.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>fgdh_spc_8</v>
+        <v>ml_stn_6</v>
       </c>
       <c r="B81" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C81" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D81" t="str">
-        <v>復古雕花</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E81">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F81">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G81" t="str">
-        <v>复古雕花.png</v>
+        <v>蜜蜡.png</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>mtx_stn_6</v>
+        <v>ml_stn_8</v>
       </c>
       <c r="B82" t="str">
         <v>珠子</v>
@@ -2273,67 +2273,67 @@
         <v>礦石</v>
       </c>
       <c r="D82" t="str">
-        <v>滿天星</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E82">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G82" t="str">
-        <v>滿天星.png</v>
+        <v>蜜蜡.png</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>mtx_stn_8</v>
+        <v>mzhd_pnd_2</v>
       </c>
       <c r="B83" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C83" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D83" t="str">
-        <v>滿天星</v>
+        <v>滿鑽蝴蝶</v>
       </c>
       <c r="E83">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F83">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G83" t="str">
-        <v>滿天星.png</v>
+        <v>满钻蝴蝶.png</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>mtx_stn_10</v>
+        <v>jd_pnd_2</v>
       </c>
       <c r="B84" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C84" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D84" t="str">
-        <v>滿天星</v>
+        <v>晶蝶</v>
       </c>
       <c r="E84">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F84">
         <v>99</v>
       </c>
       <c r="G84" t="str">
-        <v>滿天星.png</v>
+        <v>晶蝶.png</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>xxy_spc_5</v>
+        <v>lkjls_spc_6</v>
       </c>
       <c r="B85" t="str">
         <v>配件</v>
@@ -2342,389 +2342,389 @@
         <v>隔珠</v>
       </c>
       <c r="D85" t="str">
-        <v>小祥雲</v>
+        <v>鏤空金蕾絲</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F85">
         <v>59</v>
       </c>
       <c r="G85" t="str">
-        <v>小祥云.png</v>
+        <v>镂空金蕾丝.png</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>dxy_spc_5</v>
+        <v>jf_pnd_2</v>
       </c>
       <c r="B86" t="str">
         <v>配件</v>
       </c>
       <c r="C86" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D86" t="str">
-        <v>大祥雲</v>
+        <v>金福</v>
       </c>
       <c r="E86">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F86">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G86" t="str">
-        <v>大祥云.png</v>
+        <v>金福.png</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>nmhsj_cysl_6</v>
+        <v>fgdh_spc_8</v>
       </c>
       <c r="B87" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C87" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D87" t="str">
-        <v>檸檬黃水晶</v>
+        <v>復古雕花</v>
       </c>
       <c r="E87">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F87">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G87" t="str">
-        <v>檸檬黃水晶.png</v>
+        <v>复古雕花.png</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>nmhsj_cysl_8</v>
+        <v>xxy_spc_5</v>
       </c>
       <c r="B88" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C88" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D88" t="str">
-        <v>檸檬黃水晶</v>
+        <v>小祥雲</v>
       </c>
       <c r="E88">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F88">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G88" t="str">
-        <v>檸檬黃水晶.png</v>
+        <v>小祥云.png</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>nmhsj_cysl_10</v>
+        <v>dxy_spc_5</v>
       </c>
       <c r="B89" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C89" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D89" t="str">
-        <v>檸檬黃水晶</v>
+        <v>大祥雲</v>
       </c>
       <c r="E89">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F89">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G89" t="str">
-        <v>檸檬黃水晶.png</v>
+        <v>大祥云.png</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ths_stn_6</v>
+        <v>gsmm_spc_8</v>
       </c>
       <c r="B90" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C90" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D90" t="str">
-        <v>天河石</v>
+        <v>鋯石貓咪</v>
       </c>
       <c r="E90">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F90">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G90" t="str">
-        <v>天河石.png</v>
+        <v>锆石猫咪.png</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ths_stn_8</v>
+        <v>wljz_spc_5</v>
       </c>
       <c r="B91" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C91" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D91" t="str">
-        <v>天河石</v>
+        <v>五稜金鑽</v>
       </c>
       <c r="E91">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F91">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G91" t="str">
-        <v>天河石.png</v>
+        <v>五棱金钻.png</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ths_stn_10</v>
+        <v>zyd_pnd_2</v>
       </c>
       <c r="B92" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C92" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D92" t="str">
-        <v>天河石</v>
+        <v>珠遇蝶</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F92">
         <v>99</v>
       </c>
       <c r="G92" t="str">
-        <v>天河石.png</v>
+        <v>珠遇蝶.png</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>lys_stn_6</v>
+        <v>xfp_pnd_2</v>
       </c>
       <c r="B93" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C93" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D93" t="str">
-        <v>綠螢石</v>
+        <v>小福牌</v>
       </c>
       <c r="E93">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F93">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G93" t="str">
-        <v>綠螢石.png</v>
+        <v>小福牌.png</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>lys_stn_8</v>
+        <v>hlcs_pnd_2</v>
       </c>
       <c r="B94" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C94" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D94" t="str">
-        <v>綠螢石</v>
+        <v>葫蘆成雙</v>
       </c>
       <c r="E94">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F94">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G94" t="str">
-        <v>綠螢石.png</v>
+        <v>葫芦成双.png</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>lys_stn_10</v>
+        <v>gslx_spc_6</v>
       </c>
       <c r="B95" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C95" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D95" t="str">
-        <v>綠螢石</v>
+        <v>鋯石螺旋</v>
       </c>
       <c r="E95">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F95">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G95" t="str">
-        <v>綠螢石.png</v>
+        <v>锆石螺旋.png</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>gsmm_spc_8</v>
+        <v>syyl_pnd_2</v>
       </c>
       <c r="B96" t="str">
         <v>配件</v>
       </c>
       <c r="C96" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D96" t="str">
-        <v>鋯石貓咪</v>
+        <v>閃躍月亮</v>
       </c>
       <c r="E96">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F96">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G96" t="str">
-        <v>锆石猫咪.png</v>
+        <v>闪跃月亮.png</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>jfj_cysl_6</v>
+        <v>gszs_spc_5</v>
       </c>
       <c r="B97" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C97" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D97" t="str">
-        <v>金髮晶</v>
+        <v>鋯石鑽閃</v>
       </c>
       <c r="E97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F97">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G97" t="str">
-        <v>金髮晶.png</v>
+        <v>锆石钻闪.png</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>jfj_cysl_8</v>
+        <v>xns_pnd_2</v>
       </c>
       <c r="B98" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C98" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D98" t="str">
-        <v>金髮晶</v>
+        <v>小年獸</v>
       </c>
       <c r="E98">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F98">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G98" t="str">
-        <v>金髮晶.png</v>
+        <v>小年兽.png</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>jfj_cysl_10</v>
+        <v>jsxh_spc_5</v>
       </c>
       <c r="B99" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C99" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D99" t="str">
-        <v>金髮晶</v>
+        <v>金色小環</v>
       </c>
       <c r="E99">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F99">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G99" t="str">
-        <v>金髮晶.png</v>
+        <v>金色小环.png</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>wljz_spc_5</v>
+        <v>hps_stn_6</v>
       </c>
       <c r="B100" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C100" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D100" t="str">
-        <v>五稜金鑽</v>
+        <v>琥珀石</v>
       </c>
       <c r="E100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F100">
         <v>59</v>
       </c>
       <c r="G100" t="str">
-        <v>五棱金钻.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>zyd_pnd_2</v>
+        <v>hps_stn_8</v>
       </c>
       <c r="B101" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C101" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D101" t="str">
-        <v>珠遇蝶</v>
+        <v>琥珀石</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F101">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G101" t="str">
-        <v>珠遇蝶.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ymys_stn_6</v>
+        <v>hps_stn_10</v>
       </c>
       <c r="B102" t="str">
         <v>珠子</v>
@@ -2733,113 +2733,113 @@
         <v>礦石</v>
       </c>
       <c r="D102" t="str">
-        <v>羽毛螢石</v>
+        <v>琥珀石</v>
       </c>
       <c r="E102">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F102">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="G102" t="str">
-        <v>羽毛螢石.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ymys_stn_8</v>
+        <v>bjx_pnd_2</v>
       </c>
       <c r="B103" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C103" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D103" t="str">
-        <v>羽毛螢石</v>
+        <v>北極星</v>
       </c>
       <c r="E103">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F103">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G103" t="str">
-        <v>羽毛螢石.png</v>
+        <v>北极星.png</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ymys_stn_10</v>
+        <v>cgl_spc_6</v>
       </c>
       <c r="B104" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C104" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D104" t="str">
-        <v>羽毛螢石</v>
+        <v>彩鋯輪</v>
       </c>
       <c r="E104">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F104">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G104" t="str">
-        <v>羽毛螢石.png</v>
+        <v>彩锆轮.png</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>xfp_pnd_2</v>
+        <v>hlb_stn_6</v>
       </c>
       <c r="B105" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C105" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D105" t="str">
-        <v>小福牌</v>
+        <v>海藍寶</v>
       </c>
       <c r="E105">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F105">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G105" t="str">
-        <v>小福牌.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>hlcs_pnd_2</v>
+        <v>hlb_stn_8</v>
       </c>
       <c r="B106" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C106" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D106" t="str">
-        <v>葫蘆成雙</v>
+        <v>海藍寶</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F106">
         <v>99</v>
       </c>
       <c r="G106" t="str">
-        <v>葫芦成双.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>hty_jd_6</v>
+        <v>hlb_stn_10</v>
       </c>
       <c r="B107" t="str">
         <v>珠子</v>
@@ -2848,44 +2848,44 @@
         <v>礦石</v>
       </c>
       <c r="D107" t="str">
-        <v>和田玉</v>
+        <v>海藍寶</v>
       </c>
       <c r="E107">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F107">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="G107" t="str">
-        <v>和田玉.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>hty_jd_8</v>
+        <v>xs_spc_8</v>
       </c>
       <c r="B108" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C108" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D108" t="str">
-        <v>和田玉</v>
+        <v>醒獅</v>
       </c>
       <c r="E108">
         <v>8</v>
       </c>
       <c r="F108">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G108" t="str">
-        <v>和田玉.png</v>
+        <v>醒狮.png</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>hty_jd_10</v>
+        <v>ths_stn_6</v>
       </c>
       <c r="B109" t="str">
         <v>珠子</v>
@@ -2894,182 +2894,182 @@
         <v>礦石</v>
       </c>
       <c r="D109" t="str">
-        <v>和田玉</v>
+        <v>天河石</v>
       </c>
       <c r="E109">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F109">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G109" t="str">
-        <v>和田玉.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>gslx_spc_6</v>
+        <v>ths_stn_8</v>
       </c>
       <c r="B110" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C110" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D110" t="str">
-        <v>鋯石螺旋</v>
+        <v>天河石</v>
       </c>
       <c r="E110">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F110">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G110" t="str">
-        <v>锆石螺旋.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>syyl_pnd_2</v>
+        <v>ths_stn_10</v>
       </c>
       <c r="B111" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C111" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D111" t="str">
-        <v>閃躍月亮</v>
+        <v>天河石</v>
       </c>
       <c r="E111">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F111">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="G111" t="str">
-        <v>闪跃月亮.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>gszs_spc_5</v>
+        <v>gsch_pnd_2</v>
       </c>
       <c r="B112" t="str">
         <v>配件</v>
       </c>
       <c r="C112" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D112" t="str">
-        <v>鋯石鑽閃</v>
+        <v>鋯石彩虹</v>
       </c>
       <c r="E112">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F112">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G112" t="str">
-        <v>锆石钻闪.png</v>
+        <v>锆石彩虹.png</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>xns_pnd_2</v>
+        <v>xgszs_spc_5</v>
       </c>
       <c r="B113" t="str">
         <v>配件</v>
       </c>
       <c r="C113" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D113" t="str">
-        <v>小年獸</v>
+        <v>小鋯石鑽閃</v>
       </c>
       <c r="E113">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F113">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G113" t="str">
-        <v>小年兽.png</v>
+        <v>小锆石钻闪.png</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>jsxh_spc_5</v>
+        <v>wyh_pnd_2</v>
       </c>
       <c r="B114" t="str">
         <v>配件</v>
       </c>
       <c r="C114" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D114" t="str">
-        <v>金色小環</v>
+        <v>午夜花</v>
       </c>
       <c r="E114">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F114">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G114" t="str">
-        <v>金色小环.png</v>
+        <v>午夜花.png</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>bjx_pnd_2</v>
+        <v>ysxz_spc_6</v>
       </c>
       <c r="B115" t="str">
         <v>配件</v>
       </c>
       <c r="C115" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D115" t="str">
-        <v>北極星</v>
+        <v>銀色小珠</v>
       </c>
       <c r="E115">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F115">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G115" t="str">
-        <v>北极星.png</v>
+        <v>银色小珠.png</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>cgl_spc_6</v>
+        <v>jsmxyl_pnd_2</v>
       </c>
       <c r="B116" t="str">
         <v>配件</v>
       </c>
       <c r="C116" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D116" t="str">
-        <v>彩鋯輪</v>
+        <v>金色滿鑲月亮</v>
       </c>
       <c r="E116">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F116">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G116" t="str">
-        <v>彩锆轮.png</v>
+        <v>金色满镶月亮.png</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>hj_cysl_6</v>
+        <v>lcmj_cysl_6</v>
       </c>
       <c r="B117" t="str">
         <v>珠子</v>
@@ -3078,21 +3078,21 @@
         <v>水晶</v>
       </c>
       <c r="D117" t="str">
-        <v>黃膠花</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E117">
         <v>6</v>
       </c>
       <c r="F117">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G117" t="str">
-        <v>黃膠花.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>hj_cysl_8</v>
+        <v>lcmj_cysl_8</v>
       </c>
       <c r="B118" t="str">
         <v>珠子</v>
@@ -3101,21 +3101,21 @@
         <v>水晶</v>
       </c>
       <c r="D118" t="str">
-        <v>黃膠花</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E118">
         <v>8</v>
       </c>
       <c r="F118">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G118" t="str">
-        <v>黃膠花.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>hj_cysl_10</v>
+        <v>lcmj_cysl_10</v>
       </c>
       <c r="B119" t="str">
         <v>珠子</v>
@@ -3124,21 +3124,21 @@
         <v>水晶</v>
       </c>
       <c r="D119" t="str">
-        <v>黃膠花</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E119">
         <v>10</v>
       </c>
       <c r="F119">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G119" t="str">
-        <v>黃膠花.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>xs_spc_8</v>
+        <v>hbgd_spc_6</v>
       </c>
       <c r="B120" t="str">
         <v>配件</v>
@@ -3147,366 +3147,366 @@
         <v>隔珠</v>
       </c>
       <c r="D120" t="str">
-        <v>醒獅</v>
+        <v>花邊軌道</v>
       </c>
       <c r="E120">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F120">
         <v>59</v>
       </c>
       <c r="G120" t="str">
-        <v>醒狮.png</v>
+        <v>花边轨道.png</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>xyczsj_cysl_6</v>
+        <v>hcw_spc_5</v>
       </c>
       <c r="B121" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C121" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D121" t="str">
-        <v>薰衣草紫水晶</v>
+        <v>回財紋</v>
       </c>
       <c r="E121">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F121">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G121" t="str">
-        <v>薰衣草紫水晶.png</v>
+        <v>回财纹.png</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>xyczsj_cysl_8</v>
+        <v>cyjc_spc_6</v>
       </c>
       <c r="B122" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C122" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D122" t="str">
-        <v>薰衣草紫水晶</v>
+        <v>藏銀卷草</v>
       </c>
       <c r="E122">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F122">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G122" t="str">
-        <v>薰衣草紫水晶.png</v>
+        <v>藏银卷草.png</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>xyczsj_cysl_10</v>
+        <v>hx_spc_6</v>
       </c>
       <c r="B123" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C123" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D123" t="str">
-        <v>薰衣草紫水晶</v>
+        <v>花旋</v>
       </c>
       <c r="E123">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F123">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G123" t="str">
-        <v>薰衣草紫水晶.png</v>
+        <v>花旋.png</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>zlh_cysl_6</v>
+        <v>cyszh_spc_8</v>
       </c>
       <c r="B124" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C124" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D124" t="str">
-        <v>紫鋰輝</v>
+        <v>藏銀十字花</v>
       </c>
       <c r="E124">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F124">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G124" t="str">
-        <v>紫鋰輝.png</v>
+        <v>藏银十字花.png</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>zlh_cysl_8</v>
+        <v>cyym_pnd_2</v>
       </c>
       <c r="B125" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C125" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D125" t="str">
-        <v>紫鋰輝</v>
+        <v>藏銀羽毛</v>
       </c>
       <c r="E125">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F125">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G125" t="str">
-        <v>紫鋰輝.png</v>
+        <v>藏银羽毛.png</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>zlh_cysl_10</v>
+        <v>cysy_spc_6</v>
       </c>
       <c r="B126" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C126" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D126" t="str">
-        <v>紫鋰輝</v>
+        <v>藏銀樹葉</v>
       </c>
       <c r="E126">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F126">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G126" t="str">
-        <v>紫鋰輝.png</v>
+        <v>藏银树叶.png</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>gsch_pnd_2</v>
+        <v>qws_stn_8</v>
       </c>
       <c r="B127" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C127" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D127" t="str">
-        <v>鋯石彩虹</v>
+        <v>薔薇石</v>
       </c>
       <c r="E127">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F127">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G127" t="str">
-        <v>锆石彩虹.png</v>
+        <v>蔷薇石.png</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>xgszs_spc_5</v>
+        <v>qws_stn_10</v>
       </c>
       <c r="B128" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C128" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D128" t="str">
-        <v>小鋯石鑽閃</v>
+        <v>薔薇石</v>
       </c>
       <c r="E128">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F128">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G128" t="str">
-        <v>小锆石钻闪.png</v>
+        <v>蔷薇石.png</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>bcb_stn_6</v>
+        <v>jsxz_spc_6</v>
       </c>
       <c r="B129" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C129" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D129" t="str">
-        <v>冰川寶</v>
+        <v>金色小珠</v>
       </c>
       <c r="E129">
         <v>6</v>
       </c>
       <c r="F129">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G129" t="str">
-        <v>冰川寶.png</v>
+        <v>金色小珠.png</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>bcb_stn_8</v>
+        <v>gszssc_spc_6</v>
       </c>
       <c r="B130" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C130" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D130" t="str">
-        <v>冰川寶</v>
+        <v>鋯石鑽閃雙層</v>
       </c>
       <c r="E130">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F130">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G130" t="str">
-        <v>冰川寶.png</v>
+        <v>锆石钻闪双层.png</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>bcb_stn_10</v>
+        <v>cywp_spc_8</v>
       </c>
       <c r="B131" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C131" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D131" t="str">
-        <v>冰川寶</v>
+        <v>藏銀瓦片</v>
       </c>
       <c r="E131">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F131">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G131" t="str">
-        <v>冰川寶.png</v>
+        <v>藏银瓦片.png</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>htj_cysl_6</v>
+        <v>syc_pnd_2</v>
       </c>
       <c r="B132" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C132" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D132" t="str">
-        <v>黃塔晶</v>
+        <v>四葉草</v>
       </c>
       <c r="E132">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F132">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G132" t="str">
-        <v>黃塔晶.png</v>
+        <v>四叶草.png</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>htj_cysl_8</v>
+        <v>tys_stn_6</v>
       </c>
       <c r="B133" t="str">
         <v>珠子</v>
       </c>
       <c r="C133" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D133" t="str">
-        <v>黃塔晶</v>
+        <v>太陽石</v>
       </c>
       <c r="E133">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F133">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="G133" t="str">
-        <v>黃塔晶.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>htj_cysl_10</v>
+        <v>tys_stn_8</v>
       </c>
       <c r="B134" t="str">
         <v>珠子</v>
       </c>
       <c r="C134" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D134" t="str">
-        <v>黃塔晶</v>
+        <v>太陽石</v>
       </c>
       <c r="E134">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F134">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G134" t="str">
-        <v>黃塔晶.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>wyh_pnd_2</v>
+        <v>tys_stn_10</v>
       </c>
       <c r="B135" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C135" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D135" t="str">
-        <v>午夜花</v>
+        <v>太陽石</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F135">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="G135" t="str">
-        <v>午夜花.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ysxz_spc_6</v>
+        <v>yslzzy_spc_8</v>
       </c>
       <c r="B136" t="str">
         <v>配件</v>
@@ -3515,113 +3515,113 @@
         <v>隔珠</v>
       </c>
       <c r="D136" t="str">
-        <v>銀色小珠</v>
+        <v>銀色六字真言</v>
       </c>
       <c r="E136">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F136">
         <v>59</v>
       </c>
       <c r="G136" t="str">
-        <v>银色小珠.png</v>
+        <v>银色六字真言.png</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>jhy_stn_6</v>
+        <v>ketj_spc_6</v>
       </c>
       <c r="B137" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C137" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D137" t="str">
-        <v>金虎眼</v>
+        <v>凱爾特結</v>
       </c>
       <c r="E137">
         <v>6</v>
       </c>
       <c r="F137">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G137" t="str">
-        <v>金虎眼.png</v>
+        <v>凯尔特结.png</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>jhy_stn_8</v>
+        <v>zsj_cysl_6</v>
       </c>
       <c r="B138" t="str">
         <v>珠子</v>
       </c>
       <c r="C138" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D138" t="str">
-        <v>金虎眼</v>
+        <v>紫水晶</v>
       </c>
       <c r="E138">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F138">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G138" t="str">
-        <v>金虎眼.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>jhy_stn_10</v>
+        <v>zsj_cysl_8</v>
       </c>
       <c r="B139" t="str">
         <v>珠子</v>
       </c>
       <c r="C139" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D139" t="str">
-        <v>金虎眼</v>
+        <v>紫水晶</v>
       </c>
       <c r="E139">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F139">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G139" t="str">
-        <v>金虎眼.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>jsmxyl_pnd_2</v>
+        <v>zsj_cysl_10</v>
       </c>
       <c r="B140" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C140" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D140" t="str">
-        <v>金色滿鑲月亮</v>
+        <v>紫水晶</v>
       </c>
       <c r="E140">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F140">
         <v>99</v>
       </c>
       <c r="G140" t="str">
-        <v>金色满镶月亮.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>hbgd_spc_6</v>
+        <v>ysxq_spc_8</v>
       </c>
       <c r="B141" t="str">
         <v>配件</v>
@@ -3630,159 +3630,159 @@
         <v>隔珠</v>
       </c>
       <c r="D141" t="str">
-        <v>花邊軌道</v>
+        <v>銀色繡球</v>
       </c>
       <c r="E141">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F141">
         <v>59</v>
       </c>
       <c r="G141" t="str">
-        <v>花边轨道.png</v>
+        <v>银色绣球.png</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>qtxy_jd_6</v>
+        <v>wgzl_pnd_2</v>
       </c>
       <c r="B142" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C142" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D142" t="str">
-        <v>青提玉</v>
+        <v>王國之淚</v>
       </c>
       <c r="E142">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F142">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G142" t="str">
-        <v>青提玉.png</v>
+        <v>王国之泪.png</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>qtxy_jd_8</v>
+        <v>jslzzy_spc_8</v>
       </c>
       <c r="B143" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C143" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D143" t="str">
-        <v>青提玉</v>
+        <v>金色六字真言</v>
       </c>
       <c r="E143">
         <v>8</v>
       </c>
       <c r="F143">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G143" t="str">
-        <v>青提玉.png</v>
+        <v>金色六字真言.png</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>qtxy_jd_10</v>
+        <v>cmj_cysl_6</v>
       </c>
       <c r="B144" t="str">
         <v>珠子</v>
       </c>
       <c r="C144" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D144" t="str">
-        <v>青提玉</v>
+        <v>草莓晶</v>
       </c>
       <c r="E144">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F144">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G144" t="str">
-        <v>青提玉.png</v>
+        <v>草莓晶.png</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>hcw_spc_5</v>
+        <v>cmj_cysl_8</v>
       </c>
       <c r="B145" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C145" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D145" t="str">
-        <v>回財紋</v>
+        <v>草莓晶</v>
       </c>
       <c r="E145">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F145">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G145" t="str">
-        <v>回财纹.png</v>
+        <v>草莓晶.png</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>cyjc_spc_6</v>
+        <v>cmj_cysl_10</v>
       </c>
       <c r="B146" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C146" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D146" t="str">
-        <v>藏銀卷草</v>
+        <v>草莓晶</v>
       </c>
       <c r="E146">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F146">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G146" t="str">
-        <v>藏银卷草.png</v>
+        <v>草莓晶.png</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>hx_spc_6</v>
+        <v>cyhdls_pnd_2</v>
       </c>
       <c r="B147" t="str">
         <v>配件</v>
       </c>
       <c r="C147" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D147" t="str">
-        <v>花旋</v>
+        <v>藏銀蝴蝶流蘇</v>
       </c>
       <c r="E147">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F147">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G147" t="str">
-        <v>花旋.png</v>
+        <v>藏银蝴蝶流苏.png</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>cyszh_spc_8</v>
+        <v>mghh_spc_6</v>
       </c>
       <c r="B148" t="str">
         <v>配件</v>
@@ -3791,90 +3791,90 @@
         <v>隔珠</v>
       </c>
       <c r="D148" t="str">
-        <v>藏銀十字花</v>
+        <v>玫瑰花環</v>
       </c>
       <c r="E148">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F148">
         <v>59</v>
       </c>
       <c r="G148" t="str">
-        <v>藏银十字花.png</v>
+        <v>玫瑰花环.png</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>hfj_cysl_6</v>
+        <v>bmnmh_spc_8</v>
       </c>
       <c r="B149" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C149" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D149" t="str">
-        <v>黑髮晶</v>
+        <v>白瑪瑙魔盒</v>
       </c>
       <c r="E149">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F149">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G149" t="str">
-        <v>黑髮晶.png</v>
+        <v>白玛瑙魔盒.png</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>hfj_cysl_8</v>
+        <v>cyhw_spc_5</v>
       </c>
       <c r="B150" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C150" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D150" t="str">
-        <v>黑髮晶</v>
+        <v>藏銀回紋</v>
       </c>
       <c r="E150">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F150">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G150" t="str">
-        <v>黑髮晶.png</v>
+        <v>藏银回纹.png</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>hfj_cysl_10</v>
+        <v>zsmh_spc_8</v>
       </c>
       <c r="B151" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C151" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D151" t="str">
-        <v>黑髮晶</v>
+        <v>硃砂魔盒</v>
       </c>
       <c r="E151">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F151">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G151" t="str">
-        <v>黑髮晶.png</v>
+        <v>朱砂魔盒.png</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>cyym_pnd_2</v>
+        <v>cyszdz_pnd_2</v>
       </c>
       <c r="B152" t="str">
         <v>配件</v>
@@ -3883,7 +3883,7 @@
         <v>吊墜</v>
       </c>
       <c r="D152" t="str">
-        <v>藏銀羽毛</v>
+        <v>藏銀十字吊墜</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -3892,81 +3892,81 @@
         <v>99</v>
       </c>
       <c r="G152" t="str">
-        <v>藏银羽毛.png</v>
+        <v>藏银十字吊坠.png</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>hw_stn_6</v>
+        <v>cyyc_pnd_2</v>
       </c>
       <c r="B153" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C153" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D153" t="str">
-        <v>紅紋石</v>
+        <v>藏銀葉叢</v>
       </c>
       <c r="E153">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F153">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G153" t="str">
-        <v>紅紋石.png</v>
+        <v>藏银叶丛.png</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>hw_stn_8</v>
+        <v>cyxhlf_spc_8</v>
       </c>
       <c r="B154" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C154" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D154" t="str">
-        <v>紅紋石</v>
+        <v>藏銀小花立方</v>
       </c>
       <c r="E154">
         <v>8</v>
       </c>
       <c r="F154">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G154" t="str">
-        <v>紅紋石.png</v>
+        <v>藏银小花立方.png</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>hw_stn_10</v>
+        <v>cydhlf_spc_8</v>
       </c>
       <c r="B155" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C155" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D155" t="str">
-        <v>紅紋石</v>
+        <v>藏銀大花立方</v>
       </c>
       <c r="E155">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F155">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G155" t="str">
-        <v>紅紋石.png</v>
+        <v>藏银大花立方.png</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>cysy_spc_6</v>
+        <v>jtlfq_spc_8</v>
       </c>
       <c r="B156" t="str">
         <v>配件</v>
@@ -3975,113 +3975,113 @@
         <v>隔珠</v>
       </c>
       <c r="D156" t="str">
-        <v>藏銀樹葉</v>
+        <v>景泰藍福球</v>
       </c>
       <c r="E156">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F156">
         <v>59</v>
       </c>
       <c r="G156" t="str">
-        <v>藏银树叶.png</v>
+        <v>景泰蓝福球.png</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>jsxz_spc_6</v>
+        <v>nh_agt_6</v>
       </c>
       <c r="B157" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C157" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D157" t="str">
-        <v>金色小珠</v>
+        <v>南紅</v>
       </c>
       <c r="E157">
         <v>6</v>
       </c>
       <c r="F157">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G157" t="str">
-        <v>金色小珠.png</v>
+        <v>南红.png</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>gszssc_spc_6</v>
+        <v>nh_agt_8</v>
       </c>
       <c r="B158" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C158" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D158" t="str">
-        <v>鋯石鑽閃雙層</v>
+        <v>南紅</v>
       </c>
       <c r="E158">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F158">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G158" t="str">
-        <v>锆石钻闪双层.png</v>
+        <v>南红.png</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>cywp_spc_8</v>
+        <v>nh_agt_10</v>
       </c>
       <c r="B159" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C159" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D159" t="str">
-        <v>藏銀瓦片</v>
+        <v>南紅</v>
       </c>
       <c r="E159">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F159">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="G159" t="str">
-        <v>藏银瓦片.png</v>
+        <v>南红.png</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>syc_pnd_2</v>
+        <v>hyes_stn_6</v>
       </c>
       <c r="B160" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C160" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D160" t="str">
-        <v>四葉草</v>
+        <v>虎眼石</v>
       </c>
       <c r="E160">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F160">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G160" t="str">
-        <v>四叶草.png</v>
+        <v>虎眼石.png</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>hyg_stn_6</v>
+        <v>hyes_stn_8</v>
       </c>
       <c r="B161" t="str">
         <v>珠子</v>
@@ -4090,21 +4090,21 @@
         <v>礦石</v>
       </c>
       <c r="D161" t="str">
-        <v>灰月光</v>
+        <v>虎眼石</v>
       </c>
       <c r="E161">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F161">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G161" t="str">
-        <v>灰月光.png</v>
+        <v>虎眼石.png</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>hyg_stn_8</v>
+        <v>hyes_stn_10</v>
       </c>
       <c r="B162" t="str">
         <v>珠子</v>
@@ -4113,90 +4113,90 @@
         <v>礦石</v>
       </c>
       <c r="D162" t="str">
-        <v>灰月光</v>
+        <v>虎眼石</v>
       </c>
       <c r="E162">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F162">
         <v>89</v>
       </c>
       <c r="G162" t="str">
-        <v>灰月光.png</v>
+        <v>虎眼石.png</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>hyg_stn_10</v>
+        <v>gqys_agt_6</v>
       </c>
       <c r="B163" t="str">
         <v>珠子</v>
       </c>
       <c r="C163" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D163" t="str">
-        <v>灰月光</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E163">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F163">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G163" t="str">
-        <v>灰月光.png</v>
+        <v>干青玉髓.png</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>slhlb_stn_6</v>
+        <v>gqys_agt_8</v>
       </c>
       <c r="B164" t="str">
         <v>珠子</v>
       </c>
       <c r="C164" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D164" t="str">
-        <v>聖藍海寶</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E164">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F164">
         <v>69</v>
       </c>
       <c r="G164" t="str">
-        <v>聖藍海寶.png</v>
+        <v>干青玉髓.png</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>slhlb_stn_8</v>
+        <v>gqys_agt_10</v>
       </c>
       <c r="B165" t="str">
         <v>珠子</v>
       </c>
       <c r="C165" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D165" t="str">
-        <v>聖藍海寶</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E165">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F165">
         <v>89</v>
       </c>
       <c r="G165" t="str">
-        <v>聖藍海寶.png</v>
+        <v>干青玉髓.png</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>slhlb_stn_10</v>
+        <v>ljs_stn_6</v>
       </c>
       <c r="B166" t="str">
         <v>珠子</v>
@@ -4205,297 +4205,297 @@
         <v>礦石</v>
       </c>
       <c r="D166" t="str">
-        <v>聖藍海寶</v>
+        <v>藍晶石</v>
       </c>
       <c r="E166">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F166">
         <v>99</v>
       </c>
       <c r="G166" t="str">
-        <v>聖藍海寶.png</v>
+        <v>蓝晶石.png</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>yslzzy_spc_8</v>
+        <v>ljs_stn_8</v>
       </c>
       <c r="B167" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C167" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D167" t="str">
-        <v>銀色六字真言</v>
+        <v>藍晶石</v>
       </c>
       <c r="E167">
         <v>8</v>
       </c>
       <c r="F167">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="G167" t="str">
-        <v>银色六字真言.png</v>
+        <v>蓝晶石.png</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>ketj_spc_6</v>
+        <v>ljs_stn_10</v>
       </c>
       <c r="B168" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C168" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D168" t="str">
-        <v>凱爾特結</v>
+        <v>藍晶石</v>
       </c>
       <c r="E168">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F168">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="G168" t="str">
-        <v>凯尔特结.png</v>
+        <v>蓝晶石.png</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>ysxq_spc_8</v>
+        <v>bmw_pnd_2</v>
       </c>
       <c r="B169" t="str">
         <v>配件</v>
       </c>
       <c r="C169" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D169" t="str">
-        <v>銀色繡球</v>
+        <v>捕夢網</v>
       </c>
       <c r="E169">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F169">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G169" t="str">
-        <v>银色绣球.png</v>
+        <v>捕梦网.png</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>tys_stn_6</v>
+        <v>csj_cysl_6</v>
       </c>
       <c r="B170" t="str">
         <v>珠子</v>
       </c>
       <c r="C170" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D170" t="str">
-        <v>太陽石</v>
+        <v>茶水晶</v>
       </c>
       <c r="E170">
         <v>6</v>
       </c>
       <c r="F170">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G170" t="str">
-        <v>太陽石.png</v>
+        <v>茶水晶.png</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>tys_stn_8</v>
+        <v>csj_cysl_8</v>
       </c>
       <c r="B171" t="str">
         <v>珠子</v>
       </c>
       <c r="C171" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D171" t="str">
-        <v>太陽石</v>
+        <v>茶水晶</v>
       </c>
       <c r="E171">
         <v>8</v>
       </c>
       <c r="F171">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G171" t="str">
-        <v>太陽石.png</v>
+        <v>茶水晶.png</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>tys_stn_10</v>
+        <v>csj_cysl_10</v>
       </c>
       <c r="B172" t="str">
         <v>珠子</v>
       </c>
       <c r="C172" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D172" t="str">
-        <v>太陽石</v>
+        <v>茶水晶</v>
       </c>
       <c r="E172">
         <v>10</v>
       </c>
       <c r="F172">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G172" t="str">
-        <v>太陽石.png</v>
+        <v>茶水晶.png</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>wgzl_pnd_2</v>
+        <v>hmn_agt_6</v>
       </c>
       <c r="B173" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C173" t="str">
-        <v>吊墜</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D173" t="str">
-        <v>王國之淚</v>
+        <v>紅瑪瑙</v>
       </c>
       <c r="E173">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F173">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G173" t="str">
-        <v>王国之泪.png</v>
+        <v>红玛瑙.png</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>zsj_cysl_6</v>
+        <v>hmn_agt_8</v>
       </c>
       <c r="B174" t="str">
         <v>珠子</v>
       </c>
       <c r="C174" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D174" t="str">
-        <v>紫水晶</v>
+        <v>紅瑪瑙</v>
       </c>
       <c r="E174">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F174">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G174" t="str">
-        <v>紫水晶.png</v>
+        <v>红玛瑙.png</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>zsj_cysl_8</v>
+        <v>hmn_agt_10</v>
       </c>
       <c r="B175" t="str">
         <v>珠子</v>
       </c>
       <c r="C175" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D175" t="str">
-        <v>紫水晶</v>
+        <v>紅瑪瑙</v>
       </c>
       <c r="E175">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F175">
         <v>89</v>
       </c>
       <c r="G175" t="str">
-        <v>紫水晶.png</v>
+        <v>红玛瑙.png</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>zsj_cysl_10</v>
+        <v>kqs_stn_6</v>
       </c>
       <c r="B176" t="str">
         <v>珠子</v>
       </c>
       <c r="C176" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D176" t="str">
-        <v>紫水晶</v>
+        <v>孔雀石</v>
       </c>
       <c r="E176">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F176">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G176" t="str">
-        <v>紫水晶.png</v>
+        <v>孔雀石.png</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>dsj_cysl_6</v>
+        <v>kqs_stn_8</v>
       </c>
       <c r="B177" t="str">
         <v>珠子</v>
       </c>
       <c r="C177" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D177" t="str">
-        <v>豆沙晶</v>
+        <v>孔雀石</v>
       </c>
       <c r="E177">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F177">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G177" t="str">
-        <v>豆沙晶.png</v>
+        <v>孔雀石.png</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>dsj_cysl_8</v>
+        <v>kqs_stn_10</v>
       </c>
       <c r="B178" t="str">
         <v>珠子</v>
       </c>
       <c r="C178" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D178" t="str">
-        <v>豆沙晶</v>
+        <v>孔雀石</v>
       </c>
       <c r="E178">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F178">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="G178" t="str">
-        <v>豆沙晶.png</v>
+        <v>孔雀石.png</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>dsj_cysl_10</v>
+        <v>wlg_cysl_6</v>
       </c>
       <c r="B179" t="str">
         <v>珠子</v>
@@ -4504,67 +4504,67 @@
         <v>水晶</v>
       </c>
       <c r="D179" t="str">
-        <v>豆沙晶</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E179">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F179">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G179" t="str">
-        <v>豆沙晶.png</v>
+        <v>乌拉圭.png</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>yhyqws_stn_6</v>
+        <v>wlg_cysl_8</v>
       </c>
       <c r="B180" t="str">
         <v>珠子</v>
       </c>
       <c r="C180" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D180" t="str">
-        <v>櫻花石</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E180">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F180">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G180" t="str">
-        <v>櫻花石.png</v>
+        <v>乌拉圭.png</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>yhyqws_stn_8</v>
+        <v>wlg_cysl_10</v>
       </c>
       <c r="B181" t="str">
         <v>珠子</v>
       </c>
       <c r="C181" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D181" t="str">
-        <v>櫻花石</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E181">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F181">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="G181" t="str">
-        <v>櫻花石.png</v>
+        <v>乌拉圭.png</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>yhyqws_stn_10</v>
+        <v>qjs_stn_6</v>
       </c>
       <c r="B182" t="str">
         <v>珠子</v>
@@ -4573,67 +4573,67 @@
         <v>礦石</v>
       </c>
       <c r="D182" t="str">
-        <v>櫻花石</v>
+        <v>青金石</v>
       </c>
       <c r="E182">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F182">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G182" t="str">
-        <v>櫻花石.png</v>
+        <v>青金石.png</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>zfj_cysl_6</v>
+        <v>qjs_stn_8</v>
       </c>
       <c r="B183" t="str">
         <v>珠子</v>
       </c>
       <c r="C183" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D183" t="str">
-        <v>紫粉晶</v>
+        <v>青金石</v>
       </c>
       <c r="E183">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F183">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G183" t="str">
-        <v>紫粉晶.png</v>
+        <v>青金石.png</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>zfj_cysl_8</v>
+        <v>qjs_stn_10</v>
       </c>
       <c r="B184" t="str">
         <v>珠子</v>
       </c>
       <c r="C184" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D184" t="str">
-        <v>紫粉晶</v>
+        <v>青金石</v>
       </c>
       <c r="E184">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F184">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G184" t="str">
-        <v>紫粉晶.png</v>
+        <v>青金石.png</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>zfj_cysl_10</v>
+        <v>zyl_cysl_6</v>
       </c>
       <c r="B185" t="str">
         <v>珠子</v>
@@ -4642,30 +4642,30 @@
         <v>水晶</v>
       </c>
       <c r="D185" t="str">
-        <v>紫粉晶</v>
+        <v>紫幽靈</v>
       </c>
       <c r="E185">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F185">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G185" t="str">
-        <v>紫粉晶.png</v>
+        <v>紫幽灵.png</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>jslzzy_spc_8</v>
+        <v>zyl_cysl_8</v>
       </c>
       <c r="B186" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C186" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D186" t="str">
-        <v>金色六字真言</v>
+        <v>紫幽靈</v>
       </c>
       <c r="E186">
         <v>8</v>
@@ -4674,136 +4674,136 @@
         <v>59</v>
       </c>
       <c r="G186" t="str">
-        <v>金色六字真言.png</v>
+        <v>紫幽灵.png</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ccs_stn_6</v>
+        <v>he_agt_6</v>
       </c>
       <c r="B187" t="str">
         <v>珠子</v>
       </c>
       <c r="C187" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D187" t="str">
-        <v>橙彩石</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E187">
         <v>6</v>
       </c>
       <c r="F187">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G187" t="str">
-        <v>橙彩石.png</v>
+        <v>黑玛瑙.png</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>ccs_stn_8</v>
+        <v>he_agt_8</v>
       </c>
       <c r="B188" t="str">
         <v>珠子</v>
       </c>
       <c r="C188" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D188" t="str">
-        <v>橙彩石</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E188">
         <v>8</v>
       </c>
       <c r="F188">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G188" t="str">
-        <v>橙彩石.png</v>
+        <v>黑玛瑙.png</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ccs_stn_10</v>
+        <v>he_agt_10</v>
       </c>
       <c r="B189" t="str">
         <v>珠子</v>
       </c>
       <c r="C189" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D189" t="str">
-        <v>橙彩石</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E189">
         <v>10</v>
       </c>
       <c r="F189">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G189" t="str">
-        <v>橙彩石.png</v>
+        <v>黑玛瑙.png</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>lfj_cysl_6</v>
+        <v>jys_stn_6</v>
       </c>
       <c r="B190" t="str">
         <v>珠子</v>
       </c>
       <c r="C190" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D190" t="str">
-        <v>綠髮晶</v>
+        <v>金曜石</v>
       </c>
       <c r="E190">
         <v>6</v>
       </c>
       <c r="F190">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G190" t="str">
-        <v>綠髮晶.png</v>
+        <v>金曜石.png</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>lfj_cysl_8</v>
+        <v>jys_stn_8</v>
       </c>
       <c r="B191" t="str">
         <v>珠子</v>
       </c>
       <c r="C191" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D191" t="str">
-        <v>綠髮晶</v>
+        <v>金曜石</v>
       </c>
       <c r="E191">
         <v>8</v>
       </c>
       <c r="F191">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G191" t="str">
-        <v>綠髮晶.png</v>
+        <v>金曜石.png</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>lfj_cysl_10</v>
+        <v>jys_stn_10</v>
       </c>
       <c r="B192" t="str">
         <v>珠子</v>
       </c>
       <c r="C192" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D192" t="str">
-        <v>綠髮晶</v>
+        <v>金曜石</v>
       </c>
       <c r="E192">
         <v>10</v>
@@ -4812,67 +4812,67 @@
         <v>99</v>
       </c>
       <c r="G192" t="str">
-        <v>綠髮晶.png</v>
+        <v>金曜石.png</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>lcmj_cysl_6</v>
+        <v>hys_stn_6</v>
       </c>
       <c r="B193" t="str">
         <v>珠子</v>
       </c>
       <c r="C193" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D193" t="str">
-        <v>綠莓晶</v>
+        <v>黑曜石</v>
       </c>
       <c r="E193">
         <v>6</v>
       </c>
       <c r="F193">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G193" t="str">
-        <v>綠莓晶.png</v>
+        <v>黑曜石.png</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>lcmj_cysl_8</v>
+        <v>hys_stn_8</v>
       </c>
       <c r="B194" t="str">
         <v>珠子</v>
       </c>
       <c r="C194" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D194" t="str">
-        <v>綠莓晶</v>
+        <v>黑曜石</v>
       </c>
       <c r="E194">
         <v>8</v>
       </c>
       <c r="F194">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G194" t="str">
-        <v>綠莓晶.png</v>
+        <v>黑曜石.png</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>lcmj_cysl_10</v>
+        <v>hys_stn_10</v>
       </c>
       <c r="B195" t="str">
         <v>珠子</v>
       </c>
       <c r="C195" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D195" t="str">
-        <v>綠莓晶</v>
+        <v>黑曜石</v>
       </c>
       <c r="E195">
         <v>10</v>
@@ -4881,1990 +4881,12 @@
         <v>99</v>
       </c>
       <c r="G195" t="str">
-        <v>綠莓晶.png</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>hjh_cysl_6</v>
-      </c>
-      <c r="B196" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C196" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D196" t="str">
-        <v>紅膠花</v>
-      </c>
-      <c r="E196">
-        <v>6</v>
-      </c>
-      <c r="F196">
-        <v>69</v>
-      </c>
-      <c r="G196" t="str">
-        <v>紅膠花.png</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>hjh_cysl_8</v>
-      </c>
-      <c r="B197" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C197" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D197" t="str">
-        <v>紅膠花</v>
-      </c>
-      <c r="E197">
-        <v>8</v>
-      </c>
-      <c r="F197">
-        <v>89</v>
-      </c>
-      <c r="G197" t="str">
-        <v>紅膠花.png</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>hjh_cysl_10</v>
-      </c>
-      <c r="B198" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C198" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D198" t="str">
-        <v>紅膠花</v>
-      </c>
-      <c r="E198">
-        <v>10</v>
-      </c>
-      <c r="F198">
-        <v>99</v>
-      </c>
-      <c r="G198" t="str">
-        <v>紅膠花.png</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>cyhdls_pnd_2</v>
-      </c>
-      <c r="B199" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C199" t="str">
-        <v>吊墜</v>
-      </c>
-      <c r="D199" t="str">
-        <v>藏銀蝴蝶流蘇</v>
-      </c>
-      <c r="E199">
-        <v>2</v>
-      </c>
-      <c r="F199">
-        <v>99</v>
-      </c>
-      <c r="G199" t="str">
-        <v>藏银蝴蝶流苏.png</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>mghh_spc_6</v>
-      </c>
-      <c r="B200" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C200" t="str">
-        <v>隔珠</v>
-      </c>
-      <c r="D200" t="str">
-        <v>玫瑰花環</v>
-      </c>
-      <c r="E200">
-        <v>6</v>
-      </c>
-      <c r="F200">
-        <v>59</v>
-      </c>
-      <c r="G200" t="str">
-        <v>玫瑰花环.png</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>bmnmh_spc_8</v>
-      </c>
-      <c r="B201" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C201" t="str">
-        <v>隔珠</v>
-      </c>
-      <c r="D201" t="str">
-        <v>白瑪瑙魔盒</v>
-      </c>
-      <c r="E201">
-        <v>8</v>
-      </c>
-      <c r="F201">
-        <v>59</v>
-      </c>
-      <c r="G201" t="str">
-        <v>白玛瑙魔盒.png</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>cyhw_spc_5</v>
-      </c>
-      <c r="B202" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C202" t="str">
-        <v>隔珠</v>
-      </c>
-      <c r="D202" t="str">
-        <v>藏銀回紋</v>
-      </c>
-      <c r="E202">
-        <v>5</v>
-      </c>
-      <c r="F202">
-        <v>59</v>
-      </c>
-      <c r="G202" t="str">
-        <v>藏银回纹.png</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>htm_cysl_6</v>
-      </c>
-      <c r="B203" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C203" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D203" t="str">
-        <v>紅兔毛</v>
-      </c>
-      <c r="E203">
-        <v>6</v>
-      </c>
-      <c r="F203">
-        <v>69</v>
-      </c>
-      <c r="G203" t="str">
-        <v>紅兔毛.png</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>htm_cysl_8</v>
-      </c>
-      <c r="B204" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C204" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D204" t="str">
-        <v>紅兔毛</v>
-      </c>
-      <c r="E204">
-        <v>8</v>
-      </c>
-      <c r="F204">
-        <v>89</v>
-      </c>
-      <c r="G204" t="str">
-        <v>紅兔毛.png</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>htm_cysl_10</v>
-      </c>
-      <c r="B205" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C205" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D205" t="str">
-        <v>紅兔毛</v>
-      </c>
-      <c r="E205">
-        <v>10</v>
-      </c>
-      <c r="F205">
-        <v>99</v>
-      </c>
-      <c r="G205" t="str">
-        <v>紅兔毛.png</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>zsmh_spc_8</v>
-      </c>
-      <c r="B206" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C206" t="str">
-        <v>隔珠</v>
-      </c>
-      <c r="D206" t="str">
-        <v>硃砂魔盒</v>
-      </c>
-      <c r="E206">
-        <v>8</v>
-      </c>
-      <c r="F206">
-        <v>59</v>
-      </c>
-      <c r="G206" t="str">
-        <v>朱砂魔盒.png</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>cyszdz_pnd_2</v>
-      </c>
-      <c r="B207" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C207" t="str">
-        <v>吊墜</v>
-      </c>
-      <c r="D207" t="str">
-        <v>藏銀十字吊墜</v>
-      </c>
-      <c r="E207">
-        <v>2</v>
-      </c>
-      <c r="F207">
-        <v>99</v>
-      </c>
-      <c r="G207" t="str">
-        <v>藏银十字吊坠.png</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>cyyc_pnd_2</v>
-      </c>
-      <c r="B208" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C208" t="str">
-        <v>吊墜</v>
-      </c>
-      <c r="D208" t="str">
-        <v>藏銀葉叢</v>
-      </c>
-      <c r="E208">
-        <v>2</v>
-      </c>
-      <c r="F208">
-        <v>99</v>
-      </c>
-      <c r="G208" t="str">
-        <v>藏银叶丛.png</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>cyxhlf_spc_8</v>
-      </c>
-      <c r="B209" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C209" t="str">
-        <v>隔珠</v>
-      </c>
-      <c r="D209" t="str">
-        <v>藏銀小花立方</v>
-      </c>
-      <c r="E209">
-        <v>8</v>
-      </c>
-      <c r="F209">
-        <v>59</v>
-      </c>
-      <c r="G209" t="str">
-        <v>藏银小花立方.png</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>cydhlf_spc_8</v>
-      </c>
-      <c r="B210" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C210" t="str">
-        <v>隔珠</v>
-      </c>
-      <c r="D210" t="str">
-        <v>藏銀大花立方</v>
-      </c>
-      <c r="E210">
-        <v>8</v>
-      </c>
-      <c r="F210">
-        <v>59</v>
-      </c>
-      <c r="G210" t="str">
-        <v>藏银大花立方.png</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>jtys_stn_6</v>
-      </c>
-      <c r="B211" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C211" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D211" t="str">
-        <v>金陽石</v>
-      </c>
-      <c r="E211">
-        <v>6</v>
-      </c>
-      <c r="F211">
-        <v>69</v>
-      </c>
-      <c r="G211" t="str">
-        <v>金陽石.png</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>jtys_stn_8</v>
-      </c>
-      <c r="B212" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C212" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D212" t="str">
-        <v>金陽石</v>
-      </c>
-      <c r="E212">
-        <v>8</v>
-      </c>
-      <c r="F212">
-        <v>89</v>
-      </c>
-      <c r="G212" t="str">
-        <v>金陽石.png</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>jtys_stn_10</v>
-      </c>
-      <c r="B213" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C213" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D213" t="str">
-        <v>金陽石</v>
-      </c>
-      <c r="E213">
-        <v>10</v>
-      </c>
-      <c r="F213">
-        <v>99</v>
-      </c>
-      <c r="G213" t="str">
-        <v>金陽石.png</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>jtlfq_spc_8</v>
-      </c>
-      <c r="B214" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C214" t="str">
-        <v>隔珠</v>
-      </c>
-      <c r="D214" t="str">
-        <v>景泰藍福球</v>
-      </c>
-      <c r="E214">
-        <v>8</v>
-      </c>
-      <c r="F214">
-        <v>59</v>
-      </c>
-      <c r="G214" t="str">
-        <v>景泰蓝福球.png</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>hjc_stn_6</v>
-      </c>
-      <c r="B215" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C215" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D215" t="str">
-        <v>黑金超</v>
-      </c>
-      <c r="E215">
-        <v>6</v>
-      </c>
-      <c r="F215">
-        <v>69</v>
-      </c>
-      <c r="G215" t="str">
-        <v>黑金超.png</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>hjc_stn_8</v>
-      </c>
-      <c r="B216" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C216" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D216" t="str">
-        <v>黑金超</v>
-      </c>
-      <c r="E216">
-        <v>8</v>
-      </c>
-      <c r="F216">
-        <v>89</v>
-      </c>
-      <c r="G216" t="str">
-        <v>黑金超.png</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>hjc_stn_10</v>
-      </c>
-      <c r="B217" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C217" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D217" t="str">
-        <v>黑金超</v>
-      </c>
-      <c r="E217">
-        <v>10</v>
-      </c>
-      <c r="F217">
-        <v>99</v>
-      </c>
-      <c r="G217" t="str">
-        <v>黑金超.png</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>hhy_stn_6</v>
-      </c>
-      <c r="B218" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C218" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D218" t="str">
-        <v>黃虎眼</v>
-      </c>
-      <c r="E218">
-        <v>6</v>
-      </c>
-      <c r="F218">
-        <v>69</v>
-      </c>
-      <c r="G218" t="str">
-        <v>黃虎眼.png</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>hhy_stn_8</v>
-      </c>
-      <c r="B219" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C219" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D219" t="str">
-        <v>黃虎眼</v>
-      </c>
-      <c r="E219">
-        <v>8</v>
-      </c>
-      <c r="F219">
-        <v>89</v>
-      </c>
-      <c r="G219" t="str">
-        <v>黃虎眼.png</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>hhy_stn_10</v>
-      </c>
-      <c r="B220" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C220" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D220" t="str">
-        <v>黃虎眼</v>
-      </c>
-      <c r="E220">
-        <v>10</v>
-      </c>
-      <c r="F220">
-        <v>99</v>
-      </c>
-      <c r="G220" t="str">
-        <v>黃虎眼.png</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>dws_stn_6</v>
-      </c>
-      <c r="B221" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C221" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D221" t="str">
-        <v>帝王砂</v>
-      </c>
-      <c r="E221">
-        <v>6</v>
-      </c>
-      <c r="F221">
-        <v>69</v>
-      </c>
-      <c r="G221" t="str">
-        <v>帝王砂.png</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>dws_stn_8</v>
-      </c>
-      <c r="B222" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C222" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D222" t="str">
-        <v>帝王砂</v>
-      </c>
-      <c r="E222">
-        <v>8</v>
-      </c>
-      <c r="F222">
-        <v>89</v>
-      </c>
-      <c r="G222" t="str">
-        <v>帝王砂.png</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="str">
-        <v>dws_stn_10</v>
-      </c>
-      <c r="B223" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C223" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D223" t="str">
-        <v>帝王砂</v>
-      </c>
-      <c r="E223">
-        <v>10</v>
-      </c>
-      <c r="F223">
-        <v>99</v>
-      </c>
-      <c r="G223" t="str">
-        <v>帝王砂.png</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="str">
-        <v>hmn_agt_6</v>
-      </c>
-      <c r="B224" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C224" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D224" t="str">
-        <v>紅瑪瑙</v>
-      </c>
-      <c r="E224">
-        <v>6</v>
-      </c>
-      <c r="F224">
-        <v>69</v>
-      </c>
-      <c r="G224" t="str">
-        <v>紅瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>hmn_agt_8</v>
-      </c>
-      <c r="B225" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C225" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D225" t="str">
-        <v>紅瑪瑙</v>
-      </c>
-      <c r="E225">
-        <v>8</v>
-      </c>
-      <c r="F225">
-        <v>89</v>
-      </c>
-      <c r="G225" t="str">
-        <v>紅瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="str">
-        <v>hmn_agt_10</v>
-      </c>
-      <c r="B226" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C226" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D226" t="str">
-        <v>紅瑪瑙</v>
-      </c>
-      <c r="E226">
-        <v>10</v>
-      </c>
-      <c r="F226">
-        <v>99</v>
-      </c>
-      <c r="G226" t="str">
-        <v>紅瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v>bys_stn_6</v>
-      </c>
-      <c r="B227" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C227" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D227" t="str">
-        <v>冰曜石</v>
-      </c>
-      <c r="E227">
-        <v>6</v>
-      </c>
-      <c r="F227">
-        <v>69</v>
-      </c>
-      <c r="G227" t="str">
-        <v>冰曜石.png</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="str">
-        <v>bys_stn_8</v>
-      </c>
-      <c r="B228" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C228" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D228" t="str">
-        <v>冰曜石</v>
-      </c>
-      <c r="E228">
-        <v>8</v>
-      </c>
-      <c r="F228">
-        <v>89</v>
-      </c>
-      <c r="G228" t="str">
-        <v>冰曜石.png</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v>bys_stn_10</v>
-      </c>
-      <c r="B229" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C229" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D229" t="str">
-        <v>冰曜石</v>
-      </c>
-      <c r="E229">
-        <v>10</v>
-      </c>
-      <c r="F229">
-        <v>99</v>
-      </c>
-      <c r="G229" t="str">
-        <v>冰曜石.png</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="str">
-        <v>jtcj_cysl_6</v>
-      </c>
-      <c r="B230" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C230" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D230" t="str">
-        <v>淨體茶晶</v>
-      </c>
-      <c r="E230">
-        <v>6</v>
-      </c>
-      <c r="F230">
-        <v>69</v>
-      </c>
-      <c r="G230" t="str">
-        <v>淨體茶晶.png</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="str">
-        <v>jtcj_cysl_8</v>
-      </c>
-      <c r="B231" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C231" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D231" t="str">
-        <v>淨體茶晶</v>
-      </c>
-      <c r="E231">
-        <v>8</v>
-      </c>
-      <c r="F231">
-        <v>89</v>
-      </c>
-      <c r="G231" t="str">
-        <v>淨體茶晶.png</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="str">
-        <v>jtcj_cysl_10</v>
-      </c>
-      <c r="B232" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C232" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D232" t="str">
-        <v>淨體茶晶</v>
-      </c>
-      <c r="E232">
-        <v>10</v>
-      </c>
-      <c r="F232">
-        <v>99</v>
-      </c>
-      <c r="G232" t="str">
-        <v>淨體茶晶.png</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="str">
-        <v>ljs_stn_6</v>
-      </c>
-      <c r="B233" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C233" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D233" t="str">
-        <v>藍晶石</v>
-      </c>
-      <c r="E233">
-        <v>6</v>
-      </c>
-      <c r="F233">
-        <v>69</v>
-      </c>
-      <c r="G233" t="str">
-        <v>藍晶石.png</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="str">
-        <v>ljs_stn_8</v>
-      </c>
-      <c r="B234" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C234" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D234" t="str">
-        <v>藍晶石</v>
-      </c>
-      <c r="E234">
-        <v>8</v>
-      </c>
-      <c r="F234">
-        <v>89</v>
-      </c>
-      <c r="G234" t="str">
-        <v>藍晶石.png</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="str">
-        <v>ljs_stn_10</v>
-      </c>
-      <c r="B235" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C235" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D235" t="str">
-        <v>藍晶石</v>
-      </c>
-      <c r="E235">
-        <v>10</v>
-      </c>
-      <c r="F235">
-        <v>99</v>
-      </c>
-      <c r="G235" t="str">
-        <v>藍晶石.png</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="str">
-        <v>yys_stn_6</v>
-      </c>
-      <c r="B236" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C236" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D236" t="str">
-        <v>銀曜石</v>
-      </c>
-      <c r="E236">
-        <v>6</v>
-      </c>
-      <c r="F236">
-        <v>69</v>
-      </c>
-      <c r="G236" t="str">
-        <v>銀曜石.png</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="str">
-        <v>yys_stn_8</v>
-      </c>
-      <c r="B237" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C237" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D237" t="str">
-        <v>銀曜石</v>
-      </c>
-      <c r="E237">
-        <v>8</v>
-      </c>
-      <c r="F237">
-        <v>89</v>
-      </c>
-      <c r="G237" t="str">
-        <v>銀曜石.png</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="str">
-        <v>yys_stn_10</v>
-      </c>
-      <c r="B238" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C238" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D238" t="str">
-        <v>銀曜石</v>
-      </c>
-      <c r="E238">
-        <v>10</v>
-      </c>
-      <c r="F238">
-        <v>99</v>
-      </c>
-      <c r="G238" t="str">
-        <v>銀曜石.png</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="str">
-        <v>bmw_pnd_2</v>
-      </c>
-      <c r="B239" t="str">
-        <v>配件</v>
-      </c>
-      <c r="C239" t="str">
-        <v>吊墜</v>
-      </c>
-      <c r="D239" t="str">
-        <v>捕夢網</v>
-      </c>
-      <c r="E239">
-        <v>2</v>
-      </c>
-      <c r="F239">
-        <v>99</v>
-      </c>
-      <c r="G239" t="str">
-        <v>捕梦网.png</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="str">
-        <v>kqs_stn_6</v>
-      </c>
-      <c r="B240" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C240" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D240" t="str">
-        <v>孔雀石</v>
-      </c>
-      <c r="E240">
-        <v>6</v>
-      </c>
-      <c r="F240">
-        <v>69</v>
-      </c>
-      <c r="G240" t="str">
-        <v>孔雀石.png</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="str">
-        <v>kqs_stn_8</v>
-      </c>
-      <c r="B241" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C241" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D241" t="str">
-        <v>孔雀石</v>
-      </c>
-      <c r="E241">
-        <v>8</v>
-      </c>
-      <c r="F241">
-        <v>89</v>
-      </c>
-      <c r="G241" t="str">
-        <v>孔雀石.png</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="str">
-        <v>kqs_stn_10</v>
-      </c>
-      <c r="B242" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C242" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D242" t="str">
-        <v>孔雀石</v>
-      </c>
-      <c r="E242">
-        <v>10</v>
-      </c>
-      <c r="F242">
-        <v>99</v>
-      </c>
-      <c r="G242" t="str">
-        <v>孔雀石.png</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="str">
-        <v>llj_stn_6</v>
-      </c>
-      <c r="B243" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C243" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D243" t="str">
-        <v>綠龍晶</v>
-      </c>
-      <c r="E243">
-        <v>6</v>
-      </c>
-      <c r="F243">
-        <v>69</v>
-      </c>
-      <c r="G243" t="str">
-        <v>綠龍晶.png</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="str">
-        <v>llj_stn_8</v>
-      </c>
-      <c r="B244" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C244" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D244" t="str">
-        <v>綠龍晶</v>
-      </c>
-      <c r="E244">
-        <v>8</v>
-      </c>
-      <c r="F244">
-        <v>89</v>
-      </c>
-      <c r="G244" t="str">
-        <v>綠龍晶.png</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="str">
-        <v>llj_stn_10</v>
-      </c>
-      <c r="B245" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C245" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D245" t="str">
-        <v>綠龍晶</v>
-      </c>
-      <c r="E245">
-        <v>10</v>
-      </c>
-      <c r="F245">
-        <v>99</v>
-      </c>
-      <c r="G245" t="str">
-        <v>綠龍晶.png</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="str">
-        <v>wlgzsj_cysl_6</v>
-      </c>
-      <c r="B246" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C246" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D246" t="str">
-        <v>烏拉圭紫水晶</v>
-      </c>
-      <c r="E246">
-        <v>6</v>
-      </c>
-      <c r="F246">
-        <v>69</v>
-      </c>
-      <c r="G246" t="str">
-        <v>烏拉圭紫水晶.png</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="str">
-        <v>wlgzsj_cysl_8</v>
-      </c>
-      <c r="B247" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C247" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D247" t="str">
-        <v>烏拉圭紫水晶</v>
-      </c>
-      <c r="E247">
-        <v>8</v>
-      </c>
-      <c r="F247">
-        <v>89</v>
-      </c>
-      <c r="G247" t="str">
-        <v>烏拉圭紫水晶.png</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="str">
-        <v>wlgzsj_cysl_10</v>
-      </c>
-      <c r="B248" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C248" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D248" t="str">
-        <v>烏拉圭紫水晶</v>
-      </c>
-      <c r="E248">
-        <v>10</v>
-      </c>
-      <c r="F248">
-        <v>99</v>
-      </c>
-      <c r="G248" t="str">
-        <v>烏拉圭紫水晶.png</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v>lt_wd_6</v>
-      </c>
-      <c r="B249" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C249" t="str">
-        <v>木質</v>
-      </c>
-      <c r="D249" t="str">
-        <v>綠檀木</v>
-      </c>
-      <c r="E249">
-        <v>6</v>
-      </c>
-      <c r="F249">
-        <v>69</v>
-      </c>
-      <c r="G249" t="str">
-        <v>綠檀木.png</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="str">
-        <v>lt_wd_8</v>
-      </c>
-      <c r="B250" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C250" t="str">
-        <v>木質</v>
-      </c>
-      <c r="D250" t="str">
-        <v>綠檀木</v>
-      </c>
-      <c r="E250">
-        <v>8</v>
-      </c>
-      <c r="F250">
-        <v>89</v>
-      </c>
-      <c r="G250" t="str">
-        <v>綠檀木.png</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="str">
-        <v>lt_wd_10</v>
-      </c>
-      <c r="B251" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C251" t="str">
-        <v>木質</v>
-      </c>
-      <c r="D251" t="str">
-        <v>綠檀木</v>
-      </c>
-      <c r="E251">
-        <v>10</v>
-      </c>
-      <c r="F251">
-        <v>99</v>
-      </c>
-      <c r="G251" t="str">
-        <v>綠檀木.png</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="str">
-        <v>lmn_agt_6</v>
-      </c>
-      <c r="B252" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C252" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D252" t="str">
-        <v>綠瑪瑙</v>
-      </c>
-      <c r="E252">
-        <v>6</v>
-      </c>
-      <c r="F252">
-        <v>69</v>
-      </c>
-      <c r="G252" t="str">
-        <v>綠瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="str">
-        <v>lmn_agt_8</v>
-      </c>
-      <c r="B253" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C253" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D253" t="str">
-        <v>綠瑪瑙</v>
-      </c>
-      <c r="E253">
-        <v>8</v>
-      </c>
-      <c r="F253">
-        <v>89</v>
-      </c>
-      <c r="G253" t="str">
-        <v>綠瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="str">
-        <v>lmn_agt_10</v>
-      </c>
-      <c r="B254" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C254" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D254" t="str">
-        <v>綠瑪瑙</v>
-      </c>
-      <c r="E254">
-        <v>10</v>
-      </c>
-      <c r="F254">
-        <v>99</v>
-      </c>
-      <c r="G254" t="str">
-        <v>綠瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="str">
-        <v>ltm_cysl_6</v>
-      </c>
-      <c r="B255" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C255" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D255" t="str">
-        <v>綠兔毛</v>
-      </c>
-      <c r="E255">
-        <v>6</v>
-      </c>
-      <c r="F255">
-        <v>69</v>
-      </c>
-      <c r="G255" t="str">
-        <v>綠兔毛.png</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="str">
-        <v>ltm_cysl_8</v>
-      </c>
-      <c r="B256" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C256" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D256" t="str">
-        <v>綠兔毛</v>
-      </c>
-      <c r="E256">
-        <v>8</v>
-      </c>
-      <c r="F256">
-        <v>89</v>
-      </c>
-      <c r="G256" t="str">
-        <v>綠兔毛.png</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="str">
-        <v>ltm_cysl_10</v>
-      </c>
-      <c r="B257" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C257" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D257" t="str">
-        <v>綠兔毛</v>
-      </c>
-      <c r="E257">
-        <v>10</v>
-      </c>
-      <c r="F257">
-        <v>99</v>
-      </c>
-      <c r="G257" t="str">
-        <v>綠兔毛.png</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="str">
-        <v>zyl_cysl_6</v>
-      </c>
-      <c r="B258" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C258" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D258" t="str">
-        <v>紫幽靈</v>
-      </c>
-      <c r="E258">
-        <v>6</v>
-      </c>
-      <c r="F258">
-        <v>69</v>
-      </c>
-      <c r="G258" t="str">
-        <v>紫幽靈.png</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="str">
-        <v>zyl_cysl_8</v>
-      </c>
-      <c r="B259" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C259" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D259" t="str">
-        <v>紫幽靈</v>
-      </c>
-      <c r="E259">
-        <v>8</v>
-      </c>
-      <c r="F259">
-        <v>89</v>
-      </c>
-      <c r="G259" t="str">
-        <v>紫幽靈.png</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="str">
-        <v>zyl_cysl_10</v>
-      </c>
-      <c r="B260" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C260" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D260" t="str">
-        <v>紫幽靈</v>
-      </c>
-      <c r="E260">
-        <v>10</v>
-      </c>
-      <c r="F260">
-        <v>99</v>
-      </c>
-      <c r="G260" t="str">
-        <v>紫幽靈.png</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="str">
-        <v>qjs_stn_6</v>
-      </c>
-      <c r="B261" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C261" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D261" t="str">
-        <v>青金石</v>
-      </c>
-      <c r="E261">
-        <v>6</v>
-      </c>
-      <c r="F261">
-        <v>69</v>
-      </c>
-      <c r="G261" t="str">
-        <v>青金石.png</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="str">
-        <v>qjs_stn_8</v>
-      </c>
-      <c r="B262" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C262" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D262" t="str">
-        <v>青金石</v>
-      </c>
-      <c r="E262">
-        <v>8</v>
-      </c>
-      <c r="F262">
-        <v>89</v>
-      </c>
-      <c r="G262" t="str">
-        <v>青金石.png</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="str">
-        <v>qjs_stn_10</v>
-      </c>
-      <c r="B263" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C263" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D263" t="str">
-        <v>青金石</v>
-      </c>
-      <c r="E263">
-        <v>10</v>
-      </c>
-      <c r="F263">
-        <v>99</v>
-      </c>
-      <c r="G263" t="str">
-        <v>青金石.png</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="str">
-        <v>he_agt_6</v>
-      </c>
-      <c r="B264" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C264" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D264" t="str">
-        <v>黑瑪瑙</v>
-      </c>
-      <c r="E264">
-        <v>6</v>
-      </c>
-      <c r="F264">
-        <v>69</v>
-      </c>
-      <c r="G264" t="str">
-        <v>黑瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="str">
-        <v>he_agt_8</v>
-      </c>
-      <c r="B265" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C265" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D265" t="str">
-        <v>黑瑪瑙</v>
-      </c>
-      <c r="E265">
-        <v>8</v>
-      </c>
-      <c r="F265">
-        <v>89</v>
-      </c>
-      <c r="G265" t="str">
-        <v>黑瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="str">
-        <v>he_agt_10</v>
-      </c>
-      <c r="B266" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C266" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D266" t="str">
-        <v>黑瑪瑙</v>
-      </c>
-      <c r="E266">
-        <v>10</v>
-      </c>
-      <c r="F266">
-        <v>99</v>
-      </c>
-      <c r="G266" t="str">
-        <v>黑瑪瑙.png</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="str">
-        <v>lhy_stn_6</v>
-      </c>
-      <c r="B267" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C267" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D267" t="str">
-        <v>藍虎眼</v>
-      </c>
-      <c r="E267">
-        <v>6</v>
-      </c>
-      <c r="F267">
-        <v>69</v>
-      </c>
-      <c r="G267" t="str">
-        <v>藍虎眼.png</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="str">
-        <v>lhy_stn_8</v>
-      </c>
-      <c r="B268" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C268" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D268" t="str">
-        <v>藍虎眼</v>
-      </c>
-      <c r="E268">
-        <v>8</v>
-      </c>
-      <c r="F268">
-        <v>89</v>
-      </c>
-      <c r="G268" t="str">
-        <v>藍虎眼.png</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>lhy_stn_10</v>
-      </c>
-      <c r="B269" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C269" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D269" t="str">
-        <v>藍虎眼</v>
-      </c>
-      <c r="E269">
-        <v>10</v>
-      </c>
-      <c r="F269">
-        <v>99</v>
-      </c>
-      <c r="G269" t="str">
-        <v>藍虎眼.png</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="str">
-        <v>zjs_stn_6</v>
-      </c>
-      <c r="B270" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C270" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D270" t="str">
-        <v>紫金砂</v>
-      </c>
-      <c r="E270">
-        <v>6</v>
-      </c>
-      <c r="F270">
-        <v>69</v>
-      </c>
-      <c r="G270" t="str">
-        <v>紫金砂.png</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="str">
-        <v>zjs_stn_8</v>
-      </c>
-      <c r="B271" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C271" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D271" t="str">
-        <v>紫金砂</v>
-      </c>
-      <c r="E271">
-        <v>8</v>
-      </c>
-      <c r="F271">
-        <v>89</v>
-      </c>
-      <c r="G271" t="str">
-        <v>紫金砂.png</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="str">
-        <v>zjs_stn_10</v>
-      </c>
-      <c r="B272" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C272" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D272" t="str">
-        <v>紫金砂</v>
-      </c>
-      <c r="E272">
-        <v>10</v>
-      </c>
-      <c r="F272">
-        <v>99</v>
-      </c>
-      <c r="G272" t="str">
-        <v>紫金砂.png</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="str">
-        <v>hbx_stn_6</v>
-      </c>
-      <c r="B273" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C273" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D273" t="str">
-        <v>黑碧璽</v>
-      </c>
-      <c r="E273">
-        <v>6</v>
-      </c>
-      <c r="F273">
-        <v>69</v>
-      </c>
-      <c r="G273" t="str">
-        <v>黑碧璽.png</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="str">
-        <v>hbx_stn_8</v>
-      </c>
-      <c r="B274" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C274" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D274" t="str">
-        <v>黑碧璽</v>
-      </c>
-      <c r="E274">
-        <v>8</v>
-      </c>
-      <c r="F274">
-        <v>89</v>
-      </c>
-      <c r="G274" t="str">
-        <v>黑碧璽.png</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="str">
-        <v>hbx_stn_10</v>
-      </c>
-      <c r="B275" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C275" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D275" t="str">
-        <v>黑碧璽</v>
-      </c>
-      <c r="E275">
-        <v>10</v>
-      </c>
-      <c r="F275">
-        <v>99</v>
-      </c>
-      <c r="G275" t="str">
-        <v>黑碧璽.png</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="str">
-        <v>hys_stn_6</v>
-      </c>
-      <c r="B276" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C276" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D276" t="str">
-        <v>黑曜石</v>
-      </c>
-      <c r="E276">
-        <v>6</v>
-      </c>
-      <c r="F276">
-        <v>69</v>
-      </c>
-      <c r="G276" t="str">
         <v>黑曜石.png</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="str">
-        <v>hys_stn_8</v>
-      </c>
-      <c r="B277" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C277" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D277" t="str">
-        <v>黑曜石</v>
-      </c>
-      <c r="E277">
-        <v>8</v>
-      </c>
-      <c r="F277">
-        <v>89</v>
-      </c>
-      <c r="G277" t="str">
-        <v>黑曜石.png</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="str">
-        <v>hys_stn_10</v>
-      </c>
-      <c r="B278" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C278" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D278" t="str">
-        <v>黑曜石</v>
-      </c>
-      <c r="E278">
-        <v>10</v>
-      </c>
-      <c r="F278">
-        <v>99</v>
-      </c>
-      <c r="G278" t="str">
-        <v>黑曜石.png</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="str">
-        <v>jys_stn_6</v>
-      </c>
-      <c r="B279" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C279" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D279" t="str">
-        <v>金曜石</v>
-      </c>
-      <c r="E279">
-        <v>6</v>
-      </c>
-      <c r="F279">
-        <v>69</v>
-      </c>
-      <c r="G279" t="str">
-        <v>金曜石.png</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="str">
-        <v>jys_stn_8</v>
-      </c>
-      <c r="B280" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C280" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D280" t="str">
-        <v>金曜石</v>
-      </c>
-      <c r="E280">
-        <v>8</v>
-      </c>
-      <c r="F280">
-        <v>89</v>
-      </c>
-      <c r="G280" t="str">
-        <v>金曜石.png</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="str">
-        <v>jys_stn_10</v>
-      </c>
-      <c r="B281" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C281" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D281" t="str">
-        <v>金曜石</v>
-      </c>
-      <c r="E281">
-        <v>10</v>
-      </c>
-      <c r="F281">
-        <v>99</v>
-      </c>
-      <c r="G281" t="str">
-        <v>金曜石.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G281"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G255"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>xhyl_cysl_6</v>
+        <v>bsj_cysl_6</v>
       </c>
       <c r="B2" t="str">
         <v>珠子</v>
@@ -433,21 +433,21 @@
         <v>水晶</v>
       </c>
       <c r="D2" t="str">
-        <v>雪花幽靈</v>
+        <v>白水晶</v>
       </c>
       <c r="E2">
         <v>6</v>
       </c>
       <c r="F2">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G2" t="str">
-        <v>雪花幽灵.png</v>
+        <v>白水晶.png</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>xhyl_cysl_8</v>
+        <v>bsj_cysl_8</v>
       </c>
       <c r="B3" t="str">
         <v>珠子</v>
@@ -456,21 +456,21 @@
         <v>水晶</v>
       </c>
       <c r="D3" t="str">
-        <v>雪花幽靈</v>
+        <v>白水晶</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G3" t="str">
-        <v>雪花幽灵.png</v>
+        <v>白水晶.png</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>xhyl_cysl_10</v>
+        <v>bsj_cysl_10</v>
       </c>
       <c r="B4" t="str">
         <v>珠子</v>
@@ -479,21 +479,21 @@
         <v>水晶</v>
       </c>
       <c r="D4" t="str">
-        <v>雪花幽靈</v>
+        <v>白水晶</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="G4" t="str">
-        <v>雪花幽灵.png</v>
+        <v>白水晶.png</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>bsj_cysl_6</v>
+        <v>byl_cysl_8</v>
       </c>
       <c r="B5" t="str">
         <v>珠子</v>
@@ -502,21 +502,21 @@
         <v>水晶</v>
       </c>
       <c r="D5" t="str">
-        <v>白水晶</v>
+        <v>白幽靈</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G5" t="str">
-        <v>白水晶.png</v>
+        <v>白幽灵.png</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>bsj_cysl_8</v>
+        <v>xhyl_cysl_6</v>
       </c>
       <c r="B6" t="str">
         <v>珠子</v>
@@ -525,21 +525,21 @@
         <v>水晶</v>
       </c>
       <c r="D6" t="str">
-        <v>白水晶</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>59</v>
       </c>
       <c r="G6" t="str">
-        <v>白水晶.png</v>
+        <v>雪花幽灵.png</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>bsj_cysl_10</v>
+        <v>xhyl_cysl_8</v>
       </c>
       <c r="B7" t="str">
         <v>珠子</v>
@@ -548,21 +548,21 @@
         <v>水晶</v>
       </c>
       <c r="D7" t="str">
-        <v>白水晶</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>89</v>
       </c>
       <c r="G7" t="str">
-        <v>白水晶.png</v>
+        <v>雪花幽灵.png</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>byl_cysl_8</v>
+        <v>xhyl_cysl_10</v>
       </c>
       <c r="B8" t="str">
         <v>珠子</v>
@@ -571,16 +571,16 @@
         <v>水晶</v>
       </c>
       <c r="D8" t="str">
-        <v>白幽靈</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="G8" t="str">
-        <v>白幽灵.png</v>
+        <v>雪花幽灵.png</v>
       </c>
     </row>
     <row r="9">
@@ -608,53 +608,53 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>lfj_cysl_8</v>
+        <v>dszzhu_prl_6</v>
       </c>
       <c r="B10" t="str">
         <v>珠子</v>
       </c>
       <c r="C10" t="str">
-        <v>水晶</v>
+        <v>珍珠</v>
       </c>
       <c r="D10" t="str">
-        <v>綠髮晶</v>
+        <v>淡水珍珠</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>99</v>
       </c>
       <c r="G10" t="str">
-        <v>绿发晶.png</v>
+        <v>淡水珍珠.png</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>lfj_cysl_10</v>
+        <v>dszzhu_prl_8</v>
       </c>
       <c r="B11" t="str">
         <v>珠子</v>
       </c>
       <c r="C11" t="str">
-        <v>水晶</v>
+        <v>珍珠</v>
       </c>
       <c r="D11" t="str">
-        <v>綠髮晶</v>
+        <v>淡水珍珠</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="G11" t="str">
-        <v>绿发晶.png</v>
+        <v>淡水珍珠.png</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>dszzhu_prl_6</v>
+        <v>dszzhu_prl_10</v>
       </c>
       <c r="B12" t="str">
         <v>珠子</v>
@@ -666,10 +666,10 @@
         <v>淡水珍珠</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="G12" t="str">
         <v>淡水珍珠.png</v>
@@ -677,329 +677,329 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>dszzhu_prl_8</v>
+        <v>pts_stn_6</v>
       </c>
       <c r="B13" t="str">
         <v>珠子</v>
       </c>
       <c r="C13" t="str">
-        <v>珍珠</v>
+        <v>礦石</v>
       </c>
       <c r="D13" t="str">
-        <v>淡水珍珠</v>
+        <v>葡萄石</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="G13" t="str">
-        <v>淡水珍珠.png</v>
+        <v>葡萄石.png</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>dszzhu_prl_10</v>
+        <v>pts_stn_10</v>
       </c>
       <c r="B14" t="str">
         <v>珠子</v>
       </c>
       <c r="C14" t="str">
-        <v>珍珠</v>
+        <v>礦石</v>
       </c>
       <c r="D14" t="str">
-        <v>淡水珍珠</v>
+        <v>葡萄石</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>199</v>
+        <v>89</v>
       </c>
       <c r="G14" t="str">
-        <v>淡水珍珠.png</v>
+        <v>葡萄石.png</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>hfj_cysl_6</v>
+        <v>lkzls_spc_6</v>
       </c>
       <c r="B15" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C15" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D15" t="str">
-        <v>黑髮晶</v>
+        <v>鏤空鑽蕾絲</v>
       </c>
       <c r="E15">
         <v>6</v>
       </c>
       <c r="F15">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G15" t="str">
-        <v>黑发晶.png</v>
+        <v>镂空钻蕾丝.png</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>hfj_cysl_8</v>
+        <v>mxxx_pnd_2</v>
       </c>
       <c r="B16" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C16" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D16" t="str">
-        <v>黑髮晶</v>
+        <v>滿鑲星星</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G16" t="str">
-        <v>黑发晶.png</v>
+        <v>满镶星星.png</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>hfj_cysl_10</v>
+        <v>pl_pnd_2</v>
       </c>
       <c r="B17" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C17" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D17" t="str">
-        <v>黑髮晶</v>
+        <v>霹靂</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="G17" t="str">
-        <v>黑发晶.png</v>
+        <v>霹雳.png</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>pts_stn_6</v>
+        <v>lkxm_pnd_2</v>
       </c>
       <c r="B18" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C18" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D18" t="str">
-        <v>葡萄石</v>
+        <v>鏤空小貓</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G18" t="str">
-        <v>葡萄石.png</v>
+        <v>镂空小猫.png</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>pts_stn_10</v>
+        <v>axqbz_pnd_2</v>
       </c>
       <c r="B19" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C19" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D19" t="str">
-        <v>葡萄石</v>
+        <v>愛心曲別針</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G19" t="str">
-        <v>葡萄石.png</v>
+        <v>爱心曲别针.png</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>lys_stn_6</v>
+        <v>gsmhz_spc_8</v>
       </c>
       <c r="B20" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C20" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D20" t="str">
-        <v>綠螢石</v>
+        <v>鋯石魔盒鑽</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G20" t="str">
-        <v>绿萤石.png</v>
+        <v>锆石魔盒钻.png</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>lys_stn_8</v>
+        <v>by_agt_6</v>
       </c>
       <c r="B21" t="str">
         <v>珠子</v>
       </c>
       <c r="C21" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D21" t="str">
-        <v>綠螢石</v>
+        <v>白玉髓</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G21" t="str">
-        <v>绿萤石.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lkzls_spc_6</v>
+        <v>by_agt_8</v>
       </c>
       <c r="B22" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C22" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D22" t="str">
-        <v>鏤空鑽蕾絲</v>
+        <v>白玉髓</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>59</v>
       </c>
       <c r="G22" t="str">
-        <v>镂空钻蕾丝.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>mxxx_pnd_2</v>
+        <v>by_agt_10</v>
       </c>
       <c r="B23" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C23" t="str">
-        <v>吊墜</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D23" t="str">
-        <v>滿鑲星星</v>
+        <v>白玉髓</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G23" t="str">
-        <v>满镶星星.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>pl_pnd_2</v>
+        <v>zlh_cysl_6</v>
       </c>
       <c r="B24" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C24" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D24" t="str">
-        <v>霹靂</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G24" t="str">
-        <v>霹雳.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lkxm_pnd_2</v>
+        <v>zlh_cysl_8</v>
       </c>
       <c r="B25" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C25" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D25" t="str">
-        <v>鏤空小貓</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="G25" t="str">
-        <v>镂空小猫.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>axqbz_pnd_2</v>
+        <v>zlh_cysl_10</v>
       </c>
       <c r="B26" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C26" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D26" t="str">
-        <v>愛心曲別針</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="G26" t="str">
-        <v>爱心曲别针.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>gsmhz_spc_8</v>
+        <v>lglf_spc_8</v>
       </c>
       <c r="B27" t="str">
         <v>配件</v>
@@ -1008,7 +1008,7 @@
         <v>隔珠</v>
       </c>
       <c r="D27" t="str">
-        <v>鋯石魔盒鑽</v>
+        <v>菱格立方</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -1017,21 +1017,21 @@
         <v>59</v>
       </c>
       <c r="G27" t="str">
-        <v>锆石魔盒钻.png</v>
+        <v>菱格立方.png</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>by_agt_6</v>
+        <v>fsj_cysl_6</v>
       </c>
       <c r="B28" t="str">
         <v>珠子</v>
       </c>
       <c r="C28" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D28" t="str">
-        <v>白玉髓</v>
+        <v>粉水晶</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -1040,21 +1040,21 @@
         <v>39</v>
       </c>
       <c r="G28" t="str">
-        <v>白玉髓.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>by_agt_8</v>
+        <v>fsj_cysl_8</v>
       </c>
       <c r="B29" t="str">
         <v>珠子</v>
       </c>
       <c r="C29" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D29" t="str">
-        <v>白玉髓</v>
+        <v>粉水晶</v>
       </c>
       <c r="E29">
         <v>8</v>
@@ -1063,104 +1063,104 @@
         <v>59</v>
       </c>
       <c r="G29" t="str">
-        <v>白玉髓.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>by_agt_10</v>
+        <v>fsj_cysl_10</v>
       </c>
       <c r="B30" t="str">
         <v>珠子</v>
       </c>
       <c r="C30" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D30" t="str">
-        <v>白玉髓</v>
+        <v>粉水晶</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G30" t="str">
-        <v>白玉髓.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lglf_spc_8</v>
+        <v>ysmxyl_pnd_2</v>
       </c>
       <c r="B31" t="str">
         <v>配件</v>
       </c>
       <c r="C31" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D31" t="str">
-        <v>菱格立方</v>
+        <v>銀色滿鑲月亮</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G31" t="str">
-        <v>菱格立方.png</v>
+        <v>银色满镶月亮.png</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>zlh_cysl_6</v>
+        <v>gsfz_spc_6</v>
       </c>
       <c r="B32" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C32" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D32" t="str">
-        <v>紫鋰輝</v>
+        <v>鋯石方鑽</v>
       </c>
       <c r="E32">
         <v>6</v>
       </c>
       <c r="F32">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G32" t="str">
-        <v>紫锂辉.png</v>
+        <v>锆石方钻.png</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>zlh_cysl_8</v>
+        <v>lkjf_pnd_2</v>
       </c>
       <c r="B33" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C33" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D33" t="str">
-        <v>紫鋰輝</v>
+        <v>鏤空金福</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G33" t="str">
-        <v>紫锂辉.png</v>
+        <v>镂空金福.png</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>zlh_cysl_10</v>
+        <v>bas_cysl_8</v>
       </c>
       <c r="B34" t="str">
         <v>珠子</v>
@@ -1169,21 +1169,21 @@
         <v>水晶</v>
       </c>
       <c r="D34" t="str">
-        <v>紫鋰輝</v>
+        <v>白阿塞</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="G34" t="str">
-        <v>紫锂辉.png</v>
+        <v>白阿塞.png</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>fsj_cysl_6</v>
+        <v>bas_cysl_10</v>
       </c>
       <c r="B35" t="str">
         <v>珠子</v>
@@ -1192,136 +1192,136 @@
         <v>水晶</v>
       </c>
       <c r="D35" t="str">
-        <v>粉水晶</v>
+        <v>白阿塞</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F35">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G35" t="str">
-        <v>粉水晶.png</v>
+        <v>白阿塞.png</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>fsj_cysl_8</v>
+        <v>zys_agt_6</v>
       </c>
       <c r="B36" t="str">
         <v>珠子</v>
       </c>
       <c r="C36" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D36" t="str">
-        <v>粉水晶</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G36" t="str">
-        <v>粉水晶.png</v>
+        <v>紫玉髓.png</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>fsj_cysl_10</v>
+        <v>zys_agt_8</v>
       </c>
       <c r="B37" t="str">
         <v>珠子</v>
       </c>
       <c r="C37" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D37" t="str">
-        <v>粉水晶</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G37" t="str">
-        <v>粉水晶.png</v>
+        <v>紫玉髓.png</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ysmxyl_pnd_2</v>
+        <v>hws_stn_6</v>
       </c>
       <c r="B38" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C38" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D38" t="str">
-        <v>銀色滿鑲月亮</v>
+        <v>海紋石</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G38" t="str">
-        <v>银色满镶月亮.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>gsfz_spc_6</v>
+        <v>hws_stn_8</v>
       </c>
       <c r="B39" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C39" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D39" t="str">
-        <v>鋯石方鑽</v>
+        <v>海紋石</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G39" t="str">
-        <v>锆石方钻.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>lkjf_pnd_2</v>
+        <v>hws_stn_10</v>
       </c>
       <c r="B40" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C40" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D40" t="str">
-        <v>鏤空金福</v>
+        <v>海紋石</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="G40" t="str">
-        <v>镂空金福.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>bas_cysl_8</v>
+        <v>jfj_cysl_6</v>
       </c>
       <c r="B41" t="str">
         <v>珠子</v>
@@ -1330,21 +1330,21 @@
         <v>水晶</v>
       </c>
       <c r="D41" t="str">
-        <v>白阿塞</v>
+        <v>金髮晶</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G41" t="str">
-        <v>白阿塞.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>bas_cysl_10</v>
+        <v>jfj_cysl_8</v>
       </c>
       <c r="B42" t="str">
         <v>珠子</v>
@@ -1353,297 +1353,297 @@
         <v>水晶</v>
       </c>
       <c r="D42" t="str">
-        <v>白阿塞</v>
+        <v>金髮晶</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G42" t="str">
-        <v>白阿塞.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>hws_stn_6</v>
+        <v>jfj_cysl_10</v>
       </c>
       <c r="B43" t="str">
         <v>珠子</v>
       </c>
       <c r="C43" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D43" t="str">
-        <v>海紋石</v>
+        <v>金髮晶</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F43">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G43" t="str">
-        <v>海纹石.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>hws_stn_8</v>
+        <v>wlyz_spc_5</v>
       </c>
       <c r="B44" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C44" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D44" t="str">
-        <v>海紋石</v>
+        <v>五稜銀鑽</v>
       </c>
       <c r="E44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G44" t="str">
-        <v>海纹石.png</v>
+        <v>五棱银钻.png</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>hws_stn_10</v>
+        <v>gsxx_pnd_2</v>
       </c>
       <c r="B45" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C45" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D45" t="str">
-        <v>海紋石</v>
+        <v>鋯石星星</v>
       </c>
       <c r="E45">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="G45" t="str">
-        <v>海纹石.png</v>
+        <v>锆石星星.png</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>zys_agt_6</v>
+        <v>xxys_pnd_2</v>
       </c>
       <c r="B46" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C46" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D46" t="str">
-        <v>紫玉髓</v>
+        <v>尋心鑰匙</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G46" t="str">
-        <v>紫玉髓.png</v>
+        <v>寻心钥匙.png</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>zys_agt_8</v>
+        <v>bsyw_pnd_2</v>
       </c>
       <c r="B47" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C47" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D47" t="str">
-        <v>紫玉髓</v>
+        <v>白水魚尾</v>
       </c>
       <c r="E47">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F47">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G47" t="str">
-        <v>紫玉髓.png</v>
+        <v>白水鱼尾.png</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>jfj_cysl_6</v>
+        <v>zyb_spc_8</v>
       </c>
       <c r="B48" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C48" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D48" t="str">
-        <v>金髮晶</v>
+        <v>轉運柄</v>
       </c>
       <c r="E48">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F48">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G48" t="str">
-        <v>金发晶.png</v>
+        <v>转运柄.png</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>jfj_cysl_8</v>
+        <v>emzy_spc_6</v>
       </c>
       <c r="B49" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C49" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D49" t="str">
-        <v>金髮晶</v>
+        <v>惡魔之眼</v>
       </c>
       <c r="E49">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F49">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G49" t="str">
-        <v>金发晶.png</v>
+        <v>恶魔之眼.png</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>jfj_cysl_10</v>
+        <v>lwmn_agt_6</v>
       </c>
       <c r="B50" t="str">
         <v>珠子</v>
       </c>
       <c r="C50" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D50" t="str">
-        <v>金髮晶</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F50">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G50" t="str">
-        <v>金发晶.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>wlyz_spc_5</v>
+        <v>lwmn_agt_8</v>
       </c>
       <c r="B51" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C51" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D51" t="str">
-        <v>五稜銀鑽</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F51">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G51" t="str">
-        <v>五棱银钻.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>gsxx_pnd_2</v>
+        <v>lwmn_agt_10</v>
       </c>
       <c r="B52" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C52" t="str">
-        <v>吊墜</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D52" t="str">
-        <v>鋯石星星</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F52">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="G52" t="str">
-        <v>锆石星星.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>xxys_pnd_2</v>
+        <v>xyc_cysl_8</v>
       </c>
       <c r="B53" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C53" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D53" t="str">
-        <v>尋心鑰匙</v>
+        <v>薰衣草</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F53">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G53" t="str">
-        <v>寻心钥匙.png</v>
+        <v>薰衣草.png</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>bsyw_pnd_2</v>
+        <v>xyc_cysl_10</v>
       </c>
       <c r="B54" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C54" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D54" t="str">
-        <v>白水魚尾</v>
+        <v>薰衣草</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F54">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="G54" t="str">
-        <v>白水鱼尾.png</v>
+        <v>薰衣草.png</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>zyb_spc_8</v>
+        <v>nwxh_spc_5</v>
       </c>
       <c r="B55" t="str">
         <v>配件</v>
@@ -1652,136 +1652,136 @@
         <v>隔珠</v>
       </c>
       <c r="D55" t="str">
-        <v>轉運柄</v>
+        <v>扭紋小環</v>
       </c>
       <c r="E55">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F55">
         <v>59</v>
       </c>
       <c r="G55" t="str">
-        <v>转运柄.png</v>
+        <v>扭纹小环.png</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>emzy_spc_6</v>
+        <v>xxjz_pnd_2</v>
       </c>
       <c r="B56" t="str">
         <v>配件</v>
       </c>
       <c r="C56" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D56" t="str">
-        <v>惡魔之眼</v>
+        <v>星星獎章</v>
       </c>
       <c r="E56">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G56" t="str">
-        <v>恶魔之眼.png</v>
+        <v>星星奖章.png</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lwmn_agt_6</v>
+        <v>fyh_spc_6</v>
       </c>
       <c r="B57" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C57" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D57" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>粉櫻花</v>
       </c>
       <c r="E57">
         <v>6</v>
       </c>
       <c r="F57">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G57" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>粉樱花.png</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lwmn_agt_8</v>
+        <v>gshxz_spc_6</v>
       </c>
       <c r="B58" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C58" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D58" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>鋯石花形鑽</v>
       </c>
       <c r="E58">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F58">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G58" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>锆石花形钻.png</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lwmn_agt_10</v>
+        <v>gsqg_spc_5</v>
       </c>
       <c r="B59" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C59" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D59" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>鋯石切割</v>
       </c>
       <c r="E59">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F59">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="G59" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>锆石切割.png</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>nwxh_spc_5</v>
+        <v>hsj_cysl_6</v>
       </c>
       <c r="B60" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C60" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D60" t="str">
-        <v>扭紋小環</v>
+        <v>黃水晶</v>
       </c>
       <c r="E60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F60">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G60" t="str">
-        <v>扭纹小环.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>xyc_cysl_8</v>
+        <v>hsj_cysl_8</v>
       </c>
       <c r="B61" t="str">
         <v>珠子</v>
@@ -1790,7 +1790,7 @@
         <v>水晶</v>
       </c>
       <c r="D61" t="str">
-        <v>薰衣草</v>
+        <v>黃水晶</v>
       </c>
       <c r="E61">
         <v>8</v>
@@ -1799,12 +1799,12 @@
         <v>69</v>
       </c>
       <c r="G61" t="str">
-        <v>薰衣草.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>xyc_cysl_10</v>
+        <v>hsj_cysl_10</v>
       </c>
       <c r="B62" t="str">
         <v>珠子</v>
@@ -1813,573 +1813,573 @@
         <v>水晶</v>
       </c>
       <c r="D62" t="str">
-        <v>薰衣草</v>
+        <v>黃水晶</v>
       </c>
       <c r="E62">
         <v>10</v>
       </c>
       <c r="F62">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="G62" t="str">
-        <v>薰衣草.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>xxjz_pnd_2</v>
+        <v>jzj_spc_6</v>
       </c>
       <c r="B63" t="str">
         <v>配件</v>
       </c>
       <c r="C63" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D63" t="str">
-        <v>星星獎章</v>
+        <v>交織戒</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F63">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G63" t="str">
-        <v>星星奖章.png</v>
+        <v>交织戒.png</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>fyh_spc_6</v>
+        <v>gscx_pnd_2</v>
       </c>
       <c r="B64" t="str">
         <v>配件</v>
       </c>
       <c r="C64" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D64" t="str">
-        <v>粉櫻花</v>
+        <v>鋯石晨星</v>
       </c>
       <c r="E64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G64" t="str">
-        <v>粉樱花.png</v>
+        <v>锆石晨星.png</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>gshxz_spc_6</v>
+        <v>tg4_sz_7</v>
       </c>
       <c r="B65" t="str">
         <v>配件</v>
       </c>
       <c r="C65" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D65" t="str">
-        <v>鋯石花形鑽</v>
+        <v>鈦鋼4</v>
       </c>
       <c r="E65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G65" t="str">
-        <v>锆石花形钻.png</v>
+        <v>钛钢4.png</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>yys_stn_6</v>
+        <v>cyszj_spc_8</v>
       </c>
       <c r="B66" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C66" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D66" t="str">
-        <v>銀曜石</v>
+        <v>藏銀十字架</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F66">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G66" t="str">
-        <v>银曜石.png</v>
+        <v>藏银十字架.png</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>yys_stn_8</v>
+        <v>gsqgsc_spc_6</v>
       </c>
       <c r="B67" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C67" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D67" t="str">
-        <v>銀曜石</v>
+        <v>鋯石切割雙層</v>
       </c>
       <c r="E67">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F67">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G67" t="str">
-        <v>银曜石.png</v>
+        <v>锆石切割双层.png</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>yys_stn_10</v>
+        <v>ysxh_spc_5</v>
       </c>
       <c r="B68" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C68" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D68" t="str">
-        <v>銀曜石</v>
+        <v>銀色小環</v>
       </c>
       <c r="E68">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F68">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G68" t="str">
-        <v>银曜石.png</v>
+        <v>银色小环.png</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>hsj_cysl_6</v>
+        <v>tg9_sz_7</v>
       </c>
       <c r="B69" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C69" t="str">
-        <v>水晶</v>
+        <v>數字</v>
       </c>
       <c r="D69" t="str">
-        <v>黃水晶</v>
+        <v>鈦鋼9</v>
       </c>
       <c r="E69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F69">
         <v>39</v>
       </c>
       <c r="G69" t="str">
-        <v>黄水晶.png</v>
+        <v>钛钢9.png</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>hsj_cysl_8</v>
+        <v>hm_agt_6</v>
       </c>
       <c r="B70" t="str">
         <v>珠子</v>
       </c>
       <c r="C70" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D70" t="str">
-        <v>黃水晶</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F70">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G70" t="str">
-        <v>黄水晶.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>hsj_cysl_10</v>
+        <v>hm_agt_8</v>
       </c>
       <c r="B71" t="str">
         <v>珠子</v>
       </c>
       <c r="C71" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D71" t="str">
-        <v>黃水晶</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E71">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F71">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G71" t="str">
-        <v>黄水晶.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>gsqg_spc_5</v>
+        <v>hm_agt_10</v>
       </c>
       <c r="B72" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C72" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D72" t="str">
-        <v>鋯石切割</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E72">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F72">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G72" t="str">
-        <v>锆石切割.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>jzj_spc_6</v>
+        <v>ml_stn_6</v>
       </c>
       <c r="B73" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C73" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D73" t="str">
-        <v>交織戒</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E73">
         <v>6</v>
       </c>
       <c r="F73">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G73" t="str">
-        <v>交织戒.png</v>
+        <v>蜜蜡.png</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>gscx_pnd_2</v>
+        <v>ml_stn_8</v>
       </c>
       <c r="B74" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C74" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D74" t="str">
-        <v>鋯石晨星</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F74">
         <v>99</v>
       </c>
       <c r="G74" t="str">
-        <v>锆石晨星.png</v>
+        <v>蜜蜡.png</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>cyszj_spc_8</v>
+        <v>ysr_zm_4</v>
       </c>
       <c r="B75" t="str">
         <v>配件</v>
       </c>
       <c r="C75" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D75" t="str">
-        <v>藏銀十字架</v>
+        <v>銀飾R</v>
       </c>
       <c r="E75">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F75">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G75" t="str">
-        <v>藏银十字架.png</v>
+        <v>银饰R.png</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>gsqgsc_spc_6</v>
+        <v>mzhd_pnd_2</v>
       </c>
       <c r="B76" t="str">
         <v>配件</v>
       </c>
       <c r="C76" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D76" t="str">
-        <v>鋯石切割雙層</v>
+        <v>滿鑽蝴蝶</v>
       </c>
       <c r="E76">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G76" t="str">
-        <v>锆石切割双层.png</v>
+        <v>满钻蝴蝶.png</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>ysxh_spc_5</v>
+        <v>jd_pnd_2</v>
       </c>
       <c r="B77" t="str">
         <v>配件</v>
       </c>
       <c r="C77" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D77" t="str">
-        <v>銀色小環</v>
+        <v>晶蝶</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G77" t="str">
-        <v>银色小环.png</v>
+        <v>晶蝶.png</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>hm_agt_6</v>
+        <v>lkjls_spc_6</v>
       </c>
       <c r="B78" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C78" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D78" t="str">
-        <v>黃瑪瑙</v>
+        <v>鏤空金蕾絲</v>
       </c>
       <c r="E78">
         <v>6</v>
       </c>
       <c r="F78">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G78" t="str">
-        <v>黄玛瑙.png</v>
+        <v>镂空金蕾丝.png</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>hm_agt_8</v>
+        <v>tg7_sz_7</v>
       </c>
       <c r="B79" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C79" t="str">
-        <v>瑪瑙</v>
+        <v>數字</v>
       </c>
       <c r="D79" t="str">
-        <v>黃瑪瑙</v>
+        <v>鈦鋼7</v>
       </c>
       <c r="E79">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F79">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G79" t="str">
-        <v>黄玛瑙.png</v>
+        <v>钛钢7.png</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>hm_agt_10</v>
+        <v>gymj_xz_2</v>
       </c>
       <c r="B80" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C80" t="str">
-        <v>瑪瑙</v>
+        <v>星座</v>
       </c>
       <c r="D80" t="str">
-        <v>黃瑪瑙</v>
+        <v>古銀摩羯</v>
       </c>
       <c r="E80">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G80" t="str">
-        <v>黄玛瑙.png</v>
+        <v>古银摩羯.png</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ml_stn_6</v>
+        <v>tg0_sz_7</v>
       </c>
       <c r="B81" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C81" t="str">
-        <v>礦石</v>
+        <v>數字</v>
       </c>
       <c r="D81" t="str">
-        <v>蜜蠟</v>
+        <v>鈦鋼0</v>
       </c>
       <c r="E81">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F81">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G81" t="str">
-        <v>蜜蜡.png</v>
+        <v>钛钢0.png</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ml_stn_8</v>
+        <v>jf_pnd_2</v>
       </c>
       <c r="B82" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C82" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D82" t="str">
-        <v>蜜蠟</v>
+        <v>金福</v>
       </c>
       <c r="E82">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F82">
         <v>99</v>
       </c>
       <c r="G82" t="str">
-        <v>蜜蜡.png</v>
+        <v>金福.png</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>mzhd_pnd_2</v>
+        <v>fgdh_spc_8</v>
       </c>
       <c r="B83" t="str">
         <v>配件</v>
       </c>
       <c r="C83" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D83" t="str">
-        <v>滿鑽蝴蝶</v>
+        <v>復古雕花</v>
       </c>
       <c r="E83">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F83">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G83" t="str">
-        <v>满钻蝴蝶.png</v>
+        <v>复古雕花.png</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>jd_pnd_2</v>
+        <v>ysj_zm_4</v>
       </c>
       <c r="B84" t="str">
         <v>配件</v>
       </c>
       <c r="C84" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D84" t="str">
-        <v>晶蝶</v>
+        <v>銀飾J</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F84">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G84" t="str">
-        <v>晶蝶.png</v>
+        <v>银饰J.png</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>lkjls_spc_6</v>
+        <v>tg6_sz_7</v>
       </c>
       <c r="B85" t="str">
         <v>配件</v>
       </c>
       <c r="C85" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D85" t="str">
-        <v>鏤空金蕾絲</v>
+        <v>鈦鋼6</v>
       </c>
       <c r="E85">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F85">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G85" t="str">
-        <v>镂空金蕾丝.png</v>
+        <v>钛钢6.png</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>jf_pnd_2</v>
+        <v>xxy_spc_5</v>
       </c>
       <c r="B86" t="str">
         <v>配件</v>
       </c>
       <c r="C86" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D86" t="str">
-        <v>金福</v>
+        <v>小祥雲</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F86">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G86" t="str">
-        <v>金福.png</v>
+        <v>小祥云.png</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>fgdh_spc_8</v>
+        <v>dxy_spc_5</v>
       </c>
       <c r="B87" t="str">
         <v>配件</v>
@@ -2388,274 +2388,274 @@
         <v>隔珠</v>
       </c>
       <c r="D87" t="str">
-        <v>復古雕花</v>
+        <v>大祥雲</v>
       </c>
       <c r="E87">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F87">
         <v>59</v>
       </c>
       <c r="G87" t="str">
-        <v>复古雕花.png</v>
+        <v>大祥云.png</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>xxy_spc_5</v>
+        <v>lfj_cysl_8</v>
       </c>
       <c r="B88" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C88" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D88" t="str">
-        <v>小祥雲</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E88">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F88">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G88" t="str">
-        <v>小祥云.png</v>
+        <v>绿发晶.png</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>dxy_spc_5</v>
+        <v>lfj_cysl_10</v>
       </c>
       <c r="B89" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C89" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D89" t="str">
-        <v>大祥雲</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E89">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F89">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="G89" t="str">
-        <v>大祥云.png</v>
+        <v>绿发晶.png</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>gsmm_spc_8</v>
+        <v>ysi_zm_4</v>
       </c>
       <c r="B90" t="str">
         <v>配件</v>
       </c>
       <c r="C90" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D90" t="str">
-        <v>鋯石貓咪</v>
+        <v>銀飾I</v>
       </c>
       <c r="E90">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F90">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G90" t="str">
-        <v>锆石猫咪.png</v>
+        <v>银饰I.png</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>wljz_spc_5</v>
+        <v>ysu_zm_4</v>
       </c>
       <c r="B91" t="str">
         <v>配件</v>
       </c>
       <c r="C91" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D91" t="str">
-        <v>五稜金鑽</v>
+        <v>銀飾U</v>
       </c>
       <c r="E91">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F91">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G91" t="str">
-        <v>五棱金钻.png</v>
+        <v>银饰U.png</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>zyd_pnd_2</v>
+        <v>tg1_sz_7</v>
       </c>
       <c r="B92" t="str">
         <v>配件</v>
       </c>
       <c r="C92" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D92" t="str">
-        <v>珠遇蝶</v>
+        <v>鈦鋼1</v>
       </c>
       <c r="E92">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F92">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G92" t="str">
-        <v>珠遇蝶.png</v>
+        <v>钛钢1.png</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>xfp_pnd_2</v>
+        <v>tg3_sz_7</v>
       </c>
       <c r="B93" t="str">
         <v>配件</v>
       </c>
       <c r="C93" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D93" t="str">
-        <v>小福牌</v>
+        <v>鈦鋼3</v>
       </c>
       <c r="E93">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F93">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G93" t="str">
-        <v>小福牌.png</v>
+        <v>钛钢3.png</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>hlcs_pnd_2</v>
+        <v>tg2_sz_7</v>
       </c>
       <c r="B94" t="str">
         <v>配件</v>
       </c>
       <c r="C94" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D94" t="str">
-        <v>葫蘆成雙</v>
+        <v>鈦鋼2</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F94">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G94" t="str">
-        <v>葫芦成双.png</v>
+        <v>钛钢2.png</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>gslx_spc_6</v>
+        <v>tg8_sz_7</v>
       </c>
       <c r="B95" t="str">
         <v>配件</v>
       </c>
       <c r="C95" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D95" t="str">
-        <v>鋯石螺旋</v>
+        <v>鈦鋼8</v>
       </c>
       <c r="E95">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F95">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G95" t="str">
-        <v>锆石螺旋.png</v>
+        <v>钛钢8.png</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>syyl_pnd_2</v>
+        <v>tg5_sz_7</v>
       </c>
       <c r="B96" t="str">
         <v>配件</v>
       </c>
       <c r="C96" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D96" t="str">
-        <v>閃躍月亮</v>
+        <v>鈦鋼5</v>
       </c>
       <c r="E96">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F96">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G96" t="str">
-        <v>闪跃月亮.png</v>
+        <v>钛钢5.png</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>gszs_spc_5</v>
+        <v>gycn_xz_2</v>
       </c>
       <c r="B97" t="str">
         <v>配件</v>
       </c>
       <c r="C97" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D97" t="str">
-        <v>鋯石鑽閃</v>
+        <v>古銀處女</v>
       </c>
       <c r="E97">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F97">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G97" t="str">
-        <v>锆石钻闪.png</v>
+        <v>古银处女.png</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>xns_pnd_2</v>
+        <v>ysp_zm_4</v>
       </c>
       <c r="B98" t="str">
         <v>配件</v>
       </c>
       <c r="C98" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D98" t="str">
-        <v>小年獸</v>
+        <v>銀飾P</v>
       </c>
       <c r="E98">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F98">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G98" t="str">
-        <v>小年兽.png</v>
+        <v>银饰P.png</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>jsxh_spc_5</v>
+        <v>gsmm_spc_8</v>
       </c>
       <c r="B99" t="str">
         <v>配件</v>
@@ -2664,527 +2664,527 @@
         <v>隔珠</v>
       </c>
       <c r="D99" t="str">
-        <v>金色小環</v>
+        <v>鋯石貓咪</v>
       </c>
       <c r="E99">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F99">
         <v>59</v>
       </c>
       <c r="G99" t="str">
-        <v>金色小环.png</v>
+        <v>锆石猫咪.png</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>hps_stn_6</v>
+        <v>gyby_xz_2</v>
       </c>
       <c r="B100" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C100" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D100" t="str">
-        <v>琥珀石</v>
+        <v>古銀白羊</v>
       </c>
       <c r="E100">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F100">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G100" t="str">
-        <v>琥珀石.png</v>
+        <v>古银白羊.png</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>hps_stn_8</v>
+        <v>ysc_zm_4</v>
       </c>
       <c r="B101" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C101" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D101" t="str">
-        <v>琥珀石</v>
+        <v>銀飾C</v>
       </c>
       <c r="E101">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101">
-        <v>89</v>
+        <v>399</v>
       </c>
       <c r="G101" t="str">
-        <v>琥珀石.png</v>
+        <v>银饰C.png</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>hps_stn_10</v>
+        <v>ysb_zm_4</v>
       </c>
       <c r="B102" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C102" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D102" t="str">
-        <v>琥珀石</v>
+        <v>銀飾B</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F102">
-        <v>199</v>
+        <v>399</v>
       </c>
       <c r="G102" t="str">
-        <v>琥珀石.png</v>
+        <v>银饰B.png</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>bjx_pnd_2</v>
+        <v>gysp_xz_2</v>
       </c>
       <c r="B103" t="str">
         <v>配件</v>
       </c>
       <c r="C103" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D103" t="str">
-        <v>北極星</v>
+        <v>古銀水瓶</v>
       </c>
       <c r="E103">
         <v>2</v>
       </c>
       <c r="F103">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G103" t="str">
-        <v>北极星.png</v>
+        <v>古银水瓶.png</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>cgl_spc_6</v>
+        <v>yso_zm_4</v>
       </c>
       <c r="B104" t="str">
         <v>配件</v>
       </c>
       <c r="C104" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D104" t="str">
-        <v>彩鋯輪</v>
+        <v>銀飾O</v>
       </c>
       <c r="E104">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F104">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G104" t="str">
-        <v>彩锆轮.png</v>
+        <v>银饰O.png</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>hlb_stn_6</v>
+        <v>ysw_zm_4</v>
       </c>
       <c r="B105" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C105" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D105" t="str">
-        <v>海藍寶</v>
+        <v>銀飾W</v>
       </c>
       <c r="E105">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F105">
-        <v>89</v>
+        <v>399</v>
       </c>
       <c r="G105" t="str">
-        <v>海蓝宝.png</v>
+        <v>银饰W.png</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>hlb_stn_8</v>
+        <v>wljz_spc_5</v>
       </c>
       <c r="B106" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C106" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D106" t="str">
-        <v>海藍寶</v>
+        <v>五稜金鑽</v>
       </c>
       <c r="E106">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F106">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G106" t="str">
-        <v>海蓝宝.png</v>
+        <v>五棱金钻.png</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>hlb_stn_10</v>
+        <v>zyd_pnd_2</v>
       </c>
       <c r="B107" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C107" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D107" t="str">
-        <v>海藍寶</v>
+        <v>珠遇蝶</v>
       </c>
       <c r="E107">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F107">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="G107" t="str">
-        <v>海蓝宝.png</v>
+        <v>珠遇蝶.png</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>xs_spc_8</v>
+        <v>xfp_pnd_2</v>
       </c>
       <c r="B108" t="str">
         <v>配件</v>
       </c>
       <c r="C108" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D108" t="str">
-        <v>醒獅</v>
+        <v>小福牌</v>
       </c>
       <c r="E108">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F108">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G108" t="str">
-        <v>醒狮.png</v>
+        <v>小福牌.png</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ths_stn_6</v>
+        <v>ysq_zm_4</v>
       </c>
       <c r="B109" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C109" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D109" t="str">
-        <v>天河石</v>
+        <v>銀飾Q</v>
       </c>
       <c r="E109">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F109">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G109" t="str">
-        <v>天河石.png</v>
+        <v>银饰Q.png</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ths_stn_8</v>
+        <v>gyjx_xz_2</v>
       </c>
       <c r="B110" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C110" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D110" t="str">
-        <v>天河石</v>
+        <v>古銀巨蟹</v>
       </c>
       <c r="E110">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F110">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G110" t="str">
-        <v>天河石.png</v>
+        <v>古银巨蟹.png</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ths_stn_10</v>
+        <v>ysf_zm_4</v>
       </c>
       <c r="B111" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C111" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D111" t="str">
-        <v>天河石</v>
+        <v>銀飾F</v>
       </c>
       <c r="E111">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F111">
-        <v>139</v>
+        <v>399</v>
       </c>
       <c r="G111" t="str">
-        <v>天河石.png</v>
+        <v>银饰F.png</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>gsch_pnd_2</v>
+        <v>gyss_xz_2</v>
       </c>
       <c r="B112" t="str">
         <v>配件</v>
       </c>
       <c r="C112" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D112" t="str">
-        <v>鋯石彩虹</v>
+        <v>古銀射手</v>
       </c>
       <c r="E112">
         <v>2</v>
       </c>
       <c r="F112">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G112" t="str">
-        <v>锆石彩虹.png</v>
+        <v>古银射手.png</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>xgszs_spc_5</v>
+        <v>hlcs_pnd_2</v>
       </c>
       <c r="B113" t="str">
         <v>配件</v>
       </c>
       <c r="C113" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D113" t="str">
-        <v>小鋯石鑽閃</v>
+        <v>葫蘆成雙</v>
       </c>
       <c r="E113">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F113">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G113" t="str">
-        <v>小锆石钻闪.png</v>
+        <v>葫芦成双.png</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>wyh_pnd_2</v>
+        <v>gyszz_xz_2</v>
       </c>
       <c r="B114" t="str">
         <v>配件</v>
       </c>
       <c r="C114" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D114" t="str">
-        <v>午夜花</v>
+        <v>古銀雙子</v>
       </c>
       <c r="E114">
         <v>2</v>
       </c>
       <c r="F114">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G114" t="str">
-        <v>午夜花.png</v>
+        <v>古银双子.png</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ysxz_spc_6</v>
+        <v>ysn_zm_4</v>
       </c>
       <c r="B115" t="str">
         <v>配件</v>
       </c>
       <c r="C115" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D115" t="str">
-        <v>銀色小珠</v>
+        <v>銀飾N</v>
       </c>
       <c r="E115">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F115">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G115" t="str">
-        <v>银色小珠.png</v>
+        <v>银饰N.png</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>jsmxyl_pnd_2</v>
+        <v>ysm_zm_4</v>
       </c>
       <c r="B116" t="str">
         <v>配件</v>
       </c>
       <c r="C116" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D116" t="str">
-        <v>金色滿鑲月亮</v>
+        <v>銀飾M</v>
       </c>
       <c r="E116">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F116">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G116" t="str">
-        <v>金色满镶月亮.png</v>
+        <v>银饰M.png</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>lcmj_cysl_6</v>
+        <v>ysh_zm_4</v>
       </c>
       <c r="B117" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C117" t="str">
-        <v>水晶</v>
+        <v>字母</v>
       </c>
       <c r="D117" t="str">
-        <v>綠莓晶</v>
+        <v>銀飾H</v>
       </c>
       <c r="E117">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F117">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G117" t="str">
-        <v>绿莓晶.png</v>
+        <v>银饰H.png</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>lcmj_cysl_8</v>
+        <v>gytx_xz_2</v>
       </c>
       <c r="B118" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C118" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D118" t="str">
-        <v>綠莓晶</v>
+        <v>古銀天蠍</v>
       </c>
       <c r="E118">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F118">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G118" t="str">
-        <v>绿莓晶.png</v>
+        <v>古银天蝎.png</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>lcmj_cysl_10</v>
+        <v>ysg_zm_4</v>
       </c>
       <c r="B119" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C119" t="str">
-        <v>水晶</v>
+        <v>字母</v>
       </c>
       <c r="D119" t="str">
-        <v>綠莓晶</v>
+        <v>銀飾G</v>
       </c>
       <c r="E119">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F119">
-        <v>89</v>
+        <v>399</v>
       </c>
       <c r="G119" t="str">
-        <v>绿莓晶.png</v>
+        <v>银饰G.png</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>hbgd_spc_6</v>
+        <v>gytc_xz_2</v>
       </c>
       <c r="B120" t="str">
         <v>配件</v>
       </c>
       <c r="C120" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D120" t="str">
-        <v>花邊軌道</v>
+        <v>古銀天秤</v>
       </c>
       <c r="E120">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F120">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G120" t="str">
-        <v>花边轨道.png</v>
+        <v>古银天秤.png</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>hcw_spc_5</v>
+        <v>yst_zm_4</v>
       </c>
       <c r="B121" t="str">
         <v>配件</v>
       </c>
       <c r="C121" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D121" t="str">
-        <v>回財紋</v>
+        <v>銀飾T</v>
       </c>
       <c r="E121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F121">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G121" t="str">
-        <v>回财纹.png</v>
+        <v>银饰T.png</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>cyjc_spc_6</v>
+        <v>gslx_spc_6</v>
       </c>
       <c r="B122" t="str">
         <v>配件</v>
@@ -3193,7 +3193,7 @@
         <v>隔珠</v>
       </c>
       <c r="D122" t="str">
-        <v>藏銀卷草</v>
+        <v>鋯石螺旋</v>
       </c>
       <c r="E122">
         <v>6</v>
@@ -3202,58 +3202,58 @@
         <v>59</v>
       </c>
       <c r="G122" t="str">
-        <v>藏银卷草.png</v>
+        <v>锆石螺旋.png</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>hx_spc_6</v>
+        <v>yse_zm_4</v>
       </c>
       <c r="B123" t="str">
         <v>配件</v>
       </c>
       <c r="C123" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D123" t="str">
-        <v>花旋</v>
+        <v>銀飾E</v>
       </c>
       <c r="E123">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F123">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G123" t="str">
-        <v>花旋.png</v>
+        <v>银饰E.png</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>cyszh_spc_8</v>
+        <v>ysk_zm_4</v>
       </c>
       <c r="B124" t="str">
         <v>配件</v>
       </c>
       <c r="C124" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D124" t="str">
-        <v>藏銀十字花</v>
+        <v>銀飾K</v>
       </c>
       <c r="E124">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G124" t="str">
-        <v>藏银十字花.png</v>
+        <v>银饰K.png</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>cyym_pnd_2</v>
+        <v>syyl_pnd_2</v>
       </c>
       <c r="B125" t="str">
         <v>配件</v>
@@ -3262,7 +3262,7 @@
         <v>吊墜</v>
       </c>
       <c r="D125" t="str">
-        <v>藏銀羽毛</v>
+        <v>閃躍月亮</v>
       </c>
       <c r="E125">
         <v>2</v>
@@ -3271,242 +3271,242 @@
         <v>99</v>
       </c>
       <c r="G125" t="str">
-        <v>藏银羽毛.png</v>
+        <v>闪跃月亮.png</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>cysy_spc_6</v>
+        <v>ysv_zm_4</v>
       </c>
       <c r="B126" t="str">
         <v>配件</v>
       </c>
       <c r="C126" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D126" t="str">
-        <v>藏銀樹葉</v>
+        <v>銀飾V</v>
       </c>
       <c r="E126">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F126">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G126" t="str">
-        <v>藏银树叶.png</v>
+        <v>银饰V.png</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>qws_stn_8</v>
+        <v>gszs_spc_5</v>
       </c>
       <c r="B127" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C127" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D127" t="str">
-        <v>薔薇石</v>
+        <v>鋯石鑽閃</v>
       </c>
       <c r="E127">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F127">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G127" t="str">
-        <v>蔷薇石.png</v>
+        <v>锆石钻闪.png</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>qws_stn_10</v>
+        <v>ysl_zm_4</v>
       </c>
       <c r="B128" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C128" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D128" t="str">
-        <v>薔薇石</v>
+        <v>銀飾L</v>
       </c>
       <c r="E128">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F128">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G128" t="str">
-        <v>蔷薇石.png</v>
+        <v>银饰L.png</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>jsxz_spc_6</v>
+        <v>xns_pnd_2</v>
       </c>
       <c r="B129" t="str">
         <v>配件</v>
       </c>
       <c r="C129" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D129" t="str">
-        <v>金色小珠</v>
+        <v>小年獸</v>
       </c>
       <c r="E129">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F129">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G129" t="str">
-        <v>金色小珠.png</v>
+        <v>小年兽.png</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>gszssc_spc_6</v>
+        <v>ysa_zm_4</v>
       </c>
       <c r="B130" t="str">
         <v>配件</v>
       </c>
       <c r="C130" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D130" t="str">
-        <v>鋯石鑽閃雙層</v>
+        <v>銀飾A</v>
       </c>
       <c r="E130">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F130">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G130" t="str">
-        <v>锆石钻闪双层.png</v>
+        <v>银饰A.png</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>cywp_spc_8</v>
+        <v>gyjn_xz_2</v>
       </c>
       <c r="B131" t="str">
         <v>配件</v>
       </c>
       <c r="C131" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D131" t="str">
-        <v>藏銀瓦片</v>
+        <v>古銀金牛</v>
       </c>
       <c r="E131">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F131">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G131" t="str">
-        <v>藏银瓦片.png</v>
+        <v>古银金牛.png</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>syc_pnd_2</v>
+        <v>ysy_zm_4</v>
       </c>
       <c r="B132" t="str">
         <v>配件</v>
       </c>
       <c r="C132" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D132" t="str">
-        <v>四葉草</v>
+        <v>銀飾Y</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F132">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G132" t="str">
-        <v>四叶草.png</v>
+        <v>银饰Y.png</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>tys_stn_6</v>
+        <v>jsxh_spc_5</v>
       </c>
       <c r="B133" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C133" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D133" t="str">
-        <v>太陽石</v>
+        <v>金色小環</v>
       </c>
       <c r="E133">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F133">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G133" t="str">
-        <v>太阳石.png</v>
+        <v>金色小环.png</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>tys_stn_8</v>
+        <v>gyshz_xz_2</v>
       </c>
       <c r="B134" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C134" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D134" t="str">
-        <v>太陽石</v>
+        <v>古銀獅子</v>
       </c>
       <c r="E134">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F134">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G134" t="str">
-        <v>太阳石.png</v>
+        <v>古银狮子.png</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>tys_stn_10</v>
+        <v>bjx_pnd_2</v>
       </c>
       <c r="B135" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C135" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D135" t="str">
-        <v>太陽石</v>
+        <v>北極星</v>
       </c>
       <c r="E135">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F135">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="G135" t="str">
-        <v>太阳石.png</v>
+        <v>北极星.png</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>yslzzy_spc_8</v>
+        <v>cgl_spc_6</v>
       </c>
       <c r="B136" t="str">
         <v>配件</v>
@@ -3515,76 +3515,76 @@
         <v>隔珠</v>
       </c>
       <c r="D136" t="str">
-        <v>銀色六字真言</v>
+        <v>彩鋯輪</v>
       </c>
       <c r="E136">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F136">
         <v>59</v>
       </c>
       <c r="G136" t="str">
-        <v>银色六字真言.png</v>
+        <v>彩锆轮.png</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>ketj_spc_6</v>
+        <v>ysx_zm_4</v>
       </c>
       <c r="B137" t="str">
         <v>配件</v>
       </c>
       <c r="C137" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D137" t="str">
-        <v>凱爾特結</v>
+        <v>銀飾X</v>
       </c>
       <c r="E137">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F137">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G137" t="str">
-        <v>凯尔特结.png</v>
+        <v>银饰X.png</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>zsj_cysl_6</v>
+        <v>hps_stn_6</v>
       </c>
       <c r="B138" t="str">
         <v>珠子</v>
       </c>
       <c r="C138" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D138" t="str">
-        <v>紫水晶</v>
+        <v>琥珀石</v>
       </c>
       <c r="E138">
         <v>6</v>
       </c>
       <c r="F138">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G138" t="str">
-        <v>紫水晶.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>zsj_cysl_8</v>
+        <v>hps_stn_8</v>
       </c>
       <c r="B139" t="str">
         <v>珠子</v>
       </c>
       <c r="C139" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D139" t="str">
-        <v>紫水晶</v>
+        <v>琥珀石</v>
       </c>
       <c r="E139">
         <v>8</v>
@@ -3593,288 +3593,288 @@
         <v>89</v>
       </c>
       <c r="G139" t="str">
-        <v>紫水晶.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>zsj_cysl_10</v>
+        <v>hps_stn_10</v>
       </c>
       <c r="B140" t="str">
         <v>珠子</v>
       </c>
       <c r="C140" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D140" t="str">
-        <v>紫水晶</v>
+        <v>琥珀石</v>
       </c>
       <c r="E140">
         <v>10</v>
       </c>
       <c r="F140">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="G140" t="str">
-        <v>紫水晶.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ysxq_spc_8</v>
+        <v>gysy_xz_2</v>
       </c>
       <c r="B141" t="str">
         <v>配件</v>
       </c>
       <c r="C141" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D141" t="str">
-        <v>銀色繡球</v>
+        <v>古銀雙魚</v>
       </c>
       <c r="E141">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F141">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G141" t="str">
-        <v>银色绣球.png</v>
+        <v>古银双鱼.png</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>wgzl_pnd_2</v>
+        <v>xs_spc_8</v>
       </c>
       <c r="B142" t="str">
         <v>配件</v>
       </c>
       <c r="C142" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D142" t="str">
-        <v>王國之淚</v>
+        <v>醒獅</v>
       </c>
       <c r="E142">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F142">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G142" t="str">
-        <v>王国之泪.png</v>
+        <v>醒狮.png</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>jslzzy_spc_8</v>
+        <v>ysz_zm_4</v>
       </c>
       <c r="B143" t="str">
         <v>配件</v>
       </c>
       <c r="C143" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D143" t="str">
-        <v>金色六字真言</v>
+        <v>銀飾Z</v>
       </c>
       <c r="E143">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F143">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G143" t="str">
-        <v>金色六字真言.png</v>
+        <v>银饰Z.png</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>cmj_cysl_6</v>
+        <v>ths_stn_6</v>
       </c>
       <c r="B144" t="str">
         <v>珠子</v>
       </c>
       <c r="C144" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D144" t="str">
-        <v>草莓晶</v>
+        <v>天河石</v>
       </c>
       <c r="E144">
         <v>6</v>
       </c>
       <c r="F144">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G144" t="str">
-        <v>草莓晶.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>cmj_cysl_8</v>
+        <v>ths_stn_8</v>
       </c>
       <c r="B145" t="str">
         <v>珠子</v>
       </c>
       <c r="C145" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D145" t="str">
-        <v>草莓晶</v>
+        <v>天河石</v>
       </c>
       <c r="E145">
         <v>8</v>
       </c>
       <c r="F145">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G145" t="str">
-        <v>草莓晶.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>cmj_cysl_10</v>
+        <v>ths_stn_10</v>
       </c>
       <c r="B146" t="str">
         <v>珠子</v>
       </c>
       <c r="C146" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D146" t="str">
-        <v>草莓晶</v>
+        <v>天河石</v>
       </c>
       <c r="E146">
         <v>10</v>
       </c>
       <c r="F146">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="G146" t="str">
-        <v>草莓晶.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>cyhdls_pnd_2</v>
+        <v>ysd_zm_4</v>
       </c>
       <c r="B147" t="str">
         <v>配件</v>
       </c>
       <c r="C147" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D147" t="str">
-        <v>藏銀蝴蝶流蘇</v>
+        <v>銀飾D</v>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F147">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G147" t="str">
-        <v>藏银蝴蝶流苏.png</v>
+        <v>银饰D.png</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>mghh_spc_6</v>
+        <v>hlb_stn_6</v>
       </c>
       <c r="B148" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C148" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D148" t="str">
-        <v>玫瑰花環</v>
+        <v>海藍寶</v>
       </c>
       <c r="E148">
         <v>6</v>
       </c>
       <c r="F148">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G148" t="str">
-        <v>玫瑰花环.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bmnmh_spc_8</v>
+        <v>hlb_stn_8</v>
       </c>
       <c r="B149" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C149" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D149" t="str">
-        <v>白瑪瑙魔盒</v>
+        <v>海藍寶</v>
       </c>
       <c r="E149">
         <v>8</v>
       </c>
       <c r="F149">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G149" t="str">
-        <v>白玛瑙魔盒.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>cyhw_spc_5</v>
+        <v>hlb_stn_10</v>
       </c>
       <c r="B150" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C150" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D150" t="str">
-        <v>藏銀回紋</v>
+        <v>海藍寶</v>
       </c>
       <c r="E150">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F150">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="G150" t="str">
-        <v>藏银回纹.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>zsmh_spc_8</v>
+        <v>yss_zm_4</v>
       </c>
       <c r="B151" t="str">
         <v>配件</v>
       </c>
       <c r="C151" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D151" t="str">
-        <v>硃砂魔盒</v>
+        <v>銀飾S</v>
       </c>
       <c r="E151">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F151">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G151" t="str">
-        <v>朱砂魔盒.png</v>
+        <v>银饰S.png</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>cyszdz_pnd_2</v>
+        <v>gsch_pnd_2</v>
       </c>
       <c r="B152" t="str">
         <v>配件</v>
@@ -3883,7 +3883,7 @@
         <v>吊墜</v>
       </c>
       <c r="D152" t="str">
-        <v>藏銀十字吊墜</v>
+        <v>鋯石彩虹</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -3892,702 +3892,702 @@
         <v>99</v>
       </c>
       <c r="G152" t="str">
-        <v>藏银十字吊坠.png</v>
+        <v>锆石彩虹.png</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>cyyc_pnd_2</v>
+        <v>xgszs_spc_5</v>
       </c>
       <c r="B153" t="str">
         <v>配件</v>
       </c>
       <c r="C153" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D153" t="str">
-        <v>藏銀葉叢</v>
+        <v>小鋯石鑽閃</v>
       </c>
       <c r="E153">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F153">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G153" t="str">
-        <v>藏银叶丛.png</v>
+        <v>小锆石钻闪.png</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>cyxhlf_spc_8</v>
+        <v>hfj_cysl_6</v>
       </c>
       <c r="B154" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C154" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D154" t="str">
-        <v>藏銀小花立方</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E154">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F154">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G154" t="str">
-        <v>藏银小花立方.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>cydhlf_spc_8</v>
+        <v>hfj_cysl_8</v>
       </c>
       <c r="B155" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C155" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D155" t="str">
-        <v>藏銀大花立方</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E155">
         <v>8</v>
       </c>
       <c r="F155">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G155" t="str">
-        <v>藏银大花立方.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>jtlfq_spc_8</v>
+        <v>hfj_cysl_10</v>
       </c>
       <c r="B156" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C156" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D156" t="str">
-        <v>景泰藍福球</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E156">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F156">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="G156" t="str">
-        <v>景泰蓝福球.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>nh_agt_6</v>
+        <v>wyh_pnd_2</v>
       </c>
       <c r="B157" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C157" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D157" t="str">
-        <v>南紅</v>
+        <v>午夜花</v>
       </c>
       <c r="E157">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F157">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G157" t="str">
-        <v>南红.png</v>
+        <v>午夜花.png</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>nh_agt_8</v>
+        <v>ysxz_spc_6</v>
       </c>
       <c r="B158" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C158" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D158" t="str">
-        <v>南紅</v>
+        <v>銀色小珠</v>
       </c>
       <c r="E158">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F158">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G158" t="str">
-        <v>南红.png</v>
+        <v>银色小珠.png</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>nh_agt_10</v>
+        <v>jsmxyl_pnd_2</v>
       </c>
       <c r="B159" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C159" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D159" t="str">
-        <v>南紅</v>
+        <v>金色滿鑲月亮</v>
       </c>
       <c r="E159">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F159">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G159" t="str">
-        <v>南红.png</v>
+        <v>金色满镶月亮.png</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>hyes_stn_6</v>
+        <v>hbgd_spc_6</v>
       </c>
       <c r="B160" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C160" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D160" t="str">
-        <v>虎眼石</v>
+        <v>花邊軌道</v>
       </c>
       <c r="E160">
         <v>6</v>
       </c>
       <c r="F160">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G160" t="str">
-        <v>虎眼石.png</v>
+        <v>花边轨道.png</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>hyes_stn_8</v>
+        <v>lcmj_cysl_6</v>
       </c>
       <c r="B161" t="str">
         <v>珠子</v>
       </c>
       <c r="C161" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D161" t="str">
-        <v>虎眼石</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E161">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F161">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G161" t="str">
-        <v>虎眼石.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>hyes_stn_10</v>
+        <v>lcmj_cysl_8</v>
       </c>
       <c r="B162" t="str">
         <v>珠子</v>
       </c>
       <c r="C162" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D162" t="str">
-        <v>虎眼石</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E162">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F162">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G162" t="str">
-        <v>虎眼石.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>gqys_agt_6</v>
+        <v>lcmj_cysl_10</v>
       </c>
       <c r="B163" t="str">
         <v>珠子</v>
       </c>
       <c r="C163" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D163" t="str">
-        <v>乾青玉髓</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E163">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F163">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G163" t="str">
-        <v>干青玉髓.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>gqys_agt_8</v>
+        <v>hcw_spc_5</v>
       </c>
       <c r="B164" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C164" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D164" t="str">
-        <v>乾青玉髓</v>
+        <v>回財紋</v>
       </c>
       <c r="E164">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F164">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G164" t="str">
-        <v>干青玉髓.png</v>
+        <v>回财纹.png</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>gqys_agt_10</v>
+        <v>cyjc_spc_6</v>
       </c>
       <c r="B165" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C165" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D165" t="str">
-        <v>乾青玉髓</v>
+        <v>藏銀卷草</v>
       </c>
       <c r="E165">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F165">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G165" t="str">
-        <v>干青玉髓.png</v>
+        <v>藏银卷草.png</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>ljs_stn_6</v>
+        <v>hx_spc_6</v>
       </c>
       <c r="B166" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C166" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D166" t="str">
-        <v>藍晶石</v>
+        <v>花旋</v>
       </c>
       <c r="E166">
         <v>6</v>
       </c>
       <c r="F166">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G166" t="str">
-        <v>蓝晶石.png</v>
+        <v>花旋.png</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>ljs_stn_8</v>
+        <v>cyszh_spc_8</v>
       </c>
       <c r="B167" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C167" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D167" t="str">
-        <v>藍晶石</v>
+        <v>藏銀十字花</v>
       </c>
       <c r="E167">
         <v>8</v>
       </c>
       <c r="F167">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="G167" t="str">
-        <v>蓝晶石.png</v>
+        <v>藏银十字花.png</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>ljs_stn_10</v>
+        <v>cyym_pnd_2</v>
       </c>
       <c r="B168" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C168" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D168" t="str">
-        <v>藍晶石</v>
+        <v>藏銀羽毛</v>
       </c>
       <c r="E168">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F168">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="G168" t="str">
-        <v>蓝晶石.png</v>
+        <v>藏银羽毛.png</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>bmw_pnd_2</v>
+        <v>lys_stn_6</v>
       </c>
       <c r="B169" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C169" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D169" t="str">
-        <v>捕夢網</v>
+        <v>綠螢石</v>
       </c>
       <c r="E169">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F169">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G169" t="str">
-        <v>捕梦网.png</v>
+        <v>绿萤石.png</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>csj_cysl_6</v>
+        <v>lys_stn_8</v>
       </c>
       <c r="B170" t="str">
         <v>珠子</v>
       </c>
       <c r="C170" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D170" t="str">
-        <v>茶水晶</v>
+        <v>綠螢石</v>
       </c>
       <c r="E170">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F170">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G170" t="str">
-        <v>茶水晶.png</v>
+        <v>绿萤石.png</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>csj_cysl_8</v>
+        <v>cysy_spc_6</v>
       </c>
       <c r="B171" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C171" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D171" t="str">
-        <v>茶水晶</v>
+        <v>藏銀樹葉</v>
       </c>
       <c r="E171">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F171">
         <v>59</v>
       </c>
       <c r="G171" t="str">
-        <v>茶水晶.png</v>
+        <v>藏银树叶.png</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>csj_cysl_10</v>
+        <v>qws_stn_8</v>
       </c>
       <c r="B172" t="str">
         <v>珠子</v>
       </c>
       <c r="C172" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D172" t="str">
-        <v>茶水晶</v>
+        <v>薔薇石</v>
       </c>
       <c r="E172">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F172">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G172" t="str">
-        <v>茶水晶.png</v>
+        <v>蔷薇石.png</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>hmn_agt_6</v>
+        <v>qws_stn_10</v>
       </c>
       <c r="B173" t="str">
         <v>珠子</v>
       </c>
       <c r="C173" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D173" t="str">
-        <v>紅瑪瑙</v>
+        <v>薔薇石</v>
       </c>
       <c r="E173">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F173">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G173" t="str">
-        <v>红玛瑙.png</v>
+        <v>蔷薇石.png</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>hmn_agt_8</v>
+        <v>jsxz_spc_6</v>
       </c>
       <c r="B174" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C174" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D174" t="str">
-        <v>紅瑪瑙</v>
+        <v>金色小珠</v>
       </c>
       <c r="E174">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F174">
         <v>59</v>
       </c>
       <c r="G174" t="str">
-        <v>红玛瑙.png</v>
+        <v>金色小珠.png</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>hmn_agt_10</v>
+        <v>gtsp_xz_2</v>
       </c>
       <c r="B175" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C175" t="str">
-        <v>瑪瑙</v>
+        <v>星座</v>
       </c>
       <c r="D175" t="str">
-        <v>紅瑪瑙</v>
+        <v>古銅水瓶</v>
       </c>
       <c r="E175">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F175">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G175" t="str">
-        <v>红玛瑙.png</v>
+        <v>古铜水瓶.png</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>kqs_stn_6</v>
+        <v>gtby_xz_2</v>
       </c>
       <c r="B176" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C176" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D176" t="str">
-        <v>孔雀石</v>
+        <v>古銅白羊</v>
       </c>
       <c r="E176">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F176">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G176" t="str">
-        <v>孔雀石.png</v>
+        <v>古铜白羊.png</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>kqs_stn_8</v>
+        <v>gszssc_spc_6</v>
       </c>
       <c r="B177" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C177" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D177" t="str">
-        <v>孔雀石</v>
+        <v>鋯石鑽閃雙層</v>
       </c>
       <c r="E177">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F177">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G177" t="str">
-        <v>孔雀石.png</v>
+        <v>锆石钻闪双层.png</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>kqs_stn_10</v>
+        <v>cywp_spc_8</v>
       </c>
       <c r="B178" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C178" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D178" t="str">
-        <v>孔雀石</v>
+        <v>藏銀瓦片</v>
       </c>
       <c r="E178">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F178">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="G178" t="str">
-        <v>孔雀石.png</v>
+        <v>藏银瓦片.png</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>wlg_cysl_6</v>
+        <v>gtshz_xz_2</v>
       </c>
       <c r="B179" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C179" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D179" t="str">
-        <v>烏拉圭</v>
+        <v>古銅獅子</v>
       </c>
       <c r="E179">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F179">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G179" t="str">
-        <v>乌拉圭.png</v>
+        <v>古铜狮子.png</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>wlg_cysl_8</v>
+        <v>syc_pnd_2</v>
       </c>
       <c r="B180" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C180" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D180" t="str">
-        <v>烏拉圭</v>
+        <v>四葉草</v>
       </c>
       <c r="E180">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F180">
         <v>99</v>
       </c>
       <c r="G180" t="str">
-        <v>乌拉圭.png</v>
+        <v>四叶草.png</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>wlg_cysl_10</v>
+        <v>gttc_xz_2</v>
       </c>
       <c r="B181" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C181" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D181" t="str">
-        <v>烏拉圭</v>
+        <v>古銅天秤</v>
       </c>
       <c r="E181">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F181">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="G181" t="str">
-        <v>乌拉圭.png</v>
+        <v>古铜天秤.png</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>qjs_stn_6</v>
+        <v>gtcn_xz_2</v>
       </c>
       <c r="B182" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C182" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D182" t="str">
-        <v>青金石</v>
+        <v>古銅處女</v>
       </c>
       <c r="E182">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F182">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G182" t="str">
-        <v>青金石.png</v>
+        <v>古铜处女.png</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>qjs_stn_8</v>
+        <v>tys_stn_6</v>
       </c>
       <c r="B183" t="str">
         <v>珠子</v>
@@ -4596,21 +4596,21 @@
         <v>礦石</v>
       </c>
       <c r="D183" t="str">
-        <v>青金石</v>
+        <v>太陽石</v>
       </c>
       <c r="E183">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F183">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="G183" t="str">
-        <v>青金石.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>qjs_stn_10</v>
+        <v>tys_stn_8</v>
       </c>
       <c r="B184" t="str">
         <v>珠子</v>
@@ -4619,53 +4619,53 @@
         <v>礦石</v>
       </c>
       <c r="D184" t="str">
-        <v>青金石</v>
+        <v>太陽石</v>
       </c>
       <c r="E184">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F184">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G184" t="str">
-        <v>青金石.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>zyl_cysl_6</v>
+        <v>tys_stn_10</v>
       </c>
       <c r="B185" t="str">
         <v>珠子</v>
       </c>
       <c r="C185" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D185" t="str">
-        <v>紫幽靈</v>
+        <v>太陽石</v>
       </c>
       <c r="E185">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F185">
-        <v>39</v>
+        <v>169</v>
       </c>
       <c r="G185" t="str">
-        <v>紫幽灵.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>zyl_cysl_8</v>
+        <v>yslzzy_spc_8</v>
       </c>
       <c r="B186" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C186" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D186" t="str">
-        <v>紫幽靈</v>
+        <v>銀色六字真言</v>
       </c>
       <c r="E186">
         <v>8</v>
@@ -4674,44 +4674,44 @@
         <v>59</v>
       </c>
       <c r="G186" t="str">
-        <v>紫幽灵.png</v>
+        <v>银色六字真言.png</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>he_agt_6</v>
+        <v>ketj_spc_6</v>
       </c>
       <c r="B187" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C187" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D187" t="str">
-        <v>黑瑪瑙</v>
+        <v>凱爾特結</v>
       </c>
       <c r="E187">
         <v>6</v>
       </c>
       <c r="F187">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G187" t="str">
-        <v>黑玛瑙.png</v>
+        <v>凯尔特结.png</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>he_agt_8</v>
+        <v>ysxq_spc_8</v>
       </c>
       <c r="B188" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C188" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D188" t="str">
-        <v>黑瑪瑙</v>
+        <v>銀色繡球</v>
       </c>
       <c r="E188">
         <v>8</v>
@@ -4720,90 +4720,90 @@
         <v>59</v>
       </c>
       <c r="G188" t="str">
-        <v>黑玛瑙.png</v>
+        <v>银色绣球.png</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>he_agt_10</v>
+        <v>gtszz_xz_2</v>
       </c>
       <c r="B189" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C189" t="str">
-        <v>瑪瑙</v>
+        <v>星座</v>
       </c>
       <c r="D189" t="str">
-        <v>黑瑪瑙</v>
+        <v>古銅雙子</v>
       </c>
       <c r="E189">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F189">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G189" t="str">
-        <v>黑玛瑙.png</v>
+        <v>古铜双子.png</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>jys_stn_6</v>
+        <v>zsj_cysl_6</v>
       </c>
       <c r="B190" t="str">
         <v>珠子</v>
       </c>
       <c r="C190" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D190" t="str">
-        <v>金曜石</v>
+        <v>紫水晶</v>
       </c>
       <c r="E190">
         <v>6</v>
       </c>
       <c r="F190">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G190" t="str">
-        <v>金曜石.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>jys_stn_8</v>
+        <v>zsj_cysl_8</v>
       </c>
       <c r="B191" t="str">
         <v>珠子</v>
       </c>
       <c r="C191" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D191" t="str">
-        <v>金曜石</v>
+        <v>紫水晶</v>
       </c>
       <c r="E191">
         <v>8</v>
       </c>
       <c r="F191">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G191" t="str">
-        <v>金曜石.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>jys_stn_10</v>
+        <v>zsj_cysl_10</v>
       </c>
       <c r="B192" t="str">
         <v>珠子</v>
       </c>
       <c r="C192" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D192" t="str">
-        <v>金曜石</v>
+        <v>紫水晶</v>
       </c>
       <c r="E192">
         <v>10</v>
@@ -4812,81 +4812,1461 @@
         <v>99</v>
       </c>
       <c r="G192" t="str">
-        <v>金曜石.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>hys_stn_6</v>
+        <v>wgzl_pnd_2</v>
       </c>
       <c r="B193" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C193" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D193" t="str">
-        <v>黑曜石</v>
+        <v>王國之淚</v>
       </c>
       <c r="E193">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F193">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G193" t="str">
-        <v>黑曜石.png</v>
+        <v>王国之泪.png</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>hys_stn_8</v>
+        <v>gtsy_xz_2</v>
       </c>
       <c r="B194" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C194" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D194" t="str">
-        <v>黑曜石</v>
+        <v>古銅雙魚</v>
       </c>
       <c r="E194">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F194">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G194" t="str">
-        <v>黑曜石.png</v>
+        <v>古铜双鱼.png</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
+        <v>gtmj_xz_2</v>
+      </c>
+      <c r="B195" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C195" t="str">
+        <v>星座</v>
+      </c>
+      <c r="D195" t="str">
+        <v>古銅摩羯</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195">
+        <v>39</v>
+      </c>
+      <c r="G195" t="str">
+        <v>古铜摩羯.png</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>gtss_xz_2</v>
+      </c>
+      <c r="B196" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C196" t="str">
+        <v>星座</v>
+      </c>
+      <c r="D196" t="str">
+        <v>古銅射手</v>
+      </c>
+      <c r="E196">
+        <v>2</v>
+      </c>
+      <c r="F196">
+        <v>39</v>
+      </c>
+      <c r="G196" t="str">
+        <v>古铜射手.png</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>gtjn_xz_2</v>
+      </c>
+      <c r="B197" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C197" t="str">
+        <v>星座</v>
+      </c>
+      <c r="D197" t="str">
+        <v>古銅金牛</v>
+      </c>
+      <c r="E197">
+        <v>2</v>
+      </c>
+      <c r="F197">
+        <v>39</v>
+      </c>
+      <c r="G197" t="str">
+        <v>古铜金牛.png</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>gttx_xz_2</v>
+      </c>
+      <c r="B198" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C198" t="str">
+        <v>星座</v>
+      </c>
+      <c r="D198" t="str">
+        <v>古銅天蠍</v>
+      </c>
+      <c r="E198">
+        <v>2</v>
+      </c>
+      <c r="F198">
+        <v>39</v>
+      </c>
+      <c r="G198" t="str">
+        <v>古铜天蝎.png</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>jslzzy_spc_8</v>
+      </c>
+      <c r="B199" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C199" t="str">
+        <v>隔珠</v>
+      </c>
+      <c r="D199" t="str">
+        <v>金色六字真言</v>
+      </c>
+      <c r="E199">
+        <v>8</v>
+      </c>
+      <c r="F199">
+        <v>59</v>
+      </c>
+      <c r="G199" t="str">
+        <v>金色六字真言.png</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>cmj_cysl_6</v>
+      </c>
+      <c r="B200" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C200" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D200" t="str">
+        <v>草莓晶</v>
+      </c>
+      <c r="E200">
+        <v>6</v>
+      </c>
+      <c r="F200">
+        <v>39</v>
+      </c>
+      <c r="G200" t="str">
+        <v>草莓晶.png</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>cmj_cysl_8</v>
+      </c>
+      <c r="B201" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C201" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D201" t="str">
+        <v>草莓晶</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201">
+        <v>69</v>
+      </c>
+      <c r="G201" t="str">
+        <v>草莓晶.png</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>cmj_cysl_10</v>
+      </c>
+      <c r="B202" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C202" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D202" t="str">
+        <v>草莓晶</v>
+      </c>
+      <c r="E202">
+        <v>10</v>
+      </c>
+      <c r="F202">
+        <v>99</v>
+      </c>
+      <c r="G202" t="str">
+        <v>草莓晶.png</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>gtjx_xz_2</v>
+      </c>
+      <c r="B203" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C203" t="str">
+        <v>星座</v>
+      </c>
+      <c r="D203" t="str">
+        <v>古銅巨蟹</v>
+      </c>
+      <c r="E203">
+        <v>2</v>
+      </c>
+      <c r="F203">
+        <v>39</v>
+      </c>
+      <c r="G203" t="str">
+        <v>古铜巨蟹.png</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>cyhdls_pnd_2</v>
+      </c>
+      <c r="B204" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C204" t="str">
+        <v>吊墜</v>
+      </c>
+      <c r="D204" t="str">
+        <v>藏銀蝴蝶流蘇</v>
+      </c>
+      <c r="E204">
+        <v>2</v>
+      </c>
+      <c r="F204">
+        <v>99</v>
+      </c>
+      <c r="G204" t="str">
+        <v>藏银蝴蝶流苏.png</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>mghh_spc_6</v>
+      </c>
+      <c r="B205" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C205" t="str">
+        <v>隔珠</v>
+      </c>
+      <c r="D205" t="str">
+        <v>玫瑰花環</v>
+      </c>
+      <c r="E205">
+        <v>6</v>
+      </c>
+      <c r="F205">
+        <v>59</v>
+      </c>
+      <c r="G205" t="str">
+        <v>玫瑰花环.png</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>bmnmh_spc_8</v>
+      </c>
+      <c r="B206" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C206" t="str">
+        <v>隔珠</v>
+      </c>
+      <c r="D206" t="str">
+        <v>白瑪瑙魔盒</v>
+      </c>
+      <c r="E206">
+        <v>8</v>
+      </c>
+      <c r="F206">
+        <v>59</v>
+      </c>
+      <c r="G206" t="str">
+        <v>白玛瑙魔盒.png</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>cyhw_spc_5</v>
+      </c>
+      <c r="B207" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C207" t="str">
+        <v>隔珠</v>
+      </c>
+      <c r="D207" t="str">
+        <v>藏銀回紋</v>
+      </c>
+      <c r="E207">
+        <v>5</v>
+      </c>
+      <c r="F207">
+        <v>59</v>
+      </c>
+      <c r="G207" t="str">
+        <v>藏银回纹.png</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>zsmh_spc_8</v>
+      </c>
+      <c r="B208" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C208" t="str">
+        <v>隔珠</v>
+      </c>
+      <c r="D208" t="str">
+        <v>硃砂魔盒</v>
+      </c>
+      <c r="E208">
+        <v>8</v>
+      </c>
+      <c r="F208">
+        <v>59</v>
+      </c>
+      <c r="G208" t="str">
+        <v>朱砂魔盒.png</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>cyszdz_pnd_2</v>
+      </c>
+      <c r="B209" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C209" t="str">
+        <v>吊墜</v>
+      </c>
+      <c r="D209" t="str">
+        <v>藏銀十字吊墜</v>
+      </c>
+      <c r="E209">
+        <v>2</v>
+      </c>
+      <c r="F209">
+        <v>99</v>
+      </c>
+      <c r="G209" t="str">
+        <v>藏银十字吊坠.png</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>cyyc_pnd_2</v>
+      </c>
+      <c r="B210" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C210" t="str">
+        <v>吊墜</v>
+      </c>
+      <c r="D210" t="str">
+        <v>藏銀葉叢</v>
+      </c>
+      <c r="E210">
+        <v>2</v>
+      </c>
+      <c r="F210">
+        <v>99</v>
+      </c>
+      <c r="G210" t="str">
+        <v>藏银叶丛.png</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>cyxhlf_spc_8</v>
+      </c>
+      <c r="B211" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C211" t="str">
+        <v>隔珠</v>
+      </c>
+      <c r="D211" t="str">
+        <v>藏銀小花立方</v>
+      </c>
+      <c r="E211">
+        <v>8</v>
+      </c>
+      <c r="F211">
+        <v>59</v>
+      </c>
+      <c r="G211" t="str">
+        <v>藏银小花立方.png</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>cydhlf_spc_8</v>
+      </c>
+      <c r="B212" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C212" t="str">
+        <v>隔珠</v>
+      </c>
+      <c r="D212" t="str">
+        <v>藏銀大花立方</v>
+      </c>
+      <c r="E212">
+        <v>8</v>
+      </c>
+      <c r="F212">
+        <v>59</v>
+      </c>
+      <c r="G212" t="str">
+        <v>藏银大花立方.png</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>jtlfq_spc_8</v>
+      </c>
+      <c r="B213" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C213" t="str">
+        <v>隔珠</v>
+      </c>
+      <c r="D213" t="str">
+        <v>景泰藍福球</v>
+      </c>
+      <c r="E213">
+        <v>8</v>
+      </c>
+      <c r="F213">
+        <v>59</v>
+      </c>
+      <c r="G213" t="str">
+        <v>景泰蓝福球.png</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>nh_agt_6</v>
+      </c>
+      <c r="B214" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C214" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D214" t="str">
+        <v>南紅</v>
+      </c>
+      <c r="E214">
+        <v>6</v>
+      </c>
+      <c r="F214">
+        <v>39</v>
+      </c>
+      <c r="G214" t="str">
+        <v>南红.png</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>nh_agt_8</v>
+      </c>
+      <c r="B215" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C215" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D215" t="str">
+        <v>南紅</v>
+      </c>
+      <c r="E215">
+        <v>8</v>
+      </c>
+      <c r="F215">
+        <v>69</v>
+      </c>
+      <c r="G215" t="str">
+        <v>南红.png</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>nh_agt_10</v>
+      </c>
+      <c r="B216" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C216" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D216" t="str">
+        <v>南紅</v>
+      </c>
+      <c r="E216">
+        <v>10</v>
+      </c>
+      <c r="F216">
+        <v>129</v>
+      </c>
+      <c r="G216" t="str">
+        <v>南红.png</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>hyes_stn_6</v>
+      </c>
+      <c r="B217" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C217" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D217" t="str">
+        <v>虎眼石</v>
+      </c>
+      <c r="E217">
+        <v>6</v>
+      </c>
+      <c r="F217">
+        <v>39</v>
+      </c>
+      <c r="G217" t="str">
+        <v>虎眼石.png</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>hyes_stn_8</v>
+      </c>
+      <c r="B218" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C218" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D218" t="str">
+        <v>虎眼石</v>
+      </c>
+      <c r="E218">
+        <v>8</v>
+      </c>
+      <c r="F218">
+        <v>59</v>
+      </c>
+      <c r="G218" t="str">
+        <v>虎眼石.png</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>hyes_stn_10</v>
+      </c>
+      <c r="B219" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C219" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D219" t="str">
+        <v>虎眼石</v>
+      </c>
+      <c r="E219">
+        <v>10</v>
+      </c>
+      <c r="F219">
+        <v>89</v>
+      </c>
+      <c r="G219" t="str">
+        <v>虎眼石.png</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>gqys_agt_6</v>
+      </c>
+      <c r="B220" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C220" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D220" t="str">
+        <v>乾青玉髓</v>
+      </c>
+      <c r="E220">
+        <v>6</v>
+      </c>
+      <c r="F220">
+        <v>59</v>
+      </c>
+      <c r="G220" t="str">
+        <v>干青玉髓.png</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>gqys_agt_8</v>
+      </c>
+      <c r="B221" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C221" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D221" t="str">
+        <v>乾青玉髓</v>
+      </c>
+      <c r="E221">
+        <v>8</v>
+      </c>
+      <c r="F221">
+        <v>69</v>
+      </c>
+      <c r="G221" t="str">
+        <v>干青玉髓.png</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>gqys_agt_10</v>
+      </c>
+      <c r="B222" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C222" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D222" t="str">
+        <v>乾青玉髓</v>
+      </c>
+      <c r="E222">
+        <v>10</v>
+      </c>
+      <c r="F222">
+        <v>89</v>
+      </c>
+      <c r="G222" t="str">
+        <v>干青玉髓.png</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>yys_stn_6</v>
+      </c>
+      <c r="B223" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C223" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D223" t="str">
+        <v>銀曜石</v>
+      </c>
+      <c r="E223">
+        <v>6</v>
+      </c>
+      <c r="F223">
+        <v>39</v>
+      </c>
+      <c r="G223" t="str">
+        <v>银曜石.png</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>yys_stn_8</v>
+      </c>
+      <c r="B224" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C224" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D224" t="str">
+        <v>銀曜石</v>
+      </c>
+      <c r="E224">
+        <v>8</v>
+      </c>
+      <c r="F224">
+        <v>69</v>
+      </c>
+      <c r="G224" t="str">
+        <v>银曜石.png</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>yys_stn_10</v>
+      </c>
+      <c r="B225" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C225" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D225" t="str">
+        <v>銀曜石</v>
+      </c>
+      <c r="E225">
+        <v>10</v>
+      </c>
+      <c r="F225">
+        <v>99</v>
+      </c>
+      <c r="G225" t="str">
+        <v>银曜石.png</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>bmw_pnd_2</v>
+      </c>
+      <c r="B226" t="str">
+        <v>配件</v>
+      </c>
+      <c r="C226" t="str">
+        <v>吊墜</v>
+      </c>
+      <c r="D226" t="str">
+        <v>捕夢網</v>
+      </c>
+      <c r="E226">
+        <v>2</v>
+      </c>
+      <c r="F226">
+        <v>99</v>
+      </c>
+      <c r="G226" t="str">
+        <v>捕梦网.png</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>ljs_stn_6</v>
+      </c>
+      <c r="B227" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C227" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D227" t="str">
+        <v>藍晶石</v>
+      </c>
+      <c r="E227">
+        <v>6</v>
+      </c>
+      <c r="F227">
+        <v>99</v>
+      </c>
+      <c r="G227" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>ljs_stn_8</v>
+      </c>
+      <c r="B228" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C228" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D228" t="str">
+        <v>藍晶石</v>
+      </c>
+      <c r="E228">
+        <v>8</v>
+      </c>
+      <c r="F228">
+        <v>139</v>
+      </c>
+      <c r="G228" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>ljs_stn_10</v>
+      </c>
+      <c r="B229" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C229" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D229" t="str">
+        <v>藍晶石</v>
+      </c>
+      <c r="E229">
+        <v>10</v>
+      </c>
+      <c r="F229">
+        <v>199</v>
+      </c>
+      <c r="G229" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>hmn_agt_6</v>
+      </c>
+      <c r="B230" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C230" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D230" t="str">
+        <v>紅瑪瑙</v>
+      </c>
+      <c r="E230">
+        <v>6</v>
+      </c>
+      <c r="F230">
+        <v>39</v>
+      </c>
+      <c r="G230" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>hmn_agt_8</v>
+      </c>
+      <c r="B231" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C231" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D231" t="str">
+        <v>紅瑪瑙</v>
+      </c>
+      <c r="E231">
+        <v>8</v>
+      </c>
+      <c r="F231">
+        <v>59</v>
+      </c>
+      <c r="G231" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>hmn_agt_10</v>
+      </c>
+      <c r="B232" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C232" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D232" t="str">
+        <v>紅瑪瑙</v>
+      </c>
+      <c r="E232">
+        <v>10</v>
+      </c>
+      <c r="F232">
+        <v>89</v>
+      </c>
+      <c r="G232" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>csj_cysl_6</v>
+      </c>
+      <c r="B233" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C233" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D233" t="str">
+        <v>茶水晶</v>
+      </c>
+      <c r="E233">
+        <v>6</v>
+      </c>
+      <c r="F233">
+        <v>39</v>
+      </c>
+      <c r="G233" t="str">
+        <v>茶水晶.png</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>csj_cysl_8</v>
+      </c>
+      <c r="B234" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C234" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D234" t="str">
+        <v>茶水晶</v>
+      </c>
+      <c r="E234">
+        <v>8</v>
+      </c>
+      <c r="F234">
+        <v>59</v>
+      </c>
+      <c r="G234" t="str">
+        <v>茶水晶.png</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>csj_cysl_10</v>
+      </c>
+      <c r="B235" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C235" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D235" t="str">
+        <v>茶水晶</v>
+      </c>
+      <c r="E235">
+        <v>10</v>
+      </c>
+      <c r="F235">
+        <v>89</v>
+      </c>
+      <c r="G235" t="str">
+        <v>茶水晶.png</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>kqs_stn_6</v>
+      </c>
+      <c r="B236" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C236" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D236" t="str">
+        <v>孔雀石</v>
+      </c>
+      <c r="E236">
+        <v>6</v>
+      </c>
+      <c r="F236">
+        <v>69</v>
+      </c>
+      <c r="G236" t="str">
+        <v>孔雀石.png</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>kqs_stn_8</v>
+      </c>
+      <c r="B237" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C237" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D237" t="str">
+        <v>孔雀石</v>
+      </c>
+      <c r="E237">
+        <v>8</v>
+      </c>
+      <c r="F237">
+        <v>89</v>
+      </c>
+      <c r="G237" t="str">
+        <v>孔雀石.png</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>kqs_stn_10</v>
+      </c>
+      <c r="B238" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C238" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D238" t="str">
+        <v>孔雀石</v>
+      </c>
+      <c r="E238">
+        <v>10</v>
+      </c>
+      <c r="F238">
+        <v>199</v>
+      </c>
+      <c r="G238" t="str">
+        <v>孔雀石.png</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>qjs_stn_6</v>
+      </c>
+      <c r="B239" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C239" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D239" t="str">
+        <v>青金石</v>
+      </c>
+      <c r="E239">
+        <v>6</v>
+      </c>
+      <c r="F239">
+        <v>69</v>
+      </c>
+      <c r="G239" t="str">
+        <v>青金石.png</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>qjs_stn_8</v>
+      </c>
+      <c r="B240" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C240" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D240" t="str">
+        <v>青金石</v>
+      </c>
+      <c r="E240">
+        <v>8</v>
+      </c>
+      <c r="F240">
+        <v>89</v>
+      </c>
+      <c r="G240" t="str">
+        <v>青金石.png</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>qjs_stn_10</v>
+      </c>
+      <c r="B241" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C241" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D241" t="str">
+        <v>青金石</v>
+      </c>
+      <c r="E241">
+        <v>10</v>
+      </c>
+      <c r="F241">
+        <v>99</v>
+      </c>
+      <c r="G241" t="str">
+        <v>青金石.png</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>wlg_cysl_6</v>
+      </c>
+      <c r="B242" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C242" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D242" t="str">
+        <v>烏拉圭</v>
+      </c>
+      <c r="E242">
+        <v>6</v>
+      </c>
+      <c r="F242">
+        <v>69</v>
+      </c>
+      <c r="G242" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>wlg_cysl_8</v>
+      </c>
+      <c r="B243" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C243" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D243" t="str">
+        <v>烏拉圭</v>
+      </c>
+      <c r="E243">
+        <v>8</v>
+      </c>
+      <c r="F243">
+        <v>99</v>
+      </c>
+      <c r="G243" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>wlg_cysl_10</v>
+      </c>
+      <c r="B244" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C244" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D244" t="str">
+        <v>烏拉圭</v>
+      </c>
+      <c r="E244">
+        <v>10</v>
+      </c>
+      <c r="F244">
+        <v>169</v>
+      </c>
+      <c r="G244" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>zyl_cysl_6</v>
+      </c>
+      <c r="B245" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C245" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D245" t="str">
+        <v>紫幽靈</v>
+      </c>
+      <c r="E245">
+        <v>6</v>
+      </c>
+      <c r="F245">
+        <v>39</v>
+      </c>
+      <c r="G245" t="str">
+        <v>紫幽灵.png</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>zyl_cysl_8</v>
+      </c>
+      <c r="B246" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C246" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D246" t="str">
+        <v>紫幽靈</v>
+      </c>
+      <c r="E246">
+        <v>8</v>
+      </c>
+      <c r="F246">
+        <v>59</v>
+      </c>
+      <c r="G246" t="str">
+        <v>紫幽灵.png</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>he_agt_6</v>
+      </c>
+      <c r="B247" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C247" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D247" t="str">
+        <v>黑瑪瑙</v>
+      </c>
+      <c r="E247">
+        <v>6</v>
+      </c>
+      <c r="F247">
+        <v>39</v>
+      </c>
+      <c r="G247" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>he_agt_8</v>
+      </c>
+      <c r="B248" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C248" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D248" t="str">
+        <v>黑瑪瑙</v>
+      </c>
+      <c r="E248">
+        <v>8</v>
+      </c>
+      <c r="F248">
+        <v>59</v>
+      </c>
+      <c r="G248" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>he_agt_10</v>
+      </c>
+      <c r="B249" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C249" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D249" t="str">
+        <v>黑瑪瑙</v>
+      </c>
+      <c r="E249">
+        <v>10</v>
+      </c>
+      <c r="F249">
+        <v>89</v>
+      </c>
+      <c r="G249" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>jys_stn_6</v>
+      </c>
+      <c r="B250" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C250" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D250" t="str">
+        <v>金曜石</v>
+      </c>
+      <c r="E250">
+        <v>6</v>
+      </c>
+      <c r="F250">
+        <v>39</v>
+      </c>
+      <c r="G250" t="str">
+        <v>金曜石.png</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>jys_stn_8</v>
+      </c>
+      <c r="B251" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C251" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D251" t="str">
+        <v>金曜石</v>
+      </c>
+      <c r="E251">
+        <v>8</v>
+      </c>
+      <c r="F251">
+        <v>69</v>
+      </c>
+      <c r="G251" t="str">
+        <v>金曜石.png</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>jys_stn_10</v>
+      </c>
+      <c r="B252" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C252" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D252" t="str">
+        <v>金曜石</v>
+      </c>
+      <c r="E252">
+        <v>10</v>
+      </c>
+      <c r="F252">
+        <v>99</v>
+      </c>
+      <c r="G252" t="str">
+        <v>金曜石.png</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>hys_stn_6</v>
+      </c>
+      <c r="B253" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C253" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D253" t="str">
+        <v>黑曜石</v>
+      </c>
+      <c r="E253">
+        <v>6</v>
+      </c>
+      <c r="F253">
+        <v>39</v>
+      </c>
+      <c r="G253" t="str">
+        <v>黑曜石.png</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>hys_stn_8</v>
+      </c>
+      <c r="B254" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C254" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D254" t="str">
+        <v>黑曜石</v>
+      </c>
+      <c r="E254">
+        <v>8</v>
+      </c>
+      <c r="F254">
+        <v>69</v>
+      </c>
+      <c r="G254" t="str">
+        <v>黑曜石.png</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
         <v>hys_stn_10</v>
       </c>
-      <c r="B195" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C195" t="str">
+      <c r="B255" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C255" t="str">
         <v>礦石</v>
       </c>
-      <c r="D195" t="str">
+      <c r="D255" t="str">
         <v>黑曜石</v>
       </c>
-      <c r="E195">
+      <c r="E255">
         <v>10</v>
       </c>
-      <c r="F195">
+      <c r="F255">
         <v>99</v>
       </c>
-      <c r="G195" t="str">
+      <c r="G255" t="str">
         <v>黑曜石.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G255"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G255"/>
+  <dimension ref="A1:G288"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -493,7 +493,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>byl_cysl_8</v>
+        <v>xhyl_cysl_6</v>
       </c>
       <c r="B5" t="str">
         <v>珠子</v>
@@ -502,21 +502,21 @@
         <v>水晶</v>
       </c>
       <c r="D5" t="str">
-        <v>白幽靈</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G5" t="str">
-        <v>白幽灵.png</v>
+        <v>雪花幽灵.png</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>xhyl_cysl_6</v>
+        <v>xhyl_cysl_8</v>
       </c>
       <c r="B6" t="str">
         <v>珠子</v>
@@ -528,10 +528,10 @@
         <v>雪花幽靈</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G6" t="str">
         <v>雪花幽灵.png</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>xhyl_cysl_8</v>
+        <v>xhyl_cysl_10</v>
       </c>
       <c r="B7" t="str">
         <v>珠子</v>
@@ -551,10 +551,10 @@
         <v>雪花幽靈</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="G7" t="str">
         <v>雪花幽灵.png</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>xhyl_cysl_10</v>
+        <v>byl_cysl_8</v>
       </c>
       <c r="B8" t="str">
         <v>珠子</v>
@@ -571,16 +571,16 @@
         <v>水晶</v>
       </c>
       <c r="D8" t="str">
-        <v>雪花幽靈</v>
+        <v>白幽靈</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="G8" t="str">
-        <v>雪花幽灵.png</v>
+        <v>白幽灵.png</v>
       </c>
     </row>
     <row r="9">
@@ -677,122 +677,122 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>pts_stn_6</v>
+        <v>nbj_cysl_8</v>
       </c>
       <c r="B13" t="str">
         <v>珠子</v>
       </c>
       <c r="C13" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D13" t="str">
-        <v>葡萄石</v>
+        <v>奶白晶</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G13" t="str">
-        <v>葡萄石.png</v>
+        <v>奶白晶.png</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>pts_stn_10</v>
+        <v>nbj_cysl_10</v>
       </c>
       <c r="B14" t="str">
         <v>珠子</v>
       </c>
       <c r="C14" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D14" t="str">
-        <v>葡萄石</v>
+        <v>奶白晶</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G14" t="str">
-        <v>葡萄石.png</v>
+        <v>奶白晶.png</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>lkzls_spc_6</v>
+        <v>pts_stn_6</v>
       </c>
       <c r="B15" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C15" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D15" t="str">
-        <v>鏤空鑽蕾絲</v>
+        <v>葡萄石</v>
       </c>
       <c r="E15">
         <v>6</v>
       </c>
       <c r="F15">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G15" t="str">
-        <v>镂空钻蕾丝.png</v>
+        <v>葡萄石.png</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mxxx_pnd_2</v>
+        <v>pts_stn_10</v>
       </c>
       <c r="B16" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C16" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D16" t="str">
-        <v>滿鑲星星</v>
+        <v>葡萄石</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F16">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G16" t="str">
-        <v>满镶星星.png</v>
+        <v>葡萄石.png</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>pl_pnd_2</v>
+        <v>lkzls_spc_6</v>
       </c>
       <c r="B17" t="str">
         <v>配件</v>
       </c>
       <c r="C17" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D17" t="str">
-        <v>霹靂</v>
+        <v>鏤空鑽蕾絲</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G17" t="str">
-        <v>霹雳.png</v>
+        <v>镂空钻蕾丝.png</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>lkxm_pnd_2</v>
+        <v>mxxx_pnd_2</v>
       </c>
       <c r="B18" t="str">
         <v>配件</v>
@@ -801,7 +801,7 @@
         <v>吊墜</v>
       </c>
       <c r="D18" t="str">
-        <v>鏤空小貓</v>
+        <v>滿鑲星星</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -810,12 +810,12 @@
         <v>99</v>
       </c>
       <c r="G18" t="str">
-        <v>镂空小猫.png</v>
+        <v>满镶星星.png</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>axqbz_pnd_2</v>
+        <v>pl_pnd_2</v>
       </c>
       <c r="B19" t="str">
         <v>配件</v>
@@ -824,7 +824,7 @@
         <v>吊墜</v>
       </c>
       <c r="D19" t="str">
-        <v>愛心曲別針</v>
+        <v>霹靂</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -833,67 +833,67 @@
         <v>99</v>
       </c>
       <c r="G19" t="str">
-        <v>爱心曲别针.png</v>
+        <v>霹雳.png</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>gsmhz_spc_8</v>
+        <v>lkxm_pnd_2</v>
       </c>
       <c r="B20" t="str">
         <v>配件</v>
       </c>
       <c r="C20" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D20" t="str">
-        <v>鋯石魔盒鑽</v>
+        <v>鏤空小貓</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G20" t="str">
-        <v>锆石魔盒钻.png</v>
+        <v>镂空小猫.png</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>by_agt_6</v>
+        <v>axqbz_pnd_2</v>
       </c>
       <c r="B21" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C21" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D21" t="str">
-        <v>白玉髓</v>
+        <v>愛心曲別針</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G21" t="str">
-        <v>白玉髓.png</v>
+        <v>爱心曲别针.png</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>by_agt_8</v>
+        <v>gsmhz_spc_8</v>
       </c>
       <c r="B22" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C22" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D22" t="str">
-        <v>白玉髓</v>
+        <v>鋯石魔盒鑽</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -902,35 +902,35 @@
         <v>59</v>
       </c>
       <c r="G22" t="str">
-        <v>白玉髓.png</v>
+        <v>锆石魔盒钻.png</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>by_agt_10</v>
+        <v>xgfj_cysl_6</v>
       </c>
       <c r="B23" t="str">
         <v>珠子</v>
       </c>
       <c r="C23" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D23" t="str">
-        <v>白玉髓</v>
+        <v>星光粉晶</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="G23" t="str">
-        <v>白玉髓.png</v>
+        <v>星光粉晶.png</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>zlh_cysl_6</v>
+        <v>xgfj_cysl_8</v>
       </c>
       <c r="B24" t="str">
         <v>珠子</v>
@@ -939,21 +939,21 @@
         <v>水晶</v>
       </c>
       <c r="D24" t="str">
-        <v>紫鋰輝</v>
+        <v>星光粉晶</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G24" t="str">
-        <v>紫锂辉.png</v>
+        <v>星光粉晶.png</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>zlh_cysl_8</v>
+        <v>xgfj_cysl_10</v>
       </c>
       <c r="B25" t="str">
         <v>珠子</v>
@@ -962,53 +962,53 @@
         <v>水晶</v>
       </c>
       <c r="D25" t="str">
-        <v>紫鋰輝</v>
+        <v>星光粉晶</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G25" t="str">
-        <v>紫锂辉.png</v>
+        <v>星光粉晶.png</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>zlh_cysl_10</v>
+        <v>by_agt_6</v>
       </c>
       <c r="B26" t="str">
         <v>珠子</v>
       </c>
       <c r="C26" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D26" t="str">
-        <v>紫鋰輝</v>
+        <v>白玉髓</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="G26" t="str">
-        <v>紫锂辉.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lglf_spc_8</v>
+        <v>by_agt_8</v>
       </c>
       <c r="B27" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C27" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D27" t="str">
-        <v>菱格立方</v>
+        <v>白玉髓</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -1017,35 +1017,35 @@
         <v>59</v>
       </c>
       <c r="G27" t="str">
-        <v>菱格立方.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>fsj_cysl_6</v>
+        <v>by_agt_10</v>
       </c>
       <c r="B28" t="str">
         <v>珠子</v>
       </c>
       <c r="C28" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D28" t="str">
-        <v>粉水晶</v>
+        <v>白玉髓</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G28" t="str">
-        <v>粉水晶.png</v>
+        <v>白玉髓.png</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>fsj_cysl_8</v>
+        <v>zlh_cysl_6</v>
       </c>
       <c r="B29" t="str">
         <v>珠子</v>
@@ -1054,21 +1054,21 @@
         <v>水晶</v>
       </c>
       <c r="D29" t="str">
-        <v>粉水晶</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G29" t="str">
-        <v>粉水晶.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>fsj_cysl_10</v>
+        <v>zlh_cysl_8</v>
       </c>
       <c r="B30" t="str">
         <v>珠子</v>
@@ -1077,44 +1077,44 @@
         <v>水晶</v>
       </c>
       <c r="D30" t="str">
-        <v>粉水晶</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="G30" t="str">
-        <v>粉水晶.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ysmxyl_pnd_2</v>
+        <v>zlh_cysl_10</v>
       </c>
       <c r="B31" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C31" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D31" t="str">
-        <v>銀色滿鑲月亮</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="G31" t="str">
-        <v>银色满镶月亮.png</v>
+        <v>紫锂辉.png</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>gsfz_spc_6</v>
+        <v>lglf_spc_8</v>
       </c>
       <c r="B32" t="str">
         <v>配件</v>
@@ -1123,44 +1123,44 @@
         <v>隔珠</v>
       </c>
       <c r="D32" t="str">
-        <v>鋯石方鑽</v>
+        <v>菱格立方</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>59</v>
       </c>
       <c r="G32" t="str">
-        <v>锆石方钻.png</v>
+        <v>菱格立方.png</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lkjf_pnd_2</v>
+        <v>fsj_cysl_6</v>
       </c>
       <c r="B33" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C33" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D33" t="str">
-        <v>鏤空金福</v>
+        <v>粉水晶</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F33">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G33" t="str">
-        <v>镂空金福.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>bas_cysl_8</v>
+        <v>fsj_cysl_8</v>
       </c>
       <c r="B34" t="str">
         <v>珠子</v>
@@ -1169,21 +1169,21 @@
         <v>水晶</v>
       </c>
       <c r="D34" t="str">
-        <v>白阿塞</v>
+        <v>粉水晶</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
       <c r="F34">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G34" t="str">
-        <v>白阿塞.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>bas_cysl_10</v>
+        <v>fsj_cysl_10</v>
       </c>
       <c r="B35" t="str">
         <v>珠子</v>
@@ -1192,7 +1192,7 @@
         <v>水晶</v>
       </c>
       <c r="D35" t="str">
-        <v>白阿塞</v>
+        <v>粉水晶</v>
       </c>
       <c r="E35">
         <v>10</v>
@@ -1201,495 +1201,495 @@
         <v>99</v>
       </c>
       <c r="G35" t="str">
-        <v>白阿塞.png</v>
+        <v>粉水晶.png</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>zys_agt_6</v>
+        <v>ysmxyl_pnd_2</v>
       </c>
       <c r="B36" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C36" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D36" t="str">
-        <v>紫玉髓</v>
+        <v>銀色滿鑲月亮</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G36" t="str">
-        <v>紫玉髓.png</v>
+        <v>银色满镶月亮.png</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>zys_agt_8</v>
+        <v>gsfz_spc_6</v>
       </c>
       <c r="B37" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C37" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D37" t="str">
-        <v>紫玉髓</v>
+        <v>鋯石方鑽</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37">
         <v>59</v>
       </c>
       <c r="G37" t="str">
-        <v>紫玉髓.png</v>
+        <v>锆石方钻.png</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>hws_stn_6</v>
+        <v>lkjf_pnd_2</v>
       </c>
       <c r="B38" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C38" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D38" t="str">
-        <v>海紋石</v>
+        <v>鏤空金福</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G38" t="str">
-        <v>海纹石.png</v>
+        <v>镂空金福.png</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>hws_stn_8</v>
+        <v>bas_cysl_8</v>
       </c>
       <c r="B39" t="str">
         <v>珠子</v>
       </c>
       <c r="C39" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D39" t="str">
-        <v>海紋石</v>
+        <v>白阿塞</v>
       </c>
       <c r="E39">
         <v>8</v>
       </c>
       <c r="F39">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G39" t="str">
-        <v>海纹石.png</v>
+        <v>白阿塞.png</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>hws_stn_10</v>
+        <v>bas_cysl_10</v>
       </c>
       <c r="B40" t="str">
         <v>珠子</v>
       </c>
       <c r="C40" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D40" t="str">
-        <v>海紋石</v>
+        <v>白阿塞</v>
       </c>
       <c r="E40">
         <v>10</v>
       </c>
       <c r="F40">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="G40" t="str">
-        <v>海纹石.png</v>
+        <v>白阿塞.png</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>jfj_cysl_6</v>
+        <v>nyhlb_stn_6</v>
       </c>
       <c r="B41" t="str">
         <v>珠子</v>
       </c>
       <c r="C41" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D41" t="str">
-        <v>金髮晶</v>
+        <v>奶油海藍寶</v>
       </c>
       <c r="E41">
         <v>6</v>
       </c>
       <c r="F41">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G41" t="str">
-        <v>金发晶.png</v>
+        <v>奶油海蓝宝.png</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>jfj_cysl_8</v>
+        <v>nyhlb_stn_8</v>
       </c>
       <c r="B42" t="str">
         <v>珠子</v>
       </c>
       <c r="C42" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D42" t="str">
-        <v>金髮晶</v>
+        <v>奶油海藍寶</v>
       </c>
       <c r="E42">
         <v>8</v>
       </c>
       <c r="F42">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G42" t="str">
-        <v>金发晶.png</v>
+        <v>奶油海蓝宝.png</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>jfj_cysl_10</v>
+        <v>nyhlb_stn_10</v>
       </c>
       <c r="B43" t="str">
         <v>珠子</v>
       </c>
       <c r="C43" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D43" t="str">
-        <v>金髮晶</v>
+        <v>奶油海藍寶</v>
       </c>
       <c r="E43">
         <v>10</v>
       </c>
       <c r="F43">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="G43" t="str">
-        <v>金发晶.png</v>
+        <v>奶油海蓝宝.png</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>wlyz_spc_5</v>
+        <v>zys_agt_6</v>
       </c>
       <c r="B44" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C44" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D44" t="str">
-        <v>五稜銀鑽</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G44" t="str">
-        <v>五棱银钻.png</v>
+        <v>紫玉髓.png</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>gsxx_pnd_2</v>
+        <v>zys_agt_8</v>
       </c>
       <c r="B45" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C45" t="str">
-        <v>吊墜</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D45" t="str">
-        <v>鋯石星星</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F45">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G45" t="str">
-        <v>锆石星星.png</v>
+        <v>紫玉髓.png</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>xxys_pnd_2</v>
+        <v>hws_stn_6</v>
       </c>
       <c r="B46" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C46" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D46" t="str">
-        <v>尋心鑰匙</v>
+        <v>海紋石</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F46">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G46" t="str">
-        <v>寻心钥匙.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>bsyw_pnd_2</v>
+        <v>hws_stn_8</v>
       </c>
       <c r="B47" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C47" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D47" t="str">
-        <v>白水魚尾</v>
+        <v>海紋石</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F47">
         <v>99</v>
       </c>
       <c r="G47" t="str">
-        <v>白水鱼尾.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>zyb_spc_8</v>
+        <v>hws_stn_10</v>
       </c>
       <c r="B48" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C48" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D48" t="str">
-        <v>轉運柄</v>
+        <v>海紋石</v>
       </c>
       <c r="E48">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F48">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="G48" t="str">
-        <v>转运柄.png</v>
+        <v>海纹石.png</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>emzy_spc_6</v>
+        <v>jfj_cysl_6</v>
       </c>
       <c r="B49" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C49" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D49" t="str">
-        <v>惡魔之眼</v>
+        <v>金髮晶</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
       <c r="F49">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G49" t="str">
-        <v>恶魔之眼.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lwmn_agt_6</v>
+        <v>jfj_cysl_8</v>
       </c>
       <c r="B50" t="str">
         <v>珠子</v>
       </c>
       <c r="C50" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D50" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>金髮晶</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F50">
         <v>69</v>
       </c>
       <c r="G50" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lwmn_agt_8</v>
+        <v>jfj_cysl_10</v>
       </c>
       <c r="B51" t="str">
         <v>珠子</v>
       </c>
       <c r="C51" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D51" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>金髮晶</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F51">
         <v>99</v>
       </c>
       <c r="G51" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>金发晶.png</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>lwmn_agt_10</v>
+        <v>wlyz_spc_5</v>
       </c>
       <c r="B52" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C52" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D52" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>五稜銀鑽</v>
       </c>
       <c r="E52">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F52">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="G52" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>五棱银钻.png</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>xyc_cysl_8</v>
+        <v>gsxx_pnd_2</v>
       </c>
       <c r="B53" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C53" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D53" t="str">
-        <v>薰衣草</v>
+        <v>鋯石星星</v>
       </c>
       <c r="E53">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G53" t="str">
-        <v>薰衣草.png</v>
+        <v>锆石星星.png</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>xyc_cysl_10</v>
+        <v>xxys_pnd_2</v>
       </c>
       <c r="B54" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C54" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D54" t="str">
-        <v>薰衣草</v>
+        <v>尋心鑰匙</v>
       </c>
       <c r="E54">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="G54" t="str">
-        <v>薰衣草.png</v>
+        <v>寻心钥匙.png</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>nwxh_spc_5</v>
+        <v>bsyw_pnd_2</v>
       </c>
       <c r="B55" t="str">
         <v>配件</v>
       </c>
       <c r="C55" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D55" t="str">
-        <v>扭紋小環</v>
+        <v>白水魚尾</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G55" t="str">
-        <v>扭纹小环.png</v>
+        <v>白水鱼尾.png</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>xxjz_pnd_2</v>
+        <v>zyb_spc_8</v>
       </c>
       <c r="B56" t="str">
         <v>配件</v>
       </c>
       <c r="C56" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D56" t="str">
-        <v>星星獎章</v>
+        <v>轉運柄</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F56">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G56" t="str">
-        <v>星星奖章.png</v>
+        <v>转运柄.png</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>fyh_spc_6</v>
+        <v>emzy_spc_6</v>
       </c>
       <c r="B57" t="str">
         <v>配件</v>
@@ -1698,7 +1698,7 @@
         <v>隔珠</v>
       </c>
       <c r="D57" t="str">
-        <v>粉櫻花</v>
+        <v>惡魔之眼</v>
       </c>
       <c r="E57">
         <v>6</v>
@@ -1707,81 +1707,81 @@
         <v>59</v>
       </c>
       <c r="G57" t="str">
-        <v>粉樱花.png</v>
+        <v>恶魔之眼.png</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>gshxz_spc_6</v>
+        <v>lwmn_agt_6</v>
       </c>
       <c r="B58" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C58" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D58" t="str">
-        <v>鋯石花形鑽</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E58">
         <v>6</v>
       </c>
       <c r="F58">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G58" t="str">
-        <v>锆石花形钻.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>gsqg_spc_5</v>
+        <v>lwmn_agt_8</v>
       </c>
       <c r="B59" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C59" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D59" t="str">
-        <v>鋯石切割</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F59">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G59" t="str">
-        <v>锆石切割.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>hsj_cysl_6</v>
+        <v>lwmn_agt_10</v>
       </c>
       <c r="B60" t="str">
         <v>珠子</v>
       </c>
       <c r="C60" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D60" t="str">
-        <v>黃水晶</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E60">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F60">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="G60" t="str">
-        <v>黄水晶.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>hsj_cysl_8</v>
+        <v>xyc_cysl_8</v>
       </c>
       <c r="B61" t="str">
         <v>珠子</v>
@@ -1790,7 +1790,7 @@
         <v>水晶</v>
       </c>
       <c r="D61" t="str">
-        <v>黃水晶</v>
+        <v>薰衣草</v>
       </c>
       <c r="E61">
         <v>8</v>
@@ -1799,12 +1799,12 @@
         <v>69</v>
       </c>
       <c r="G61" t="str">
-        <v>黄水晶.png</v>
+        <v>薰衣草.png</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>hsj_cysl_10</v>
+        <v>xyc_cysl_10</v>
       </c>
       <c r="B62" t="str">
         <v>珠子</v>
@@ -1813,21 +1813,21 @@
         <v>水晶</v>
       </c>
       <c r="D62" t="str">
-        <v>黃水晶</v>
+        <v>薰衣草</v>
       </c>
       <c r="E62">
         <v>10</v>
       </c>
       <c r="F62">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="G62" t="str">
-        <v>黄水晶.png</v>
+        <v>薰衣草.png</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>jzj_spc_6</v>
+        <v>nwxh_spc_5</v>
       </c>
       <c r="B63" t="str">
         <v>配件</v>
@@ -1836,21 +1836,21 @@
         <v>隔珠</v>
       </c>
       <c r="D63" t="str">
-        <v>交織戒</v>
+        <v>扭紋小環</v>
       </c>
       <c r="E63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F63">
         <v>59</v>
       </c>
       <c r="G63" t="str">
-        <v>交织戒.png</v>
+        <v>扭纹小环.png</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>gscx_pnd_2</v>
+        <v>xxjz_pnd_2</v>
       </c>
       <c r="B64" t="str">
         <v>配件</v>
@@ -1859,7 +1859,7 @@
         <v>吊墜</v>
       </c>
       <c r="D64" t="str">
-        <v>鋯石晨星</v>
+        <v>星星獎章</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -1868,35 +1868,35 @@
         <v>99</v>
       </c>
       <c r="G64" t="str">
-        <v>锆石晨星.png</v>
+        <v>星星奖章.png</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>tg4_sz_7</v>
+        <v>fyh_spc_6</v>
       </c>
       <c r="B65" t="str">
         <v>配件</v>
       </c>
       <c r="C65" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D65" t="str">
-        <v>鈦鋼4</v>
+        <v>粉櫻花</v>
       </c>
       <c r="E65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F65">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G65" t="str">
-        <v>钛钢4.png</v>
+        <v>粉樱花.png</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>cyszj_spc_8</v>
+        <v>gshxz_spc_6</v>
       </c>
       <c r="B66" t="str">
         <v>配件</v>
@@ -1905,21 +1905,21 @@
         <v>隔珠</v>
       </c>
       <c r="D66" t="str">
-        <v>藏銀十字架</v>
+        <v>鋯石花形鑽</v>
       </c>
       <c r="E66">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F66">
         <v>59</v>
       </c>
       <c r="G66" t="str">
-        <v>藏银十字架.png</v>
+        <v>锆石花形钻.png</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>gsqgsc_spc_6</v>
+        <v>gsqg_spc_5</v>
       </c>
       <c r="B67" t="str">
         <v>配件</v>
@@ -1928,435 +1928,435 @@
         <v>隔珠</v>
       </c>
       <c r="D67" t="str">
-        <v>鋯石切割雙層</v>
+        <v>鋯石切割</v>
       </c>
       <c r="E67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F67">
         <v>59</v>
       </c>
       <c r="G67" t="str">
-        <v>锆石切割双层.png</v>
+        <v>锆石切割.png</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ysxh_spc_5</v>
+        <v>hsj_cysl_6</v>
       </c>
       <c r="B68" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C68" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D68" t="str">
-        <v>銀色小環</v>
+        <v>黃水晶</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F68">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G68" t="str">
-        <v>银色小环.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>tg9_sz_7</v>
+        <v>hsj_cysl_8</v>
       </c>
       <c r="B69" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C69" t="str">
-        <v>數字</v>
+        <v>水晶</v>
       </c>
       <c r="D69" t="str">
-        <v>鈦鋼9</v>
+        <v>黃水晶</v>
       </c>
       <c r="E69">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F69">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G69" t="str">
-        <v>钛钢9.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>hm_agt_6</v>
+        <v>hsj_cysl_10</v>
       </c>
       <c r="B70" t="str">
         <v>珠子</v>
       </c>
       <c r="C70" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D70" t="str">
-        <v>黃瑪瑙</v>
+        <v>黃水晶</v>
       </c>
       <c r="E70">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F70">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G70" t="str">
-        <v>黄玛瑙.png</v>
+        <v>黄水晶.png</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>hm_agt_8</v>
+        <v>jzj_spc_6</v>
       </c>
       <c r="B71" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C71" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D71" t="str">
-        <v>黃瑪瑙</v>
+        <v>交織戒</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F71">
         <v>59</v>
       </c>
       <c r="G71" t="str">
-        <v>黄玛瑙.png</v>
+        <v>交织戒.png</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>hm_agt_10</v>
+        <v>gscx_pnd_2</v>
       </c>
       <c r="B72" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C72" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D72" t="str">
-        <v>黃瑪瑙</v>
+        <v>鋯石晨星</v>
       </c>
       <c r="E72">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G72" t="str">
-        <v>黄玛瑙.png</v>
+        <v>锆石晨星.png</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ml_stn_6</v>
+        <v>tg4_sz_7</v>
       </c>
       <c r="B73" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C73" t="str">
-        <v>礦石</v>
+        <v>數字</v>
       </c>
       <c r="D73" t="str">
-        <v>蜜蠟</v>
+        <v>鈦鋼4</v>
       </c>
       <c r="E73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G73" t="str">
-        <v>蜜蜡.png</v>
+        <v>钛钢4.png</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>ml_stn_8</v>
+        <v>cyszj_spc_8</v>
       </c>
       <c r="B74" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C74" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D74" t="str">
-        <v>蜜蠟</v>
+        <v>藏銀十字架</v>
       </c>
       <c r="E74">
         <v>8</v>
       </c>
       <c r="F74">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G74" t="str">
-        <v>蜜蜡.png</v>
+        <v>藏银十字架.png</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>ysr_zm_4</v>
+        <v>gsqgsc_spc_6</v>
       </c>
       <c r="B75" t="str">
         <v>配件</v>
       </c>
       <c r="C75" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D75" t="str">
-        <v>銀飾R</v>
+        <v>鋯石切割雙層</v>
       </c>
       <c r="E75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F75">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G75" t="str">
-        <v>银饰R.png</v>
+        <v>锆石切割双层.png</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>mzhd_pnd_2</v>
+        <v>ysxh_spc_5</v>
       </c>
       <c r="B76" t="str">
         <v>配件</v>
       </c>
       <c r="C76" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D76" t="str">
-        <v>滿鑽蝴蝶</v>
+        <v>銀色小環</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F76">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G76" t="str">
-        <v>满钻蝴蝶.png</v>
+        <v>银色小环.png</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>jd_pnd_2</v>
+        <v>tg9_sz_7</v>
       </c>
       <c r="B77" t="str">
         <v>配件</v>
       </c>
       <c r="C77" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D77" t="str">
-        <v>晶蝶</v>
+        <v>鈦鋼9</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F77">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G77" t="str">
-        <v>晶蝶.png</v>
+        <v>钛钢9.png</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>lkjls_spc_6</v>
+        <v>hm_agt_6</v>
       </c>
       <c r="B78" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C78" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D78" t="str">
-        <v>鏤空金蕾絲</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E78">
         <v>6</v>
       </c>
       <c r="F78">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G78" t="str">
-        <v>镂空金蕾丝.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>tg7_sz_7</v>
+        <v>hm_agt_8</v>
       </c>
       <c r="B79" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C79" t="str">
-        <v>數字</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D79" t="str">
-        <v>鈦鋼7</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F79">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G79" t="str">
-        <v>钛钢7.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>gymj_xz_2</v>
+        <v>hm_agt_10</v>
       </c>
       <c r="B80" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C80" t="str">
-        <v>星座</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D80" t="str">
-        <v>古銀摩羯</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F80">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G80" t="str">
-        <v>古银摩羯.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>tg0_sz_7</v>
+        <v>ml_stn_6</v>
       </c>
       <c r="B81" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C81" t="str">
-        <v>數字</v>
+        <v>礦石</v>
       </c>
       <c r="D81" t="str">
-        <v>鈦鋼0</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F81">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G81" t="str">
-        <v>钛钢0.png</v>
+        <v>蜜蜡.png</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>jf_pnd_2</v>
+        <v>ml_stn_8</v>
       </c>
       <c r="B82" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C82" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D82" t="str">
-        <v>金福</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F82">
         <v>99</v>
       </c>
       <c r="G82" t="str">
-        <v>金福.png</v>
+        <v>蜜蜡.png</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>fgdh_spc_8</v>
+        <v>ysr_zm_4</v>
       </c>
       <c r="B83" t="str">
         <v>配件</v>
       </c>
       <c r="C83" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D83" t="str">
-        <v>復古雕花</v>
+        <v>銀飾R</v>
       </c>
       <c r="E83">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F83">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G83" t="str">
-        <v>复古雕花.png</v>
+        <v>银饰R.png</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ysj_zm_4</v>
+        <v>mzhd_pnd_2</v>
       </c>
       <c r="B84" t="str">
         <v>配件</v>
       </c>
       <c r="C84" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D84" t="str">
-        <v>銀飾J</v>
+        <v>滿鑽蝴蝶</v>
       </c>
       <c r="E84">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="G84" t="str">
-        <v>银饰J.png</v>
+        <v>满钻蝴蝶.png</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>tg6_sz_7</v>
+        <v>jd_pnd_2</v>
       </c>
       <c r="B85" t="str">
         <v>配件</v>
       </c>
       <c r="C85" t="str">
-        <v>數字</v>
+        <v>吊墜</v>
       </c>
       <c r="D85" t="str">
-        <v>鈦鋼6</v>
+        <v>晶蝶</v>
       </c>
       <c r="E85">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F85">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G85" t="str">
-        <v>钛钢6.png</v>
+        <v>晶蝶.png</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>xxy_spc_5</v>
+        <v>lkjls_spc_6</v>
       </c>
       <c r="B86" t="str">
         <v>配件</v>
@@ -2365,182 +2365,182 @@
         <v>隔珠</v>
       </c>
       <c r="D86" t="str">
-        <v>小祥雲</v>
+        <v>鏤空金蕾絲</v>
       </c>
       <c r="E86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F86">
         <v>59</v>
       </c>
       <c r="G86" t="str">
-        <v>小祥云.png</v>
+        <v>镂空金蕾丝.png</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>dxy_spc_5</v>
+        <v>tg7_sz_7</v>
       </c>
       <c r="B87" t="str">
         <v>配件</v>
       </c>
       <c r="C87" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D87" t="str">
-        <v>大祥雲</v>
+        <v>鈦鋼7</v>
       </c>
       <c r="E87">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F87">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G87" t="str">
-        <v>大祥云.png</v>
+        <v>钛钢7.png</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>lfj_cysl_8</v>
+        <v>jpts_stn_8</v>
       </c>
       <c r="B88" t="str">
         <v>珠子</v>
       </c>
       <c r="C88" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D88" t="str">
-        <v>綠髮晶</v>
+        <v>金葡萄石</v>
       </c>
       <c r="E88">
         <v>8</v>
       </c>
       <c r="F88">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G88" t="str">
-        <v>绿发晶.png</v>
+        <v>金葡萄石.png</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>lfj_cysl_10</v>
+        <v>gymj_xz_2</v>
       </c>
       <c r="B89" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C89" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D89" t="str">
-        <v>綠髮晶</v>
+        <v>古銀摩羯</v>
       </c>
       <c r="E89">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F89">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="G89" t="str">
-        <v>绿发晶.png</v>
+        <v>古银摩羯.png</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ysi_zm_4</v>
+        <v>tg0_sz_7</v>
       </c>
       <c r="B90" t="str">
         <v>配件</v>
       </c>
       <c r="C90" t="str">
-        <v>字母</v>
+        <v>數字</v>
       </c>
       <c r="D90" t="str">
-        <v>銀飾I</v>
+        <v>鈦鋼0</v>
       </c>
       <c r="E90">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F90">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G90" t="str">
-        <v>银饰I.png</v>
+        <v>钛钢0.png</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ysu_zm_4</v>
+        <v>jf_pnd_2</v>
       </c>
       <c r="B91" t="str">
         <v>配件</v>
       </c>
       <c r="C91" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D91" t="str">
-        <v>銀飾U</v>
+        <v>金福</v>
       </c>
       <c r="E91">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F91">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="G91" t="str">
-        <v>银饰U.png</v>
+        <v>金福.png</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>tg1_sz_7</v>
+        <v>fgdh_spc_8</v>
       </c>
       <c r="B92" t="str">
         <v>配件</v>
       </c>
       <c r="C92" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D92" t="str">
-        <v>鈦鋼1</v>
+        <v>復古雕花</v>
       </c>
       <c r="E92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F92">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G92" t="str">
-        <v>钛钢1.png</v>
+        <v>复古雕花.png</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>tg3_sz_7</v>
+        <v>ysj_zm_4</v>
       </c>
       <c r="B93" t="str">
         <v>配件</v>
       </c>
       <c r="C93" t="str">
-        <v>數字</v>
+        <v>字母</v>
       </c>
       <c r="D93" t="str">
-        <v>鈦鋼3</v>
+        <v>銀飾J</v>
       </c>
       <c r="E93">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F93">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G93" t="str">
-        <v>钛钢3.png</v>
+        <v>银饰J.png</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>tg2_sz_7</v>
+        <v>tg6_sz_7</v>
       </c>
       <c r="B94" t="str">
         <v>配件</v>
@@ -2549,7 +2549,7 @@
         <v>數字</v>
       </c>
       <c r="D94" t="str">
-        <v>鈦鋼2</v>
+        <v>鈦鋼6</v>
       </c>
       <c r="E94">
         <v>7</v>
@@ -2558,81 +2558,81 @@
         <v>39</v>
       </c>
       <c r="G94" t="str">
-        <v>钛钢2.png</v>
+        <v>钛钢6.png</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>tg8_sz_7</v>
+        <v>xxy_spc_5</v>
       </c>
       <c r="B95" t="str">
         <v>配件</v>
       </c>
       <c r="C95" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D95" t="str">
-        <v>鈦鋼8</v>
+        <v>小祥雲</v>
       </c>
       <c r="E95">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F95">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G95" t="str">
-        <v>钛钢8.png</v>
+        <v>小祥云.png</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>tg5_sz_7</v>
+        <v>dxy_spc_5</v>
       </c>
       <c r="B96" t="str">
         <v>配件</v>
       </c>
       <c r="C96" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D96" t="str">
-        <v>鈦鋼5</v>
+        <v>大祥雲</v>
       </c>
       <c r="E96">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F96">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G96" t="str">
-        <v>钛钢5.png</v>
+        <v>大祥云.png</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>gycn_xz_2</v>
+        <v>ysi_zm_4</v>
       </c>
       <c r="B97" t="str">
         <v>配件</v>
       </c>
       <c r="C97" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D97" t="str">
-        <v>古銀處女</v>
+        <v>銀飾I</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F97">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G97" t="str">
-        <v>古银处女.png</v>
+        <v>银饰I.png</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ysp_zm_4</v>
+        <v>ysu_zm_4</v>
       </c>
       <c r="B98" t="str">
         <v>配件</v>
@@ -2641,7 +2641,7 @@
         <v>字母</v>
       </c>
       <c r="D98" t="str">
-        <v>銀飾P</v>
+        <v>銀飾U</v>
       </c>
       <c r="E98">
         <v>4</v>
@@ -2650,104 +2650,104 @@
         <v>399</v>
       </c>
       <c r="G98" t="str">
-        <v>银饰P.png</v>
+        <v>银饰U.png</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>gsmm_spc_8</v>
+        <v>tg3_sz_7</v>
       </c>
       <c r="B99" t="str">
         <v>配件</v>
       </c>
       <c r="C99" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D99" t="str">
-        <v>鋯石貓咪</v>
+        <v>鈦鋼3</v>
       </c>
       <c r="E99">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F99">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G99" t="str">
-        <v>锆石猫咪.png</v>
+        <v>钛钢3.png</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>gyby_xz_2</v>
+        <v>tg2_sz_7</v>
       </c>
       <c r="B100" t="str">
         <v>配件</v>
       </c>
       <c r="C100" t="str">
-        <v>星座</v>
+        <v>數字</v>
       </c>
       <c r="D100" t="str">
-        <v>古銀白羊</v>
+        <v>鈦鋼2</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F100">
         <v>39</v>
       </c>
       <c r="G100" t="str">
-        <v>古银白羊.png</v>
+        <v>钛钢2.png</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>ysc_zm_4</v>
+        <v>tg8_sz_7</v>
       </c>
       <c r="B101" t="str">
         <v>配件</v>
       </c>
       <c r="C101" t="str">
-        <v>字母</v>
+        <v>數字</v>
       </c>
       <c r="D101" t="str">
-        <v>銀飾C</v>
+        <v>鈦鋼8</v>
       </c>
       <c r="E101">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F101">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G101" t="str">
-        <v>银饰C.png</v>
+        <v>钛钢8.png</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ysb_zm_4</v>
+        <v>tg5_sz_7</v>
       </c>
       <c r="B102" t="str">
         <v>配件</v>
       </c>
       <c r="C102" t="str">
-        <v>字母</v>
+        <v>數字</v>
       </c>
       <c r="D102" t="str">
-        <v>銀飾B</v>
+        <v>鈦鋼5</v>
       </c>
       <c r="E102">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F102">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G102" t="str">
-        <v>银饰B.png</v>
+        <v>钛钢5.png</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>gysp_xz_2</v>
+        <v>gycn_xz_2</v>
       </c>
       <c r="B103" t="str">
         <v>配件</v>
@@ -2756,7 +2756,7 @@
         <v>星座</v>
       </c>
       <c r="D103" t="str">
-        <v>古銀水瓶</v>
+        <v>古銀處女</v>
       </c>
       <c r="E103">
         <v>2</v>
@@ -2765,12 +2765,12 @@
         <v>39</v>
       </c>
       <c r="G103" t="str">
-        <v>古银水瓶.png</v>
+        <v>古银处女.png</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>yso_zm_4</v>
+        <v>ysp_zm_4</v>
       </c>
       <c r="B104" t="str">
         <v>配件</v>
@@ -2779,7 +2779,7 @@
         <v>字母</v>
       </c>
       <c r="D104" t="str">
-        <v>銀飾O</v>
+        <v>銀飾P</v>
       </c>
       <c r="E104">
         <v>4</v>
@@ -2788,104 +2788,104 @@
         <v>399</v>
       </c>
       <c r="G104" t="str">
-        <v>银饰O.png</v>
+        <v>银饰P.png</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ysw_zm_4</v>
+        <v>gsmm_spc_8</v>
       </c>
       <c r="B105" t="str">
         <v>配件</v>
       </c>
       <c r="C105" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D105" t="str">
-        <v>銀飾W</v>
+        <v>鋯石貓咪</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F105">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G105" t="str">
-        <v>银饰W.png</v>
+        <v>锆石猫咪.png</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>wljz_spc_5</v>
+        <v>gyby_xz_2</v>
       </c>
       <c r="B106" t="str">
         <v>配件</v>
       </c>
       <c r="C106" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D106" t="str">
-        <v>五稜金鑽</v>
+        <v>古銀白羊</v>
       </c>
       <c r="E106">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F106">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G106" t="str">
-        <v>五棱金钻.png</v>
+        <v>古银白羊.png</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>zyd_pnd_2</v>
+        <v>lfj_cysl_8</v>
       </c>
       <c r="B107" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C107" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D107" t="str">
-        <v>珠遇蝶</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E107">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F107">
         <v>99</v>
       </c>
       <c r="G107" t="str">
-        <v>珠遇蝶.png</v>
+        <v>绿发晶.png</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>xfp_pnd_2</v>
+        <v>lfj_cysl_10</v>
       </c>
       <c r="B108" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C108" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D108" t="str">
-        <v>小福牌</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E108">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F108">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="G108" t="str">
-        <v>小福牌.png</v>
+        <v>绿发晶.png</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ysq_zm_4</v>
+        <v>ysc_zm_4</v>
       </c>
       <c r="B109" t="str">
         <v>配件</v>
@@ -2894,7 +2894,7 @@
         <v>字母</v>
       </c>
       <c r="D109" t="str">
-        <v>銀飾Q</v>
+        <v>銀飾C</v>
       </c>
       <c r="E109">
         <v>4</v>
@@ -2903,173 +2903,173 @@
         <v>399</v>
       </c>
       <c r="G109" t="str">
-        <v>银饰Q.png</v>
+        <v>银饰C.png</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>gyjx_xz_2</v>
+        <v>ysb_zm_4</v>
       </c>
       <c r="B110" t="str">
         <v>配件</v>
       </c>
       <c r="C110" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D110" t="str">
-        <v>古銀巨蟹</v>
+        <v>銀飾B</v>
       </c>
       <c r="E110">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F110">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G110" t="str">
-        <v>古银巨蟹.png</v>
+        <v>银饰B.png</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ysf_zm_4</v>
+        <v>gysp_xz_2</v>
       </c>
       <c r="B111" t="str">
         <v>配件</v>
       </c>
       <c r="C111" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D111" t="str">
-        <v>銀飾F</v>
+        <v>古銀水瓶</v>
       </c>
       <c r="E111">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F111">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G111" t="str">
-        <v>银饰F.png</v>
+        <v>古银水瓶.png</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>gyss_xz_2</v>
+        <v>yso_zm_4</v>
       </c>
       <c r="B112" t="str">
         <v>配件</v>
       </c>
       <c r="C112" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D112" t="str">
-        <v>古銀射手</v>
+        <v>銀飾O</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F112">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G112" t="str">
-        <v>古银射手.png</v>
+        <v>银饰O.png</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>hlcs_pnd_2</v>
+        <v>ysw_zm_4</v>
       </c>
       <c r="B113" t="str">
         <v>配件</v>
       </c>
       <c r="C113" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D113" t="str">
-        <v>葫蘆成雙</v>
+        <v>銀飾W</v>
       </c>
       <c r="E113">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F113">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G113" t="str">
-        <v>葫芦成双.png</v>
+        <v>银饰W.png</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>gyszz_xz_2</v>
+        <v>wljz_spc_5</v>
       </c>
       <c r="B114" t="str">
         <v>配件</v>
       </c>
       <c r="C114" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D114" t="str">
-        <v>古銀雙子</v>
+        <v>五稜金鑽</v>
       </c>
       <c r="E114">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F114">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G114" t="str">
-        <v>古银双子.png</v>
+        <v>五棱金钻.png</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ysn_zm_4</v>
+        <v>zyd_pnd_2</v>
       </c>
       <c r="B115" t="str">
         <v>配件</v>
       </c>
       <c r="C115" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D115" t="str">
-        <v>銀飾N</v>
+        <v>珠遇蝶</v>
       </c>
       <c r="E115">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F115">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="G115" t="str">
-        <v>银饰N.png</v>
+        <v>珠遇蝶.png</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ysm_zm_4</v>
+        <v>xfp_pnd_2</v>
       </c>
       <c r="B116" t="str">
         <v>配件</v>
       </c>
       <c r="C116" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D116" t="str">
-        <v>銀飾M</v>
+        <v>小福牌</v>
       </c>
       <c r="E116">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F116">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="G116" t="str">
-        <v>银饰M.png</v>
+        <v>小福牌.png</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ysh_zm_4</v>
+        <v>ysq_zm_4</v>
       </c>
       <c r="B117" t="str">
         <v>配件</v>
@@ -3078,7 +3078,7 @@
         <v>字母</v>
       </c>
       <c r="D117" t="str">
-        <v>銀飾H</v>
+        <v>銀飾Q</v>
       </c>
       <c r="E117">
         <v>4</v>
@@ -3087,150 +3087,150 @@
         <v>399</v>
       </c>
       <c r="G117" t="str">
-        <v>银饰H.png</v>
+        <v>银饰Q.png</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>gytx_xz_2</v>
+        <v>ymys_stn_10</v>
       </c>
       <c r="B118" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C118" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D118" t="str">
-        <v>古銀天蠍</v>
+        <v>羽毛螢石</v>
       </c>
       <c r="E118">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F118">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="G118" t="str">
-        <v>古银天蝎.png</v>
+        <v>羽毛萤石.png</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ysg_zm_4</v>
+        <v>gyjx_xz_2</v>
       </c>
       <c r="B119" t="str">
         <v>配件</v>
       </c>
       <c r="C119" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D119" t="str">
-        <v>銀飾G</v>
+        <v>古銀巨蟹</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F119">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G119" t="str">
-        <v>银饰G.png</v>
+        <v>古银巨蟹.png</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>gytc_xz_2</v>
+        <v>ysf_zm_4</v>
       </c>
       <c r="B120" t="str">
         <v>配件</v>
       </c>
       <c r="C120" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D120" t="str">
-        <v>古銀天秤</v>
+        <v>銀飾F</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F120">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G120" t="str">
-        <v>古银天秤.png</v>
+        <v>银饰F.png</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>yst_zm_4</v>
+        <v>gyss_xz_2</v>
       </c>
       <c r="B121" t="str">
         <v>配件</v>
       </c>
       <c r="C121" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D121" t="str">
-        <v>銀飾T</v>
+        <v>古銀射手</v>
       </c>
       <c r="E121">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F121">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G121" t="str">
-        <v>银饰T.png</v>
+        <v>古银射手.png</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>gslx_spc_6</v>
+        <v>hlcs_pnd_2</v>
       </c>
       <c r="B122" t="str">
         <v>配件</v>
       </c>
       <c r="C122" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D122" t="str">
-        <v>鋯石螺旋</v>
+        <v>葫蘆成雙</v>
       </c>
       <c r="E122">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F122">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G122" t="str">
-        <v>锆石螺旋.png</v>
+        <v>葫芦成双.png</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>yse_zm_4</v>
+        <v>gyszz_xz_2</v>
       </c>
       <c r="B123" t="str">
         <v>配件</v>
       </c>
       <c r="C123" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D123" t="str">
-        <v>銀飾E</v>
+        <v>古銀雙子</v>
       </c>
       <c r="E123">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F123">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G123" t="str">
-        <v>银饰E.png</v>
+        <v>古银双子.png</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ysk_zm_4</v>
+        <v>ysn_zm_4</v>
       </c>
       <c r="B124" t="str">
         <v>配件</v>
@@ -3239,7 +3239,7 @@
         <v>字母</v>
       </c>
       <c r="D124" t="str">
-        <v>銀飾K</v>
+        <v>銀飾N</v>
       </c>
       <c r="E124">
         <v>4</v>
@@ -3248,35 +3248,35 @@
         <v>399</v>
       </c>
       <c r="G124" t="str">
-        <v>银饰K.png</v>
+        <v>银饰N.png</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>syyl_pnd_2</v>
+        <v>ysm_zm_4</v>
       </c>
       <c r="B125" t="str">
         <v>配件</v>
       </c>
       <c r="C125" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D125" t="str">
-        <v>閃躍月亮</v>
+        <v>銀飾M</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F125">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G125" t="str">
-        <v>闪跃月亮.png</v>
+        <v>银饰M.png</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ysv_zm_4</v>
+        <v>ysh_zm_4</v>
       </c>
       <c r="B126" t="str">
         <v>配件</v>
@@ -3285,7 +3285,7 @@
         <v>字母</v>
       </c>
       <c r="D126" t="str">
-        <v>銀飾V</v>
+        <v>銀飾H</v>
       </c>
       <c r="E126">
         <v>4</v>
@@ -3294,35 +3294,35 @@
         <v>399</v>
       </c>
       <c r="G126" t="str">
-        <v>银饰V.png</v>
+        <v>银饰H.png</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>gszs_spc_5</v>
+        <v>gytx_xz_2</v>
       </c>
       <c r="B127" t="str">
         <v>配件</v>
       </c>
       <c r="C127" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D127" t="str">
-        <v>鋯石鑽閃</v>
+        <v>古銀天蠍</v>
       </c>
       <c r="E127">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F127">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G127" t="str">
-        <v>锆石钻闪.png</v>
+        <v>古银天蝎.png</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ysl_zm_4</v>
+        <v>ysg_zm_4</v>
       </c>
       <c r="B128" t="str">
         <v>配件</v>
@@ -3331,7 +3331,7 @@
         <v>字母</v>
       </c>
       <c r="D128" t="str">
-        <v>銀飾L</v>
+        <v>銀飾G</v>
       </c>
       <c r="E128">
         <v>4</v>
@@ -3340,35 +3340,35 @@
         <v>399</v>
       </c>
       <c r="G128" t="str">
-        <v>银饰L.png</v>
+        <v>银饰G.png</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>xns_pnd_2</v>
+        <v>gytc_xz_2</v>
       </c>
       <c r="B129" t="str">
         <v>配件</v>
       </c>
       <c r="C129" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D129" t="str">
-        <v>小年獸</v>
+        <v>古銀天秤</v>
       </c>
       <c r="E129">
         <v>2</v>
       </c>
       <c r="F129">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G129" t="str">
-        <v>小年兽.png</v>
+        <v>古银天秤.png</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>ysa_zm_4</v>
+        <v>yst_zm_4</v>
       </c>
       <c r="B130" t="str">
         <v>配件</v>
@@ -3377,7 +3377,7 @@
         <v>字母</v>
       </c>
       <c r="D130" t="str">
-        <v>銀飾A</v>
+        <v>銀飾T</v>
       </c>
       <c r="E130">
         <v>4</v>
@@ -3386,35 +3386,35 @@
         <v>399</v>
       </c>
       <c r="G130" t="str">
-        <v>银饰A.png</v>
+        <v>银饰T.png</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>gyjn_xz_2</v>
+        <v>gslx_spc_6</v>
       </c>
       <c r="B131" t="str">
         <v>配件</v>
       </c>
       <c r="C131" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D131" t="str">
-        <v>古銀金牛</v>
+        <v>鋯石螺旋</v>
       </c>
       <c r="E131">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F131">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G131" t="str">
-        <v>古银金牛.png</v>
+        <v>锆石螺旋.png</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>ysy_zm_4</v>
+        <v>yse_zm_4</v>
       </c>
       <c r="B132" t="str">
         <v>配件</v>
@@ -3423,7 +3423,7 @@
         <v>字母</v>
       </c>
       <c r="D132" t="str">
-        <v>銀飾Y</v>
+        <v>銀飾E</v>
       </c>
       <c r="E132">
         <v>4</v>
@@ -3432,81 +3432,81 @@
         <v>399</v>
       </c>
       <c r="G132" t="str">
-        <v>银饰Y.png</v>
+        <v>银饰E.png</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>jsxh_spc_5</v>
+        <v>ysk_zm_4</v>
       </c>
       <c r="B133" t="str">
         <v>配件</v>
       </c>
       <c r="C133" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D133" t="str">
-        <v>金色小環</v>
+        <v>銀飾K</v>
       </c>
       <c r="E133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F133">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G133" t="str">
-        <v>金色小环.png</v>
+        <v>银饰K.png</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>gyshz_xz_2</v>
+        <v>syyl_pnd_2</v>
       </c>
       <c r="B134" t="str">
         <v>配件</v>
       </c>
       <c r="C134" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D134" t="str">
-        <v>古銀獅子</v>
+        <v>閃躍月亮</v>
       </c>
       <c r="E134">
         <v>2</v>
       </c>
       <c r="F134">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G134" t="str">
-        <v>古银狮子.png</v>
+        <v>闪跃月亮.png</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>bjx_pnd_2</v>
+        <v>ysv_zm_4</v>
       </c>
       <c r="B135" t="str">
         <v>配件</v>
       </c>
       <c r="C135" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D135" t="str">
-        <v>北極星</v>
+        <v>銀飾V</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F135">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G135" t="str">
-        <v>北极星.png</v>
+        <v>银饰V.png</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>cgl_spc_6</v>
+        <v>gszs_spc_5</v>
       </c>
       <c r="B136" t="str">
         <v>配件</v>
@@ -3515,21 +3515,21 @@
         <v>隔珠</v>
       </c>
       <c r="D136" t="str">
-        <v>彩鋯輪</v>
+        <v>鋯石鑽閃</v>
       </c>
       <c r="E136">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F136">
         <v>59</v>
       </c>
       <c r="G136" t="str">
-        <v>彩锆轮.png</v>
+        <v>锆石钻闪.png</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>ysx_zm_4</v>
+        <v>ysl_zm_4</v>
       </c>
       <c r="B137" t="str">
         <v>配件</v>
@@ -3538,7 +3538,7 @@
         <v>字母</v>
       </c>
       <c r="D137" t="str">
-        <v>銀飾X</v>
+        <v>銀飾L</v>
       </c>
       <c r="E137">
         <v>4</v>
@@ -3547,104 +3547,104 @@
         <v>399</v>
       </c>
       <c r="G137" t="str">
-        <v>银饰X.png</v>
+        <v>银饰L.png</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>hps_stn_6</v>
+        <v>xns_pnd_2</v>
       </c>
       <c r="B138" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C138" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D138" t="str">
-        <v>琥珀石</v>
+        <v>小年獸</v>
       </c>
       <c r="E138">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F138">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G138" t="str">
-        <v>琥珀石.png</v>
+        <v>小年兽.png</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>hps_stn_8</v>
+        <v>ysa_zm_4</v>
       </c>
       <c r="B139" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C139" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D139" t="str">
-        <v>琥珀石</v>
+        <v>銀飾A</v>
       </c>
       <c r="E139">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139">
-        <v>89</v>
+        <v>399</v>
       </c>
       <c r="G139" t="str">
-        <v>琥珀石.png</v>
+        <v>银饰A.png</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>hps_stn_10</v>
+        <v>gyjn_xz_2</v>
       </c>
       <c r="B140" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C140" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D140" t="str">
-        <v>琥珀石</v>
+        <v>古銀金牛</v>
       </c>
       <c r="E140">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F140">
-        <v>199</v>
+        <v>39</v>
       </c>
       <c r="G140" t="str">
-        <v>琥珀石.png</v>
+        <v>古银金牛.png</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>gysy_xz_2</v>
+        <v>ysy_zm_4</v>
       </c>
       <c r="B141" t="str">
         <v>配件</v>
       </c>
       <c r="C141" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D141" t="str">
-        <v>古銀雙魚</v>
+        <v>銀飾Y</v>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F141">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G141" t="str">
-        <v>古银双鱼.png</v>
+        <v>银饰Y.png</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>xs_spc_8</v>
+        <v>jsxh_spc_5</v>
       </c>
       <c r="B142" t="str">
         <v>配件</v>
@@ -3653,136 +3653,136 @@
         <v>隔珠</v>
       </c>
       <c r="D142" t="str">
-        <v>醒獅</v>
+        <v>金色小環</v>
       </c>
       <c r="E142">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F142">
         <v>59</v>
       </c>
       <c r="G142" t="str">
-        <v>醒狮.png</v>
+        <v>金色小环.png</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ysz_zm_4</v>
+        <v>gyshz_xz_2</v>
       </c>
       <c r="B143" t="str">
         <v>配件</v>
       </c>
       <c r="C143" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D143" t="str">
-        <v>銀飾Z</v>
+        <v>古銀獅子</v>
       </c>
       <c r="E143">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F143">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G143" t="str">
-        <v>银饰Z.png</v>
+        <v>古银狮子.png</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>ths_stn_6</v>
+        <v>bjx_pnd_2</v>
       </c>
       <c r="B144" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C144" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D144" t="str">
-        <v>天河石</v>
+        <v>北極星</v>
       </c>
       <c r="E144">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F144">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G144" t="str">
-        <v>天河石.png</v>
+        <v>北极星.png</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ths_stn_8</v>
+        <v>cgl_spc_6</v>
       </c>
       <c r="B145" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C145" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D145" t="str">
-        <v>天河石</v>
+        <v>彩鋯輪</v>
       </c>
       <c r="E145">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F145">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G145" t="str">
-        <v>天河石.png</v>
+        <v>彩锆轮.png</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ths_stn_10</v>
+        <v>ysx_zm_4</v>
       </c>
       <c r="B146" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C146" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D146" t="str">
-        <v>天河石</v>
+        <v>銀飾X</v>
       </c>
       <c r="E146">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F146">
-        <v>139</v>
+        <v>399</v>
       </c>
       <c r="G146" t="str">
-        <v>天河石.png</v>
+        <v>银饰X.png</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>ysd_zm_4</v>
+        <v>hps_stn_6</v>
       </c>
       <c r="B147" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C147" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D147" t="str">
-        <v>銀飾D</v>
+        <v>琥珀石</v>
       </c>
       <c r="E147">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F147">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G147" t="str">
-        <v>银饰D.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>hlb_stn_6</v>
+        <v>hps_stn_8</v>
       </c>
       <c r="B148" t="str">
         <v>珠子</v>
@@ -3791,21 +3791,21 @@
         <v>礦石</v>
       </c>
       <c r="D148" t="str">
-        <v>海藍寶</v>
+        <v>琥珀石</v>
       </c>
       <c r="E148">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F148">
         <v>89</v>
       </c>
       <c r="G148" t="str">
-        <v>海蓝宝.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>hlb_stn_8</v>
+        <v>hps_stn_10</v>
       </c>
       <c r="B149" t="str">
         <v>珠子</v>
@@ -3814,320 +3814,320 @@
         <v>礦石</v>
       </c>
       <c r="D149" t="str">
-        <v>海藍寶</v>
+        <v>琥珀石</v>
       </c>
       <c r="E149">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F149">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="G149" t="str">
-        <v>海蓝宝.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>hlb_stn_10</v>
+        <v>gysy_xz_2</v>
       </c>
       <c r="B150" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C150" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D150" t="str">
-        <v>海藍寶</v>
+        <v>古銀雙魚</v>
       </c>
       <c r="E150">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F150">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="G150" t="str">
-        <v>海蓝宝.png</v>
+        <v>古银双鱼.png</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>yss_zm_4</v>
+        <v>xs_spc_8</v>
       </c>
       <c r="B151" t="str">
         <v>配件</v>
       </c>
       <c r="C151" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D151" t="str">
-        <v>銀飾S</v>
+        <v>醒獅</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F151">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G151" t="str">
-        <v>银饰S.png</v>
+        <v>醒狮.png</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>gsch_pnd_2</v>
+        <v>ysz_zm_4</v>
       </c>
       <c r="B152" t="str">
         <v>配件</v>
       </c>
       <c r="C152" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D152" t="str">
-        <v>鋯石彩虹</v>
+        <v>銀飾Z</v>
       </c>
       <c r="E152">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F152">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G152" t="str">
-        <v>锆石彩虹.png</v>
+        <v>银饰Z.png</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>xgszs_spc_5</v>
+        <v>ths_stn_6</v>
       </c>
       <c r="B153" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C153" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D153" t="str">
-        <v>小鋯石鑽閃</v>
+        <v>天河石</v>
       </c>
       <c r="E153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F153">
         <v>59</v>
       </c>
       <c r="G153" t="str">
-        <v>小锆石钻闪.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>hfj_cysl_6</v>
+        <v>ths_stn_8</v>
       </c>
       <c r="B154" t="str">
         <v>珠子</v>
       </c>
       <c r="C154" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D154" t="str">
-        <v>黑髮晶</v>
+        <v>天河石</v>
       </c>
       <c r="E154">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F154">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G154" t="str">
-        <v>黑发晶.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>hfj_cysl_8</v>
+        <v>ths_stn_10</v>
       </c>
       <c r="B155" t="str">
         <v>珠子</v>
       </c>
       <c r="C155" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D155" t="str">
-        <v>黑髮晶</v>
+        <v>天河石</v>
       </c>
       <c r="E155">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F155">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="G155" t="str">
-        <v>黑发晶.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>hfj_cysl_10</v>
+        <v>ysd_zm_4</v>
       </c>
       <c r="B156" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C156" t="str">
-        <v>水晶</v>
+        <v>字母</v>
       </c>
       <c r="D156" t="str">
-        <v>黑髮晶</v>
+        <v>銀飾D</v>
       </c>
       <c r="E156">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F156">
-        <v>169</v>
+        <v>399</v>
       </c>
       <c r="G156" t="str">
-        <v>黑发晶.png</v>
+        <v>银饰D.png</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>wyh_pnd_2</v>
+        <v>hlb_stn_6</v>
       </c>
       <c r="B157" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C157" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D157" t="str">
-        <v>午夜花</v>
+        <v>海藍寶</v>
       </c>
       <c r="E157">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F157">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G157" t="str">
-        <v>午夜花.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ysxz_spc_6</v>
+        <v>hlb_stn_8</v>
       </c>
       <c r="B158" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C158" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D158" t="str">
-        <v>銀色小珠</v>
+        <v>海藍寶</v>
       </c>
       <c r="E158">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F158">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G158" t="str">
-        <v>银色小珠.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>jsmxyl_pnd_2</v>
+        <v>hlb_stn_10</v>
       </c>
       <c r="B159" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C159" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D159" t="str">
-        <v>金色滿鑲月亮</v>
+        <v>海藍寶</v>
       </c>
       <c r="E159">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F159">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="G159" t="str">
-        <v>金色满镶月亮.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>hbgd_spc_6</v>
+        <v>yss_zm_4</v>
       </c>
       <c r="B160" t="str">
         <v>配件</v>
       </c>
       <c r="C160" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D160" t="str">
-        <v>花邊軌道</v>
+        <v>銀飾S</v>
       </c>
       <c r="E160">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F160">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G160" t="str">
-        <v>花边轨道.png</v>
+        <v>银饰S.png</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>lcmj_cysl_6</v>
+        <v>gsch_pnd_2</v>
       </c>
       <c r="B161" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C161" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D161" t="str">
-        <v>綠莓晶</v>
+        <v>鋯石彩虹</v>
       </c>
       <c r="E161">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F161">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G161" t="str">
-        <v>绿莓晶.png</v>
+        <v>锆石彩虹.png</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>lcmj_cysl_8</v>
+        <v>xgszs_spc_5</v>
       </c>
       <c r="B162" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C162" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D162" t="str">
-        <v>綠莓晶</v>
+        <v>小鋯石鑽閃</v>
       </c>
       <c r="E162">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F162">
         <v>59</v>
       </c>
       <c r="G162" t="str">
-        <v>绿莓晶.png</v>
+        <v>小锆石钻闪.png</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>lcmj_cysl_10</v>
+        <v>htj_cysl_6</v>
       </c>
       <c r="B163" t="str">
         <v>珠子</v>
@@ -4136,205 +4136,205 @@
         <v>水晶</v>
       </c>
       <c r="D163" t="str">
-        <v>綠莓晶</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E163">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F163">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="G163" t="str">
-        <v>绿莓晶.png</v>
+        <v>黄塔晶.png</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>hcw_spc_5</v>
+        <v>htj_cysl_8</v>
       </c>
       <c r="B164" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C164" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D164" t="str">
-        <v>回財紋</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E164">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F164">
         <v>59</v>
       </c>
       <c r="G164" t="str">
-        <v>回财纹.png</v>
+        <v>黄塔晶.png</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>cyjc_spc_6</v>
+        <v>htj_cysl_10</v>
       </c>
       <c r="B165" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C165" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D165" t="str">
-        <v>藏銀卷草</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E165">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F165">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G165" t="str">
-        <v>藏银卷草.png</v>
+        <v>黄塔晶.png</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>hx_spc_6</v>
+        <v>wyh_pnd_2</v>
       </c>
       <c r="B166" t="str">
         <v>配件</v>
       </c>
       <c r="C166" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D166" t="str">
-        <v>花旋</v>
+        <v>午夜花</v>
       </c>
       <c r="E166">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F166">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G166" t="str">
-        <v>花旋.png</v>
+        <v>午夜花.png</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>cyszh_spc_8</v>
+        <v>hfj_cysl_6</v>
       </c>
       <c r="B167" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C167" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D167" t="str">
-        <v>藏銀十字花</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E167">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F167">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G167" t="str">
-        <v>藏银十字花.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>cyym_pnd_2</v>
+        <v>hfj_cysl_8</v>
       </c>
       <c r="B168" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C168" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D168" t="str">
-        <v>藏銀羽毛</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E168">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F168">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G168" t="str">
-        <v>藏银羽毛.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>lys_stn_6</v>
+        <v>hfj_cysl_10</v>
       </c>
       <c r="B169" t="str">
         <v>珠子</v>
       </c>
       <c r="C169" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D169" t="str">
-        <v>綠螢石</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E169">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F169">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="G169" t="str">
-        <v>绿萤石.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>lys_stn_8</v>
+        <v>ysxz_spc_6</v>
       </c>
       <c r="B170" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C170" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D170" t="str">
-        <v>綠螢石</v>
+        <v>銀色小珠</v>
       </c>
       <c r="E170">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F170">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G170" t="str">
-        <v>绿萤石.png</v>
+        <v>银色小珠.png</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>cysy_spc_6</v>
+        <v>jhy_stn_6</v>
       </c>
       <c r="B171" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C171" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D171" t="str">
-        <v>藏銀樹葉</v>
+        <v>金虎眼</v>
       </c>
       <c r="E171">
         <v>6</v>
       </c>
       <c r="F171">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G171" t="str">
-        <v>藏银树叶.png</v>
+        <v>金虎眼.png</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>qws_stn_8</v>
+        <v>jhy_stn_8</v>
       </c>
       <c r="B172" t="str">
         <v>珠子</v>
@@ -4343,7 +4343,7 @@
         <v>礦石</v>
       </c>
       <c r="D172" t="str">
-        <v>薔薇石</v>
+        <v>金虎眼</v>
       </c>
       <c r="E172">
         <v>8</v>
@@ -4352,12 +4352,12 @@
         <v>69</v>
       </c>
       <c r="G172" t="str">
-        <v>蔷薇石.png</v>
+        <v>金虎眼.png</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>qws_stn_10</v>
+        <v>jhy_stn_10</v>
       </c>
       <c r="B173" t="str">
         <v>珠子</v>
@@ -4366,481 +4366,481 @@
         <v>礦石</v>
       </c>
       <c r="D173" t="str">
-        <v>薔薇石</v>
+        <v>金虎眼</v>
       </c>
       <c r="E173">
         <v>10</v>
       </c>
       <c r="F173">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G173" t="str">
-        <v>蔷薇石.png</v>
+        <v>金虎眼.png</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>jsxz_spc_6</v>
+        <v>jsmxyl_pnd_2</v>
       </c>
       <c r="B174" t="str">
         <v>配件</v>
       </c>
       <c r="C174" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D174" t="str">
-        <v>金色小珠</v>
+        <v>金色滿鑲月亮</v>
       </c>
       <c r="E174">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F174">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G174" t="str">
-        <v>金色小珠.png</v>
+        <v>金色满镶月亮.png</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gtsp_xz_2</v>
+        <v>hbgd_spc_6</v>
       </c>
       <c r="B175" t="str">
         <v>配件</v>
       </c>
       <c r="C175" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D175" t="str">
-        <v>古銅水瓶</v>
+        <v>花邊軌道</v>
       </c>
       <c r="E175">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F175">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G175" t="str">
-        <v>古铜水瓶.png</v>
+        <v>花边轨道.png</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>gtby_xz_2</v>
+        <v>lcmj_cysl_6</v>
       </c>
       <c r="B176" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C176" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D176" t="str">
-        <v>古銅白羊</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E176">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F176">
         <v>39</v>
       </c>
       <c r="G176" t="str">
-        <v>古铜白羊.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>gszssc_spc_6</v>
+        <v>lcmj_cysl_8</v>
       </c>
       <c r="B177" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C177" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D177" t="str">
-        <v>鋯石鑽閃雙層</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E177">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F177">
         <v>59</v>
       </c>
       <c r="G177" t="str">
-        <v>锆石钻闪双层.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>cywp_spc_8</v>
+        <v>lcmj_cysl_10</v>
       </c>
       <c r="B178" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C178" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D178" t="str">
-        <v>藏銀瓦片</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E178">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F178">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G178" t="str">
-        <v>藏银瓦片.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>gtshz_xz_2</v>
+        <v>xy_stn_6</v>
       </c>
       <c r="B179" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C179" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D179" t="str">
-        <v>古銅獅子</v>
+        <v>岫玉</v>
       </c>
       <c r="E179">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F179">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G179" t="str">
-        <v>古铜狮子.png</v>
+        <v>岫玉.png</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>syc_pnd_2</v>
+        <v>xy_stn_8</v>
       </c>
       <c r="B180" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C180" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D180" t="str">
-        <v>四葉草</v>
+        <v>岫玉</v>
       </c>
       <c r="E180">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F180">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G180" t="str">
-        <v>四叶草.png</v>
+        <v>岫玉.png</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>gttc_xz_2</v>
+        <v>xy_stn_10</v>
       </c>
       <c r="B181" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C181" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D181" t="str">
-        <v>古銅天秤</v>
+        <v>岫玉</v>
       </c>
       <c r="E181">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F181">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G181" t="str">
-        <v>古铜天秤.png</v>
+        <v>岫玉.png</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>gtcn_xz_2</v>
+        <v>hcw_spc_5</v>
       </c>
       <c r="B182" t="str">
         <v>配件</v>
       </c>
       <c r="C182" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D182" t="str">
-        <v>古銅處女</v>
+        <v>回財紋</v>
       </c>
       <c r="E182">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F182">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G182" t="str">
-        <v>古铜处女.png</v>
+        <v>回财纹.png</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>tys_stn_6</v>
+        <v>cyjc_spc_6</v>
       </c>
       <c r="B183" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C183" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D183" t="str">
-        <v>太陽石</v>
+        <v>藏銀卷草</v>
       </c>
       <c r="E183">
         <v>6</v>
       </c>
       <c r="F183">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G183" t="str">
-        <v>太阳石.png</v>
+        <v>藏银卷草.png</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>tys_stn_8</v>
+        <v>hx_spc_6</v>
       </c>
       <c r="B184" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C184" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D184" t="str">
-        <v>太陽石</v>
+        <v>花旋</v>
       </c>
       <c r="E184">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F184">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G184" t="str">
-        <v>太阳石.png</v>
+        <v>花旋.png</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>tys_stn_10</v>
+        <v>cyszh_spc_8</v>
       </c>
       <c r="B185" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C185" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D185" t="str">
-        <v>太陽石</v>
+        <v>藏銀十字花</v>
       </c>
       <c r="E185">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F185">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="G185" t="str">
-        <v>太阳石.png</v>
+        <v>藏银十字花.png</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>yslzzy_spc_8</v>
+        <v>cyym_pnd_2</v>
       </c>
       <c r="B186" t="str">
         <v>配件</v>
       </c>
       <c r="C186" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D186" t="str">
-        <v>銀色六字真言</v>
+        <v>藏銀羽毛</v>
       </c>
       <c r="E186">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F186">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G186" t="str">
-        <v>银色六字真言.png</v>
+        <v>藏银羽毛.png</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ketj_spc_6</v>
+        <v>lys_stn_6</v>
       </c>
       <c r="B187" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C187" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D187" t="str">
-        <v>凱爾特結</v>
+        <v>綠螢石</v>
       </c>
       <c r="E187">
         <v>6</v>
       </c>
       <c r="F187">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G187" t="str">
-        <v>凯尔特结.png</v>
+        <v>绿萤石.png</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>ysxq_spc_8</v>
+        <v>lys_stn_8</v>
       </c>
       <c r="B188" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C188" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D188" t="str">
-        <v>銀色繡球</v>
+        <v>綠螢石</v>
       </c>
       <c r="E188">
         <v>8</v>
       </c>
       <c r="F188">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G188" t="str">
-        <v>银色绣球.png</v>
+        <v>绿萤石.png</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>gtszz_xz_2</v>
+        <v>cysy_spc_6</v>
       </c>
       <c r="B189" t="str">
         <v>配件</v>
       </c>
       <c r="C189" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D189" t="str">
-        <v>古銅雙子</v>
+        <v>藏銀樹葉</v>
       </c>
       <c r="E189">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F189">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G189" t="str">
-        <v>古铜双子.png</v>
+        <v>藏银树叶.png</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>zsj_cysl_6</v>
+        <v>qws_stn_8</v>
       </c>
       <c r="B190" t="str">
         <v>珠子</v>
       </c>
       <c r="C190" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D190" t="str">
-        <v>紫水晶</v>
+        <v>薔薇石</v>
       </c>
       <c r="E190">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F190">
         <v>69</v>
       </c>
       <c r="G190" t="str">
-        <v>紫水晶.png</v>
+        <v>蔷薇石.png</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>zsj_cysl_8</v>
+        <v>qws_stn_10</v>
       </c>
       <c r="B191" t="str">
         <v>珠子</v>
       </c>
       <c r="C191" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D191" t="str">
-        <v>紫水晶</v>
+        <v>薔薇石</v>
       </c>
       <c r="E191">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F191">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G191" t="str">
-        <v>紫水晶.png</v>
+        <v>蔷薇石.png</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>zsj_cysl_10</v>
+        <v>jsxz_spc_6</v>
       </c>
       <c r="B192" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C192" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D192" t="str">
-        <v>紫水晶</v>
+        <v>金色小珠</v>
       </c>
       <c r="E192">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F192">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G192" t="str">
-        <v>紫水晶.png</v>
+        <v>金色小珠.png</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>wgzl_pnd_2</v>
+        <v>gtsp_xz_2</v>
       </c>
       <c r="B193" t="str">
         <v>配件</v>
       </c>
       <c r="C193" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D193" t="str">
-        <v>王國之淚</v>
+        <v>古銅水瓶</v>
       </c>
       <c r="E193">
         <v>2</v>
       </c>
       <c r="F193">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G193" t="str">
-        <v>王国之泪.png</v>
+        <v>古铜水瓶.png</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>gtsy_xz_2</v>
+        <v>gtby_xz_2</v>
       </c>
       <c r="B194" t="str">
         <v>配件</v>
@@ -4849,7 +4849,7 @@
         <v>星座</v>
       </c>
       <c r="D194" t="str">
-        <v>古銅雙魚</v>
+        <v>古銅白羊</v>
       </c>
       <c r="E194">
         <v>2</v>
@@ -4858,58 +4858,58 @@
         <v>39</v>
       </c>
       <c r="G194" t="str">
-        <v>古铜双鱼.png</v>
+        <v>古铜白羊.png</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>gtmj_xz_2</v>
+        <v>gszssc_spc_6</v>
       </c>
       <c r="B195" t="str">
         <v>配件</v>
       </c>
       <c r="C195" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D195" t="str">
-        <v>古銅摩羯</v>
+        <v>鋯石鑽閃雙層</v>
       </c>
       <c r="E195">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F195">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G195" t="str">
-        <v>古铜摩羯.png</v>
+        <v>锆石钻闪双层.png</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>gtss_xz_2</v>
+        <v>cywp_spc_8</v>
       </c>
       <c r="B196" t="str">
         <v>配件</v>
       </c>
       <c r="C196" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D196" t="str">
-        <v>古銅射手</v>
+        <v>藏銀瓦片</v>
       </c>
       <c r="E196">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F196">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G196" t="str">
-        <v>古铜射手.png</v>
+        <v>藏银瓦片.png</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>gtjn_xz_2</v>
+        <v>gtshz_xz_2</v>
       </c>
       <c r="B197" t="str">
         <v>配件</v>
@@ -4918,7 +4918,7 @@
         <v>星座</v>
       </c>
       <c r="D197" t="str">
-        <v>古銅金牛</v>
+        <v>古銅獅子</v>
       </c>
       <c r="E197">
         <v>2</v>
@@ -4927,311 +4927,311 @@
         <v>39</v>
       </c>
       <c r="G197" t="str">
-        <v>古铜金牛.png</v>
+        <v>古铜狮子.png</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>gttx_xz_2</v>
+        <v>syc_pnd_2</v>
       </c>
       <c r="B198" t="str">
         <v>配件</v>
       </c>
       <c r="C198" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D198" t="str">
-        <v>古銅天蠍</v>
+        <v>四葉草</v>
       </c>
       <c r="E198">
         <v>2</v>
       </c>
       <c r="F198">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G198" t="str">
-        <v>古铜天蝎.png</v>
+        <v>四叶草.png</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>jslzzy_spc_8</v>
+        <v>gttc_xz_2</v>
       </c>
       <c r="B199" t="str">
         <v>配件</v>
       </c>
       <c r="C199" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D199" t="str">
-        <v>金色六字真言</v>
+        <v>古銅天秤</v>
       </c>
       <c r="E199">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F199">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G199" t="str">
-        <v>金色六字真言.png</v>
+        <v>古铜天秤.png</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>cmj_cysl_6</v>
+        <v>gtcn_xz_2</v>
       </c>
       <c r="B200" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C200" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D200" t="str">
-        <v>草莓晶</v>
+        <v>古銅處女</v>
       </c>
       <c r="E200">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F200">
         <v>39</v>
       </c>
       <c r="G200" t="str">
-        <v>草莓晶.png</v>
+        <v>古铜处女.png</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>cmj_cysl_8</v>
+        <v>ygs_stn_6</v>
       </c>
       <c r="B201" t="str">
         <v>珠子</v>
       </c>
       <c r="C201" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D201" t="str">
-        <v>草莓晶</v>
+        <v>月光石</v>
       </c>
       <c r="E201">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F201">
         <v>69</v>
       </c>
       <c r="G201" t="str">
-        <v>草莓晶.png</v>
+        <v>月光石.png</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>cmj_cysl_10</v>
+        <v>ygs_stn_8</v>
       </c>
       <c r="B202" t="str">
         <v>珠子</v>
       </c>
       <c r="C202" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D202" t="str">
-        <v>草莓晶</v>
+        <v>月光石</v>
       </c>
       <c r="E202">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F202">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G202" t="str">
-        <v>草莓晶.png</v>
+        <v>月光石.png</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>gtjx_xz_2</v>
+        <v>ygs_stn_10</v>
       </c>
       <c r="B203" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C203" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D203" t="str">
-        <v>古銅巨蟹</v>
+        <v>月光石</v>
       </c>
       <c r="E203">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F203">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="G203" t="str">
-        <v>古铜巨蟹.png</v>
+        <v>月光石.png</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>cyhdls_pnd_2</v>
+        <v>tys_stn_6</v>
       </c>
       <c r="B204" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C204" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D204" t="str">
-        <v>藏銀蝴蝶流蘇</v>
+        <v>太陽石</v>
       </c>
       <c r="E204">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F204">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="G204" t="str">
-        <v>藏银蝴蝶流苏.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mghh_spc_6</v>
+        <v>tys_stn_8</v>
       </c>
       <c r="B205" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C205" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D205" t="str">
-        <v>玫瑰花環</v>
+        <v>太陽石</v>
       </c>
       <c r="E205">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F205">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G205" t="str">
-        <v>玫瑰花环.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>bmnmh_spc_8</v>
+        <v>tys_stn_10</v>
       </c>
       <c r="B206" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C206" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D206" t="str">
-        <v>白瑪瑙魔盒</v>
+        <v>太陽石</v>
       </c>
       <c r="E206">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F206">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="G206" t="str">
-        <v>白玛瑙魔盒.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>cyhw_spc_5</v>
+        <v>shlb_stn_8</v>
       </c>
       <c r="B207" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C207" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D207" t="str">
-        <v>藏銀回紋</v>
+        <v>聖海藍寶</v>
       </c>
       <c r="E207">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F207">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G207" t="str">
-        <v>藏银回纹.png</v>
+        <v>圣海蓝宝.png</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>zsmh_spc_8</v>
+        <v>shlb_stn_10</v>
       </c>
       <c r="B208" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C208" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D208" t="str">
-        <v>硃砂魔盒</v>
+        <v>聖海藍寶</v>
       </c>
       <c r="E208">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F208">
-        <v>59</v>
+        <v>699</v>
       </c>
       <c r="G208" t="str">
-        <v>朱砂魔盒.png</v>
+        <v>圣海蓝宝.png</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>cyszdz_pnd_2</v>
+        <v>yslzzy_spc_8</v>
       </c>
       <c r="B209" t="str">
         <v>配件</v>
       </c>
       <c r="C209" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D209" t="str">
-        <v>藏銀十字吊墜</v>
+        <v>銀色六字真言</v>
       </c>
       <c r="E209">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F209">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G209" t="str">
-        <v>藏银十字吊坠.png</v>
+        <v>银色六字真言.png</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>cyyc_pnd_2</v>
+        <v>ketj_spc_6</v>
       </c>
       <c r="B210" t="str">
         <v>配件</v>
       </c>
       <c r="C210" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D210" t="str">
-        <v>藏銀葉叢</v>
+        <v>凱爾特結</v>
       </c>
       <c r="E210">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F210">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G210" t="str">
-        <v>藏银叶丛.png</v>
+        <v>凯尔特结.png</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>cyxhlf_spc_8</v>
+        <v>ysxq_spc_8</v>
       </c>
       <c r="B211" t="str">
         <v>配件</v>
@@ -5240,7 +5240,7 @@
         <v>隔珠</v>
       </c>
       <c r="D211" t="str">
-        <v>藏銀小花立方</v>
+        <v>銀色繡球</v>
       </c>
       <c r="E211">
         <v>8</v>
@@ -5249,228 +5249,228 @@
         <v>59</v>
       </c>
       <c r="G211" t="str">
-        <v>藏银小花立方.png</v>
+        <v>银色绣球.png</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>cydhlf_spc_8</v>
+        <v>gtszz_xz_2</v>
       </c>
       <c r="B212" t="str">
         <v>配件</v>
       </c>
       <c r="C212" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D212" t="str">
-        <v>藏銀大花立方</v>
+        <v>古銅雙子</v>
       </c>
       <c r="E212">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F212">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G212" t="str">
-        <v>藏银大花立方.png</v>
+        <v>古铜双子.png</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>jtlfq_spc_8</v>
+        <v>zsj_cysl_6</v>
       </c>
       <c r="B213" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C213" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D213" t="str">
-        <v>景泰藍福球</v>
+        <v>紫水晶</v>
       </c>
       <c r="E213">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F213">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G213" t="str">
-        <v>景泰蓝福球.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>nh_agt_6</v>
+        <v>zsj_cysl_8</v>
       </c>
       <c r="B214" t="str">
         <v>珠子</v>
       </c>
       <c r="C214" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D214" t="str">
-        <v>南紅</v>
+        <v>紫水晶</v>
       </c>
       <c r="E214">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F214">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G214" t="str">
-        <v>南红.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>nh_agt_8</v>
+        <v>zsj_cysl_10</v>
       </c>
       <c r="B215" t="str">
         <v>珠子</v>
       </c>
       <c r="C215" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D215" t="str">
-        <v>南紅</v>
+        <v>紫水晶</v>
       </c>
       <c r="E215">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F215">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G215" t="str">
-        <v>南红.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>nh_agt_10</v>
+        <v>wgzl_pnd_2</v>
       </c>
       <c r="B216" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C216" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D216" t="str">
-        <v>南紅</v>
+        <v>王國之淚</v>
       </c>
       <c r="E216">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F216">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G216" t="str">
-        <v>南红.png</v>
+        <v>王国之泪.png</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>hyes_stn_6</v>
+        <v>gtsy_xz_2</v>
       </c>
       <c r="B217" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C217" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D217" t="str">
-        <v>虎眼石</v>
+        <v>古銅雙魚</v>
       </c>
       <c r="E217">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F217">
         <v>39</v>
       </c>
       <c r="G217" t="str">
-        <v>虎眼石.png</v>
+        <v>古铜双鱼.png</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>hyes_stn_8</v>
+        <v>gtmj_xz_2</v>
       </c>
       <c r="B218" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C218" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D218" t="str">
-        <v>虎眼石</v>
+        <v>古銅摩羯</v>
       </c>
       <c r="E218">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F218">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G218" t="str">
-        <v>虎眼石.png</v>
+        <v>古铜摩羯.png</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>hyes_stn_10</v>
+        <v>gtss_xz_2</v>
       </c>
       <c r="B219" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C219" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D219" t="str">
-        <v>虎眼石</v>
+        <v>古銅射手</v>
       </c>
       <c r="E219">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F219">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G219" t="str">
-        <v>虎眼石.png</v>
+        <v>古铜射手.png</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>gqys_agt_6</v>
+        <v>gtjn_xz_2</v>
       </c>
       <c r="B220" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C220" t="str">
-        <v>瑪瑙</v>
+        <v>星座</v>
       </c>
       <c r="D220" t="str">
-        <v>乾青玉髓</v>
+        <v>古銅金牛</v>
       </c>
       <c r="E220">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F220">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G220" t="str">
-        <v>干青玉髓.png</v>
+        <v>古铜金牛.png</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>gqys_agt_8</v>
+        <v>zfj_cysl_8</v>
       </c>
       <c r="B221" t="str">
         <v>珠子</v>
       </c>
       <c r="C221" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D221" t="str">
-        <v>乾青玉髓</v>
+        <v>紫粉晶</v>
       </c>
       <c r="E221">
         <v>8</v>
@@ -5479,297 +5479,297 @@
         <v>69</v>
       </c>
       <c r="G221" t="str">
-        <v>干青玉髓.png</v>
+        <v>紫粉晶.png</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>gqys_agt_10</v>
+        <v>zfj_cysl_10</v>
       </c>
       <c r="B222" t="str">
         <v>珠子</v>
       </c>
       <c r="C222" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D222" t="str">
-        <v>乾青玉髓</v>
+        <v>紫粉晶</v>
       </c>
       <c r="E222">
         <v>10</v>
       </c>
       <c r="F222">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G222" t="str">
-        <v>干青玉髓.png</v>
+        <v>紫粉晶.png</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>yys_stn_6</v>
+        <v>gttx_xz_2</v>
       </c>
       <c r="B223" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C223" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D223" t="str">
-        <v>銀曜石</v>
+        <v>古銅天蠍</v>
       </c>
       <c r="E223">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F223">
         <v>39</v>
       </c>
       <c r="G223" t="str">
-        <v>银曜石.png</v>
+        <v>古铜天蝎.png</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>yys_stn_8</v>
+        <v>jslzzy_spc_8</v>
       </c>
       <c r="B224" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C224" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D224" t="str">
-        <v>銀曜石</v>
+        <v>金色六字真言</v>
       </c>
       <c r="E224">
         <v>8</v>
       </c>
       <c r="F224">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G224" t="str">
-        <v>银曜石.png</v>
+        <v>金色六字真言.png</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>yys_stn_10</v>
+        <v>cmj_cysl_6</v>
       </c>
       <c r="B225" t="str">
         <v>珠子</v>
       </c>
       <c r="C225" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D225" t="str">
-        <v>銀曜石</v>
+        <v>草莓晶</v>
       </c>
       <c r="E225">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F225">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G225" t="str">
-        <v>银曜石.png</v>
+        <v>草莓晶.png</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>bmw_pnd_2</v>
+        <v>cmj_cysl_8</v>
       </c>
       <c r="B226" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C226" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D226" t="str">
-        <v>捕夢網</v>
+        <v>草莓晶</v>
       </c>
       <c r="E226">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F226">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G226" t="str">
-        <v>捕梦网.png</v>
+        <v>草莓晶.png</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>ljs_stn_6</v>
+        <v>cmj_cysl_10</v>
       </c>
       <c r="B227" t="str">
         <v>珠子</v>
       </c>
       <c r="C227" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D227" t="str">
-        <v>藍晶石</v>
+        <v>草莓晶</v>
       </c>
       <c r="E227">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F227">
         <v>99</v>
       </c>
       <c r="G227" t="str">
-        <v>蓝晶石.png</v>
+        <v>草莓晶.png</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>ljs_stn_8</v>
+        <v>tg1_sz_7</v>
       </c>
       <c r="B228" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C228" t="str">
-        <v>礦石</v>
+        <v>數字</v>
       </c>
       <c r="D228" t="str">
-        <v>藍晶石</v>
+        <v>鈦鋼1</v>
       </c>
       <c r="E228">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F228">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="G228" t="str">
-        <v>蓝晶石.png</v>
+        <v>钛钢1.png</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>ljs_stn_10</v>
+        <v>gtjx_xz_2</v>
       </c>
       <c r="B229" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C229" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D229" t="str">
-        <v>藍晶石</v>
+        <v>古銅巨蟹</v>
       </c>
       <c r="E229">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F229">
-        <v>199</v>
+        <v>39</v>
       </c>
       <c r="G229" t="str">
-        <v>蓝晶石.png</v>
+        <v>古铜巨蟹.png</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>hmn_agt_6</v>
+        <v>cyhdls_pnd_2</v>
       </c>
       <c r="B230" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C230" t="str">
-        <v>瑪瑙</v>
+        <v>吊墜</v>
       </c>
       <c r="D230" t="str">
-        <v>紅瑪瑙</v>
+        <v>藏銀蝴蝶流蘇</v>
       </c>
       <c r="E230">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F230">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G230" t="str">
-        <v>红玛瑙.png</v>
+        <v>藏银蝴蝶流苏.png</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>hmn_agt_8</v>
+        <v>mghh_spc_6</v>
       </c>
       <c r="B231" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C231" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D231" t="str">
-        <v>紅瑪瑙</v>
+        <v>玫瑰花環</v>
       </c>
       <c r="E231">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F231">
         <v>59</v>
       </c>
       <c r="G231" t="str">
-        <v>红玛瑙.png</v>
+        <v>玫瑰花环.png</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>hmn_agt_10</v>
+        <v>bmnmh_spc_8</v>
       </c>
       <c r="B232" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C232" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D232" t="str">
-        <v>紅瑪瑙</v>
+        <v>白瑪瑙魔盒</v>
       </c>
       <c r="E232">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F232">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G232" t="str">
-        <v>红玛瑙.png</v>
+        <v>白玛瑙魔盒.png</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>csj_cysl_6</v>
+        <v>cyhw_spc_5</v>
       </c>
       <c r="B233" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C233" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D233" t="str">
-        <v>茶水晶</v>
+        <v>藏銀回紋</v>
       </c>
       <c r="E233">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F233">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G233" t="str">
-        <v>茶水晶.png</v>
+        <v>藏银回纹.png</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>csj_cysl_8</v>
+        <v>zsmh_spc_8</v>
       </c>
       <c r="B234" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C234" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D234" t="str">
-        <v>茶水晶</v>
+        <v>硃砂魔盒</v>
       </c>
       <c r="E234">
         <v>8</v>
@@ -5778,173 +5778,173 @@
         <v>59</v>
       </c>
       <c r="G234" t="str">
-        <v>茶水晶.png</v>
+        <v>朱砂魔盒.png</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>csj_cysl_10</v>
+        <v>cyszdz_pnd_2</v>
       </c>
       <c r="B235" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C235" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D235" t="str">
-        <v>茶水晶</v>
+        <v>藏銀十字吊墜</v>
       </c>
       <c r="E235">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F235">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G235" t="str">
-        <v>茶水晶.png</v>
+        <v>藏银十字吊坠.png</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>kqs_stn_6</v>
+        <v>cyyc_pnd_2</v>
       </c>
       <c r="B236" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C236" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D236" t="str">
-        <v>孔雀石</v>
+        <v>藏銀葉叢</v>
       </c>
       <c r="E236">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F236">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G236" t="str">
-        <v>孔雀石.png</v>
+        <v>藏银叶丛.png</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>kqs_stn_8</v>
+        <v>cyxhlf_spc_8</v>
       </c>
       <c r="B237" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C237" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D237" t="str">
-        <v>孔雀石</v>
+        <v>藏銀小花立方</v>
       </c>
       <c r="E237">
         <v>8</v>
       </c>
       <c r="F237">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G237" t="str">
-        <v>孔雀石.png</v>
+        <v>藏银小花立方.png</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>kqs_stn_10</v>
+        <v>cydhlf_spc_8</v>
       </c>
       <c r="B238" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C238" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D238" t="str">
-        <v>孔雀石</v>
+        <v>藏銀大花立方</v>
       </c>
       <c r="E238">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F238">
-        <v>199</v>
+        <v>59</v>
       </c>
       <c r="G238" t="str">
-        <v>孔雀石.png</v>
+        <v>藏银大花立方.png</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>qjs_stn_6</v>
+        <v>jtlfq_spc_8</v>
       </c>
       <c r="B239" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C239" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D239" t="str">
-        <v>青金石</v>
+        <v>景泰藍福球</v>
       </c>
       <c r="E239">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F239">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G239" t="str">
-        <v>青金石.png</v>
+        <v>景泰蓝福球.png</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>qjs_stn_8</v>
+        <v>hjc_cysl_6</v>
       </c>
       <c r="B240" t="str">
         <v>珠子</v>
       </c>
       <c r="C240" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D240" t="str">
-        <v>青金石</v>
+        <v>黑金超</v>
       </c>
       <c r="E240">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F240">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="G240" t="str">
-        <v>青金石.png</v>
+        <v>黑金超.png</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>qjs_stn_10</v>
+        <v>hjc_cysl_8</v>
       </c>
       <c r="B241" t="str">
         <v>珠子</v>
       </c>
       <c r="C241" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D241" t="str">
-        <v>青金石</v>
+        <v>黑金超</v>
       </c>
       <c r="E241">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F241">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G241" t="str">
-        <v>青金石.png</v>
+        <v>黑金超.png</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>wlg_cysl_6</v>
+        <v>hjc_cysl_10</v>
       </c>
       <c r="B242" t="str">
         <v>珠子</v>
@@ -5953,159 +5953,159 @@
         <v>水晶</v>
       </c>
       <c r="D242" t="str">
-        <v>烏拉圭</v>
+        <v>黑金超</v>
       </c>
       <c r="E242">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F242">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G242" t="str">
-        <v>乌拉圭.png</v>
+        <v>黑金超.png</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>wlg_cysl_8</v>
+        <v>nh_agt_6</v>
       </c>
       <c r="B243" t="str">
         <v>珠子</v>
       </c>
       <c r="C243" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D243" t="str">
-        <v>烏拉圭</v>
+        <v>南紅</v>
       </c>
       <c r="E243">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F243">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G243" t="str">
-        <v>乌拉圭.png</v>
+        <v>南红.png</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>wlg_cysl_10</v>
+        <v>nh_agt_8</v>
       </c>
       <c r="B244" t="str">
         <v>珠子</v>
       </c>
       <c r="C244" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D244" t="str">
-        <v>烏拉圭</v>
+        <v>南紅</v>
       </c>
       <c r="E244">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F244">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="G244" t="str">
-        <v>乌拉圭.png</v>
+        <v>南红.png</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>zyl_cysl_6</v>
+        <v>nh_agt_10</v>
       </c>
       <c r="B245" t="str">
         <v>珠子</v>
       </c>
       <c r="C245" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D245" t="str">
-        <v>紫幽靈</v>
+        <v>南紅</v>
       </c>
       <c r="E245">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F245">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="G245" t="str">
-        <v>紫幽灵.png</v>
+        <v>南红.png</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>zyl_cysl_8</v>
+        <v>hyes_stn_6</v>
       </c>
       <c r="B246" t="str">
         <v>珠子</v>
       </c>
       <c r="C246" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D246" t="str">
-        <v>紫幽靈</v>
+        <v>虎眼石</v>
       </c>
       <c r="E246">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F246">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G246" t="str">
-        <v>紫幽灵.png</v>
+        <v>虎眼石.png</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>he_agt_6</v>
+        <v>hyes_stn_8</v>
       </c>
       <c r="B247" t="str">
         <v>珠子</v>
       </c>
       <c r="C247" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D247" t="str">
-        <v>黑瑪瑙</v>
+        <v>虎眼石</v>
       </c>
       <c r="E247">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F247">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G247" t="str">
-        <v>黑玛瑙.png</v>
+        <v>虎眼石.png</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>he_agt_8</v>
+        <v>hyes_stn_10</v>
       </c>
       <c r="B248" t="str">
         <v>珠子</v>
       </c>
       <c r="C248" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D248" t="str">
-        <v>黑瑪瑙</v>
+        <v>虎眼石</v>
       </c>
       <c r="E248">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F248">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G248" t="str">
-        <v>黑玛瑙.png</v>
+        <v>虎眼石.png</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>he_agt_10</v>
+        <v>gqys_agt_6</v>
       </c>
       <c r="B249" t="str">
         <v>珠子</v>
@@ -6114,67 +6114,67 @@
         <v>瑪瑙</v>
       </c>
       <c r="D249" t="str">
-        <v>黑瑪瑙</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E249">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F249">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G249" t="str">
-        <v>黑玛瑙.png</v>
+        <v>干青玉髓.png</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>jys_stn_6</v>
+        <v>gqys_agt_8</v>
       </c>
       <c r="B250" t="str">
         <v>珠子</v>
       </c>
       <c r="C250" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D250" t="str">
-        <v>金曜石</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E250">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F250">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G250" t="str">
-        <v>金曜石.png</v>
+        <v>干青玉髓.png</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>jys_stn_8</v>
+        <v>gqys_agt_10</v>
       </c>
       <c r="B251" t="str">
         <v>珠子</v>
       </c>
       <c r="C251" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D251" t="str">
-        <v>金曜石</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E251">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F251">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G251" t="str">
-        <v>金曜石.png</v>
+        <v>干青玉髓.png</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>jys_stn_10</v>
+        <v>yys_stn_6</v>
       </c>
       <c r="B252" t="str">
         <v>珠子</v>
@@ -6183,21 +6183,21 @@
         <v>礦石</v>
       </c>
       <c r="D252" t="str">
-        <v>金曜石</v>
+        <v>銀曜石</v>
       </c>
       <c r="E252">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F252">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G252" t="str">
-        <v>金曜石.png</v>
+        <v>银曜石.png</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>hys_stn_6</v>
+        <v>yys_stn_8</v>
       </c>
       <c r="B253" t="str">
         <v>珠子</v>
@@ -6206,21 +6206,21 @@
         <v>礦石</v>
       </c>
       <c r="D253" t="str">
-        <v>黑曜石</v>
+        <v>銀曜石</v>
       </c>
       <c r="E253">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F253">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G253" t="str">
-        <v>黑曜石.png</v>
+        <v>银曜石.png</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>hys_stn_8</v>
+        <v>yys_stn_10</v>
       </c>
       <c r="B254" t="str">
         <v>珠子</v>
@@ -6229,44 +6229,803 @@
         <v>礦石</v>
       </c>
       <c r="D254" t="str">
-        <v>黑曜石</v>
+        <v>銀曜石</v>
       </c>
       <c r="E254">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F254">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G254" t="str">
-        <v>黑曜石.png</v>
+        <v>银曜石.png</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>hys_stn_10</v>
+        <v>bmw_pnd_2</v>
       </c>
       <c r="B255" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C255" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D255" t="str">
-        <v>黑曜石</v>
+        <v>捕夢網</v>
       </c>
       <c r="E255">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F255">
         <v>99</v>
       </c>
       <c r="G255" t="str">
+        <v>捕梦网.png</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>zs_stn_6</v>
+      </c>
+      <c r="B256" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C256" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D256" t="str">
+        <v>硃砂</v>
+      </c>
+      <c r="E256">
+        <v>6</v>
+      </c>
+      <c r="F256">
+        <v>99</v>
+      </c>
+      <c r="G256" t="str">
+        <v>朱砂.png</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>ljs_stn_6</v>
+      </c>
+      <c r="B257" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C257" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D257" t="str">
+        <v>藍晶石</v>
+      </c>
+      <c r="E257">
+        <v>6</v>
+      </c>
+      <c r="F257">
+        <v>99</v>
+      </c>
+      <c r="G257" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>ljs_stn_8</v>
+      </c>
+      <c r="B258" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C258" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D258" t="str">
+        <v>藍晶石</v>
+      </c>
+      <c r="E258">
+        <v>8</v>
+      </c>
+      <c r="F258">
+        <v>139</v>
+      </c>
+      <c r="G258" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>ljs_stn_10</v>
+      </c>
+      <c r="B259" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C259" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D259" t="str">
+        <v>藍晶石</v>
+      </c>
+      <c r="E259">
+        <v>10</v>
+      </c>
+      <c r="F259">
+        <v>199</v>
+      </c>
+      <c r="G259" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>hmn_agt_6</v>
+      </c>
+      <c r="B260" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C260" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D260" t="str">
+        <v>紅瑪瑙</v>
+      </c>
+      <c r="E260">
+        <v>6</v>
+      </c>
+      <c r="F260">
+        <v>39</v>
+      </c>
+      <c r="G260" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>hmn_agt_8</v>
+      </c>
+      <c r="B261" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C261" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D261" t="str">
+        <v>紅瑪瑙</v>
+      </c>
+      <c r="E261">
+        <v>8</v>
+      </c>
+      <c r="F261">
+        <v>59</v>
+      </c>
+      <c r="G261" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>hmn_agt_10</v>
+      </c>
+      <c r="B262" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C262" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D262" t="str">
+        <v>紅瑪瑙</v>
+      </c>
+      <c r="E262">
+        <v>10</v>
+      </c>
+      <c r="F262">
+        <v>89</v>
+      </c>
+      <c r="G262" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>csj_cysl_6</v>
+      </c>
+      <c r="B263" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C263" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D263" t="str">
+        <v>茶水晶</v>
+      </c>
+      <c r="E263">
+        <v>6</v>
+      </c>
+      <c r="F263">
+        <v>39</v>
+      </c>
+      <c r="G263" t="str">
+        <v>茶水晶.png</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>csj_cysl_8</v>
+      </c>
+      <c r="B264" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C264" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D264" t="str">
+        <v>茶水晶</v>
+      </c>
+      <c r="E264">
+        <v>8</v>
+      </c>
+      <c r="F264">
+        <v>59</v>
+      </c>
+      <c r="G264" t="str">
+        <v>茶水晶.png</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>csj_cysl_10</v>
+      </c>
+      <c r="B265" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C265" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D265" t="str">
+        <v>茶水晶</v>
+      </c>
+      <c r="E265">
+        <v>10</v>
+      </c>
+      <c r="F265">
+        <v>89</v>
+      </c>
+      <c r="G265" t="str">
+        <v>茶水晶.png</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>kqs_stn_6</v>
+      </c>
+      <c r="B266" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C266" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D266" t="str">
+        <v>孔雀石</v>
+      </c>
+      <c r="E266">
+        <v>6</v>
+      </c>
+      <c r="F266">
+        <v>69</v>
+      </c>
+      <c r="G266" t="str">
+        <v>孔雀石.png</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>kqs_stn_8</v>
+      </c>
+      <c r="B267" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C267" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D267" t="str">
+        <v>孔雀石</v>
+      </c>
+      <c r="E267">
+        <v>8</v>
+      </c>
+      <c r="F267">
+        <v>89</v>
+      </c>
+      <c r="G267" t="str">
+        <v>孔雀石.png</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>kqs_stn_10</v>
+      </c>
+      <c r="B268" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C268" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D268" t="str">
+        <v>孔雀石</v>
+      </c>
+      <c r="E268">
+        <v>10</v>
+      </c>
+      <c r="F268">
+        <v>199</v>
+      </c>
+      <c r="G268" t="str">
+        <v>孔雀石.png</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>qjs_stn_6</v>
+      </c>
+      <c r="B269" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C269" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D269" t="str">
+        <v>青金石</v>
+      </c>
+      <c r="E269">
+        <v>6</v>
+      </c>
+      <c r="F269">
+        <v>69</v>
+      </c>
+      <c r="G269" t="str">
+        <v>青金石.png</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>qjs_stn_8</v>
+      </c>
+      <c r="B270" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C270" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D270" t="str">
+        <v>青金石</v>
+      </c>
+      <c r="E270">
+        <v>8</v>
+      </c>
+      <c r="F270">
+        <v>89</v>
+      </c>
+      <c r="G270" t="str">
+        <v>青金石.png</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>qjs_stn_10</v>
+      </c>
+      <c r="B271" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C271" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D271" t="str">
+        <v>青金石</v>
+      </c>
+      <c r="E271">
+        <v>10</v>
+      </c>
+      <c r="F271">
+        <v>99</v>
+      </c>
+      <c r="G271" t="str">
+        <v>青金石.png</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>wlg_cysl_6</v>
+      </c>
+      <c r="B272" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C272" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D272" t="str">
+        <v>烏拉圭</v>
+      </c>
+      <c r="E272">
+        <v>6</v>
+      </c>
+      <c r="F272">
+        <v>69</v>
+      </c>
+      <c r="G272" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>wlg_cysl_8</v>
+      </c>
+      <c r="B273" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C273" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D273" t="str">
+        <v>烏拉圭</v>
+      </c>
+      <c r="E273">
+        <v>8</v>
+      </c>
+      <c r="F273">
+        <v>99</v>
+      </c>
+      <c r="G273" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>wlg_cysl_10</v>
+      </c>
+      <c r="B274" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C274" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D274" t="str">
+        <v>烏拉圭</v>
+      </c>
+      <c r="E274">
+        <v>10</v>
+      </c>
+      <c r="F274">
+        <v>169</v>
+      </c>
+      <c r="G274" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>zyl_cysl_6</v>
+      </c>
+      <c r="B275" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C275" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D275" t="str">
+        <v>紫幽靈</v>
+      </c>
+      <c r="E275">
+        <v>6</v>
+      </c>
+      <c r="F275">
+        <v>39</v>
+      </c>
+      <c r="G275" t="str">
+        <v>紫幽灵.png</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>zyl_cysl_8</v>
+      </c>
+      <c r="B276" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C276" t="str">
+        <v>水晶</v>
+      </c>
+      <c r="D276" t="str">
+        <v>紫幽靈</v>
+      </c>
+      <c r="E276">
+        <v>8</v>
+      </c>
+      <c r="F276">
+        <v>59</v>
+      </c>
+      <c r="G276" t="str">
+        <v>紫幽灵.png</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>he_agt_6</v>
+      </c>
+      <c r="B277" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C277" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D277" t="str">
+        <v>黑瑪瑙</v>
+      </c>
+      <c r="E277">
+        <v>6</v>
+      </c>
+      <c r="F277">
+        <v>39</v>
+      </c>
+      <c r="G277" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>he_agt_8</v>
+      </c>
+      <c r="B278" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C278" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D278" t="str">
+        <v>黑瑪瑙</v>
+      </c>
+      <c r="E278">
+        <v>8</v>
+      </c>
+      <c r="F278">
+        <v>59</v>
+      </c>
+      <c r="G278" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>he_agt_10</v>
+      </c>
+      <c r="B279" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C279" t="str">
+        <v>瑪瑙</v>
+      </c>
+      <c r="D279" t="str">
+        <v>黑瑪瑙</v>
+      </c>
+      <c r="E279">
+        <v>10</v>
+      </c>
+      <c r="F279">
+        <v>89</v>
+      </c>
+      <c r="G279" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>zjs_stn_6</v>
+      </c>
+      <c r="B280" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C280" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D280" t="str">
+        <v>紫金砂</v>
+      </c>
+      <c r="E280">
+        <v>6</v>
+      </c>
+      <c r="F280">
+        <v>69</v>
+      </c>
+      <c r="G280" t="str">
+        <v>紫金砂.png</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>zjs_stn_8</v>
+      </c>
+      <c r="B281" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C281" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D281" t="str">
+        <v>紫金砂</v>
+      </c>
+      <c r="E281">
+        <v>8</v>
+      </c>
+      <c r="F281">
+        <v>99</v>
+      </c>
+      <c r="G281" t="str">
+        <v>紫金砂.png</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>zjs_stn_10</v>
+      </c>
+      <c r="B282" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C282" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D282" t="str">
+        <v>紫金砂</v>
+      </c>
+      <c r="E282">
+        <v>10</v>
+      </c>
+      <c r="F282">
+        <v>129</v>
+      </c>
+      <c r="G282" t="str">
+        <v>紫金砂.png</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>jys_stn_6</v>
+      </c>
+      <c r="B283" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C283" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D283" t="str">
+        <v>金曜石</v>
+      </c>
+      <c r="E283">
+        <v>6</v>
+      </c>
+      <c r="F283">
+        <v>39</v>
+      </c>
+      <c r="G283" t="str">
+        <v>金曜石.png</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>jys_stn_8</v>
+      </c>
+      <c r="B284" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C284" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D284" t="str">
+        <v>金曜石</v>
+      </c>
+      <c r="E284">
+        <v>8</v>
+      </c>
+      <c r="F284">
+        <v>69</v>
+      </c>
+      <c r="G284" t="str">
+        <v>金曜石.png</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>jys_stn_10</v>
+      </c>
+      <c r="B285" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C285" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D285" t="str">
+        <v>金曜石</v>
+      </c>
+      <c r="E285">
+        <v>10</v>
+      </c>
+      <c r="F285">
+        <v>99</v>
+      </c>
+      <c r="G285" t="str">
+        <v>金曜石.png</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>hys_stn_6</v>
+      </c>
+      <c r="B286" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C286" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D286" t="str">
+        <v>黑曜石</v>
+      </c>
+      <c r="E286">
+        <v>6</v>
+      </c>
+      <c r="F286">
+        <v>39</v>
+      </c>
+      <c r="G286" t="str">
+        <v>黑曜石.png</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>hys_stn_8</v>
+      </c>
+      <c r="B287" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C287" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D287" t="str">
+        <v>黑曜石</v>
+      </c>
+      <c r="E287">
+        <v>8</v>
+      </c>
+      <c r="F287">
+        <v>69</v>
+      </c>
+      <c r="G287" t="str">
+        <v>黑曜石.png</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>hys_stn_10</v>
+      </c>
+      <c r="B288" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C288" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D288" t="str">
+        <v>黑曜石</v>
+      </c>
+      <c r="E288">
+        <v>10</v>
+      </c>
+      <c r="F288">
+        <v>99</v>
+      </c>
+      <c r="G288" t="str">
         <v>黑曜石.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G255"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G288"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:G289"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1215,7 +1215,7 @@
         <v>吊墜</v>
       </c>
       <c r="D36" t="str">
-        <v>銀色滿鑲月亮</v>
+        <v>滿鑲月亮</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -1224,7 +1224,7 @@
         <v>99</v>
       </c>
       <c r="G36" t="str">
-        <v>银色满镶月亮.png</v>
+        <v>满镶月亮.png</v>
       </c>
     </row>
     <row r="37">
@@ -2172,30 +2172,30 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>hm_agt_6</v>
+        <v>gh_spc_6</v>
       </c>
       <c r="B78" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C78" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D78" t="str">
-        <v>黃瑪瑙</v>
+        <v>桂花</v>
       </c>
       <c r="E78">
         <v>6</v>
       </c>
       <c r="F78">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="G78" t="str">
-        <v>黄玛瑙.png</v>
+        <v>桂花.png</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>hm_agt_8</v>
+        <v>hm_agt_6</v>
       </c>
       <c r="B79" t="str">
         <v>珠子</v>
@@ -2207,10 +2207,10 @@
         <v>黃瑪瑙</v>
       </c>
       <c r="E79">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F79">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G79" t="str">
         <v>黄玛瑙.png</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>hm_agt_10</v>
+        <v>hm_agt_8</v>
       </c>
       <c r="B80" t="str">
         <v>珠子</v>
@@ -2230,10 +2230,10 @@
         <v>黃瑪瑙</v>
       </c>
       <c r="E80">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F80">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G80" t="str">
         <v>黄玛瑙.png</v>
@@ -2241,30 +2241,30 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ml_stn_6</v>
+        <v>hm_agt_10</v>
       </c>
       <c r="B81" t="str">
         <v>珠子</v>
       </c>
       <c r="C81" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D81" t="str">
-        <v>蜜蠟</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E81">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F81">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G81" t="str">
-        <v>蜜蜡.png</v>
+        <v>黄玛瑙.png</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ml_stn_8</v>
+        <v>ml_stn_6</v>
       </c>
       <c r="B82" t="str">
         <v>珠子</v>
@@ -2276,10 +2276,10 @@
         <v>蜜蠟</v>
       </c>
       <c r="E82">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F82">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G82" t="str">
         <v>蜜蜡.png</v>
@@ -2287,53 +2287,53 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ysr_zm_4</v>
+        <v>ml_stn_8</v>
       </c>
       <c r="B83" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C83" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D83" t="str">
-        <v>銀飾R</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E83">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F83">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="G83" t="str">
-        <v>银饰R.png</v>
+        <v>蜜蜡.png</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>mzhd_pnd_2</v>
+        <v>ysr_zm_4</v>
       </c>
       <c r="B84" t="str">
         <v>配件</v>
       </c>
       <c r="C84" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D84" t="str">
-        <v>滿鑽蝴蝶</v>
+        <v>銀飾R</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F84">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G84" t="str">
-        <v>满钻蝴蝶.png</v>
+        <v>银饰R.png</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>jd_pnd_2</v>
+        <v>mzhd_pnd_2</v>
       </c>
       <c r="B85" t="str">
         <v>配件</v>
@@ -2342,7 +2342,7 @@
         <v>吊墜</v>
       </c>
       <c r="D85" t="str">
-        <v>晶蝶</v>
+        <v>滿鑽蝴蝶</v>
       </c>
       <c r="E85">
         <v>2</v>
@@ -2351,242 +2351,242 @@
         <v>99</v>
       </c>
       <c r="G85" t="str">
-        <v>晶蝶.png</v>
+        <v>满钻蝴蝶.png</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>lkjls_spc_6</v>
+        <v>jd_pnd_2</v>
       </c>
       <c r="B86" t="str">
         <v>配件</v>
       </c>
       <c r="C86" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D86" t="str">
-        <v>鏤空金蕾絲</v>
+        <v>晶蝶</v>
       </c>
       <c r="E86">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F86">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G86" t="str">
-        <v>镂空金蕾丝.png</v>
+        <v>晶蝶.png</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>tg7_sz_7</v>
+        <v>lkjls_spc_6</v>
       </c>
       <c r="B87" t="str">
         <v>配件</v>
       </c>
       <c r="C87" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D87" t="str">
-        <v>鈦鋼7</v>
+        <v>鏤空金蕾絲</v>
       </c>
       <c r="E87">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F87">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G87" t="str">
-        <v>钛钢7.png</v>
+        <v>镂空金蕾丝.png</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>jpts_stn_8</v>
+        <v>tg7_sz_7</v>
       </c>
       <c r="B88" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C88" t="str">
-        <v>礦石</v>
+        <v>數字</v>
       </c>
       <c r="D88" t="str">
-        <v>金葡萄石</v>
+        <v>鈦鋼7</v>
       </c>
       <c r="E88">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G88" t="str">
-        <v>金葡萄石.png</v>
+        <v>钛钢7.png</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>gymj_xz_2</v>
+        <v>jpts_stn_8</v>
       </c>
       <c r="B89" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C89" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D89" t="str">
-        <v>古銀摩羯</v>
+        <v>金葡萄石</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F89">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G89" t="str">
-        <v>古银摩羯.png</v>
+        <v>金葡萄石.png</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>tg0_sz_7</v>
+        <v>gymj_xz_2</v>
       </c>
       <c r="B90" t="str">
         <v>配件</v>
       </c>
       <c r="C90" t="str">
-        <v>數字</v>
+        <v>星座</v>
       </c>
       <c r="D90" t="str">
-        <v>鈦鋼0</v>
+        <v>古銀摩羯</v>
       </c>
       <c r="E90">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F90">
         <v>39</v>
       </c>
       <c r="G90" t="str">
-        <v>钛钢0.png</v>
+        <v>古银摩羯.png</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>jf_pnd_2</v>
+        <v>tg0_sz_7</v>
       </c>
       <c r="B91" t="str">
         <v>配件</v>
       </c>
       <c r="C91" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D91" t="str">
-        <v>金福</v>
+        <v>鈦鋼0</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F91">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G91" t="str">
-        <v>金福.png</v>
+        <v>钛钢0.png</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>fgdh_spc_8</v>
+        <v>jf_pnd_2</v>
       </c>
       <c r="B92" t="str">
         <v>配件</v>
       </c>
       <c r="C92" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D92" t="str">
-        <v>復古雕花</v>
+        <v>金福</v>
       </c>
       <c r="E92">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F92">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G92" t="str">
-        <v>复古雕花.png</v>
+        <v>金福.png</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>ysj_zm_4</v>
+        <v>fgdh_spc_8</v>
       </c>
       <c r="B93" t="str">
         <v>配件</v>
       </c>
       <c r="C93" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D93" t="str">
-        <v>銀飾J</v>
+        <v>復古雕花</v>
       </c>
       <c r="E93">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G93" t="str">
-        <v>银饰J.png</v>
+        <v>复古雕花.png</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>tg6_sz_7</v>
+        <v>ysj_zm_4</v>
       </c>
       <c r="B94" t="str">
         <v>配件</v>
       </c>
       <c r="C94" t="str">
-        <v>數字</v>
+        <v>字母</v>
       </c>
       <c r="D94" t="str">
-        <v>鈦鋼6</v>
+        <v>銀飾J</v>
       </c>
       <c r="E94">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F94">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G94" t="str">
-        <v>钛钢6.png</v>
+        <v>银饰J.png</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>xxy_spc_5</v>
+        <v>tg6_sz_7</v>
       </c>
       <c r="B95" t="str">
         <v>配件</v>
       </c>
       <c r="C95" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D95" t="str">
-        <v>小祥雲</v>
+        <v>鈦鋼6</v>
       </c>
       <c r="E95">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F95">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G95" t="str">
-        <v>小祥云.png</v>
+        <v>钛钢6.png</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>dxy_spc_5</v>
+        <v>xxy_spc_5</v>
       </c>
       <c r="B96" t="str">
         <v>配件</v>
@@ -2595,7 +2595,7 @@
         <v>隔珠</v>
       </c>
       <c r="D96" t="str">
-        <v>大祥雲</v>
+        <v>小祥雲</v>
       </c>
       <c r="E96">
         <v>5</v>
@@ -2604,35 +2604,35 @@
         <v>59</v>
       </c>
       <c r="G96" t="str">
-        <v>大祥云.png</v>
+        <v>小祥云.png</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ysi_zm_4</v>
+        <v>dxy_spc_5</v>
       </c>
       <c r="B97" t="str">
         <v>配件</v>
       </c>
       <c r="C97" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D97" t="str">
-        <v>銀飾I</v>
+        <v>大祥雲</v>
       </c>
       <c r="E97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F97">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G97" t="str">
-        <v>银饰I.png</v>
+        <v>大祥云.png</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ysu_zm_4</v>
+        <v>ysi_zm_4</v>
       </c>
       <c r="B98" t="str">
         <v>配件</v>
@@ -2641,7 +2641,7 @@
         <v>字母</v>
       </c>
       <c r="D98" t="str">
-        <v>銀飾U</v>
+        <v>銀飾I</v>
       </c>
       <c r="E98">
         <v>4</v>
@@ -2650,35 +2650,35 @@
         <v>399</v>
       </c>
       <c r="G98" t="str">
-        <v>银饰U.png</v>
+        <v>银饰I.png</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>tg3_sz_7</v>
+        <v>ysu_zm_4</v>
       </c>
       <c r="B99" t="str">
         <v>配件</v>
       </c>
       <c r="C99" t="str">
-        <v>數字</v>
+        <v>字母</v>
       </c>
       <c r="D99" t="str">
-        <v>鈦鋼3</v>
+        <v>銀飾U</v>
       </c>
       <c r="E99">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F99">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G99" t="str">
-        <v>钛钢3.png</v>
+        <v>银饰U.png</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>tg2_sz_7</v>
+        <v>tg3_sz_7</v>
       </c>
       <c r="B100" t="str">
         <v>配件</v>
@@ -2687,7 +2687,7 @@
         <v>數字</v>
       </c>
       <c r="D100" t="str">
-        <v>鈦鋼2</v>
+        <v>鈦鋼3</v>
       </c>
       <c r="E100">
         <v>7</v>
@@ -2696,12 +2696,12 @@
         <v>39</v>
       </c>
       <c r="G100" t="str">
-        <v>钛钢2.png</v>
+        <v>钛钢3.png</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>tg8_sz_7</v>
+        <v>tg2_sz_7</v>
       </c>
       <c r="B101" t="str">
         <v>配件</v>
@@ -2710,7 +2710,7 @@
         <v>數字</v>
       </c>
       <c r="D101" t="str">
-        <v>鈦鋼8</v>
+        <v>鈦鋼2</v>
       </c>
       <c r="E101">
         <v>7</v>
@@ -2719,12 +2719,12 @@
         <v>39</v>
       </c>
       <c r="G101" t="str">
-        <v>钛钢8.png</v>
+        <v>钛钢2.png</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>tg5_sz_7</v>
+        <v>tg8_sz_7</v>
       </c>
       <c r="B102" t="str">
         <v>配件</v>
@@ -2733,7 +2733,7 @@
         <v>數字</v>
       </c>
       <c r="D102" t="str">
-        <v>鈦鋼5</v>
+        <v>鈦鋼8</v>
       </c>
       <c r="E102">
         <v>7</v>
@@ -2742,127 +2742,127 @@
         <v>39</v>
       </c>
       <c r="G102" t="str">
-        <v>钛钢5.png</v>
+        <v>钛钢8.png</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>gycn_xz_2</v>
+        <v>tg5_sz_7</v>
       </c>
       <c r="B103" t="str">
         <v>配件</v>
       </c>
       <c r="C103" t="str">
-        <v>星座</v>
+        <v>數字</v>
       </c>
       <c r="D103" t="str">
-        <v>古銀處女</v>
+        <v>鈦鋼5</v>
       </c>
       <c r="E103">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F103">
         <v>39</v>
       </c>
       <c r="G103" t="str">
-        <v>古银处女.png</v>
+        <v>钛钢5.png</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ysp_zm_4</v>
+        <v>gycn_xz_2</v>
       </c>
       <c r="B104" t="str">
         <v>配件</v>
       </c>
       <c r="C104" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D104" t="str">
-        <v>銀飾P</v>
+        <v>古銀處女</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F104">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G104" t="str">
-        <v>银饰P.png</v>
+        <v>古银处女.png</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>gsmm_spc_8</v>
+        <v>ysp_zm_4</v>
       </c>
       <c r="B105" t="str">
         <v>配件</v>
       </c>
       <c r="C105" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D105" t="str">
-        <v>鋯石貓咪</v>
+        <v>銀飾P</v>
       </c>
       <c r="E105">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F105">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G105" t="str">
-        <v>锆石猫咪.png</v>
+        <v>银饰P.png</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>gyby_xz_2</v>
+        <v>gsmm_spc_8</v>
       </c>
       <c r="B106" t="str">
         <v>配件</v>
       </c>
       <c r="C106" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D106" t="str">
-        <v>古銀白羊</v>
+        <v>鋯石貓咪</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F106">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G106" t="str">
-        <v>古银白羊.png</v>
+        <v>锆石猫咪.png</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>lfj_cysl_8</v>
+        <v>gyby_xz_2</v>
       </c>
       <c r="B107" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C107" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D107" t="str">
-        <v>綠髮晶</v>
+        <v>古銀白羊</v>
       </c>
       <c r="E107">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F107">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G107" t="str">
-        <v>绿发晶.png</v>
+        <v>古银白羊.png</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>lfj_cysl_10</v>
+        <v>lfj_cysl_8</v>
       </c>
       <c r="B108" t="str">
         <v>珠子</v>
@@ -2874,10 +2874,10 @@
         <v>綠髮晶</v>
       </c>
       <c r="E108">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F108">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="G108" t="str">
         <v>绿发晶.png</v>
@@ -2885,30 +2885,30 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ysc_zm_4</v>
+        <v>lfj_cysl_10</v>
       </c>
       <c r="B109" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C109" t="str">
-        <v>字母</v>
+        <v>水晶</v>
       </c>
       <c r="D109" t="str">
-        <v>銀飾C</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E109">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F109">
-        <v>399</v>
+        <v>139</v>
       </c>
       <c r="G109" t="str">
-        <v>银饰C.png</v>
+        <v>绿发晶.png</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ysb_zm_4</v>
+        <v>ysc_zm_4</v>
       </c>
       <c r="B110" t="str">
         <v>配件</v>
@@ -2917,7 +2917,7 @@
         <v>字母</v>
       </c>
       <c r="D110" t="str">
-        <v>銀飾B</v>
+        <v>銀飾C</v>
       </c>
       <c r="E110">
         <v>4</v>
@@ -2926,58 +2926,58 @@
         <v>399</v>
       </c>
       <c r="G110" t="str">
-        <v>银饰B.png</v>
+        <v>银饰C.png</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>gysp_xz_2</v>
+        <v>ysb_zm_4</v>
       </c>
       <c r="B111" t="str">
         <v>配件</v>
       </c>
       <c r="C111" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D111" t="str">
-        <v>古銀水瓶</v>
+        <v>銀飾B</v>
       </c>
       <c r="E111">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F111">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G111" t="str">
-        <v>古银水瓶.png</v>
+        <v>银饰B.png</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>yso_zm_4</v>
+        <v>gysp_xz_2</v>
       </c>
       <c r="B112" t="str">
         <v>配件</v>
       </c>
       <c r="C112" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D112" t="str">
-        <v>銀飾O</v>
+        <v>古銀水瓶</v>
       </c>
       <c r="E112">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F112">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G112" t="str">
-        <v>银饰O.png</v>
+        <v>古银水瓶.png</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ysw_zm_4</v>
+        <v>yso_zm_4</v>
       </c>
       <c r="B113" t="str">
         <v>配件</v>
@@ -2986,7 +2986,7 @@
         <v>字母</v>
       </c>
       <c r="D113" t="str">
-        <v>銀飾W</v>
+        <v>銀飾O</v>
       </c>
       <c r="E113">
         <v>4</v>
@@ -2995,58 +2995,58 @@
         <v>399</v>
       </c>
       <c r="G113" t="str">
-        <v>银饰W.png</v>
+        <v>银饰O.png</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>wljz_spc_5</v>
+        <v>ysw_zm_4</v>
       </c>
       <c r="B114" t="str">
         <v>配件</v>
       </c>
       <c r="C114" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D114" t="str">
-        <v>五稜金鑽</v>
+        <v>銀飾W</v>
       </c>
       <c r="E114">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F114">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G114" t="str">
-        <v>五棱金钻.png</v>
+        <v>银饰W.png</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>zyd_pnd_2</v>
+        <v>wljz_spc_5</v>
       </c>
       <c r="B115" t="str">
         <v>配件</v>
       </c>
       <c r="C115" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D115" t="str">
-        <v>珠遇蝶</v>
+        <v>五稜金鑽</v>
       </c>
       <c r="E115">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F115">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G115" t="str">
-        <v>珠遇蝶.png</v>
+        <v>五棱金钻.png</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>xfp_pnd_2</v>
+        <v>zyd_pnd_2</v>
       </c>
       <c r="B116" t="str">
         <v>配件</v>
@@ -3055,7 +3055,7 @@
         <v>吊墜</v>
       </c>
       <c r="D116" t="str">
-        <v>小福牌</v>
+        <v>珠遇蝶</v>
       </c>
       <c r="E116">
         <v>2</v>
@@ -3064,196 +3064,196 @@
         <v>99</v>
       </c>
       <c r="G116" t="str">
-        <v>小福牌.png</v>
+        <v>珠遇蝶.png</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ysq_zm_4</v>
+        <v>xfp_pnd_2</v>
       </c>
       <c r="B117" t="str">
         <v>配件</v>
       </c>
       <c r="C117" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D117" t="str">
-        <v>銀飾Q</v>
+        <v>招財</v>
       </c>
       <c r="E117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F117">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="G117" t="str">
-        <v>银饰Q.png</v>
+        <v>招财.png</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ymys_stn_10</v>
+        <v>ysq_zm_4</v>
       </c>
       <c r="B118" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C118" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D118" t="str">
-        <v>羽毛螢石</v>
+        <v>銀飾Q</v>
       </c>
       <c r="E118">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F118">
-        <v>139</v>
+        <v>399</v>
       </c>
       <c r="G118" t="str">
-        <v>羽毛萤石.png</v>
+        <v>银饰Q.png</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>gyjx_xz_2</v>
+        <v>ymys_stn_10</v>
       </c>
       <c r="B119" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C119" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D119" t="str">
-        <v>古銀巨蟹</v>
+        <v>羽毛螢石</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F119">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="G119" t="str">
-        <v>古银巨蟹.png</v>
+        <v>羽毛萤石.png</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ysf_zm_4</v>
+        <v>gyjx_xz_2</v>
       </c>
       <c r="B120" t="str">
         <v>配件</v>
       </c>
       <c r="C120" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D120" t="str">
-        <v>銀飾F</v>
+        <v>古銀巨蟹</v>
       </c>
       <c r="E120">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F120">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G120" t="str">
-        <v>银饰F.png</v>
+        <v>古银巨蟹.png</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>gyss_xz_2</v>
+        <v>ysf_zm_4</v>
       </c>
       <c r="B121" t="str">
         <v>配件</v>
       </c>
       <c r="C121" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D121" t="str">
-        <v>古銀射手</v>
+        <v>銀飾F</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F121">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G121" t="str">
-        <v>古银射手.png</v>
+        <v>银饰F.png</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>hlcs_pnd_2</v>
+        <v>gyss_xz_2</v>
       </c>
       <c r="B122" t="str">
         <v>配件</v>
       </c>
       <c r="C122" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D122" t="str">
-        <v>葫蘆成雙</v>
+        <v>古銀射手</v>
       </c>
       <c r="E122">
         <v>2</v>
       </c>
       <c r="F122">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G122" t="str">
-        <v>葫芦成双.png</v>
+        <v>古银射手.png</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>gyszz_xz_2</v>
+        <v>hlcs_pnd_2</v>
       </c>
       <c r="B123" t="str">
         <v>配件</v>
       </c>
       <c r="C123" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D123" t="str">
-        <v>古銀雙子</v>
+        <v>葫蘆成雙</v>
       </c>
       <c r="E123">
         <v>2</v>
       </c>
       <c r="F123">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G123" t="str">
-        <v>古银双子.png</v>
+        <v>葫芦成双.png</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ysn_zm_4</v>
+        <v>gyszz_xz_2</v>
       </c>
       <c r="B124" t="str">
         <v>配件</v>
       </c>
       <c r="C124" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D124" t="str">
-        <v>銀飾N</v>
+        <v>古銀雙子</v>
       </c>
       <c r="E124">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F124">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G124" t="str">
-        <v>银饰N.png</v>
+        <v>古银双子.png</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ysm_zm_4</v>
+        <v>ysn_zm_4</v>
       </c>
       <c r="B125" t="str">
         <v>配件</v>
@@ -3262,7 +3262,7 @@
         <v>字母</v>
       </c>
       <c r="D125" t="str">
-        <v>銀飾M</v>
+        <v>銀飾N</v>
       </c>
       <c r="E125">
         <v>4</v>
@@ -3271,12 +3271,12 @@
         <v>399</v>
       </c>
       <c r="G125" t="str">
-        <v>银饰M.png</v>
+        <v>银饰N.png</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ysh_zm_4</v>
+        <v>ysm_zm_4</v>
       </c>
       <c r="B126" t="str">
         <v>配件</v>
@@ -3285,7 +3285,7 @@
         <v>字母</v>
       </c>
       <c r="D126" t="str">
-        <v>銀飾H</v>
+        <v>銀飾M</v>
       </c>
       <c r="E126">
         <v>4</v>
@@ -3294,150 +3294,150 @@
         <v>399</v>
       </c>
       <c r="G126" t="str">
-        <v>银饰H.png</v>
+        <v>银饰M.png</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>gytx_xz_2</v>
+        <v>ysh_zm_4</v>
       </c>
       <c r="B127" t="str">
         <v>配件</v>
       </c>
       <c r="C127" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D127" t="str">
-        <v>古銀天蠍</v>
+        <v>銀飾H</v>
       </c>
       <c r="E127">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F127">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G127" t="str">
-        <v>古银天蝎.png</v>
+        <v>银饰H.png</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ysg_zm_4</v>
+        <v>gytx_xz_2</v>
       </c>
       <c r="B128" t="str">
         <v>配件</v>
       </c>
       <c r="C128" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D128" t="str">
-        <v>銀飾G</v>
+        <v>古銀天蠍</v>
       </c>
       <c r="E128">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F128">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G128" t="str">
-        <v>银饰G.png</v>
+        <v>古银天蝎.png</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>gytc_xz_2</v>
+        <v>ysg_zm_4</v>
       </c>
       <c r="B129" t="str">
         <v>配件</v>
       </c>
       <c r="C129" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D129" t="str">
-        <v>古銀天秤</v>
+        <v>銀飾G</v>
       </c>
       <c r="E129">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F129">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G129" t="str">
-        <v>古银天秤.png</v>
+        <v>银饰G.png</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>yst_zm_4</v>
+        <v>gytc_xz_2</v>
       </c>
       <c r="B130" t="str">
         <v>配件</v>
       </c>
       <c r="C130" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D130" t="str">
-        <v>銀飾T</v>
+        <v>古銀天秤</v>
       </c>
       <c r="E130">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F130">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G130" t="str">
-        <v>银饰T.png</v>
+        <v>古银天秤.png</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>gslx_spc_6</v>
+        <v>yst_zm_4</v>
       </c>
       <c r="B131" t="str">
         <v>配件</v>
       </c>
       <c r="C131" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D131" t="str">
-        <v>鋯石螺旋</v>
+        <v>銀飾T</v>
       </c>
       <c r="E131">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F131">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G131" t="str">
-        <v>锆石螺旋.png</v>
+        <v>银饰T.png</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>yse_zm_4</v>
+        <v>gslx_spc_6</v>
       </c>
       <c r="B132" t="str">
         <v>配件</v>
       </c>
       <c r="C132" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D132" t="str">
-        <v>銀飾E</v>
+        <v>鋯石螺旋</v>
       </c>
       <c r="E132">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F132">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G132" t="str">
-        <v>银饰E.png</v>
+        <v>锆石螺旋.png</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>ysk_zm_4</v>
+        <v>yse_zm_4</v>
       </c>
       <c r="B133" t="str">
         <v>配件</v>
@@ -3446,7 +3446,7 @@
         <v>字母</v>
       </c>
       <c r="D133" t="str">
-        <v>銀飾K</v>
+        <v>銀飾E</v>
       </c>
       <c r="E133">
         <v>4</v>
@@ -3455,334 +3455,334 @@
         <v>399</v>
       </c>
       <c r="G133" t="str">
-        <v>银饰K.png</v>
+        <v>银饰E.png</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>syyl_pnd_2</v>
+        <v>ysk_zm_4</v>
       </c>
       <c r="B134" t="str">
         <v>配件</v>
       </c>
       <c r="C134" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D134" t="str">
-        <v>閃躍月亮</v>
+        <v>銀飾K</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F134">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G134" t="str">
-        <v>闪跃月亮.png</v>
+        <v>银饰K.png</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ysv_zm_4</v>
+        <v>syyl_pnd_2</v>
       </c>
       <c r="B135" t="str">
         <v>配件</v>
       </c>
       <c r="C135" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D135" t="str">
-        <v>銀飾V</v>
+        <v>閃躍月亮</v>
       </c>
       <c r="E135">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F135">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="G135" t="str">
-        <v>银饰V.png</v>
+        <v>闪跃月亮.png</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>gszs_spc_5</v>
+        <v>ysv_zm_4</v>
       </c>
       <c r="B136" t="str">
         <v>配件</v>
       </c>
       <c r="C136" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D136" t="str">
-        <v>鋯石鑽閃</v>
+        <v>銀飾V</v>
       </c>
       <c r="E136">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F136">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G136" t="str">
-        <v>锆石钻闪.png</v>
+        <v>银饰V.png</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>ysl_zm_4</v>
+        <v>gszs_spc_5</v>
       </c>
       <c r="B137" t="str">
         <v>配件</v>
       </c>
       <c r="C137" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D137" t="str">
-        <v>銀飾L</v>
+        <v>藏銀繡球鋯石細閃</v>
       </c>
       <c r="E137">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F137">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G137" t="str">
-        <v>银饰L.png</v>
+        <v>藏银绣球锆石细闪.png</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>xns_pnd_2</v>
+        <v>ysl_zm_4</v>
       </c>
       <c r="B138" t="str">
         <v>配件</v>
       </c>
       <c r="C138" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D138" t="str">
-        <v>小年獸</v>
+        <v>銀飾L</v>
       </c>
       <c r="E138">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F138">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G138" t="str">
-        <v>小年兽.png</v>
+        <v>银饰L.png</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>ysa_zm_4</v>
+        <v>xns_pnd_2</v>
       </c>
       <c r="B139" t="str">
         <v>配件</v>
       </c>
       <c r="C139" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D139" t="str">
-        <v>銀飾A</v>
+        <v>小年獸</v>
       </c>
       <c r="E139">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F139">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="G139" t="str">
-        <v>银饰A.png</v>
+        <v>小年兽.png</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>gyjn_xz_2</v>
+        <v>ysa_zm_4</v>
       </c>
       <c r="B140" t="str">
         <v>配件</v>
       </c>
       <c r="C140" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D140" t="str">
-        <v>古銀金牛</v>
+        <v>銀飾A</v>
       </c>
       <c r="E140">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F140">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="G140" t="str">
-        <v>古银金牛.png</v>
+        <v>银饰A.png</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ysy_zm_4</v>
+        <v>gyjn_xz_2</v>
       </c>
       <c r="B141" t="str">
         <v>配件</v>
       </c>
       <c r="C141" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D141" t="str">
-        <v>銀飾Y</v>
+        <v>古銀金牛</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F141">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="G141" t="str">
-        <v>银饰Y.png</v>
+        <v>古银金牛.png</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>jsxh_spc_5</v>
+        <v>ysy_zm_4</v>
       </c>
       <c r="B142" t="str">
         <v>配件</v>
       </c>
       <c r="C142" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D142" t="str">
-        <v>金色小環</v>
+        <v>銀飾Y</v>
       </c>
       <c r="E142">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F142">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G142" t="str">
-        <v>金色小环.png</v>
+        <v>银饰Y.png</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>gyshz_xz_2</v>
+        <v>jsxh_spc_5</v>
       </c>
       <c r="B143" t="str">
         <v>配件</v>
       </c>
       <c r="C143" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D143" t="str">
-        <v>古銀獅子</v>
+        <v>金色小環</v>
       </c>
       <c r="E143">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F143">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G143" t="str">
-        <v>古银狮子.png</v>
+        <v>金色小环.png</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>bjx_pnd_2</v>
+        <v>gyshz_xz_2</v>
       </c>
       <c r="B144" t="str">
         <v>配件</v>
       </c>
       <c r="C144" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D144" t="str">
-        <v>北極星</v>
+        <v>古銀獅子</v>
       </c>
       <c r="E144">
         <v>2</v>
       </c>
       <c r="F144">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G144" t="str">
-        <v>北极星.png</v>
+        <v>古银狮子.png</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>cgl_spc_6</v>
+        <v>bjx_pnd_2</v>
       </c>
       <c r="B145" t="str">
         <v>配件</v>
       </c>
       <c r="C145" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D145" t="str">
-        <v>彩鋯輪</v>
+        <v>北極星</v>
       </c>
       <c r="E145">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F145">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G145" t="str">
-        <v>彩锆轮.png</v>
+        <v>北极星.png</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ysx_zm_4</v>
+        <v>cgl_spc_6</v>
       </c>
       <c r="B146" t="str">
         <v>配件</v>
       </c>
       <c r="C146" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D146" t="str">
-        <v>銀飾X</v>
+        <v>彩鋯輪</v>
       </c>
       <c r="E146">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F146">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G146" t="str">
-        <v>银饰X.png</v>
+        <v>彩锆轮.png</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>hps_stn_6</v>
+        <v>ysx_zm_4</v>
       </c>
       <c r="B147" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C147" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D147" t="str">
-        <v>琥珀石</v>
+        <v>銀飾X</v>
       </c>
       <c r="E147">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F147">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G147" t="str">
-        <v>琥珀石.png</v>
+        <v>银饰X.png</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>hps_stn_8</v>
+        <v>hps_stn_6</v>
       </c>
       <c r="B148" t="str">
         <v>珠子</v>
@@ -3794,10 +3794,10 @@
         <v>琥珀石</v>
       </c>
       <c r="E148">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F148">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G148" t="str">
         <v>琥珀石.png</v>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>hps_stn_10</v>
+        <v>hps_stn_8</v>
       </c>
       <c r="B149" t="str">
         <v>珠子</v>
@@ -3817,10 +3817,10 @@
         <v>琥珀石</v>
       </c>
       <c r="E149">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F149">
-        <v>199</v>
+        <v>89</v>
       </c>
       <c r="G149" t="str">
         <v>琥珀石.png</v>
@@ -3828,99 +3828,99 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>gysy_xz_2</v>
+        <v>hps_stn_10</v>
       </c>
       <c r="B150" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C150" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D150" t="str">
-        <v>古銀雙魚</v>
+        <v>琥珀石</v>
       </c>
       <c r="E150">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F150">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="G150" t="str">
-        <v>古银双鱼.png</v>
+        <v>琥珀石.png</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>xs_spc_8</v>
+        <v>gysy_xz_2</v>
       </c>
       <c r="B151" t="str">
         <v>配件</v>
       </c>
       <c r="C151" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D151" t="str">
-        <v>醒獅</v>
+        <v>古銀雙魚</v>
       </c>
       <c r="E151">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F151">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G151" t="str">
-        <v>醒狮.png</v>
+        <v>古银双鱼.png</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ysz_zm_4</v>
+        <v>xs_spc_8</v>
       </c>
       <c r="B152" t="str">
         <v>配件</v>
       </c>
       <c r="C152" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D152" t="str">
-        <v>銀飾Z</v>
+        <v>醒獅</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F152">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="G152" t="str">
-        <v>银饰Z.png</v>
+        <v>醒狮.png</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ths_stn_6</v>
+        <v>ysz_zm_4</v>
       </c>
       <c r="B153" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C153" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D153" t="str">
-        <v>天河石</v>
+        <v>銀飾Z</v>
       </c>
       <c r="E153">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F153">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G153" t="str">
-        <v>天河石.png</v>
+        <v>银饰Z.png</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ths_stn_8</v>
+        <v>ths_stn_6</v>
       </c>
       <c r="B154" t="str">
         <v>珠子</v>
@@ -3932,10 +3932,10 @@
         <v>天河石</v>
       </c>
       <c r="E154">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F154">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G154" t="str">
         <v>天河石.png</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>ths_stn_10</v>
+        <v>ths_stn_8</v>
       </c>
       <c r="B155" t="str">
         <v>珠子</v>
@@ -3955,10 +3955,10 @@
         <v>天河石</v>
       </c>
       <c r="E155">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F155">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="G155" t="str">
         <v>天河石.png</v>
@@ -3966,53 +3966,53 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ysd_zm_4</v>
+        <v>ths_stn_10</v>
       </c>
       <c r="B156" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C156" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D156" t="str">
-        <v>銀飾D</v>
+        <v>天河石</v>
       </c>
       <c r="E156">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F156">
-        <v>399</v>
+        <v>139</v>
       </c>
       <c r="G156" t="str">
-        <v>银饰D.png</v>
+        <v>天河石.png</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>hlb_stn_6</v>
+        <v>ysd_zm_4</v>
       </c>
       <c r="B157" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C157" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D157" t="str">
-        <v>海藍寶</v>
+        <v>銀飾D</v>
       </c>
       <c r="E157">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F157">
-        <v>89</v>
+        <v>399</v>
       </c>
       <c r="G157" t="str">
-        <v>海蓝宝.png</v>
+        <v>银饰D.png</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>hlb_stn_8</v>
+        <v>hlb_stn_6</v>
       </c>
       <c r="B158" t="str">
         <v>珠子</v>
@@ -4024,10 +4024,10 @@
         <v>海藍寶</v>
       </c>
       <c r="E158">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F158">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G158" t="str">
         <v>海蓝宝.png</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>hlb_stn_10</v>
+        <v>hlb_stn_8</v>
       </c>
       <c r="B159" t="str">
         <v>珠子</v>
@@ -4047,10 +4047,10 @@
         <v>海藍寶</v>
       </c>
       <c r="E159">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F159">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="G159" t="str">
         <v>海蓝宝.png</v>
@@ -4058,99 +4058,99 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>yss_zm_4</v>
+        <v>hlb_stn_10</v>
       </c>
       <c r="B160" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C160" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D160" t="str">
-        <v>銀飾S</v>
+        <v>海藍寶</v>
       </c>
       <c r="E160">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F160">
-        <v>399</v>
+        <v>169</v>
       </c>
       <c r="G160" t="str">
-        <v>银饰S.png</v>
+        <v>海蓝宝.png</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>gsch_pnd_2</v>
+        <v>yss_zm_4</v>
       </c>
       <c r="B161" t="str">
         <v>配件</v>
       </c>
       <c r="C161" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D161" t="str">
-        <v>鋯石彩虹</v>
+        <v>銀飾S</v>
       </c>
       <c r="E161">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F161">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="G161" t="str">
-        <v>锆石彩虹.png</v>
+        <v>银饰S.png</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>xgszs_spc_5</v>
+        <v>gsch_pnd_2</v>
       </c>
       <c r="B162" t="str">
         <v>配件</v>
       </c>
       <c r="C162" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D162" t="str">
-        <v>小鋯石鑽閃</v>
+        <v>鋯石彩虹</v>
       </c>
       <c r="E162">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F162">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G162" t="str">
-        <v>小锆石钻闪.png</v>
+        <v>锆石彩虹.png</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>htj_cysl_6</v>
+        <v>xgszs_spc_5</v>
       </c>
       <c r="B163" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C163" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D163" t="str">
-        <v>黃塔晶</v>
+        <v>小鋯石鑽閃</v>
       </c>
       <c r="E163">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F163">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G163" t="str">
-        <v>黄塔晶.png</v>
+        <v>小锆石钻闪.png</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>htj_cysl_8</v>
+        <v>htj_cysl_6</v>
       </c>
       <c r="B164" t="str">
         <v>珠子</v>
@@ -4162,10 +4162,10 @@
         <v>黃塔晶</v>
       </c>
       <c r="E164">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F164">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G164" t="str">
         <v>黄塔晶.png</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>htj_cysl_10</v>
+        <v>htj_cysl_8</v>
       </c>
       <c r="B165" t="str">
         <v>珠子</v>
@@ -4185,10 +4185,10 @@
         <v>黃塔晶</v>
       </c>
       <c r="E165">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F165">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G165" t="str">
         <v>黄塔晶.png</v>
@@ -4196,53 +4196,53 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>wyh_pnd_2</v>
+        <v>htj_cysl_10</v>
       </c>
       <c r="B166" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C166" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D166" t="str">
-        <v>午夜花</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E166">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F166">
         <v>99</v>
       </c>
       <c r="G166" t="str">
-        <v>午夜花.png</v>
+        <v>黄塔晶.png</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>hfj_cysl_6</v>
+        <v>wyh_pnd_2</v>
       </c>
       <c r="B167" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C167" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D167" t="str">
-        <v>黑髮晶</v>
+        <v>午夜花</v>
       </c>
       <c r="E167">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F167">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G167" t="str">
-        <v>黑发晶.png</v>
+        <v>午夜花.png</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>hfj_cysl_8</v>
+        <v>hfj_cysl_6</v>
       </c>
       <c r="B168" t="str">
         <v>珠子</v>
@@ -4254,10 +4254,10 @@
         <v>黑髮晶</v>
       </c>
       <c r="E168">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F168">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G168" t="str">
         <v>黑发晶.png</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>hfj_cysl_10</v>
+        <v>hfj_cysl_8</v>
       </c>
       <c r="B169" t="str">
         <v>珠子</v>
@@ -4277,10 +4277,10 @@
         <v>黑髮晶</v>
       </c>
       <c r="E169">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F169">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="G169" t="str">
         <v>黑发晶.png</v>
@@ -4288,76 +4288,76 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>ysxz_spc_6</v>
+        <v>hfj_cysl_10</v>
       </c>
       <c r="B170" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C170" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D170" t="str">
-        <v>銀色小珠</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E170">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F170">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="G170" t="str">
-        <v>银色小珠.png</v>
+        <v>黑发晶.png</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>jhy_stn_6</v>
+        <v>tz_spc_10</v>
       </c>
       <c r="B171" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C171" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D171" t="str">
-        <v>金虎眼</v>
+        <v>天珠</v>
       </c>
       <c r="E171">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F171">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G171" t="str">
-        <v>金虎眼.png</v>
+        <v>天珠.png</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>jhy_stn_8</v>
+        <v>ysxz_spc_6</v>
       </c>
       <c r="B172" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C172" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D172" t="str">
-        <v>金虎眼</v>
+        <v>銀色小珠</v>
       </c>
       <c r="E172">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F172">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G172" t="str">
-        <v>金虎眼.png</v>
+        <v>银色小珠.png</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>jhy_stn_10</v>
+        <v>jhy_stn_6</v>
       </c>
       <c r="B173" t="str">
         <v>珠子</v>
@@ -4369,10 +4369,10 @@
         <v>金虎眼</v>
       </c>
       <c r="E173">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F173">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="G173" t="str">
         <v>金虎眼.png</v>
@@ -4380,99 +4380,99 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>jsmxyl_pnd_2</v>
+        <v>jhy_stn_8</v>
       </c>
       <c r="B174" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C174" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D174" t="str">
-        <v>金色滿鑲月亮</v>
+        <v>金虎眼</v>
       </c>
       <c r="E174">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F174">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G174" t="str">
-        <v>金色满镶月亮.png</v>
+        <v>金虎眼.png</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>hbgd_spc_6</v>
+        <v>jhy_stn_10</v>
       </c>
       <c r="B175" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C175" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D175" t="str">
-        <v>花邊軌道</v>
+        <v>金虎眼</v>
       </c>
       <c r="E175">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F175">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G175" t="str">
-        <v>花边轨道.png</v>
+        <v>金虎眼.png</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>lcmj_cysl_6</v>
+        <v>jsmxyl_pnd_2</v>
       </c>
       <c r="B176" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C176" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D176" t="str">
-        <v>綠莓晶</v>
+        <v>滿鑲彩月</v>
       </c>
       <c r="E176">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F176">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G176" t="str">
-        <v>绿莓晶.png</v>
+        <v>满镶彩月.png</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>lcmj_cysl_8</v>
+        <v>hbgd_spc_6</v>
       </c>
       <c r="B177" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C177" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D177" t="str">
-        <v>綠莓晶</v>
+        <v>花邊軌道</v>
       </c>
       <c r="E177">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F177">
         <v>59</v>
       </c>
       <c r="G177" t="str">
-        <v>绿莓晶.png</v>
+        <v>花边轨道.png</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>lcmj_cysl_10</v>
+        <v>lcmj_cysl_6</v>
       </c>
       <c r="B178" t="str">
         <v>珠子</v>
@@ -4484,10 +4484,10 @@
         <v>綠莓晶</v>
       </c>
       <c r="E178">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F178">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G178" t="str">
         <v>绿莓晶.png</v>
@@ -4495,53 +4495,53 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>xy_stn_6</v>
+        <v>lcmj_cysl_8</v>
       </c>
       <c r="B179" t="str">
         <v>珠子</v>
       </c>
       <c r="C179" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D179" t="str">
-        <v>岫玉</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E179">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F179">
         <v>59</v>
       </c>
       <c r="G179" t="str">
-        <v>岫玉.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>xy_stn_8</v>
+        <v>lcmj_cysl_10</v>
       </c>
       <c r="B180" t="str">
         <v>珠子</v>
       </c>
       <c r="C180" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D180" t="str">
-        <v>岫玉</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E180">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F180">
         <v>89</v>
       </c>
       <c r="G180" t="str">
-        <v>岫玉.png</v>
+        <v>绿莓晶.png</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>xy_stn_10</v>
+        <v>xy_stn_6</v>
       </c>
       <c r="B181" t="str">
         <v>珠子</v>
@@ -4553,10 +4553,10 @@
         <v>岫玉</v>
       </c>
       <c r="E181">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F181">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G181" t="str">
         <v>岫玉.png</v>
@@ -4564,53 +4564,53 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>hcw_spc_5</v>
+        <v>xy_stn_8</v>
       </c>
       <c r="B182" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C182" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D182" t="str">
-        <v>回財紋</v>
+        <v>岫玉</v>
       </c>
       <c r="E182">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F182">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G182" t="str">
-        <v>回财纹.png</v>
+        <v>岫玉.png</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>cyjc_spc_6</v>
+        <v>xy_stn_10</v>
       </c>
       <c r="B183" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C183" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D183" t="str">
-        <v>藏銀卷草</v>
+        <v>岫玉</v>
       </c>
       <c r="E183">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F183">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G183" t="str">
-        <v>藏银卷草.png</v>
+        <v>岫玉.png</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>hx_spc_6</v>
+        <v>hcw_spc_5</v>
       </c>
       <c r="B184" t="str">
         <v>配件</v>
@@ -4619,21 +4619,21 @@
         <v>隔珠</v>
       </c>
       <c r="D184" t="str">
-        <v>花旋</v>
+        <v>回財紋</v>
       </c>
       <c r="E184">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F184">
         <v>59</v>
       </c>
       <c r="G184" t="str">
-        <v>花旋.png</v>
+        <v>回财纹.png</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>cyszh_spc_8</v>
+        <v>cyjc_spc_6</v>
       </c>
       <c r="B185" t="str">
         <v>配件</v>
@@ -4642,113 +4642,113 @@
         <v>隔珠</v>
       </c>
       <c r="D185" t="str">
-        <v>藏銀十字花</v>
+        <v>藏銀卷草</v>
       </c>
       <c r="E185">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F185">
         <v>59</v>
       </c>
       <c r="G185" t="str">
-        <v>藏银十字花.png</v>
+        <v>藏银卷草.png</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>cyym_pnd_2</v>
+        <v>hx_spc_6</v>
       </c>
       <c r="B186" t="str">
         <v>配件</v>
       </c>
       <c r="C186" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D186" t="str">
-        <v>藏銀羽毛</v>
+        <v>花旋</v>
       </c>
       <c r="E186">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F186">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G186" t="str">
-        <v>藏银羽毛.png</v>
+        <v>花旋.png</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>lys_stn_6</v>
+        <v>cyszh_spc_8</v>
       </c>
       <c r="B187" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C187" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D187" t="str">
-        <v>綠螢石</v>
+        <v>藏銀十字花</v>
       </c>
       <c r="E187">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F187">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G187" t="str">
-        <v>绿萤石.png</v>
+        <v>藏银十字花.png</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>lys_stn_8</v>
+        <v>cyym_pnd_2</v>
       </c>
       <c r="B188" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C188" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D188" t="str">
-        <v>綠螢石</v>
+        <v>藏銀羽毛</v>
       </c>
       <c r="E188">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F188">
         <v>99</v>
       </c>
       <c r="G188" t="str">
-        <v>绿萤石.png</v>
+        <v>藏银羽毛.png</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>cysy_spc_6</v>
+        <v>lys_stn_6</v>
       </c>
       <c r="B189" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C189" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D189" t="str">
-        <v>藏銀樹葉</v>
+        <v>綠螢石</v>
       </c>
       <c r="E189">
         <v>6</v>
       </c>
       <c r="F189">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G189" t="str">
-        <v>藏银树叶.png</v>
+        <v>绿萤石.png</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>qws_stn_8</v>
+        <v>lys_stn_8</v>
       </c>
       <c r="B190" t="str">
         <v>珠子</v>
@@ -4757,205 +4757,205 @@
         <v>礦石</v>
       </c>
       <c r="D190" t="str">
-        <v>薔薇石</v>
+        <v>綠螢石</v>
       </c>
       <c r="E190">
         <v>8</v>
       </c>
       <c r="F190">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G190" t="str">
-        <v>蔷薇石.png</v>
+        <v>绿萤石.png</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>qws_stn_10</v>
+        <v>cysy_spc_6</v>
       </c>
       <c r="B191" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C191" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D191" t="str">
-        <v>薔薇石</v>
+        <v>藏銀樹葉</v>
       </c>
       <c r="E191">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F191">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G191" t="str">
-        <v>蔷薇石.png</v>
+        <v>藏银树叶.png</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>jsxz_spc_6</v>
+        <v>qws_stn_8</v>
       </c>
       <c r="B192" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C192" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D192" t="str">
-        <v>金色小珠</v>
+        <v>薔薇石</v>
       </c>
       <c r="E192">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F192">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G192" t="str">
-        <v>金色小珠.png</v>
+        <v>蔷薇石.png</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>gtsp_xz_2</v>
+        <v>qws_stn_10</v>
       </c>
       <c r="B193" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C193" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D193" t="str">
-        <v>古銅水瓶</v>
+        <v>薔薇石</v>
       </c>
       <c r="E193">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F193">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G193" t="str">
-        <v>古铜水瓶.png</v>
+        <v>蔷薇石.png</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>gtby_xz_2</v>
+        <v>jsxz_spc_6</v>
       </c>
       <c r="B194" t="str">
         <v>配件</v>
       </c>
       <c r="C194" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D194" t="str">
-        <v>古銅白羊</v>
+        <v>金色小珠</v>
       </c>
       <c r="E194">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F194">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G194" t="str">
-        <v>古铜白羊.png</v>
+        <v>金色小珠.png</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>gszssc_spc_6</v>
+        <v>gtsp_xz_2</v>
       </c>
       <c r="B195" t="str">
         <v>配件</v>
       </c>
       <c r="C195" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D195" t="str">
-        <v>鋯石鑽閃雙層</v>
+        <v>古銅水瓶</v>
       </c>
       <c r="E195">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F195">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G195" t="str">
-        <v>锆石钻闪双层.png</v>
+        <v>古铜水瓶.png</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>cywp_spc_8</v>
+        <v>gtby_xz_2</v>
       </c>
       <c r="B196" t="str">
         <v>配件</v>
       </c>
       <c r="C196" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D196" t="str">
-        <v>藏銀瓦片</v>
+        <v>古銅白羊</v>
       </c>
       <c r="E196">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F196">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G196" t="str">
-        <v>藏银瓦片.png</v>
+        <v>古铜白羊.png</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>gtshz_xz_2</v>
+        <v>gszssc_spc_6</v>
       </c>
       <c r="B197" t="str">
         <v>配件</v>
       </c>
       <c r="C197" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D197" t="str">
-        <v>古銅獅子</v>
+        <v>鋯石鑽閃雙層</v>
       </c>
       <c r="E197">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F197">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G197" t="str">
-        <v>古铜狮子.png</v>
+        <v>锆石钻闪双层.png</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>syc_pnd_2</v>
+        <v>cywp_spc_8</v>
       </c>
       <c r="B198" t="str">
         <v>配件</v>
       </c>
       <c r="C198" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D198" t="str">
-        <v>四葉草</v>
+        <v>藏銀瓦片</v>
       </c>
       <c r="E198">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F198">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G198" t="str">
-        <v>四叶草.png</v>
+        <v>藏银瓦片.png</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>gttc_xz_2</v>
+        <v>gtshz_xz_2</v>
       </c>
       <c r="B199" t="str">
         <v>配件</v>
@@ -4964,7 +4964,7 @@
         <v>星座</v>
       </c>
       <c r="D199" t="str">
-        <v>古銅天秤</v>
+        <v>古銅獅子</v>
       </c>
       <c r="E199">
         <v>2</v>
@@ -4973,81 +4973,81 @@
         <v>39</v>
       </c>
       <c r="G199" t="str">
-        <v>古铜天秤.png</v>
+        <v>古铜狮子.png</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>gtcn_xz_2</v>
+        <v>syc_pnd_2</v>
       </c>
       <c r="B200" t="str">
         <v>配件</v>
       </c>
       <c r="C200" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D200" t="str">
-        <v>古銅處女</v>
+        <v>四葉草</v>
       </c>
       <c r="E200">
         <v>2</v>
       </c>
       <c r="F200">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G200" t="str">
-        <v>古铜处女.png</v>
+        <v>四叶草.png</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>ygs_stn_6</v>
+        <v>gttc_xz_2</v>
       </c>
       <c r="B201" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C201" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D201" t="str">
-        <v>月光石</v>
+        <v>古銅天秤</v>
       </c>
       <c r="E201">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F201">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G201" t="str">
-        <v>月光石.png</v>
+        <v>古铜天秤.png</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>ygs_stn_8</v>
+        <v>gtcn_xz_2</v>
       </c>
       <c r="B202" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C202" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D202" t="str">
-        <v>月光石</v>
+        <v>古銅處女</v>
       </c>
       <c r="E202">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F202">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G202" t="str">
-        <v>月光石.png</v>
+        <v>古铜处女.png</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>ygs_stn_10</v>
+        <v>ygs_stn_6</v>
       </c>
       <c r="B203" t="str">
         <v>珠子</v>
@@ -5059,10 +5059,10 @@
         <v>月光石</v>
       </c>
       <c r="E203">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F203">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="G203" t="str">
         <v>月光石.png</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>tys_stn_6</v>
+        <v>ygs_stn_8</v>
       </c>
       <c r="B204" t="str">
         <v>珠子</v>
@@ -5079,21 +5079,21 @@
         <v>礦石</v>
       </c>
       <c r="D204" t="str">
-        <v>太陽石</v>
+        <v>月光石</v>
       </c>
       <c r="E204">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F204">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="G204" t="str">
-        <v>太阳石.png</v>
+        <v>月光石.png</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>tys_stn_8</v>
+        <v>ygs_stn_10</v>
       </c>
       <c r="B205" t="str">
         <v>珠子</v>
@@ -5102,21 +5102,21 @@
         <v>礦石</v>
       </c>
       <c r="D205" t="str">
-        <v>太陽石</v>
+        <v>月光石</v>
       </c>
       <c r="E205">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F205">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="G205" t="str">
-        <v>太阳石.png</v>
+        <v>月光石.png</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>tys_stn_10</v>
+        <v>tys_stn_6</v>
       </c>
       <c r="B206" t="str">
         <v>珠子</v>
@@ -5128,10 +5128,10 @@
         <v>太陽石</v>
       </c>
       <c r="E206">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F206">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="G206" t="str">
         <v>太阳石.png</v>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>shlb_stn_8</v>
+        <v>tys_stn_8</v>
       </c>
       <c r="B207" t="str">
         <v>珠子</v>
@@ -5148,21 +5148,21 @@
         <v>礦石</v>
       </c>
       <c r="D207" t="str">
-        <v>聖海藍寶</v>
+        <v>太陽石</v>
       </c>
       <c r="E207">
         <v>8</v>
       </c>
       <c r="F207">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="G207" t="str">
-        <v>圣海蓝宝.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>shlb_stn_10</v>
+        <v>tys_stn_10</v>
       </c>
       <c r="B208" t="str">
         <v>珠子</v>
@@ -5171,67 +5171,67 @@
         <v>礦石</v>
       </c>
       <c r="D208" t="str">
-        <v>聖海藍寶</v>
+        <v>太陽石</v>
       </c>
       <c r="E208">
         <v>10</v>
       </c>
       <c r="F208">
-        <v>699</v>
+        <v>169</v>
       </c>
       <c r="G208" t="str">
-        <v>圣海蓝宝.png</v>
+        <v>太阳石.png</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>yslzzy_spc_8</v>
+        <v>shlb_stn_8</v>
       </c>
       <c r="B209" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C209" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D209" t="str">
-        <v>銀色六字真言</v>
+        <v>聖海藍寶</v>
       </c>
       <c r="E209">
         <v>8</v>
       </c>
       <c r="F209">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="G209" t="str">
-        <v>银色六字真言.png</v>
+        <v>圣海蓝宝.png</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>ketj_spc_6</v>
+        <v>shlb_stn_10</v>
       </c>
       <c r="B210" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C210" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D210" t="str">
-        <v>凱爾特結</v>
+        <v>聖海藍寶</v>
       </c>
       <c r="E210">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F210">
-        <v>59</v>
+        <v>699</v>
       </c>
       <c r="G210" t="str">
-        <v>凯尔特结.png</v>
+        <v>圣海蓝宝.png</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>ysxq_spc_8</v>
+        <v>yslzzy_spc_8</v>
       </c>
       <c r="B211" t="str">
         <v>配件</v>
@@ -5240,7 +5240,7 @@
         <v>隔珠</v>
       </c>
       <c r="D211" t="str">
-        <v>銀色繡球</v>
+        <v>銀六字箴言</v>
       </c>
       <c r="E211">
         <v>8</v>
@@ -5249,81 +5249,81 @@
         <v>59</v>
       </c>
       <c r="G211" t="str">
-        <v>银色绣球.png</v>
+        <v>银六字箴言.png</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>gtszz_xz_2</v>
+        <v>ketj_spc_6</v>
       </c>
       <c r="B212" t="str">
         <v>配件</v>
       </c>
       <c r="C212" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D212" t="str">
-        <v>古銅雙子</v>
+        <v>凱爾特結</v>
       </c>
       <c r="E212">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F212">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G212" t="str">
-        <v>古铜双子.png</v>
+        <v>凯尔特结.png</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>zsj_cysl_6</v>
+        <v>ysxq_spc_8</v>
       </c>
       <c r="B213" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C213" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D213" t="str">
-        <v>紫水晶</v>
+        <v>藏銀繡球</v>
       </c>
       <c r="E213">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F213">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G213" t="str">
-        <v>紫水晶.png</v>
+        <v>藏银绣球.png</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>zsj_cysl_8</v>
+        <v>gtszz_xz_2</v>
       </c>
       <c r="B214" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C214" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D214" t="str">
-        <v>紫水晶</v>
+        <v>古銅雙子</v>
       </c>
       <c r="E214">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F214">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="G214" t="str">
-        <v>紫水晶.png</v>
+        <v>古铜双子.png</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>zsj_cysl_10</v>
+        <v>zsj_cysl_6</v>
       </c>
       <c r="B215" t="str">
         <v>珠子</v>
@@ -5335,10 +5335,10 @@
         <v>紫水晶</v>
       </c>
       <c r="E215">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F215">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G215" t="str">
         <v>紫水晶.png</v>
@@ -5346,76 +5346,76 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>wgzl_pnd_2</v>
+        <v>zsj_cysl_8</v>
       </c>
       <c r="B216" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C216" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D216" t="str">
-        <v>王國之淚</v>
+        <v>紫水晶</v>
       </c>
       <c r="E216">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F216">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G216" t="str">
-        <v>王国之泪.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>gtsy_xz_2</v>
+        <v>zsj_cysl_10</v>
       </c>
       <c r="B217" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C217" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D217" t="str">
-        <v>古銅雙魚</v>
+        <v>紫水晶</v>
       </c>
       <c r="E217">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F217">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G217" t="str">
-        <v>古铜双鱼.png</v>
+        <v>紫水晶.png</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>gtmj_xz_2</v>
+        <v>wgzl_pnd_2</v>
       </c>
       <c r="B218" t="str">
         <v>配件</v>
       </c>
       <c r="C218" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D218" t="str">
-        <v>古銅摩羯</v>
+        <v>國王之淚</v>
       </c>
       <c r="E218">
         <v>2</v>
       </c>
       <c r="F218">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G218" t="str">
-        <v>古铜摩羯.png</v>
+        <v>国王之泪.png</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>gtss_xz_2</v>
+        <v>gtsy_xz_2</v>
       </c>
       <c r="B219" t="str">
         <v>配件</v>
@@ -5424,7 +5424,7 @@
         <v>星座</v>
       </c>
       <c r="D219" t="str">
-        <v>古銅射手</v>
+        <v>古銅雙魚</v>
       </c>
       <c r="E219">
         <v>2</v>
@@ -5433,12 +5433,12 @@
         <v>39</v>
       </c>
       <c r="G219" t="str">
-        <v>古铜射手.png</v>
+        <v>古铜双鱼.png</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>gtjn_xz_2</v>
+        <v>gtmj_xz_2</v>
       </c>
       <c r="B220" t="str">
         <v>配件</v>
@@ -5447,7 +5447,7 @@
         <v>星座</v>
       </c>
       <c r="D220" t="str">
-        <v>古銅金牛</v>
+        <v>古銅摩羯</v>
       </c>
       <c r="E220">
         <v>2</v>
@@ -5456,150 +5456,150 @@
         <v>39</v>
       </c>
       <c r="G220" t="str">
-        <v>古铜金牛.png</v>
+        <v>古铜摩羯.png</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>zfj_cysl_8</v>
+        <v>gtss_xz_2</v>
       </c>
       <c r="B221" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C221" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D221" t="str">
-        <v>紫粉晶</v>
+        <v>古銅射手</v>
       </c>
       <c r="E221">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F221">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G221" t="str">
-        <v>紫粉晶.png</v>
+        <v>古铜射手.png</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>zfj_cysl_10</v>
+        <v>gtjn_xz_2</v>
       </c>
       <c r="B222" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C222" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D222" t="str">
-        <v>紫粉晶</v>
+        <v>古銅金牛</v>
       </c>
       <c r="E222">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F222">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G222" t="str">
-        <v>紫粉晶.png</v>
+        <v>古铜金牛.png</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>gttx_xz_2</v>
+        <v>zfj_cysl_8</v>
       </c>
       <c r="B223" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C223" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D223" t="str">
-        <v>古銅天蠍</v>
+        <v>紫粉晶</v>
       </c>
       <c r="E223">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F223">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G223" t="str">
-        <v>古铜天蝎.png</v>
+        <v>紫粉晶.png</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>jslzzy_spc_8</v>
+        <v>zfj_cysl_10</v>
       </c>
       <c r="B224" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C224" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D224" t="str">
-        <v>金色六字真言</v>
+        <v>紫粉晶</v>
       </c>
       <c r="E224">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F224">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G224" t="str">
-        <v>金色六字真言.png</v>
+        <v>紫粉晶.png</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>cmj_cysl_6</v>
+        <v>gttx_xz_2</v>
       </c>
       <c r="B225" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C225" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D225" t="str">
-        <v>草莓晶</v>
+        <v>古銅天蠍</v>
       </c>
       <c r="E225">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F225">
         <v>39</v>
       </c>
       <c r="G225" t="str">
-        <v>草莓晶.png</v>
+        <v>古铜天蝎.png</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>cmj_cysl_8</v>
+        <v>jslzzy_spc_8</v>
       </c>
       <c r="B226" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C226" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D226" t="str">
-        <v>草莓晶</v>
+        <v>金六字箴言</v>
       </c>
       <c r="E226">
         <v>8</v>
       </c>
       <c r="F226">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G226" t="str">
-        <v>草莓晶.png</v>
+        <v>金六字箴言.png</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>cmj_cysl_10</v>
+        <v>cmj_cysl_6</v>
       </c>
       <c r="B227" t="str">
         <v>珠子</v>
@@ -5611,10 +5611,10 @@
         <v>草莓晶</v>
       </c>
       <c r="E227">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F227">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G227" t="str">
         <v>草莓晶.png</v>
@@ -5622,122 +5622,122 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>tg1_sz_7</v>
+        <v>cmj_cysl_8</v>
       </c>
       <c r="B228" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C228" t="str">
-        <v>數字</v>
+        <v>水晶</v>
       </c>
       <c r="D228" t="str">
-        <v>鈦鋼1</v>
+        <v>草莓晶</v>
       </c>
       <c r="E228">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F228">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G228" t="str">
-        <v>钛钢1.png</v>
+        <v>草莓晶.png</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>gtjx_xz_2</v>
+        <v>cmj_cysl_10</v>
       </c>
       <c r="B229" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C229" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D229" t="str">
-        <v>古銅巨蟹</v>
+        <v>草莓晶</v>
       </c>
       <c r="E229">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F229">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G229" t="str">
-        <v>古铜巨蟹.png</v>
+        <v>草莓晶.png</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>cyhdls_pnd_2</v>
+        <v>tg1_sz_7</v>
       </c>
       <c r="B230" t="str">
         <v>配件</v>
       </c>
       <c r="C230" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D230" t="str">
-        <v>藏銀蝴蝶流蘇</v>
+        <v>鈦鋼1</v>
       </c>
       <c r="E230">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F230">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="G230" t="str">
-        <v>藏银蝴蝶流苏.png</v>
+        <v>钛钢1.png</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>mghh_spc_6</v>
+        <v>gtjx_xz_2</v>
       </c>
       <c r="B231" t="str">
         <v>配件</v>
       </c>
       <c r="C231" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D231" t="str">
-        <v>玫瑰花環</v>
+        <v>古銅巨蟹</v>
       </c>
       <c r="E231">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F231">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G231" t="str">
-        <v>玫瑰花环.png</v>
+        <v>古铜巨蟹.png</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>bmnmh_spc_8</v>
+        <v>cyhdls_pnd_2</v>
       </c>
       <c r="B232" t="str">
         <v>配件</v>
       </c>
       <c r="C232" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D232" t="str">
-        <v>白瑪瑙魔盒</v>
+        <v>藏銀蝴蝶流蘇</v>
       </c>
       <c r="E232">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F232">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G232" t="str">
-        <v>白玛瑙魔盒.png</v>
+        <v>藏银蝴蝶流苏.png</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>cyhw_spc_5</v>
+        <v>mghh_spc_6</v>
       </c>
       <c r="B233" t="str">
         <v>配件</v>
@@ -5746,21 +5746,21 @@
         <v>隔珠</v>
       </c>
       <c r="D233" t="str">
-        <v>藏銀回紋</v>
+        <v>玫瑰花環</v>
       </c>
       <c r="E233">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F233">
         <v>59</v>
       </c>
       <c r="G233" t="str">
-        <v>藏银回纹.png</v>
+        <v>玫瑰花环.png</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>zsmh_spc_8</v>
+        <v>bmnmh_spc_8</v>
       </c>
       <c r="B234" t="str">
         <v>配件</v>
@@ -5769,7 +5769,7 @@
         <v>隔珠</v>
       </c>
       <c r="D234" t="str">
-        <v>硃砂魔盒</v>
+        <v>白瑪瑙魔盒</v>
       </c>
       <c r="E234">
         <v>8</v>
@@ -5778,104 +5778,104 @@
         <v>59</v>
       </c>
       <c r="G234" t="str">
-        <v>朱砂魔盒.png</v>
+        <v>白玛瑙魔盒.png</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>cyszdz_pnd_2</v>
+        <v>cyhw_spc_5</v>
       </c>
       <c r="B235" t="str">
         <v>配件</v>
       </c>
       <c r="C235" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D235" t="str">
-        <v>藏銀十字吊墜</v>
+        <v>藏銀回紋</v>
       </c>
       <c r="E235">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F235">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G235" t="str">
-        <v>藏银十字吊坠.png</v>
+        <v>藏银回纹.png</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>cyyc_pnd_2</v>
+        <v>zsmh_spc_8</v>
       </c>
       <c r="B236" t="str">
         <v>配件</v>
       </c>
       <c r="C236" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D236" t="str">
-        <v>藏銀葉叢</v>
+        <v>硃砂魔盒</v>
       </c>
       <c r="E236">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F236">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G236" t="str">
-        <v>藏银叶丛.png</v>
+        <v>朱砂魔盒.png</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>cyxhlf_spc_8</v>
+        <v>cyszdz_pnd_2</v>
       </c>
       <c r="B237" t="str">
         <v>配件</v>
       </c>
       <c r="C237" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D237" t="str">
-        <v>藏銀小花立方</v>
+        <v>藏銀十字</v>
       </c>
       <c r="E237">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F237">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G237" t="str">
-        <v>藏银小花立方.png</v>
+        <v>藏银十字.png</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>cydhlf_spc_8</v>
+        <v>cyyc_pnd_2</v>
       </c>
       <c r="B238" t="str">
         <v>配件</v>
       </c>
       <c r="C238" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D238" t="str">
-        <v>藏銀大花立方</v>
+        <v>藏銀葉叢</v>
       </c>
       <c r="E238">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F238">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G238" t="str">
-        <v>藏银大花立方.png</v>
+        <v>藏银叶丛.png</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>jtlfq_spc_8</v>
+        <v>cydhlf_spc_8</v>
       </c>
       <c r="B239" t="str">
         <v>配件</v>
@@ -5884,7 +5884,7 @@
         <v>隔珠</v>
       </c>
       <c r="D239" t="str">
-        <v>景泰藍福球</v>
+        <v>藏銀立方</v>
       </c>
       <c r="E239">
         <v>8</v>
@@ -5893,35 +5893,35 @@
         <v>59</v>
       </c>
       <c r="G239" t="str">
-        <v>景泰蓝福球.png</v>
+        <v>藏银立方.png</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>hjc_cysl_6</v>
+        <v>jtlfq_spc_8</v>
       </c>
       <c r="B240" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C240" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D240" t="str">
-        <v>黑金超</v>
+        <v>景泰藍</v>
       </c>
       <c r="E240">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F240">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G240" t="str">
-        <v>黑金超.png</v>
+        <v>景泰蓝.png</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>hjc_cysl_8</v>
+        <v>hjc_cysl_6</v>
       </c>
       <c r="B241" t="str">
         <v>珠子</v>
@@ -5933,10 +5933,10 @@
         <v>黑金超</v>
       </c>
       <c r="E241">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F241">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G241" t="str">
         <v>黑金超.png</v>
@@ -5944,7 +5944,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>hjc_cysl_10</v>
+        <v>hjc_cysl_8</v>
       </c>
       <c r="B242" t="str">
         <v>珠子</v>
@@ -5956,10 +5956,10 @@
         <v>黑金超</v>
       </c>
       <c r="E242">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F242">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G242" t="str">
         <v>黑金超.png</v>
@@ -5967,30 +5967,30 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>nh_agt_6</v>
+        <v>hjc_cysl_10</v>
       </c>
       <c r="B243" t="str">
         <v>珠子</v>
       </c>
       <c r="C243" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D243" t="str">
-        <v>南紅</v>
+        <v>黑金超</v>
       </c>
       <c r="E243">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F243">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G243" t="str">
-        <v>南红.png</v>
+        <v>黑金超.png</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>nh_agt_8</v>
+        <v>nh_agt_6</v>
       </c>
       <c r="B244" t="str">
         <v>珠子</v>
@@ -6002,10 +6002,10 @@
         <v>南紅</v>
       </c>
       <c r="E244">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F244">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G244" t="str">
         <v>南红.png</v>
@@ -6013,7 +6013,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>nh_agt_10</v>
+        <v>nh_agt_8</v>
       </c>
       <c r="B245" t="str">
         <v>珠子</v>
@@ -6025,10 +6025,10 @@
         <v>南紅</v>
       </c>
       <c r="E245">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F245">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="G245" t="str">
         <v>南红.png</v>
@@ -6036,30 +6036,30 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>hyes_stn_6</v>
+        <v>nh_agt_10</v>
       </c>
       <c r="B246" t="str">
         <v>珠子</v>
       </c>
       <c r="C246" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D246" t="str">
-        <v>虎眼石</v>
+        <v>南紅</v>
       </c>
       <c r="E246">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F246">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="G246" t="str">
-        <v>虎眼石.png</v>
+        <v>南红.png</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>hyes_stn_8</v>
+        <v>hyes_stn_6</v>
       </c>
       <c r="B247" t="str">
         <v>珠子</v>
@@ -6071,10 +6071,10 @@
         <v>虎眼石</v>
       </c>
       <c r="E247">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F247">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G247" t="str">
         <v>虎眼石.png</v>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>hyes_stn_10</v>
+        <v>hyes_stn_8</v>
       </c>
       <c r="B248" t="str">
         <v>珠子</v>
@@ -6094,10 +6094,10 @@
         <v>虎眼石</v>
       </c>
       <c r="E248">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F248">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G248" t="str">
         <v>虎眼石.png</v>
@@ -6105,30 +6105,30 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>gqys_agt_6</v>
+        <v>hyes_stn_10</v>
       </c>
       <c r="B249" t="str">
         <v>珠子</v>
       </c>
       <c r="C249" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D249" t="str">
-        <v>乾青玉髓</v>
+        <v>虎眼石</v>
       </c>
       <c r="E249">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F249">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G249" t="str">
-        <v>干青玉髓.png</v>
+        <v>虎眼石.png</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>gqys_agt_8</v>
+        <v>gqys_agt_6</v>
       </c>
       <c r="B250" t="str">
         <v>珠子</v>
@@ -6140,10 +6140,10 @@
         <v>乾青玉髓</v>
       </c>
       <c r="E250">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F250">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G250" t="str">
         <v>干青玉髓.png</v>
@@ -6151,7 +6151,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>gqys_agt_10</v>
+        <v>gqys_agt_8</v>
       </c>
       <c r="B251" t="str">
         <v>珠子</v>
@@ -6163,10 +6163,10 @@
         <v>乾青玉髓</v>
       </c>
       <c r="E251">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F251">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G251" t="str">
         <v>干青玉髓.png</v>
@@ -6174,30 +6174,30 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>yys_stn_6</v>
+        <v>gqys_agt_10</v>
       </c>
       <c r="B252" t="str">
         <v>珠子</v>
       </c>
       <c r="C252" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D252" t="str">
-        <v>銀曜石</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E252">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F252">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G252" t="str">
-        <v>银曜石.png</v>
+        <v>干青玉髓.png</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>yys_stn_8</v>
+        <v>yys_stn_6</v>
       </c>
       <c r="B253" t="str">
         <v>珠子</v>
@@ -6209,10 +6209,10 @@
         <v>銀曜石</v>
       </c>
       <c r="E253">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F253">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G253" t="str">
         <v>银曜石.png</v>
@@ -6220,7 +6220,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>yys_stn_10</v>
+        <v>yys_stn_8</v>
       </c>
       <c r="B254" t="str">
         <v>珠子</v>
@@ -6232,10 +6232,10 @@
         <v>銀曜石</v>
       </c>
       <c r="E254">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F254">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G254" t="str">
         <v>银曜石.png</v>
@@ -6243,53 +6243,53 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>bmw_pnd_2</v>
+        <v>yys_stn_10</v>
       </c>
       <c r="B255" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C255" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D255" t="str">
-        <v>捕夢網</v>
+        <v>銀曜石</v>
       </c>
       <c r="E255">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F255">
         <v>99</v>
       </c>
       <c r="G255" t="str">
-        <v>捕梦网.png</v>
+        <v>银曜石.png</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>zs_stn_6</v>
+        <v>bmw_pnd_2</v>
       </c>
       <c r="B256" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C256" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D256" t="str">
-        <v>硃砂</v>
+        <v>捕夢網</v>
       </c>
       <c r="E256">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F256">
         <v>99</v>
       </c>
       <c r="G256" t="str">
-        <v>朱砂.png</v>
+        <v>捕梦网.png</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>ljs_stn_6</v>
+        <v>zs_stn_6</v>
       </c>
       <c r="B257" t="str">
         <v>珠子</v>
@@ -6298,7 +6298,7 @@
         <v>礦石</v>
       </c>
       <c r="D257" t="str">
-        <v>藍晶石</v>
+        <v>硃砂</v>
       </c>
       <c r="E257">
         <v>6</v>
@@ -6307,12 +6307,12 @@
         <v>99</v>
       </c>
       <c r="G257" t="str">
-        <v>蓝晶石.png</v>
+        <v>朱砂.png</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>ljs_stn_8</v>
+        <v>ljs_stn_6</v>
       </c>
       <c r="B258" t="str">
         <v>珠子</v>
@@ -6324,10 +6324,10 @@
         <v>藍晶石</v>
       </c>
       <c r="E258">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F258">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="G258" t="str">
         <v>蓝晶石.png</v>
@@ -6335,7 +6335,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>ljs_stn_10</v>
+        <v>ljs_stn_8</v>
       </c>
       <c r="B259" t="str">
         <v>珠子</v>
@@ -6347,10 +6347,10 @@
         <v>藍晶石</v>
       </c>
       <c r="E259">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F259">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="G259" t="str">
         <v>蓝晶石.png</v>
@@ -6358,30 +6358,30 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>hmn_agt_6</v>
+        <v>ljs_stn_10</v>
       </c>
       <c r="B260" t="str">
         <v>珠子</v>
       </c>
       <c r="C260" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D260" t="str">
-        <v>紅瑪瑙</v>
+        <v>藍晶石</v>
       </c>
       <c r="E260">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F260">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="G260" t="str">
-        <v>红玛瑙.png</v>
+        <v>蓝晶石.png</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>hmn_agt_8</v>
+        <v>hmn_agt_6</v>
       </c>
       <c r="B261" t="str">
         <v>珠子</v>
@@ -6393,10 +6393,10 @@
         <v>紅瑪瑙</v>
       </c>
       <c r="E261">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F261">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G261" t="str">
         <v>红玛瑙.png</v>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>hmn_agt_10</v>
+        <v>hmn_agt_8</v>
       </c>
       <c r="B262" t="str">
         <v>珠子</v>
@@ -6416,10 +6416,10 @@
         <v>紅瑪瑙</v>
       </c>
       <c r="E262">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F262">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G262" t="str">
         <v>红玛瑙.png</v>
@@ -6427,30 +6427,30 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>csj_cysl_6</v>
+        <v>hmn_agt_10</v>
       </c>
       <c r="B263" t="str">
         <v>珠子</v>
       </c>
       <c r="C263" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D263" t="str">
-        <v>茶水晶</v>
+        <v>紅瑪瑙</v>
       </c>
       <c r="E263">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F263">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G263" t="str">
-        <v>茶水晶.png</v>
+        <v>红玛瑙.png</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>csj_cysl_8</v>
+        <v>csj_cysl_6</v>
       </c>
       <c r="B264" t="str">
         <v>珠子</v>
@@ -6462,10 +6462,10 @@
         <v>茶水晶</v>
       </c>
       <c r="E264">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F264">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G264" t="str">
         <v>茶水晶.png</v>
@@ -6473,7 +6473,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>csj_cysl_10</v>
+        <v>csj_cysl_8</v>
       </c>
       <c r="B265" t="str">
         <v>珠子</v>
@@ -6485,10 +6485,10 @@
         <v>茶水晶</v>
       </c>
       <c r="E265">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F265">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G265" t="str">
         <v>茶水晶.png</v>
@@ -6496,30 +6496,30 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>kqs_stn_6</v>
+        <v>csj_cysl_10</v>
       </c>
       <c r="B266" t="str">
         <v>珠子</v>
       </c>
       <c r="C266" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D266" t="str">
-        <v>孔雀石</v>
+        <v>茶水晶</v>
       </c>
       <c r="E266">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F266">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G266" t="str">
-        <v>孔雀石.png</v>
+        <v>茶水晶.png</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>kqs_stn_8</v>
+        <v>kqs_stn_6</v>
       </c>
       <c r="B267" t="str">
         <v>珠子</v>
@@ -6531,10 +6531,10 @@
         <v>孔雀石</v>
       </c>
       <c r="E267">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F267">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G267" t="str">
         <v>孔雀石.png</v>
@@ -6542,7 +6542,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>kqs_stn_10</v>
+        <v>kqs_stn_8</v>
       </c>
       <c r="B268" t="str">
         <v>珠子</v>
@@ -6554,10 +6554,10 @@
         <v>孔雀石</v>
       </c>
       <c r="E268">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F268">
-        <v>199</v>
+        <v>89</v>
       </c>
       <c r="G268" t="str">
         <v>孔雀石.png</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>qjs_stn_6</v>
+        <v>kqs_stn_10</v>
       </c>
       <c r="B269" t="str">
         <v>珠子</v>
@@ -6574,21 +6574,21 @@
         <v>礦石</v>
       </c>
       <c r="D269" t="str">
-        <v>青金石</v>
+        <v>孔雀石</v>
       </c>
       <c r="E269">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F269">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="G269" t="str">
-        <v>青金石.png</v>
+        <v>孔雀石.png</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>qjs_stn_8</v>
+        <v>qjs_stn_6</v>
       </c>
       <c r="B270" t="str">
         <v>珠子</v>
@@ -6600,10 +6600,10 @@
         <v>青金石</v>
       </c>
       <c r="E270">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F270">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G270" t="str">
         <v>青金石.png</v>
@@ -6611,7 +6611,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>qjs_stn_10</v>
+        <v>qjs_stn_8</v>
       </c>
       <c r="B271" t="str">
         <v>珠子</v>
@@ -6623,10 +6623,10 @@
         <v>青金石</v>
       </c>
       <c r="E271">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F271">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G271" t="str">
         <v>青金石.png</v>
@@ -6634,30 +6634,30 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>wlg_cysl_6</v>
+        <v>qjs_stn_10</v>
       </c>
       <c r="B272" t="str">
         <v>珠子</v>
       </c>
       <c r="C272" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D272" t="str">
-        <v>烏拉圭</v>
+        <v>青金石</v>
       </c>
       <c r="E272">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F272">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G272" t="str">
-        <v>乌拉圭.png</v>
+        <v>青金石.png</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>wlg_cysl_8</v>
+        <v>wlg_cysl_6</v>
       </c>
       <c r="B273" t="str">
         <v>珠子</v>
@@ -6669,10 +6669,10 @@
         <v>烏拉圭</v>
       </c>
       <c r="E273">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F273">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G273" t="str">
         <v>乌拉圭.png</v>
@@ -6680,7 +6680,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>wlg_cysl_10</v>
+        <v>wlg_cysl_8</v>
       </c>
       <c r="B274" t="str">
         <v>珠子</v>
@@ -6692,10 +6692,10 @@
         <v>烏拉圭</v>
       </c>
       <c r="E274">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F274">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="G274" t="str">
         <v>乌拉圭.png</v>
@@ -6703,7 +6703,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>zyl_cysl_6</v>
+        <v>wlg_cysl_10</v>
       </c>
       <c r="B275" t="str">
         <v>珠子</v>
@@ -6712,21 +6712,21 @@
         <v>水晶</v>
       </c>
       <c r="D275" t="str">
-        <v>紫幽靈</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E275">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F275">
-        <v>39</v>
+        <v>169</v>
       </c>
       <c r="G275" t="str">
-        <v>紫幽灵.png</v>
+        <v>乌拉圭.png</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>zyl_cysl_8</v>
+        <v>zyl_cysl_6</v>
       </c>
       <c r="B276" t="str">
         <v>珠子</v>
@@ -6738,10 +6738,10 @@
         <v>紫幽靈</v>
       </c>
       <c r="E276">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F276">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G276" t="str">
         <v>紫幽灵.png</v>
@@ -6749,30 +6749,30 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>he_agt_6</v>
+        <v>zyl_cysl_8</v>
       </c>
       <c r="B277" t="str">
         <v>珠子</v>
       </c>
       <c r="C277" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D277" t="str">
-        <v>黑瑪瑙</v>
+        <v>紫幽靈</v>
       </c>
       <c r="E277">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F277">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G277" t="str">
-        <v>黑玛瑙.png</v>
+        <v>紫幽灵.png</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>he_agt_8</v>
+        <v>he_agt_6</v>
       </c>
       <c r="B278" t="str">
         <v>珠子</v>
@@ -6784,10 +6784,10 @@
         <v>黑瑪瑙</v>
       </c>
       <c r="E278">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F278">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G278" t="str">
         <v>黑玛瑙.png</v>
@@ -6795,7 +6795,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>he_agt_10</v>
+        <v>he_agt_8</v>
       </c>
       <c r="B279" t="str">
         <v>珠子</v>
@@ -6807,10 +6807,10 @@
         <v>黑瑪瑙</v>
       </c>
       <c r="E279">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F279">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G279" t="str">
         <v>黑玛瑙.png</v>
@@ -6818,30 +6818,30 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>zjs_stn_6</v>
+        <v>he_agt_10</v>
       </c>
       <c r="B280" t="str">
         <v>珠子</v>
       </c>
       <c r="C280" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D280" t="str">
-        <v>紫金砂</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E280">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F280">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G280" t="str">
-        <v>紫金砂.png</v>
+        <v>黑玛瑙.png</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>zjs_stn_8</v>
+        <v>zjs_stn_6</v>
       </c>
       <c r="B281" t="str">
         <v>珠子</v>
@@ -6853,10 +6853,10 @@
         <v>紫金砂</v>
       </c>
       <c r="E281">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F281">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G281" t="str">
         <v>紫金砂.png</v>
@@ -6864,7 +6864,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>zjs_stn_10</v>
+        <v>zjs_stn_8</v>
       </c>
       <c r="B282" t="str">
         <v>珠子</v>
@@ -6876,10 +6876,10 @@
         <v>紫金砂</v>
       </c>
       <c r="E282">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F282">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G282" t="str">
         <v>紫金砂.png</v>
@@ -6887,7 +6887,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>jys_stn_6</v>
+        <v>zjs_stn_10</v>
       </c>
       <c r="B283" t="str">
         <v>珠子</v>
@@ -6896,21 +6896,21 @@
         <v>礦石</v>
       </c>
       <c r="D283" t="str">
-        <v>金曜石</v>
+        <v>紫金砂</v>
       </c>
       <c r="E283">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F283">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="G283" t="str">
-        <v>金曜石.png</v>
+        <v>紫金砂.png</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>jys_stn_8</v>
+        <v>jys_stn_6</v>
       </c>
       <c r="B284" t="str">
         <v>珠子</v>
@@ -6922,10 +6922,10 @@
         <v>金曜石</v>
       </c>
       <c r="E284">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F284">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G284" t="str">
         <v>金曜石.png</v>
@@ -6933,7 +6933,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>jys_stn_10</v>
+        <v>jys_stn_8</v>
       </c>
       <c r="B285" t="str">
         <v>珠子</v>
@@ -6945,10 +6945,10 @@
         <v>金曜石</v>
       </c>
       <c r="E285">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F285">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G285" t="str">
         <v>金曜石.png</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>hys_stn_6</v>
+        <v>jys_stn_10</v>
       </c>
       <c r="B286" t="str">
         <v>珠子</v>
@@ -6965,21 +6965,21 @@
         <v>礦石</v>
       </c>
       <c r="D286" t="str">
-        <v>黑曜石</v>
+        <v>金曜石</v>
       </c>
       <c r="E286">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F286">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G286" t="str">
-        <v>黑曜石.png</v>
+        <v>金曜石.png</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>hys_stn_8</v>
+        <v>hys_stn_6</v>
       </c>
       <c r="B287" t="str">
         <v>珠子</v>
@@ -6991,10 +6991,10 @@
         <v>黑曜石</v>
       </c>
       <c r="E287">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F287">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G287" t="str">
         <v>黑曜石.png</v>
@@ -7002,7 +7002,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>hys_stn_10</v>
+        <v>hys_stn_8</v>
       </c>
       <c r="B288" t="str">
         <v>珠子</v>
@@ -7014,18 +7014,41 @@
         <v>黑曜石</v>
       </c>
       <c r="E288">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F288">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G288" t="str">
         <v>黑曜石.png</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>hys_stn_10</v>
+      </c>
+      <c r="B289" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C289" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D289" t="str">
+        <v>黑曜石</v>
+      </c>
+      <c r="E289">
+        <v>10</v>
+      </c>
+      <c r="F289">
+        <v>99</v>
+      </c>
+      <c r="G289" t="str">
+        <v>黑曜石.png</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G288"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G289"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G289"/>
+  <dimension ref="A1:I259"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,10 +416,16 @@
         <v>size_mm</v>
       </c>
       <c r="F1" t="str">
+        <v>high_mm</v>
+      </c>
+      <c r="G1" t="str">
         <v>price_twd</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>picture</v>
+      </c>
+      <c r="I1" t="str">
+        <v>supply</v>
       </c>
     </row>
     <row r="2">
@@ -439,10 +445,16 @@
         <v>6</v>
       </c>
       <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
         <v>39</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>白水晶.png</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -462,10 +474,16 @@
         <v>8</v>
       </c>
       <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
         <v>59</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>白水晶.png</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -485,10 +503,16 @@
         <v>10</v>
       </c>
       <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
         <v>89</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>白水晶.png</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -508,10 +532,16 @@
         <v>6</v>
       </c>
       <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
         <v>59</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>雪花幽灵.png</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -531,10 +561,16 @@
         <v>8</v>
       </c>
       <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
         <v>89</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>雪花幽灵.png</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -554,10 +590,16 @@
         <v>10</v>
       </c>
       <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
         <v>139</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>雪花幽灵.png</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -577,38 +619,50 @@
         <v>8</v>
       </c>
       <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
         <v>69</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>白幽灵.png</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>sd_pnd_2</v>
+        <v>dszzhu_prl_6</v>
       </c>
       <c r="B9" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C9" t="str">
-        <v>吊墜</v>
+        <v>珍珠</v>
       </c>
       <c r="D9" t="str">
-        <v>絲帶</v>
+        <v>淡水珍珠</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
         <v>99</v>
       </c>
-      <c r="G9" t="str">
-        <v>丝带.png</v>
+      <c r="H9" t="str">
+        <v>淡水珍珠.png</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>dszzhu_prl_6</v>
+        <v>dszzhu_prl_8</v>
       </c>
       <c r="B10" t="str">
         <v>珠子</v>
@@ -620,18 +674,24 @@
         <v>淡水珍珠</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>99</v>
-      </c>
-      <c r="G10" t="str">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>169</v>
+      </c>
+      <c r="H10" t="str">
         <v>淡水珍珠.png</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>dszzhu_prl_8</v>
+        <v>dszzhu_prl_10</v>
       </c>
       <c r="B11" t="str">
         <v>珠子</v>
@@ -643,41 +703,53 @@
         <v>淡水珍珠</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>169</v>
-      </c>
-      <c r="G11" t="str">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>199</v>
+      </c>
+      <c r="H11" t="str">
         <v>淡水珍珠.png</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>dszzhu_prl_10</v>
+        <v>nbj_cysl_8</v>
       </c>
       <c r="B12" t="str">
         <v>珠子</v>
       </c>
       <c r="C12" t="str">
-        <v>珍珠</v>
+        <v>水晶</v>
       </c>
       <c r="D12" t="str">
-        <v>淡水珍珠</v>
+        <v>奶白晶</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>199</v>
-      </c>
-      <c r="G12" t="str">
-        <v>淡水珍珠.png</v>
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>69</v>
+      </c>
+      <c r="H12" t="str">
+        <v>奶白晶.png</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>nbj_cysl_8</v>
+        <v>nbj_cysl_10</v>
       </c>
       <c r="B13" t="str">
         <v>珠子</v>
@@ -689,41 +761,53 @@
         <v>奶白晶</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13">
-        <v>69</v>
-      </c>
-      <c r="G13" t="str">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>99</v>
+      </c>
+      <c r="H13" t="str">
         <v>奶白晶.png</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>nbj_cysl_10</v>
+        <v>pts_stn_6</v>
       </c>
       <c r="B14" t="str">
         <v>珠子</v>
       </c>
       <c r="C14" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D14" t="str">
-        <v>奶白晶</v>
+        <v>葡萄石</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>99</v>
-      </c>
-      <c r="G14" t="str">
-        <v>奶白晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>49</v>
+      </c>
+      <c r="H14" t="str">
+        <v>葡萄石.png</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>pts_stn_6</v>
+        <v>pts_stn_10</v>
       </c>
       <c r="B15" t="str">
         <v>珠子</v>
@@ -735,64 +819,82 @@
         <v>葡萄石</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>49</v>
-      </c>
-      <c r="G15" t="str">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>89</v>
+      </c>
+      <c r="H15" t="str">
         <v>葡萄石.png</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>pts_stn_10</v>
+        <v>mxxx_pnd_2</v>
       </c>
       <c r="B16" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C16" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D16" t="str">
-        <v>葡萄石</v>
+        <v>滿鑲星星</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>89</v>
-      </c>
-      <c r="G16" t="str">
-        <v>葡萄石.png</v>
+        <v>20</v>
+      </c>
+      <c r="G16">
+        <v>69</v>
+      </c>
+      <c r="H16" t="str">
+        <v>满镶星星.png</v>
+      </c>
+      <c r="I16" t="str">
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>lkzls_spc_6</v>
+        <v>pl_pnd_5</v>
       </c>
       <c r="B17" t="str">
         <v>配件</v>
       </c>
       <c r="C17" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D17" t="str">
-        <v>鏤空鑽蕾絲</v>
+        <v>霹靂</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>59</v>
-      </c>
-      <c r="G17" t="str">
-        <v>镂空钻蕾丝.png</v>
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>49</v>
+      </c>
+      <c r="H17" t="str">
+        <v>霹雳.png</v>
+      </c>
+      <c r="I17" t="str">
+        <v>義烏市眾帆</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>mxxx_pnd_2</v>
+        <v>axqbz_pnd_2</v>
       </c>
       <c r="B18" t="str">
         <v>配件</v>
@@ -801,159 +903,201 @@
         <v>吊墜</v>
       </c>
       <c r="D18" t="str">
-        <v>滿鑲星星</v>
+        <v>愛心曲別針</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>99</v>
-      </c>
-      <c r="G18" t="str">
-        <v>满镶星星.png</v>
+        <v>30</v>
+      </c>
+      <c r="G18">
+        <v>59</v>
+      </c>
+      <c r="H18" t="str">
+        <v>爱心曲别针.png</v>
+      </c>
+      <c r="I18" t="str">
+        <v>義烏市爆財</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>pl_pnd_2</v>
+        <v>xgfj_cysl_6</v>
       </c>
       <c r="B19" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C19" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D19" t="str">
-        <v>霹靂</v>
+        <v>星光粉晶</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F19">
-        <v>99</v>
-      </c>
-      <c r="G19" t="str">
-        <v>霹雳.png</v>
+        <v>6</v>
+      </c>
+      <c r="G19">
+        <v>49</v>
+      </c>
+      <c r="H19" t="str">
+        <v>星光粉晶.png</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>lkxm_pnd_2</v>
+        <v>xgfj_cysl_8</v>
       </c>
       <c r="B20" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C20" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D20" t="str">
-        <v>鏤空小貓</v>
+        <v>星光粉晶</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>99</v>
-      </c>
-      <c r="G20" t="str">
-        <v>镂空小猫.png</v>
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>69</v>
+      </c>
+      <c r="H20" t="str">
+        <v>星光粉晶.png</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>axqbz_pnd_2</v>
+        <v>xgfj_cysl_10</v>
       </c>
       <c r="B21" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C21" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D21" t="str">
-        <v>愛心曲別針</v>
+        <v>星光粉晶</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
         <v>99</v>
       </c>
-      <c r="G21" t="str">
-        <v>爱心曲别针.png</v>
+      <c r="H21" t="str">
+        <v>星光粉晶.png</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>gsmhz_spc_8</v>
+        <v>by_agt_6</v>
       </c>
       <c r="B22" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C22" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D22" t="str">
-        <v>鋯石魔盒鑽</v>
+        <v>白玉髓</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>59</v>
-      </c>
-      <c r="G22" t="str">
-        <v>锆石魔盒钻.png</v>
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <v>39</v>
+      </c>
+      <c r="H22" t="str">
+        <v>白玉髓.png</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>xgfj_cysl_6</v>
+        <v>by_agt_8</v>
       </c>
       <c r="B23" t="str">
         <v>珠子</v>
       </c>
       <c r="C23" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D23" t="str">
-        <v>星光粉晶</v>
+        <v>白玉髓</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>49</v>
-      </c>
-      <c r="G23" t="str">
-        <v>星光粉晶.png</v>
+        <v>8</v>
+      </c>
+      <c r="G23">
+        <v>59</v>
+      </c>
+      <c r="H23" t="str">
+        <v>白玉髓.png</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>xgfj_cysl_8</v>
+        <v>by_agt_10</v>
       </c>
       <c r="B24" t="str">
         <v>珠子</v>
       </c>
       <c r="C24" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D24" t="str">
-        <v>星光粉晶</v>
+        <v>白玉髓</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>69</v>
-      </c>
-      <c r="G24" t="str">
-        <v>星光粉晶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>89</v>
+      </c>
+      <c r="H24" t="str">
+        <v>白玉髓.png</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>xgfj_cysl_10</v>
+        <v>zlh_cysl_6</v>
       </c>
       <c r="B25" t="str">
         <v>珠子</v>
@@ -962,90 +1106,114 @@
         <v>水晶</v>
       </c>
       <c r="D25" t="str">
-        <v>星光粉晶</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F25">
-        <v>99</v>
-      </c>
-      <c r="G25" t="str">
-        <v>星光粉晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G25">
+        <v>89</v>
+      </c>
+      <c r="H25" t="str">
+        <v>紫锂辉.png</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>by_agt_6</v>
+        <v>zlh_cysl_8</v>
       </c>
       <c r="B26" t="str">
         <v>珠子</v>
       </c>
       <c r="C26" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D26" t="str">
-        <v>白玉髓</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26">
-        <v>39</v>
-      </c>
-      <c r="G26" t="str">
-        <v>白玉髓.png</v>
+        <v>8</v>
+      </c>
+      <c r="G26">
+        <v>129</v>
+      </c>
+      <c r="H26" t="str">
+        <v>紫锂辉.png</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>by_agt_8</v>
+        <v>zlh_cysl_10</v>
       </c>
       <c r="B27" t="str">
         <v>珠子</v>
       </c>
       <c r="C27" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D27" t="str">
-        <v>白玉髓</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>59</v>
-      </c>
-      <c r="G27" t="str">
-        <v>白玉髓.png</v>
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>169</v>
+      </c>
+      <c r="H27" t="str">
+        <v>紫锂辉.png</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>by_agt_10</v>
+        <v>lglf_spc_8</v>
       </c>
       <c r="B28" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C28" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D28" t="str">
-        <v>白玉髓</v>
+        <v>菱格立方</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>89</v>
-      </c>
-      <c r="G28" t="str">
-        <v>白玉髓.png</v>
+        <v>8</v>
+      </c>
+      <c r="G28">
+        <v>99</v>
+      </c>
+      <c r="H28" t="str">
+        <v>菱格立方.png</v>
+      </c>
+      <c r="I28" t="str">
+        <v>廣州市荔灣區金嶠旭</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>zlh_cysl_6</v>
+        <v>fsj_cysl_6</v>
       </c>
       <c r="B29" t="str">
         <v>珠子</v>
@@ -1054,21 +1222,27 @@
         <v>水晶</v>
       </c>
       <c r="D29" t="str">
-        <v>紫鋰輝</v>
+        <v>粉水晶</v>
       </c>
       <c r="E29">
         <v>6</v>
       </c>
       <c r="F29">
-        <v>89</v>
-      </c>
-      <c r="G29" t="str">
-        <v>紫锂辉.png</v>
+        <v>6</v>
+      </c>
+      <c r="G29">
+        <v>39</v>
+      </c>
+      <c r="H29" t="str">
+        <v>粉水晶.png</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>zlh_cysl_8</v>
+        <v>fsj_cysl_8</v>
       </c>
       <c r="B30" t="str">
         <v>珠子</v>
@@ -1077,21 +1251,27 @@
         <v>水晶</v>
       </c>
       <c r="D30" t="str">
-        <v>紫鋰輝</v>
+        <v>粉水晶</v>
       </c>
       <c r="E30">
         <v>8</v>
       </c>
       <c r="F30">
-        <v>129</v>
-      </c>
-      <c r="G30" t="str">
-        <v>紫锂辉.png</v>
+        <v>8</v>
+      </c>
+      <c r="G30">
+        <v>59</v>
+      </c>
+      <c r="H30" t="str">
+        <v>粉水晶.png</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>zlh_cysl_10</v>
+        <v>fsj_cysl_10</v>
       </c>
       <c r="B31" t="str">
         <v>珠子</v>
@@ -1100,67 +1280,85 @@
         <v>水晶</v>
       </c>
       <c r="D31" t="str">
-        <v>紫鋰輝</v>
+        <v>粉水晶</v>
       </c>
       <c r="E31">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>169</v>
-      </c>
-      <c r="G31" t="str">
-        <v>紫锂辉.png</v>
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>99</v>
+      </c>
+      <c r="H31" t="str">
+        <v>粉水晶.png</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lglf_spc_8</v>
+        <v>ysmxyl_pnd_2</v>
       </c>
       <c r="B32" t="str">
         <v>配件</v>
       </c>
       <c r="C32" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D32" t="str">
-        <v>菱格立方</v>
+        <v>滿鑲月亮</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>59</v>
-      </c>
-      <c r="G32" t="str">
-        <v>菱格立方.png</v>
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>69</v>
+      </c>
+      <c r="H32" t="str">
+        <v>满镶月亮.png</v>
+      </c>
+      <c r="I32" t="str">
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>fsj_cysl_6</v>
+        <v>lkjf_pnd_2</v>
       </c>
       <c r="B33" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C33" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D33" t="str">
-        <v>粉水晶</v>
+        <v>鏤空金福</v>
       </c>
       <c r="E33">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>39</v>
-      </c>
-      <c r="G33" t="str">
-        <v>粉水晶.png</v>
+        <v>14</v>
+      </c>
+      <c r="G33">
+        <v>599</v>
+      </c>
+      <c r="H33" t="str">
+        <v>镂空金福.png</v>
+      </c>
+      <c r="I33" t="str">
+        <v>廣州市荔灣區嘉明銀飾</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>fsj_cysl_8</v>
+        <v>bas_cysl_8</v>
       </c>
       <c r="B34" t="str">
         <v>珠子</v>
@@ -1169,21 +1367,27 @@
         <v>水晶</v>
       </c>
       <c r="D34" t="str">
-        <v>粉水晶</v>
+        <v>白阿塞</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
       <c r="F34">
-        <v>59</v>
-      </c>
-      <c r="G34" t="str">
-        <v>粉水晶.png</v>
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>69</v>
+      </c>
+      <c r="H34" t="str">
+        <v>白阿塞.png</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>fsj_cysl_10</v>
+        <v>bas_cysl_10</v>
       </c>
       <c r="B35" t="str">
         <v>珠子</v>
@@ -1192,136 +1396,172 @@
         <v>水晶</v>
       </c>
       <c r="D35" t="str">
-        <v>粉水晶</v>
+        <v>白阿塞</v>
       </c>
       <c r="E35">
         <v>10</v>
       </c>
       <c r="F35">
+        <v>10</v>
+      </c>
+      <c r="G35">
         <v>99</v>
       </c>
-      <c r="G35" t="str">
-        <v>粉水晶.png</v>
+      <c r="H35" t="str">
+        <v>白阿塞.png</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ysmxyl_pnd_2</v>
+        <v>nyhlb_stn_6</v>
       </c>
       <c r="B36" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C36" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D36" t="str">
-        <v>滿鑲月亮</v>
+        <v>奶油海藍寶</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>99</v>
-      </c>
-      <c r="G36" t="str">
-        <v>满镶月亮.png</v>
+        <v>6</v>
+      </c>
+      <c r="G36">
+        <v>69</v>
+      </c>
+      <c r="H36" t="str">
+        <v>奶油海蓝宝.png</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>gsfz_spc_6</v>
+        <v>nyhlb_stn_8</v>
       </c>
       <c r="B37" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C37" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D37" t="str">
-        <v>鋯石方鑽</v>
+        <v>奶油海藍寶</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>59</v>
-      </c>
-      <c r="G37" t="str">
-        <v>锆石方钻.png</v>
+        <v>8</v>
+      </c>
+      <c r="G37">
+        <v>99</v>
+      </c>
+      <c r="H37" t="str">
+        <v>奶油海蓝宝.png</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>lkjf_pnd_2</v>
+        <v>nyhlb_stn_10</v>
       </c>
       <c r="B38" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C38" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D38" t="str">
-        <v>鏤空金福</v>
+        <v>奶油海藍寶</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F38">
-        <v>99</v>
-      </c>
-      <c r="G38" t="str">
-        <v>镂空金福.png</v>
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>139</v>
+      </c>
+      <c r="H38" t="str">
+        <v>奶油海蓝宝.png</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>bas_cysl_8</v>
+        <v>zys_agt_6</v>
       </c>
       <c r="B39" t="str">
         <v>珠子</v>
       </c>
       <c r="C39" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D39" t="str">
-        <v>白阿塞</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>69</v>
-      </c>
-      <c r="G39" t="str">
-        <v>白阿塞.png</v>
+        <v>6</v>
+      </c>
+      <c r="G39">
+        <v>39</v>
+      </c>
+      <c r="H39" t="str">
+        <v>紫玉髓.png</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>bas_cysl_10</v>
+        <v>zys_agt_8</v>
       </c>
       <c r="B40" t="str">
         <v>珠子</v>
       </c>
       <c r="C40" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D40" t="str">
-        <v>白阿塞</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F40">
-        <v>99</v>
-      </c>
-      <c r="G40" t="str">
-        <v>白阿塞.png</v>
+        <v>8</v>
+      </c>
+      <c r="G40">
+        <v>59</v>
+      </c>
+      <c r="H40" t="str">
+        <v>紫玉髓.png</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>nyhlb_stn_6</v>
+        <v>hws_stn_6</v>
       </c>
       <c r="B41" t="str">
         <v>珠子</v>
@@ -1330,21 +1570,27 @@
         <v>礦石</v>
       </c>
       <c r="D41" t="str">
-        <v>奶油海藍寶</v>
+        <v>海紋石</v>
       </c>
       <c r="E41">
         <v>6</v>
       </c>
       <c r="F41">
+        <v>6</v>
+      </c>
+      <c r="G41">
         <v>69</v>
       </c>
-      <c r="G41" t="str">
-        <v>奶油海蓝宝.png</v>
+      <c r="H41" t="str">
+        <v>海纹石.png</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>nyhlb_stn_8</v>
+        <v>hws_stn_8</v>
       </c>
       <c r="B42" t="str">
         <v>珠子</v>
@@ -1353,21 +1599,27 @@
         <v>礦石</v>
       </c>
       <c r="D42" t="str">
-        <v>奶油海藍寶</v>
+        <v>海紋石</v>
       </c>
       <c r="E42">
         <v>8</v>
       </c>
       <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42">
         <v>99</v>
       </c>
-      <c r="G42" t="str">
-        <v>奶油海蓝宝.png</v>
+      <c r="H42" t="str">
+        <v>海纹石.png</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>nyhlb_stn_10</v>
+        <v>hws_stn_10</v>
       </c>
       <c r="B43" t="str">
         <v>珠子</v>
@@ -1376,297 +1628,375 @@
         <v>礦石</v>
       </c>
       <c r="D43" t="str">
-        <v>奶油海藍寶</v>
+        <v>海紋石</v>
       </c>
       <c r="E43">
         <v>10</v>
       </c>
       <c r="F43">
-        <v>139</v>
-      </c>
-      <c r="G43" t="str">
-        <v>奶油海蓝宝.png</v>
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>169</v>
+      </c>
+      <c r="H43" t="str">
+        <v>海纹石.png</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>zys_agt_6</v>
+        <v>jfj_cysl_6</v>
       </c>
       <c r="B44" t="str">
         <v>珠子</v>
       </c>
       <c r="C44" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D44" t="str">
-        <v>紫玉髓</v>
+        <v>金髮晶</v>
       </c>
       <c r="E44">
         <v>6</v>
       </c>
       <c r="F44">
-        <v>39</v>
-      </c>
-      <c r="G44" t="str">
-        <v>紫玉髓.png</v>
+        <v>6</v>
+      </c>
+      <c r="G44">
+        <v>49</v>
+      </c>
+      <c r="H44" t="str">
+        <v>金发晶.png</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>zys_agt_8</v>
+        <v>jfj_cysl_8</v>
       </c>
       <c r="B45" t="str">
         <v>珠子</v>
       </c>
       <c r="C45" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D45" t="str">
-        <v>紫玉髓</v>
+        <v>金髮晶</v>
       </c>
       <c r="E45">
         <v>8</v>
       </c>
       <c r="F45">
-        <v>59</v>
-      </c>
-      <c r="G45" t="str">
-        <v>紫玉髓.png</v>
+        <v>8</v>
+      </c>
+      <c r="G45">
+        <v>69</v>
+      </c>
+      <c r="H45" t="str">
+        <v>金发晶.png</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>hws_stn_6</v>
+        <v>jfj_cysl_10</v>
       </c>
       <c r="B46" t="str">
         <v>珠子</v>
       </c>
       <c r="C46" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D46" t="str">
-        <v>海紋石</v>
+        <v>金髮晶</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>69</v>
-      </c>
-      <c r="G46" t="str">
-        <v>海纹石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G46">
+        <v>99</v>
+      </c>
+      <c r="H46" t="str">
+        <v>金发晶.png</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>hws_stn_8</v>
+        <v>bsyw_pnd_2</v>
       </c>
       <c r="B47" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C47" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D47" t="str">
-        <v>海紋石</v>
+        <v>白水魚尾</v>
       </c>
       <c r="E47">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F47">
-        <v>99</v>
-      </c>
-      <c r="G47" t="str">
-        <v>海纹石.png</v>
+        <v>14</v>
+      </c>
+      <c r="G47">
+        <v>699</v>
+      </c>
+      <c r="H47" t="str">
+        <v>白水鱼尾.png</v>
+      </c>
+      <c r="I47" t="str">
+        <v>廣州市荔灣區嘉明</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>hws_stn_10</v>
+        <v>zyb_spc_6</v>
       </c>
       <c r="B48" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C48" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D48" t="str">
-        <v>海紋石</v>
+        <v>轉運柄</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F48">
-        <v>169</v>
-      </c>
-      <c r="G48" t="str">
-        <v>海纹石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G48">
+        <v>399</v>
+      </c>
+      <c r="H48" t="str">
+        <v>转运柄.png</v>
+      </c>
+      <c r="I48" t="str">
+        <v>莆田市秀嶼區東嶠寶鑫格</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>jfj_cysl_6</v>
+        <v>lwmn_agt_6</v>
       </c>
       <c r="B49" t="str">
         <v>珠子</v>
       </c>
       <c r="C49" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D49" t="str">
-        <v>金髮晶</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
       <c r="F49">
-        <v>49</v>
-      </c>
-      <c r="G49" t="str">
-        <v>金发晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G49">
+        <v>69</v>
+      </c>
+      <c r="H49" t="str">
+        <v>蓝纹玛瑙.png</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>jfj_cysl_8</v>
+        <v>lwmn_agt_8</v>
       </c>
       <c r="B50" t="str">
         <v>珠子</v>
       </c>
       <c r="C50" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D50" t="str">
-        <v>金髮晶</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E50">
         <v>8</v>
       </c>
       <c r="F50">
-        <v>69</v>
-      </c>
-      <c r="G50" t="str">
-        <v>金发晶.png</v>
+        <v>8</v>
+      </c>
+      <c r="G50">
+        <v>99</v>
+      </c>
+      <c r="H50" t="str">
+        <v>蓝纹玛瑙.png</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>jfj_cysl_10</v>
+        <v>lwmn_agt_10</v>
       </c>
       <c r="B51" t="str">
         <v>珠子</v>
       </c>
       <c r="C51" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D51" t="str">
-        <v>金髮晶</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E51">
         <v>10</v>
       </c>
       <c r="F51">
-        <v>99</v>
-      </c>
-      <c r="G51" t="str">
-        <v>金发晶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G51">
+        <v>199</v>
+      </c>
+      <c r="H51" t="str">
+        <v>蓝纹玛瑙.png</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>wlyz_spc_5</v>
+        <v>xyc_cysl_8</v>
       </c>
       <c r="B52" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C52" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D52" t="str">
-        <v>五稜銀鑽</v>
+        <v>薰衣草</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F52">
-        <v>59</v>
-      </c>
-      <c r="G52" t="str">
-        <v>五棱银钻.png</v>
+        <v>8</v>
+      </c>
+      <c r="G52">
+        <v>69</v>
+      </c>
+      <c r="H52" t="str">
+        <v>薰衣草.png</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>gsxx_pnd_2</v>
+        <v>xyc_cysl_10</v>
       </c>
       <c r="B53" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C53" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D53" t="str">
-        <v>鋯石星星</v>
+        <v>薰衣草</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F53">
-        <v>99</v>
-      </c>
-      <c r="G53" t="str">
-        <v>锆石星星.png</v>
+        <v>10</v>
+      </c>
+      <c r="G53">
+        <v>139</v>
+      </c>
+      <c r="H53" t="str">
+        <v>薰衣草.png</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>xxys_pnd_2</v>
+        <v>fyh_spc_12</v>
       </c>
       <c r="B54" t="str">
         <v>配件</v>
       </c>
       <c r="C54" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D54" t="str">
-        <v>尋心鑰匙</v>
+        <v>粉櫻花</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F54">
-        <v>99</v>
-      </c>
-      <c r="G54" t="str">
-        <v>寻心钥匙.png</v>
+        <v>12</v>
+      </c>
+      <c r="G54">
+        <v>69</v>
+      </c>
+      <c r="H54" t="str">
+        <v>粉樱花.png</v>
+      </c>
+      <c r="I54" t="str">
+        <v>義烏市聚飾優</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>bsyw_pnd_2</v>
+        <v>gshxz_spc_10</v>
       </c>
       <c r="B55" t="str">
         <v>配件</v>
       </c>
       <c r="C55" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D55" t="str">
-        <v>白水魚尾</v>
+        <v>鋯石花形鑽</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F55">
+        <v>10</v>
+      </c>
+      <c r="G55">
         <v>99</v>
       </c>
-      <c r="G55" t="str">
-        <v>白水鱼尾.png</v>
+      <c r="H55" t="str">
+        <v>锆石花形钻.png</v>
+      </c>
+      <c r="I55" t="str">
+        <v>義烏市闊乘</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>zyb_spc_8</v>
+        <v>gsqg_spc_5</v>
       </c>
       <c r="B56" t="str">
         <v>配件</v>
@@ -1675,159 +2005,201 @@
         <v>隔珠</v>
       </c>
       <c r="D56" t="str">
-        <v>轉運柄</v>
+        <v>鋯石切割</v>
       </c>
       <c r="E56">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F56">
-        <v>59</v>
-      </c>
-      <c r="G56" t="str">
-        <v>转运柄.png</v>
+        <v>8</v>
+      </c>
+      <c r="G56">
+        <v>159</v>
+      </c>
+      <c r="H56" t="str">
+        <v>锆石切割.png</v>
+      </c>
+      <c r="I56" t="str">
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>emzy_spc_6</v>
+        <v>hsj_cysl_6</v>
       </c>
       <c r="B57" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C57" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D57" t="str">
-        <v>惡魔之眼</v>
+        <v>黃水晶</v>
       </c>
       <c r="E57">
         <v>6</v>
       </c>
       <c r="F57">
-        <v>59</v>
-      </c>
-      <c r="G57" t="str">
-        <v>恶魔之眼.png</v>
+        <v>6</v>
+      </c>
+      <c r="G57">
+        <v>39</v>
+      </c>
+      <c r="H57" t="str">
+        <v>黄水晶.png</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lwmn_agt_6</v>
+        <v>hsj_cysl_8</v>
       </c>
       <c r="B58" t="str">
         <v>珠子</v>
       </c>
       <c r="C58" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D58" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>黃水晶</v>
       </c>
       <c r="E58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F58">
+        <v>8</v>
+      </c>
+      <c r="G58">
         <v>69</v>
       </c>
-      <c r="G58" t="str">
-        <v>蓝纹玛瑙.png</v>
+      <c r="H58" t="str">
+        <v>黄水晶.png</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lwmn_agt_8</v>
+        <v>hsj_cysl_10</v>
       </c>
       <c r="B59" t="str">
         <v>珠子</v>
       </c>
       <c r="C59" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D59" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>黃水晶</v>
       </c>
       <c r="E59">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F59">
+        <v>10</v>
+      </c>
+      <c r="G59">
         <v>99</v>
       </c>
-      <c r="G59" t="str">
-        <v>蓝纹玛瑙.png</v>
+      <c r="H59" t="str">
+        <v>黄水晶.png</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>lwmn_agt_10</v>
+        <v>jzj_spc_4</v>
       </c>
       <c r="B60" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C60" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D60" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>交織戒</v>
       </c>
       <c r="E60">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>199</v>
-      </c>
-      <c r="G60" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>8</v>
+      </c>
+      <c r="G60">
+        <v>69</v>
+      </c>
+      <c r="H60" t="str">
+        <v>交织戒.png</v>
+      </c>
+      <c r="I60" t="str">
+        <v>廣州市弘達</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>xyc_cysl_8</v>
+        <v>gscx_pnd_2</v>
       </c>
       <c r="B61" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C61" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D61" t="str">
-        <v>薰衣草</v>
+        <v>鋯石晨星</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F61">
+        <v>14</v>
+      </c>
+      <c r="G61">
         <v>69</v>
       </c>
-      <c r="G61" t="str">
-        <v>薰衣草.png</v>
+      <c r="H61" t="str">
+        <v>锆石晨星.png</v>
+      </c>
+      <c r="I61" t="str">
+        <v>義烏市適旗</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>xyc_cysl_10</v>
+        <v>tg4_sz_7</v>
       </c>
       <c r="B62" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C62" t="str">
-        <v>水晶</v>
+        <v>數字</v>
       </c>
       <c r="D62" t="str">
-        <v>薰衣草</v>
+        <v>鈦鋼4</v>
       </c>
       <c r="E62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F62">
-        <v>139</v>
-      </c>
-      <c r="G62" t="str">
-        <v>薰衣草.png</v>
+        <v>7</v>
+      </c>
+      <c r="G62">
+        <v>59</v>
+      </c>
+      <c r="H62" t="str">
+        <v>钛钢4.png</v>
+      </c>
+      <c r="I62" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>nwxh_spc_5</v>
+        <v>cyszj_spc_13</v>
       </c>
       <c r="B63" t="str">
         <v>配件</v>
@@ -1836,67 +2208,85 @@
         <v>隔珠</v>
       </c>
       <c r="D63" t="str">
-        <v>扭紋小環</v>
+        <v>藏銀十字架</v>
       </c>
       <c r="E63">
+        <v>13</v>
+      </c>
+      <c r="F63">
         <v>5</v>
       </c>
-      <c r="F63">
-        <v>59</v>
-      </c>
-      <c r="G63" t="str">
-        <v>扭纹小环.png</v>
+      <c r="G63">
+        <v>69</v>
+      </c>
+      <c r="H63" t="str">
+        <v>藏银十字架.png</v>
+      </c>
+      <c r="I63" t="str">
+        <v>義烏市尋意</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>xxjz_pnd_2</v>
+        <v>ysxh_spc_2</v>
       </c>
       <c r="B64" t="str">
         <v>配件</v>
       </c>
       <c r="C64" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D64" t="str">
-        <v>星星獎章</v>
+        <v>銀色小環</v>
       </c>
       <c r="E64">
         <v>2</v>
       </c>
       <c r="F64">
-        <v>99</v>
-      </c>
-      <c r="G64" t="str">
-        <v>星星奖章.png</v>
+        <v>6</v>
+      </c>
+      <c r="G64">
+        <v>39</v>
+      </c>
+      <c r="H64" t="str">
+        <v>银色小环.png</v>
+      </c>
+      <c r="I64" t="str">
+        <v>廣州鑫鈺</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>fyh_spc_6</v>
+        <v>tg9_sz_7</v>
       </c>
       <c r="B65" t="str">
         <v>配件</v>
       </c>
       <c r="C65" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D65" t="str">
-        <v>粉櫻花</v>
+        <v>鈦鋼9</v>
       </c>
       <c r="E65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65">
+        <v>7</v>
+      </c>
+      <c r="G65">
         <v>59</v>
       </c>
-      <c r="G65" t="str">
-        <v>粉樱花.png</v>
+      <c r="H65" t="str">
+        <v>钛钢9.png</v>
+      </c>
+      <c r="I65" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>gshxz_spc_6</v>
+        <v>gh_spc_6</v>
       </c>
       <c r="B66" t="str">
         <v>配件</v>
@@ -1905,251 +2295,317 @@
         <v>隔珠</v>
       </c>
       <c r="D66" t="str">
-        <v>鋯石花形鑽</v>
+        <v>桂花</v>
       </c>
       <c r="E66">
         <v>6</v>
       </c>
       <c r="F66">
-        <v>59</v>
-      </c>
-      <c r="G66" t="str">
-        <v>锆石花形钻.png</v>
+        <v>6</v>
+      </c>
+      <c r="G66">
+        <v>69</v>
+      </c>
+      <c r="H66" t="str">
+        <v>桂花.png</v>
+      </c>
+      <c r="I66" t="str">
+        <v>廣州嘉鈺</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>gsqg_spc_5</v>
+        <v>hm_agt_6</v>
       </c>
       <c r="B67" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C67" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D67" t="str">
-        <v>鋯石切割</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F67">
-        <v>59</v>
-      </c>
-      <c r="G67" t="str">
-        <v>锆石切割.png</v>
+        <v>6</v>
+      </c>
+      <c r="G67">
+        <v>39</v>
+      </c>
+      <c r="H67" t="str">
+        <v>黄玛瑙.png</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>hsj_cysl_6</v>
+        <v>hm_agt_8</v>
       </c>
       <c r="B68" t="str">
         <v>珠子</v>
       </c>
       <c r="C68" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D68" t="str">
-        <v>黃水晶</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F68">
-        <v>39</v>
-      </c>
-      <c r="G68" t="str">
-        <v>黄水晶.png</v>
+        <v>8</v>
+      </c>
+      <c r="G68">
+        <v>59</v>
+      </c>
+      <c r="H68" t="str">
+        <v>黄玛瑙.png</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>hsj_cysl_8</v>
+        <v>hm_agt_10</v>
       </c>
       <c r="B69" t="str">
         <v>珠子</v>
       </c>
       <c r="C69" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D69" t="str">
-        <v>黃水晶</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F69">
-        <v>69</v>
-      </c>
-      <c r="G69" t="str">
-        <v>黄水晶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G69">
+        <v>89</v>
+      </c>
+      <c r="H69" t="str">
+        <v>黄玛瑙.png</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>hsj_cysl_10</v>
+        <v>ml_stn_6</v>
       </c>
       <c r="B70" t="str">
         <v>珠子</v>
       </c>
       <c r="C70" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D70" t="str">
-        <v>黃水晶</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F70">
-        <v>99</v>
-      </c>
-      <c r="G70" t="str">
-        <v>黄水晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G70">
+        <v>69</v>
+      </c>
+      <c r="H70" t="str">
+        <v>蜜蜡.png</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>jzj_spc_6</v>
+        <v>ml_stn_8</v>
       </c>
       <c r="B71" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C71" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D71" t="str">
-        <v>交織戒</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F71">
-        <v>59</v>
-      </c>
-      <c r="G71" t="str">
-        <v>交织戒.png</v>
+        <v>8</v>
+      </c>
+      <c r="G71">
+        <v>99</v>
+      </c>
+      <c r="H71" t="str">
+        <v>蜜蜡.png</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>gscx_pnd_2</v>
+        <v>ysr_zm_4</v>
       </c>
       <c r="B72" t="str">
         <v>配件</v>
       </c>
       <c r="C72" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D72" t="str">
-        <v>鋯石晨星</v>
+        <v>銀飾R</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72">
-        <v>99</v>
-      </c>
-      <c r="G72" t="str">
-        <v>锆石晨星.png</v>
+        <v>10</v>
+      </c>
+      <c r="G72">
+        <v>399</v>
+      </c>
+      <c r="H72" t="str">
+        <v>银饰R.png</v>
+      </c>
+      <c r="I72" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>tg4_sz_7</v>
+        <v>jd_pnd_2</v>
       </c>
       <c r="B73" t="str">
         <v>配件</v>
       </c>
       <c r="C73" t="str">
-        <v>數字</v>
+        <v>吊墜</v>
       </c>
       <c r="D73" t="str">
-        <v>鈦鋼4</v>
+        <v>晶蝶</v>
       </c>
       <c r="E73">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>39</v>
-      </c>
-      <c r="G73" t="str">
-        <v>钛钢4.png</v>
+        <v>9</v>
+      </c>
+      <c r="G73">
+        <v>69</v>
+      </c>
+      <c r="H73" t="str">
+        <v>晶蝶.png</v>
+      </c>
+      <c r="I73" t="str">
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>cyszj_spc_8</v>
+        <v>tg7_sz_7</v>
       </c>
       <c r="B74" t="str">
         <v>配件</v>
       </c>
       <c r="C74" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D74" t="str">
-        <v>藏銀十字架</v>
+        <v>鈦鋼7</v>
       </c>
       <c r="E74">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F74">
+        <v>7</v>
+      </c>
+      <c r="G74">
         <v>59</v>
       </c>
-      <c r="G74" t="str">
-        <v>藏银十字架.png</v>
+      <c r="H74" t="str">
+        <v>钛钢7.png</v>
+      </c>
+      <c r="I74" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>gsqgsc_spc_6</v>
+        <v>jpts_stn_8</v>
       </c>
       <c r="B75" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C75" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D75" t="str">
-        <v>鋯石切割雙層</v>
+        <v>金葡萄石</v>
       </c>
       <c r="E75">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F75">
-        <v>59</v>
-      </c>
-      <c r="G75" t="str">
-        <v>锆石切割双层.png</v>
+        <v>8</v>
+      </c>
+      <c r="G75">
+        <v>89</v>
+      </c>
+      <c r="H75" t="str">
+        <v>金葡萄石.png</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ysxh_spc_5</v>
+        <v>gymj_xz_3</v>
       </c>
       <c r="B76" t="str">
         <v>配件</v>
       </c>
       <c r="C76" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D76" t="str">
-        <v>銀色小環</v>
+        <v>古銀摩羯</v>
       </c>
       <c r="E76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>59</v>
-      </c>
-      <c r="G76" t="str">
-        <v>银色小环.png</v>
+        <v>10</v>
+      </c>
+      <c r="G76">
+        <v>39</v>
+      </c>
+      <c r="H76" t="str">
+        <v>古银摩羯.png</v>
+      </c>
+      <c r="I76" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>tg9_sz_7</v>
+        <v>tg0_sz_7</v>
       </c>
       <c r="B77" t="str">
         <v>配件</v>
@@ -2158,159 +2614,201 @@
         <v>數字</v>
       </c>
       <c r="D77" t="str">
-        <v>鈦鋼9</v>
+        <v>鈦鋼0</v>
       </c>
       <c r="E77">
         <v>7</v>
       </c>
       <c r="F77">
-        <v>39</v>
-      </c>
-      <c r="G77" t="str">
-        <v>钛钢9.png</v>
+        <v>7</v>
+      </c>
+      <c r="G77">
+        <v>59</v>
+      </c>
+      <c r="H77" t="str">
+        <v>钛钢0.png</v>
+      </c>
+      <c r="I77" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>gh_spc_6</v>
+        <v>jf_pnd_2</v>
       </c>
       <c r="B78" t="str">
         <v>配件</v>
       </c>
       <c r="C78" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D78" t="str">
-        <v>桂花</v>
+        <v>金福</v>
       </c>
       <c r="E78">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>139</v>
-      </c>
-      <c r="G78" t="str">
-        <v>桂花.png</v>
+        <v>10</v>
+      </c>
+      <c r="G78">
+        <v>49</v>
+      </c>
+      <c r="H78" t="str">
+        <v>金福.png</v>
+      </c>
+      <c r="I78" t="str">
+        <v>義烏市曉磊</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>hm_agt_6</v>
+        <v>ysj_zm_4</v>
       </c>
       <c r="B79" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C79" t="str">
-        <v>瑪瑙</v>
+        <v>字母</v>
       </c>
       <c r="D79" t="str">
-        <v>黃瑪瑙</v>
+        <v>銀飾J</v>
       </c>
       <c r="E79">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>39</v>
-      </c>
-      <c r="G79" t="str">
-        <v>黄玛瑙.png</v>
+        <v>10</v>
+      </c>
+      <c r="G79">
+        <v>399</v>
+      </c>
+      <c r="H79" t="str">
+        <v>银饰J.png</v>
+      </c>
+      <c r="I79" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>hm_agt_8</v>
+        <v>tg6_sz_7</v>
       </c>
       <c r="B80" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C80" t="str">
-        <v>瑪瑙</v>
+        <v>數字</v>
       </c>
       <c r="D80" t="str">
-        <v>黃瑪瑙</v>
+        <v>鈦鋼6</v>
       </c>
       <c r="E80">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80">
+        <v>7</v>
+      </c>
+      <c r="G80">
         <v>59</v>
       </c>
-      <c r="G80" t="str">
-        <v>黄玛瑙.png</v>
+      <c r="H80" t="str">
+        <v>钛钢6.png</v>
+      </c>
+      <c r="I80" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>hm_agt_10</v>
+        <v>xxy_spc_2</v>
       </c>
       <c r="B81" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C81" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D81" t="str">
-        <v>黃瑪瑙</v>
+        <v>小祥雲</v>
       </c>
       <c r="E81">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F81">
+        <v>8</v>
+      </c>
+      <c r="G81">
         <v>89</v>
       </c>
-      <c r="G81" t="str">
-        <v>黄玛瑙.png</v>
+      <c r="H81" t="str">
+        <v>小祥云.png</v>
+      </c>
+      <c r="I81" t="str">
+        <v>廣州璐悠</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ml_stn_6</v>
+        <v>dxy_spc_3</v>
       </c>
       <c r="B82" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C82" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D82" t="str">
-        <v>蜜蠟</v>
+        <v>大祥雲</v>
       </c>
       <c r="E82">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F82">
-        <v>69</v>
-      </c>
-      <c r="G82" t="str">
-        <v>蜜蜡.png</v>
+        <v>10</v>
+      </c>
+      <c r="G82">
+        <v>99</v>
+      </c>
+      <c r="H82" t="str">
+        <v>大祥云.png</v>
+      </c>
+      <c r="I82" t="str">
+        <v>廣州璐悠</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ml_stn_8</v>
+        <v>ysi_zm_4</v>
       </c>
       <c r="B83" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C83" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D83" t="str">
-        <v>蜜蠟</v>
+        <v>銀飾I</v>
       </c>
       <c r="E83">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F83">
-        <v>99</v>
-      </c>
-      <c r="G83" t="str">
-        <v>蜜蜡.png</v>
+        <v>10</v>
+      </c>
+      <c r="G83">
+        <v>399</v>
+      </c>
+      <c r="H83" t="str">
+        <v>银饰I.png</v>
+      </c>
+      <c r="I83" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ysr_zm_4</v>
+        <v>ysu_zm_4</v>
       </c>
       <c r="B84" t="str">
         <v>配件</v>
@@ -2319,90 +2817,114 @@
         <v>字母</v>
       </c>
       <c r="D84" t="str">
-        <v>銀飾R</v>
+        <v>銀飾U</v>
       </c>
       <c r="E84">
         <v>4</v>
       </c>
       <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84">
         <v>399</v>
       </c>
-      <c r="G84" t="str">
-        <v>银饰R.png</v>
+      <c r="H84" t="str">
+        <v>银饰U.png</v>
+      </c>
+      <c r="I84" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>mzhd_pnd_2</v>
+        <v>tg3_sz_7</v>
       </c>
       <c r="B85" t="str">
         <v>配件</v>
       </c>
       <c r="C85" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D85" t="str">
-        <v>滿鑽蝴蝶</v>
+        <v>鈦鋼3</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F85">
-        <v>99</v>
-      </c>
-      <c r="G85" t="str">
-        <v>满钻蝴蝶.png</v>
+        <v>7</v>
+      </c>
+      <c r="G85">
+        <v>59</v>
+      </c>
+      <c r="H85" t="str">
+        <v>钛钢3.png</v>
+      </c>
+      <c r="I85" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>jd_pnd_2</v>
+        <v>tg2_sz_7</v>
       </c>
       <c r="B86" t="str">
         <v>配件</v>
       </c>
       <c r="C86" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D86" t="str">
-        <v>晶蝶</v>
+        <v>鈦鋼2</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F86">
-        <v>99</v>
-      </c>
-      <c r="G86" t="str">
-        <v>晶蝶.png</v>
+        <v>7</v>
+      </c>
+      <c r="G86">
+        <v>59</v>
+      </c>
+      <c r="H86" t="str">
+        <v>钛钢2.png</v>
+      </c>
+      <c r="I86" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>lkjls_spc_6</v>
+        <v>tg8_sz_7</v>
       </c>
       <c r="B87" t="str">
         <v>配件</v>
       </c>
       <c r="C87" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D87" t="str">
-        <v>鏤空金蕾絲</v>
+        <v>鈦鋼8</v>
       </c>
       <c r="E87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F87">
+        <v>7</v>
+      </c>
+      <c r="G87">
         <v>59</v>
       </c>
-      <c r="G87" t="str">
-        <v>镂空金蕾丝.png</v>
+      <c r="H87" t="str">
+        <v>钛钢8.png</v>
+      </c>
+      <c r="I87" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>tg7_sz_7</v>
+        <v>tg5_sz_7</v>
       </c>
       <c r="B88" t="str">
         <v>配件</v>
@@ -2411,136 +2933,172 @@
         <v>數字</v>
       </c>
       <c r="D88" t="str">
-        <v>鈦鋼7</v>
+        <v>鈦鋼5</v>
       </c>
       <c r="E88">
         <v>7</v>
       </c>
       <c r="F88">
-        <v>39</v>
-      </c>
-      <c r="G88" t="str">
-        <v>钛钢7.png</v>
+        <v>7</v>
+      </c>
+      <c r="G88">
+        <v>59</v>
+      </c>
+      <c r="H88" t="str">
+        <v>钛钢5.png</v>
+      </c>
+      <c r="I88" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>jpts_stn_8</v>
+        <v>gycn_xz_3</v>
       </c>
       <c r="B89" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C89" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D89" t="str">
-        <v>金葡萄石</v>
+        <v>古銀處女</v>
       </c>
       <c r="E89">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F89">
-        <v>89</v>
-      </c>
-      <c r="G89" t="str">
-        <v>金葡萄石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G89">
+        <v>39</v>
+      </c>
+      <c r="H89" t="str">
+        <v>古银处女.png</v>
+      </c>
+      <c r="I89" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>gymj_xz_2</v>
+        <v>ysp_zm_4</v>
       </c>
       <c r="B90" t="str">
         <v>配件</v>
       </c>
       <c r="C90" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D90" t="str">
-        <v>古銀摩羯</v>
+        <v>銀飾P</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F90">
-        <v>39</v>
-      </c>
-      <c r="G90" t="str">
-        <v>古银摩羯.png</v>
+        <v>10</v>
+      </c>
+      <c r="G90">
+        <v>399</v>
+      </c>
+      <c r="H90" t="str">
+        <v>银饰P.png</v>
+      </c>
+      <c r="I90" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>tg0_sz_7</v>
+        <v>gyby_xz_3</v>
       </c>
       <c r="B91" t="str">
         <v>配件</v>
       </c>
       <c r="C91" t="str">
-        <v>數字</v>
+        <v>星座</v>
       </c>
       <c r="D91" t="str">
-        <v>鈦鋼0</v>
+        <v>古銀白羊</v>
       </c>
       <c r="E91">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F91">
+        <v>10</v>
+      </c>
+      <c r="G91">
         <v>39</v>
       </c>
-      <c r="G91" t="str">
-        <v>钛钢0.png</v>
+      <c r="H91" t="str">
+        <v>古银白羊.png</v>
+      </c>
+      <c r="I91" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>jf_pnd_2</v>
+        <v>lfj_cysl_8</v>
       </c>
       <c r="B92" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C92" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D92" t="str">
-        <v>金福</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E92">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F92">
+        <v>8</v>
+      </c>
+      <c r="G92">
         <v>99</v>
       </c>
-      <c r="G92" t="str">
-        <v>金福.png</v>
+      <c r="H92" t="str">
+        <v>绿发晶.png</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fgdh_spc_8</v>
+        <v>lfj_cysl_10</v>
       </c>
       <c r="B93" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C93" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D93" t="str">
-        <v>復古雕花</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E93">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F93">
-        <v>59</v>
-      </c>
-      <c r="G93" t="str">
-        <v>复古雕花.png</v>
+        <v>10</v>
+      </c>
+      <c r="G93">
+        <v>139</v>
+      </c>
+      <c r="H93" t="str">
+        <v>绿发晶.png</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ysj_zm_4</v>
+        <v>ysc_zm_4</v>
       </c>
       <c r="B94" t="str">
         <v>配件</v>
@@ -2549,90 +3107,114 @@
         <v>字母</v>
       </c>
       <c r="D94" t="str">
-        <v>銀飾J</v>
+        <v>銀飾C</v>
       </c>
       <c r="E94">
         <v>4</v>
       </c>
       <c r="F94">
+        <v>10</v>
+      </c>
+      <c r="G94">
         <v>399</v>
       </c>
-      <c r="G94" t="str">
-        <v>银饰J.png</v>
+      <c r="H94" t="str">
+        <v>银饰C.png</v>
+      </c>
+      <c r="I94" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>tg6_sz_7</v>
+        <v>ysb_zm_4</v>
       </c>
       <c r="B95" t="str">
         <v>配件</v>
       </c>
       <c r="C95" t="str">
-        <v>數字</v>
+        <v>字母</v>
       </c>
       <c r="D95" t="str">
-        <v>鈦鋼6</v>
+        <v>銀飾B</v>
       </c>
       <c r="E95">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F95">
-        <v>39</v>
-      </c>
-      <c r="G95" t="str">
-        <v>钛钢6.png</v>
+        <v>10</v>
+      </c>
+      <c r="G95">
+        <v>399</v>
+      </c>
+      <c r="H95" t="str">
+        <v>银饰B.png</v>
+      </c>
+      <c r="I95" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>xxy_spc_5</v>
+        <v>gysp_xz_3</v>
       </c>
       <c r="B96" t="str">
         <v>配件</v>
       </c>
       <c r="C96" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D96" t="str">
-        <v>小祥雲</v>
+        <v>古銀水瓶</v>
       </c>
       <c r="E96">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F96">
-        <v>59</v>
-      </c>
-      <c r="G96" t="str">
-        <v>小祥云.png</v>
+        <v>10</v>
+      </c>
+      <c r="G96">
+        <v>39</v>
+      </c>
+      <c r="H96" t="str">
+        <v>古银水瓶.png</v>
+      </c>
+      <c r="I96" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>dxy_spc_5</v>
+        <v>yso_zm_4</v>
       </c>
       <c r="B97" t="str">
         <v>配件</v>
       </c>
       <c r="C97" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D97" t="str">
-        <v>大祥雲</v>
+        <v>銀飾O</v>
       </c>
       <c r="E97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F97">
-        <v>59</v>
-      </c>
-      <c r="G97" t="str">
-        <v>大祥云.png</v>
+        <v>10</v>
+      </c>
+      <c r="G97">
+        <v>399</v>
+      </c>
+      <c r="H97" t="str">
+        <v>银饰O.png</v>
+      </c>
+      <c r="I97" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ysi_zm_4</v>
+        <v>ysw_zm_4</v>
       </c>
       <c r="B98" t="str">
         <v>配件</v>
@@ -2641,205 +3223,259 @@
         <v>字母</v>
       </c>
       <c r="D98" t="str">
-        <v>銀飾I</v>
+        <v>銀飾W</v>
       </c>
       <c r="E98">
         <v>4</v>
       </c>
       <c r="F98">
+        <v>10</v>
+      </c>
+      <c r="G98">
         <v>399</v>
       </c>
-      <c r="G98" t="str">
-        <v>银饰I.png</v>
+      <c r="H98" t="str">
+        <v>银饰W.png</v>
+      </c>
+      <c r="I98" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>ysu_zm_4</v>
+        <v>zyd_pnd_2</v>
       </c>
       <c r="B99" t="str">
         <v>配件</v>
       </c>
       <c r="C99" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D99" t="str">
-        <v>銀飾U</v>
+        <v>珠遇蝶</v>
       </c>
       <c r="E99">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F99">
-        <v>399</v>
-      </c>
-      <c r="G99" t="str">
-        <v>银饰U.png</v>
+        <v>20</v>
+      </c>
+      <c r="G99">
+        <v>59</v>
+      </c>
+      <c r="H99" t="str">
+        <v>珠遇蝶.png</v>
+      </c>
+      <c r="I99" t="str">
+        <v>廣州瑤心飾品</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>tg3_sz_7</v>
+        <v>xfp_pnd_2</v>
       </c>
       <c r="B100" t="str">
         <v>配件</v>
       </c>
       <c r="C100" t="str">
-        <v>數字</v>
+        <v>吊墜</v>
       </c>
       <c r="D100" t="str">
-        <v>鈦鋼3</v>
+        <v>招財</v>
       </c>
       <c r="E100">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F100">
-        <v>39</v>
-      </c>
-      <c r="G100" t="str">
-        <v>钛钢3.png</v>
+        <v>10</v>
+      </c>
+      <c r="G100">
+        <v>59</v>
+      </c>
+      <c r="H100" t="str">
+        <v>招财.png</v>
+      </c>
+      <c r="I100" t="str">
+        <v>義烏市歌爾</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>tg2_sz_7</v>
+        <v>ysq_zm_4</v>
       </c>
       <c r="B101" t="str">
         <v>配件</v>
       </c>
       <c r="C101" t="str">
-        <v>數字</v>
+        <v>字母</v>
       </c>
       <c r="D101" t="str">
-        <v>鈦鋼2</v>
+        <v>銀飾Q</v>
       </c>
       <c r="E101">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F101">
-        <v>39</v>
-      </c>
-      <c r="G101" t="str">
-        <v>钛钢2.png</v>
+        <v>10</v>
+      </c>
+      <c r="G101">
+        <v>399</v>
+      </c>
+      <c r="H101" t="str">
+        <v>银饰Q.png</v>
+      </c>
+      <c r="I101" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>tg8_sz_7</v>
+        <v>ymys_stn_10</v>
       </c>
       <c r="B102" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C102" t="str">
-        <v>數字</v>
+        <v>礦石</v>
       </c>
       <c r="D102" t="str">
-        <v>鈦鋼8</v>
+        <v>羽毛螢石</v>
       </c>
       <c r="E102">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F102">
-        <v>39</v>
-      </c>
-      <c r="G102" t="str">
-        <v>钛钢8.png</v>
+        <v>10</v>
+      </c>
+      <c r="G102">
+        <v>139</v>
+      </c>
+      <c r="H102" t="str">
+        <v>羽毛萤石.png</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>tg5_sz_7</v>
+        <v>gyjx_xz_3</v>
       </c>
       <c r="B103" t="str">
         <v>配件</v>
       </c>
       <c r="C103" t="str">
-        <v>數字</v>
+        <v>星座</v>
       </c>
       <c r="D103" t="str">
-        <v>鈦鋼5</v>
+        <v>古銀巨蟹</v>
       </c>
       <c r="E103">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F103">
+        <v>10</v>
+      </c>
+      <c r="G103">
         <v>39</v>
       </c>
-      <c r="G103" t="str">
-        <v>钛钢5.png</v>
+      <c r="H103" t="str">
+        <v>古银巨蟹.png</v>
+      </c>
+      <c r="I103" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>gycn_xz_2</v>
+        <v>ysf_zm_4</v>
       </c>
       <c r="B104" t="str">
         <v>配件</v>
       </c>
       <c r="C104" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D104" t="str">
-        <v>古銀處女</v>
+        <v>銀飾F</v>
       </c>
       <c r="E104">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F104">
-        <v>39</v>
-      </c>
-      <c r="G104" t="str">
-        <v>古银处女.png</v>
+        <v>10</v>
+      </c>
+      <c r="G104">
+        <v>399</v>
+      </c>
+      <c r="H104" t="str">
+        <v>银饰F.png</v>
+      </c>
+      <c r="I104" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ysp_zm_4</v>
+        <v>gyss_xz_3</v>
       </c>
       <c r="B105" t="str">
         <v>配件</v>
       </c>
       <c r="C105" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D105" t="str">
-        <v>銀飾P</v>
+        <v>古銀射手</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F105">
-        <v>399</v>
-      </c>
-      <c r="G105" t="str">
-        <v>银饰P.png</v>
+        <v>10</v>
+      </c>
+      <c r="G105">
+        <v>39</v>
+      </c>
+      <c r="H105" t="str">
+        <v>古银射手.png</v>
+      </c>
+      <c r="I105" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>gsmm_spc_8</v>
+        <v>hlcs_pnd_3</v>
       </c>
       <c r="B106" t="str">
         <v>配件</v>
       </c>
       <c r="C106" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D106" t="str">
-        <v>鋯石貓咪</v>
+        <v>葫蘆成雙</v>
       </c>
       <c r="E106">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F106">
-        <v>59</v>
-      </c>
-      <c r="G106" t="str">
-        <v>锆石猫咪.png</v>
+        <v>40</v>
+      </c>
+      <c r="G106">
+        <v>299</v>
+      </c>
+      <c r="H106" t="str">
+        <v>葫芦成双.png</v>
+      </c>
+      <c r="I106" t="str">
+        <v>東海縣花眠</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>gyby_xz_2</v>
+        <v>gyszz_xz_3</v>
       </c>
       <c r="B107" t="str">
         <v>配件</v>
@@ -2848,67 +3484,85 @@
         <v>星座</v>
       </c>
       <c r="D107" t="str">
-        <v>古銀白羊</v>
+        <v>古銀雙子</v>
       </c>
       <c r="E107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107">
+        <v>10</v>
+      </c>
+      <c r="G107">
         <v>39</v>
       </c>
-      <c r="G107" t="str">
-        <v>古银白羊.png</v>
+      <c r="H107" t="str">
+        <v>古银双子.png</v>
+      </c>
+      <c r="I107" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>lfj_cysl_8</v>
+        <v>ysn_zm_4</v>
       </c>
       <c r="B108" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C108" t="str">
-        <v>水晶</v>
+        <v>字母</v>
       </c>
       <c r="D108" t="str">
-        <v>綠髮晶</v>
+        <v>銀飾N</v>
       </c>
       <c r="E108">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F108">
-        <v>99</v>
-      </c>
-      <c r="G108" t="str">
-        <v>绿发晶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G108">
+        <v>399</v>
+      </c>
+      <c r="H108" t="str">
+        <v>银饰N.png</v>
+      </c>
+      <c r="I108" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>lfj_cysl_10</v>
+        <v>ysm_zm_4</v>
       </c>
       <c r="B109" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C109" t="str">
-        <v>水晶</v>
+        <v>字母</v>
       </c>
       <c r="D109" t="str">
-        <v>綠髮晶</v>
+        <v>銀飾M</v>
       </c>
       <c r="E109">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F109">
-        <v>139</v>
-      </c>
-      <c r="G109" t="str">
-        <v>绿发晶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G109">
+        <v>399</v>
+      </c>
+      <c r="H109" t="str">
+        <v>银饰M.png</v>
+      </c>
+      <c r="I109" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ysc_zm_4</v>
+        <v>ysh_zm_4</v>
       </c>
       <c r="B110" t="str">
         <v>配件</v>
@@ -2917,90 +3571,114 @@
         <v>字母</v>
       </c>
       <c r="D110" t="str">
-        <v>銀飾C</v>
+        <v>銀飾H</v>
       </c>
       <c r="E110">
         <v>4</v>
       </c>
       <c r="F110">
+        <v>10</v>
+      </c>
+      <c r="G110">
         <v>399</v>
       </c>
-      <c r="G110" t="str">
-        <v>银饰C.png</v>
+      <c r="H110" t="str">
+        <v>银饰H.png</v>
+      </c>
+      <c r="I110" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ysb_zm_4</v>
+        <v>gytx_xz_3</v>
       </c>
       <c r="B111" t="str">
         <v>配件</v>
       </c>
       <c r="C111" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D111" t="str">
-        <v>銀飾B</v>
+        <v>古銀天蠍</v>
       </c>
       <c r="E111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F111">
-        <v>399</v>
-      </c>
-      <c r="G111" t="str">
-        <v>银饰B.png</v>
+        <v>10</v>
+      </c>
+      <c r="G111">
+        <v>39</v>
+      </c>
+      <c r="H111" t="str">
+        <v>古银天蝎.png</v>
+      </c>
+      <c r="I111" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>gysp_xz_2</v>
+        <v>ysg_zm_4</v>
       </c>
       <c r="B112" t="str">
         <v>配件</v>
       </c>
       <c r="C112" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D112" t="str">
-        <v>古銀水瓶</v>
+        <v>銀飾G</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F112">
-        <v>39</v>
-      </c>
-      <c r="G112" t="str">
-        <v>古银水瓶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G112">
+        <v>399</v>
+      </c>
+      <c r="H112" t="str">
+        <v>银饰G.png</v>
+      </c>
+      <c r="I112" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>yso_zm_4</v>
+        <v>gytc_xz_3</v>
       </c>
       <c r="B113" t="str">
         <v>配件</v>
       </c>
       <c r="C113" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D113" t="str">
-        <v>銀飾O</v>
+        <v>古銀天秤</v>
       </c>
       <c r="E113">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F113">
-        <v>399</v>
-      </c>
-      <c r="G113" t="str">
-        <v>银饰O.png</v>
+        <v>10</v>
+      </c>
+      <c r="G113">
+        <v>39</v>
+      </c>
+      <c r="H113" t="str">
+        <v>古银天秤.png</v>
+      </c>
+      <c r="I113" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ysw_zm_4</v>
+        <v>yst_zm_4</v>
       </c>
       <c r="B114" t="str">
         <v>配件</v>
@@ -3009,67 +3687,85 @@
         <v>字母</v>
       </c>
       <c r="D114" t="str">
-        <v>銀飾W</v>
+        <v>銀飾T</v>
       </c>
       <c r="E114">
         <v>4</v>
       </c>
       <c r="F114">
+        <v>10</v>
+      </c>
+      <c r="G114">
         <v>399</v>
       </c>
-      <c r="G114" t="str">
-        <v>银饰W.png</v>
+      <c r="H114" t="str">
+        <v>银饰T.png</v>
+      </c>
+      <c r="I114" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>wljz_spc_5</v>
+        <v>yse_zm_4</v>
       </c>
       <c r="B115" t="str">
         <v>配件</v>
       </c>
       <c r="C115" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D115" t="str">
-        <v>五稜金鑽</v>
+        <v>銀飾E</v>
       </c>
       <c r="E115">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F115">
-        <v>59</v>
-      </c>
-      <c r="G115" t="str">
-        <v>五棱金钻.png</v>
+        <v>10</v>
+      </c>
+      <c r="G115">
+        <v>399</v>
+      </c>
+      <c r="H115" t="str">
+        <v>银饰E.png</v>
+      </c>
+      <c r="I115" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>zyd_pnd_2</v>
+        <v>ysk_zm_4</v>
       </c>
       <c r="B116" t="str">
         <v>配件</v>
       </c>
       <c r="C116" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D116" t="str">
-        <v>珠遇蝶</v>
+        <v>銀飾K</v>
       </c>
       <c r="E116">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F116">
-        <v>99</v>
-      </c>
-      <c r="G116" t="str">
-        <v>珠遇蝶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G116">
+        <v>399</v>
+      </c>
+      <c r="H116" t="str">
+        <v>银饰K.png</v>
+      </c>
+      <c r="I116" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>xfp_pnd_2</v>
+        <v>syyl_pnd_2</v>
       </c>
       <c r="B117" t="str">
         <v>配件</v>
@@ -3078,21 +3774,27 @@
         <v>吊墜</v>
       </c>
       <c r="D117" t="str">
-        <v>招財</v>
+        <v>閃躍月亮</v>
       </c>
       <c r="E117">
         <v>2</v>
       </c>
       <c r="F117">
-        <v>99</v>
-      </c>
-      <c r="G117" t="str">
-        <v>招财.png</v>
+        <v>11</v>
+      </c>
+      <c r="G117">
+        <v>69</v>
+      </c>
+      <c r="H117" t="str">
+        <v>闪跃月亮.png</v>
+      </c>
+      <c r="I117" t="str">
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ysq_zm_4</v>
+        <v>ysv_zm_4</v>
       </c>
       <c r="B118" t="str">
         <v>配件</v>
@@ -3101,67 +3803,85 @@
         <v>字母</v>
       </c>
       <c r="D118" t="str">
-        <v>銀飾Q</v>
+        <v>銀飾V</v>
       </c>
       <c r="E118">
         <v>4</v>
       </c>
       <c r="F118">
+        <v>10</v>
+      </c>
+      <c r="G118">
         <v>399</v>
       </c>
-      <c r="G118" t="str">
-        <v>银饰Q.png</v>
+      <c r="H118" t="str">
+        <v>银饰V.png</v>
+      </c>
+      <c r="I118" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ymys_stn_10</v>
+        <v>gszs_spc_3</v>
       </c>
       <c r="B119" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C119" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D119" t="str">
-        <v>羽毛螢石</v>
+        <v>藏銀繡球鋯石細閃</v>
       </c>
       <c r="E119">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F119">
-        <v>139</v>
-      </c>
-      <c r="G119" t="str">
-        <v>羽毛萤石.png</v>
+        <v>7</v>
+      </c>
+      <c r="G119">
+        <v>129</v>
+      </c>
+      <c r="H119" t="str">
+        <v>藏银绣球锆石细闪.png</v>
+      </c>
+      <c r="I119" t="str">
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>gyjx_xz_2</v>
+        <v>ysl_zm_4</v>
       </c>
       <c r="B120" t="str">
         <v>配件</v>
       </c>
       <c r="C120" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D120" t="str">
-        <v>古銀巨蟹</v>
+        <v>銀飾L</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F120">
-        <v>39</v>
-      </c>
-      <c r="G120" t="str">
-        <v>古银巨蟹.png</v>
+        <v>10</v>
+      </c>
+      <c r="G120">
+        <v>399</v>
+      </c>
+      <c r="H120" t="str">
+        <v>银饰L.png</v>
+      </c>
+      <c r="I120" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>ysf_zm_4</v>
+        <v>ysa_zm_4</v>
       </c>
       <c r="B121" t="str">
         <v>配件</v>
@@ -3170,21 +3890,27 @@
         <v>字母</v>
       </c>
       <c r="D121" t="str">
-        <v>銀飾F</v>
+        <v>銀飾A</v>
       </c>
       <c r="E121">
         <v>4</v>
       </c>
       <c r="F121">
+        <v>10</v>
+      </c>
+      <c r="G121">
         <v>399</v>
       </c>
-      <c r="G121" t="str">
-        <v>银饰F.png</v>
+      <c r="H121" t="str">
+        <v>银饰A.png</v>
+      </c>
+      <c r="I121" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>gyss_xz_2</v>
+        <v>gyjn_xz_3</v>
       </c>
       <c r="B122" t="str">
         <v>配件</v>
@@ -3193,113 +3919,143 @@
         <v>星座</v>
       </c>
       <c r="D122" t="str">
-        <v>古銀射手</v>
+        <v>古銀金牛</v>
       </c>
       <c r="E122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122">
+        <v>10</v>
+      </c>
+      <c r="G122">
         <v>39</v>
       </c>
-      <c r="G122" t="str">
-        <v>古银射手.png</v>
+      <c r="H122" t="str">
+        <v>古银金牛.png</v>
+      </c>
+      <c r="I122" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>hlcs_pnd_2</v>
+        <v>ysy_zm_4</v>
       </c>
       <c r="B123" t="str">
         <v>配件</v>
       </c>
       <c r="C123" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D123" t="str">
-        <v>葫蘆成雙</v>
+        <v>銀飾Y</v>
       </c>
       <c r="E123">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F123">
-        <v>99</v>
-      </c>
-      <c r="G123" t="str">
-        <v>葫芦成双.png</v>
+        <v>10</v>
+      </c>
+      <c r="G123">
+        <v>399</v>
+      </c>
+      <c r="H123" t="str">
+        <v>银饰Y.png</v>
+      </c>
+      <c r="I123" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>gyszz_xz_2</v>
+        <v>jsxh_spc_2</v>
       </c>
       <c r="B124" t="str">
         <v>配件</v>
       </c>
       <c r="C124" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D124" t="str">
-        <v>古銀雙子</v>
+        <v>金色小環</v>
       </c>
       <c r="E124">
         <v>2</v>
       </c>
       <c r="F124">
+        <v>6</v>
+      </c>
+      <c r="G124">
         <v>39</v>
       </c>
-      <c r="G124" t="str">
-        <v>古银双子.png</v>
+      <c r="H124" t="str">
+        <v>金色小环.png</v>
+      </c>
+      <c r="I124" t="str">
+        <v>廣州鑫鈺</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ysn_zm_4</v>
+        <v>gyshz_xz_3</v>
       </c>
       <c r="B125" t="str">
         <v>配件</v>
       </c>
       <c r="C125" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D125" t="str">
-        <v>銀飾N</v>
+        <v>古銀獅子</v>
       </c>
       <c r="E125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F125">
-        <v>399</v>
-      </c>
-      <c r="G125" t="str">
-        <v>银饰N.png</v>
+        <v>10</v>
+      </c>
+      <c r="G125">
+        <v>39</v>
+      </c>
+      <c r="H125" t="str">
+        <v>古银狮子.png</v>
+      </c>
+      <c r="I125" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ysm_zm_4</v>
+        <v>bjx_pnd_2</v>
       </c>
       <c r="B126" t="str">
         <v>配件</v>
       </c>
       <c r="C126" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D126" t="str">
-        <v>銀飾M</v>
+        <v>北極星</v>
       </c>
       <c r="E126">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F126">
-        <v>399</v>
-      </c>
-      <c r="G126" t="str">
-        <v>银饰M.png</v>
+        <v>13</v>
+      </c>
+      <c r="G126">
+        <v>299</v>
+      </c>
+      <c r="H126" t="str">
+        <v>北极星.png</v>
+      </c>
+      <c r="I126" t="str">
+        <v>海豐縣梅隴鎮創藝祺</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ysh_zm_4</v>
+        <v>ysx_zm_4</v>
       </c>
       <c r="B127" t="str">
         <v>配件</v>
@@ -3308,113 +4064,143 @@
         <v>字母</v>
       </c>
       <c r="D127" t="str">
-        <v>銀飾H</v>
+        <v>銀飾X</v>
       </c>
       <c r="E127">
         <v>4</v>
       </c>
       <c r="F127">
+        <v>10</v>
+      </c>
+      <c r="G127">
         <v>399</v>
       </c>
-      <c r="G127" t="str">
-        <v>银饰H.png</v>
+      <c r="H127" t="str">
+        <v>银饰X.png</v>
+      </c>
+      <c r="I127" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>gytx_xz_2</v>
+        <v>hps_stn_6</v>
       </c>
       <c r="B128" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C128" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D128" t="str">
-        <v>古銀天蠍</v>
+        <v>琥珀石</v>
       </c>
       <c r="E128">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F128">
-        <v>39</v>
-      </c>
-      <c r="G128" t="str">
-        <v>古银天蝎.png</v>
+        <v>6</v>
+      </c>
+      <c r="G128">
+        <v>59</v>
+      </c>
+      <c r="H128" t="str">
+        <v>琥珀石.png</v>
+      </c>
+      <c r="I128" t="str">
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>ysg_zm_4</v>
+        <v>hps_stn_8</v>
       </c>
       <c r="B129" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C129" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D129" t="str">
-        <v>銀飾G</v>
+        <v>琥珀石</v>
       </c>
       <c r="E129">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F129">
-        <v>399</v>
-      </c>
-      <c r="G129" t="str">
-        <v>银饰G.png</v>
+        <v>8</v>
+      </c>
+      <c r="G129">
+        <v>89</v>
+      </c>
+      <c r="H129" t="str">
+        <v>琥珀石.png</v>
+      </c>
+      <c r="I129" t="str">
+        <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>gytc_xz_2</v>
+        <v>hps_stn_10</v>
       </c>
       <c r="B130" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C130" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D130" t="str">
-        <v>古銀天秤</v>
+        <v>琥珀石</v>
       </c>
       <c r="E130">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F130">
-        <v>39</v>
-      </c>
-      <c r="G130" t="str">
-        <v>古银天秤.png</v>
+        <v>10</v>
+      </c>
+      <c r="G130">
+        <v>199</v>
+      </c>
+      <c r="H130" t="str">
+        <v>琥珀石.png</v>
+      </c>
+      <c r="I130" t="str">
+        <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>yst_zm_4</v>
+        <v>gysy_xz_3</v>
       </c>
       <c r="B131" t="str">
         <v>配件</v>
       </c>
       <c r="C131" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D131" t="str">
-        <v>銀飾T</v>
+        <v>古銀雙魚</v>
       </c>
       <c r="E131">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F131">
-        <v>399</v>
-      </c>
-      <c r="G131" t="str">
-        <v>银饰T.png</v>
+        <v>10</v>
+      </c>
+      <c r="G131">
+        <v>39</v>
+      </c>
+      <c r="H131" t="str">
+        <v>古银双鱼.png</v>
+      </c>
+      <c r="I131" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>gslx_spc_6</v>
+        <v>xs_spc_10</v>
       </c>
       <c r="B132" t="str">
         <v>配件</v>
@@ -3423,21 +4209,27 @@
         <v>隔珠</v>
       </c>
       <c r="D132" t="str">
-        <v>鋯石螺旋</v>
+        <v>醒獅</v>
       </c>
       <c r="E132">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F132">
-        <v>59</v>
-      </c>
-      <c r="G132" t="str">
-        <v>锆石螺旋.png</v>
+        <v>10</v>
+      </c>
+      <c r="G132">
+        <v>399</v>
+      </c>
+      <c r="H132" t="str">
+        <v>醒狮.png</v>
+      </c>
+      <c r="I132" t="str">
+        <v>連雲港趣界</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>yse_zm_4</v>
+        <v>ysz_zm_4</v>
       </c>
       <c r="B133" t="str">
         <v>配件</v>
@@ -3446,228 +4238,288 @@
         <v>字母</v>
       </c>
       <c r="D133" t="str">
-        <v>銀飾E</v>
+        <v>銀飾Z</v>
       </c>
       <c r="E133">
         <v>4</v>
       </c>
       <c r="F133">
+        <v>10</v>
+      </c>
+      <c r="G133">
         <v>399</v>
       </c>
-      <c r="G133" t="str">
-        <v>银饰E.png</v>
+      <c r="H133" t="str">
+        <v>银饰Z.png</v>
+      </c>
+      <c r="I133" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ysk_zm_4</v>
+        <v>ths_stn_6</v>
       </c>
       <c r="B134" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C134" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D134" t="str">
-        <v>銀飾K</v>
+        <v>天河石</v>
       </c>
       <c r="E134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F134">
-        <v>399</v>
-      </c>
-      <c r="G134" t="str">
-        <v>银饰K.png</v>
+        <v>6</v>
+      </c>
+      <c r="G134">
+        <v>59</v>
+      </c>
+      <c r="H134" t="str">
+        <v>天河石.png</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>syyl_pnd_2</v>
+        <v>ths_stn_8</v>
       </c>
       <c r="B135" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C135" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D135" t="str">
-        <v>閃躍月亮</v>
+        <v>天河石</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F135">
+        <v>8</v>
+      </c>
+      <c r="G135">
         <v>99</v>
       </c>
-      <c r="G135" t="str">
-        <v>闪跃月亮.png</v>
+      <c r="H135" t="str">
+        <v>天河石.png</v>
+      </c>
+      <c r="I135" t="str">
+        <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ysv_zm_4</v>
+        <v>ths_stn_10</v>
       </c>
       <c r="B136" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C136" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D136" t="str">
-        <v>銀飾V</v>
+        <v>天河石</v>
       </c>
       <c r="E136">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F136">
-        <v>399</v>
-      </c>
-      <c r="G136" t="str">
-        <v>银饰V.png</v>
+        <v>10</v>
+      </c>
+      <c r="G136">
+        <v>139</v>
+      </c>
+      <c r="H136" t="str">
+        <v>天河石.png</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>gszs_spc_5</v>
+        <v>ysd_zm_4</v>
       </c>
       <c r="B137" t="str">
         <v>配件</v>
       </c>
       <c r="C137" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D137" t="str">
-        <v>藏銀繡球鋯石細閃</v>
+        <v>銀飾D</v>
       </c>
       <c r="E137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F137">
-        <v>59</v>
-      </c>
-      <c r="G137" t="str">
-        <v>藏银绣球锆石细闪.png</v>
+        <v>10</v>
+      </c>
+      <c r="G137">
+        <v>399</v>
+      </c>
+      <c r="H137" t="str">
+        <v>银饰D.png</v>
+      </c>
+      <c r="I137" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>ysl_zm_4</v>
+        <v>hlb_stn_6</v>
       </c>
       <c r="B138" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C138" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D138" t="str">
-        <v>銀飾L</v>
+        <v>海藍寶</v>
       </c>
       <c r="E138">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F138">
-        <v>399</v>
-      </c>
-      <c r="G138" t="str">
-        <v>银饰L.png</v>
+        <v>6</v>
+      </c>
+      <c r="G138">
+        <v>89</v>
+      </c>
+      <c r="H138" t="str">
+        <v>海蓝宝.png</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>xns_pnd_2</v>
+        <v>hlb_stn_8</v>
       </c>
       <c r="B139" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C139" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D139" t="str">
-        <v>小年獸</v>
+        <v>海藍寶</v>
       </c>
       <c r="E139">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F139">
+        <v>8</v>
+      </c>
+      <c r="G139">
         <v>99</v>
       </c>
-      <c r="G139" t="str">
-        <v>小年兽.png</v>
+      <c r="H139" t="str">
+        <v>海蓝宝.png</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>ysa_zm_4</v>
+        <v>hlb_stn_10</v>
       </c>
       <c r="B140" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C140" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D140" t="str">
-        <v>銀飾A</v>
+        <v>海藍寶</v>
       </c>
       <c r="E140">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F140">
-        <v>399</v>
-      </c>
-      <c r="G140" t="str">
-        <v>银饰A.png</v>
+        <v>10</v>
+      </c>
+      <c r="G140">
+        <v>169</v>
+      </c>
+      <c r="H140" t="str">
+        <v>海蓝宝.png</v>
+      </c>
+      <c r="I140" t="str">
+        <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>gyjn_xz_2</v>
+        <v>yss_zm_4</v>
       </c>
       <c r="B141" t="str">
         <v>配件</v>
       </c>
       <c r="C141" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D141" t="str">
-        <v>古銀金牛</v>
+        <v>銀飾S</v>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F141">
-        <v>39</v>
-      </c>
-      <c r="G141" t="str">
-        <v>古银金牛.png</v>
+        <v>10</v>
+      </c>
+      <c r="G141">
+        <v>399</v>
+      </c>
+      <c r="H141" t="str">
+        <v>银饰S.png</v>
+      </c>
+      <c r="I141" t="str">
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ysy_zm_4</v>
+        <v>gsch_pnd_2</v>
       </c>
       <c r="B142" t="str">
         <v>配件</v>
       </c>
       <c r="C142" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D142" t="str">
-        <v>銀飾Y</v>
+        <v>鋯石彩虹</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F142">
-        <v>399</v>
-      </c>
-      <c r="G142" t="str">
-        <v>银饰Y.png</v>
+        <v>15</v>
+      </c>
+      <c r="G142">
+        <v>199</v>
+      </c>
+      <c r="H142" t="str">
+        <v>锆石彩虹.png</v>
+      </c>
+      <c r="I142" t="str">
+        <v>東海縣慕戀夢</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>jsxh_spc_5</v>
+        <v>xgszs_spc_6</v>
       </c>
       <c r="B143" t="str">
         <v>配件</v>
@@ -3676,205 +4528,259 @@
         <v>隔珠</v>
       </c>
       <c r="D143" t="str">
-        <v>金色小環</v>
+        <v>小鋯石鑽閃</v>
       </c>
       <c r="E143">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F143">
-        <v>59</v>
-      </c>
-      <c r="G143" t="str">
-        <v>金色小环.png</v>
+        <v>6</v>
+      </c>
+      <c r="G143">
+        <v>69</v>
+      </c>
+      <c r="H143" t="str">
+        <v>小锆石钻闪.png</v>
+      </c>
+      <c r="I143" t="str">
+        <v>廣州戴芙妮</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>gyshz_xz_2</v>
+        <v>htj_cysl_6</v>
       </c>
       <c r="B144" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C144" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D144" t="str">
-        <v>古銀獅子</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E144">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F144">
-        <v>39</v>
-      </c>
-      <c r="G144" t="str">
-        <v>古银狮子.png</v>
+        <v>6</v>
+      </c>
+      <c r="G144">
+        <v>49</v>
+      </c>
+      <c r="H144" t="str">
+        <v>黄塔晶.png</v>
+      </c>
+      <c r="I144" t="str">
+        <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>bjx_pnd_2</v>
+        <v>htj_cysl_8</v>
       </c>
       <c r="B145" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C145" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D145" t="str">
-        <v>北極星</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E145">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F145">
-        <v>99</v>
-      </c>
-      <c r="G145" t="str">
-        <v>北极星.png</v>
+        <v>8</v>
+      </c>
+      <c r="G145">
+        <v>59</v>
+      </c>
+      <c r="H145" t="str">
+        <v>黄塔晶.png</v>
+      </c>
+      <c r="I145" t="str">
+        <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>cgl_spc_6</v>
+        <v>htj_cysl_10</v>
       </c>
       <c r="B146" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C146" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D146" t="str">
-        <v>彩鋯輪</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E146">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F146">
-        <v>59</v>
-      </c>
-      <c r="G146" t="str">
-        <v>彩锆轮.png</v>
+        <v>10</v>
+      </c>
+      <c r="G146">
+        <v>99</v>
+      </c>
+      <c r="H146" t="str">
+        <v>黄塔晶.png</v>
+      </c>
+      <c r="I146" t="str">
+        <v/>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>ysx_zm_4</v>
+        <v>wyh_pnd_2</v>
       </c>
       <c r="B147" t="str">
         <v>配件</v>
       </c>
       <c r="C147" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D147" t="str">
-        <v>銀飾X</v>
+        <v>午夜花</v>
       </c>
       <c r="E147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F147">
-        <v>399</v>
-      </c>
-      <c r="G147" t="str">
-        <v>银饰X.png</v>
+        <v>9</v>
+      </c>
+      <c r="G147">
+        <v>99</v>
+      </c>
+      <c r="H147" t="str">
+        <v>午夜花.png</v>
+      </c>
+      <c r="I147" t="str">
+        <v>義烏市亮飛</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>hps_stn_6</v>
+        <v>hfj_cysl_6</v>
       </c>
       <c r="B148" t="str">
         <v>珠子</v>
       </c>
       <c r="C148" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D148" t="str">
-        <v>琥珀石</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E148">
         <v>6</v>
       </c>
       <c r="F148">
-        <v>59</v>
-      </c>
-      <c r="G148" t="str">
-        <v>琥珀石.png</v>
+        <v>6</v>
+      </c>
+      <c r="G148">
+        <v>49</v>
+      </c>
+      <c r="H148" t="str">
+        <v>黑发晶.png</v>
+      </c>
+      <c r="I148" t="str">
+        <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>hps_stn_8</v>
+        <v>hfj_cysl_8</v>
       </c>
       <c r="B149" t="str">
         <v>珠子</v>
       </c>
       <c r="C149" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D149" t="str">
-        <v>琥珀石</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E149">
         <v>8</v>
       </c>
       <c r="F149">
-        <v>89</v>
-      </c>
-      <c r="G149" t="str">
-        <v>琥珀石.png</v>
+        <v>8</v>
+      </c>
+      <c r="G149">
+        <v>69</v>
+      </c>
+      <c r="H149" t="str">
+        <v>黑发晶.png</v>
+      </c>
+      <c r="I149" t="str">
+        <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>hps_stn_10</v>
+        <v>hfj_cysl_10</v>
       </c>
       <c r="B150" t="str">
         <v>珠子</v>
       </c>
       <c r="C150" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D150" t="str">
-        <v>琥珀石</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E150">
         <v>10</v>
       </c>
       <c r="F150">
-        <v>199</v>
-      </c>
-      <c r="G150" t="str">
-        <v>琥珀石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G150">
+        <v>169</v>
+      </c>
+      <c r="H150" t="str">
+        <v>黑发晶.png</v>
+      </c>
+      <c r="I150" t="str">
+        <v/>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>gysy_xz_2</v>
+        <v>tz_spc_19</v>
       </c>
       <c r="B151" t="str">
         <v>配件</v>
       </c>
       <c r="C151" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D151" t="str">
-        <v>古銀雙魚</v>
+        <v>天珠</v>
       </c>
       <c r="E151">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F151">
-        <v>39</v>
-      </c>
-      <c r="G151" t="str">
-        <v>古银双鱼.png</v>
+        <v>7</v>
+      </c>
+      <c r="G151">
+        <v>69</v>
+      </c>
+      <c r="H151" t="str">
+        <v>天珠.png</v>
+      </c>
+      <c r="I151" t="str">
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>xs_spc_8</v>
+        <v>ysxz_spc_4</v>
       </c>
       <c r="B152" t="str">
         <v>配件</v>
@@ -3883,44 +4789,56 @@
         <v>隔珠</v>
       </c>
       <c r="D152" t="str">
-        <v>醒獅</v>
+        <v>銀色小珠</v>
       </c>
       <c r="E152">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F152">
-        <v>59</v>
-      </c>
-      <c r="G152" t="str">
-        <v>醒狮.png</v>
+        <v>4</v>
+      </c>
+      <c r="G152">
+        <v>69</v>
+      </c>
+      <c r="H152" t="str">
+        <v>银色小珠.png</v>
+      </c>
+      <c r="I152" t="str">
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ysz_zm_4</v>
+        <v>jhy_stn_6</v>
       </c>
       <c r="B153" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C153" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D153" t="str">
-        <v>銀飾Z</v>
+        <v>金虎眼</v>
       </c>
       <c r="E153">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F153">
-        <v>399</v>
-      </c>
-      <c r="G153" t="str">
-        <v>银饰Z.png</v>
+        <v>6</v>
+      </c>
+      <c r="G153">
+        <v>49</v>
+      </c>
+      <c r="H153" t="str">
+        <v>金虎眼.png</v>
+      </c>
+      <c r="I153" t="str">
+        <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ths_stn_6</v>
+        <v>jhy_stn_8</v>
       </c>
       <c r="B154" t="str">
         <v>珠子</v>
@@ -3929,21 +4847,27 @@
         <v>礦石</v>
       </c>
       <c r="D154" t="str">
-        <v>天河石</v>
+        <v>金虎眼</v>
       </c>
       <c r="E154">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F154">
-        <v>59</v>
-      </c>
-      <c r="G154" t="str">
-        <v>天河石.png</v>
+        <v>8</v>
+      </c>
+      <c r="G154">
+        <v>69</v>
+      </c>
+      <c r="H154" t="str">
+        <v>金虎眼.png</v>
+      </c>
+      <c r="I154" t="str">
+        <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>ths_stn_8</v>
+        <v>jhy_stn_10</v>
       </c>
       <c r="B155" t="str">
         <v>珠子</v>
@@ -3952,113 +4876,143 @@
         <v>礦石</v>
       </c>
       <c r="D155" t="str">
-        <v>天河石</v>
+        <v>金虎眼</v>
       </c>
       <c r="E155">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F155">
-        <v>99</v>
-      </c>
-      <c r="G155" t="str">
-        <v>天河石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G155">
+        <v>89</v>
+      </c>
+      <c r="H155" t="str">
+        <v>金虎眼.png</v>
+      </c>
+      <c r="I155" t="str">
+        <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ths_stn_10</v>
+        <v>jsmxyl_pnd_2</v>
       </c>
       <c r="B156" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C156" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D156" t="str">
-        <v>天河石</v>
+        <v>滿鑲彩月</v>
       </c>
       <c r="E156">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F156">
-        <v>139</v>
-      </c>
-      <c r="G156" t="str">
-        <v>天河石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G156">
+        <v>69</v>
+      </c>
+      <c r="H156" t="str">
+        <v>满镶彩月.png</v>
+      </c>
+      <c r="I156" t="str">
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ysd_zm_4</v>
+        <v>lcmj_cysl_6</v>
       </c>
       <c r="B157" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C157" t="str">
-        <v>字母</v>
+        <v>水晶</v>
       </c>
       <c r="D157" t="str">
-        <v>銀飾D</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E157">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F157">
-        <v>399</v>
-      </c>
-      <c r="G157" t="str">
-        <v>银饰D.png</v>
+        <v>6</v>
+      </c>
+      <c r="G157">
+        <v>39</v>
+      </c>
+      <c r="H157" t="str">
+        <v>绿莓晶.png</v>
+      </c>
+      <c r="I157" t="str">
+        <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>hlb_stn_6</v>
+        <v>lcmj_cysl_8</v>
       </c>
       <c r="B158" t="str">
         <v>珠子</v>
       </c>
       <c r="C158" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D158" t="str">
-        <v>海藍寶</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E158">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F158">
-        <v>89</v>
-      </c>
-      <c r="G158" t="str">
-        <v>海蓝宝.png</v>
+        <v>8</v>
+      </c>
+      <c r="G158">
+        <v>59</v>
+      </c>
+      <c r="H158" t="str">
+        <v>绿莓晶.png</v>
+      </c>
+      <c r="I158" t="str">
+        <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>hlb_stn_8</v>
+        <v>lcmj_cysl_10</v>
       </c>
       <c r="B159" t="str">
         <v>珠子</v>
       </c>
       <c r="C159" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D159" t="str">
-        <v>海藍寶</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E159">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F159">
-        <v>99</v>
-      </c>
-      <c r="G159" t="str">
-        <v>海蓝宝.png</v>
+        <v>10</v>
+      </c>
+      <c r="G159">
+        <v>89</v>
+      </c>
+      <c r="H159" t="str">
+        <v>绿莓晶.png</v>
+      </c>
+      <c r="I159" t="str">
+        <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>hlb_stn_10</v>
+        <v>xy_stn_6</v>
       </c>
       <c r="B160" t="str">
         <v>珠子</v>
@@ -4067,67 +5021,85 @@
         <v>礦石</v>
       </c>
       <c r="D160" t="str">
-        <v>海藍寶</v>
+        <v>岫玉</v>
       </c>
       <c r="E160">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F160">
-        <v>169</v>
-      </c>
-      <c r="G160" t="str">
-        <v>海蓝宝.png</v>
+        <v>6</v>
+      </c>
+      <c r="G160">
+        <v>59</v>
+      </c>
+      <c r="H160" t="str">
+        <v>岫玉.png</v>
+      </c>
+      <c r="I160" t="str">
+        <v/>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>yss_zm_4</v>
+        <v>xy_stn_8</v>
       </c>
       <c r="B161" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C161" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D161" t="str">
-        <v>銀飾S</v>
+        <v>岫玉</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F161">
-        <v>399</v>
-      </c>
-      <c r="G161" t="str">
-        <v>银饰S.png</v>
+        <v>8</v>
+      </c>
+      <c r="G161">
+        <v>89</v>
+      </c>
+      <c r="H161" t="str">
+        <v>岫玉.png</v>
+      </c>
+      <c r="I161" t="str">
+        <v/>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>gsch_pnd_2</v>
+        <v>xy_stn_10</v>
       </c>
       <c r="B162" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C162" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D162" t="str">
-        <v>鋯石彩虹</v>
+        <v>岫玉</v>
       </c>
       <c r="E162">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F162">
+        <v>10</v>
+      </c>
+      <c r="G162">
         <v>99</v>
       </c>
-      <c r="G162" t="str">
-        <v>锆石彩虹.png</v>
+      <c r="H162" t="str">
+        <v>岫玉.png</v>
+      </c>
+      <c r="I162" t="str">
+        <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>xgszs_spc_5</v>
+        <v>cyszh_spc_10</v>
       </c>
       <c r="B163" t="str">
         <v>配件</v>
@@ -4136,412 +5108,520 @@
         <v>隔珠</v>
       </c>
       <c r="D163" t="str">
-        <v>小鋯石鑽閃</v>
+        <v>藏銀十字花</v>
       </c>
       <c r="E163">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F163">
-        <v>59</v>
-      </c>
-      <c r="G163" t="str">
-        <v>小锆石钻闪.png</v>
+        <v>10</v>
+      </c>
+      <c r="G163">
+        <v>69</v>
+      </c>
+      <c r="H163" t="str">
+        <v>藏银十字花.png</v>
+      </c>
+      <c r="I163" t="str">
+        <v>義烏市楓瑢</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>htj_cysl_6</v>
+        <v>cyym_pnd_2</v>
       </c>
       <c r="B164" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C164" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D164" t="str">
-        <v>黃塔晶</v>
+        <v>藏銀羽毛</v>
       </c>
       <c r="E164">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F164">
-        <v>49</v>
-      </c>
-      <c r="G164" t="str">
-        <v>黄塔晶.png</v>
+        <v>24</v>
+      </c>
+      <c r="G164">
+        <v>599</v>
+      </c>
+      <c r="H164" t="str">
+        <v>藏银羽毛.png</v>
+      </c>
+      <c r="I164" t="str">
+        <v>廣州市無風帶</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>htj_cysl_8</v>
+        <v>lys_stn_6</v>
       </c>
       <c r="B165" t="str">
         <v>珠子</v>
       </c>
       <c r="C165" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D165" t="str">
-        <v>黃塔晶</v>
+        <v>綠螢石</v>
       </c>
       <c r="E165">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F165">
-        <v>59</v>
-      </c>
-      <c r="G165" t="str">
-        <v>黄塔晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G165">
+        <v>69</v>
+      </c>
+      <c r="H165" t="str">
+        <v>绿萤石.png</v>
+      </c>
+      <c r="I165" t="str">
+        <v/>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>htj_cysl_10</v>
+        <v>lys_stn_8</v>
       </c>
       <c r="B166" t="str">
         <v>珠子</v>
       </c>
       <c r="C166" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D166" t="str">
-        <v>黃塔晶</v>
+        <v>綠螢石</v>
       </c>
       <c r="E166">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F166">
+        <v>8</v>
+      </c>
+      <c r="G166">
         <v>99</v>
       </c>
-      <c r="G166" t="str">
-        <v>黄塔晶.png</v>
+      <c r="H166" t="str">
+        <v>绿萤石.png</v>
+      </c>
+      <c r="I166" t="str">
+        <v/>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>wyh_pnd_2</v>
+        <v>cysy_spc_4</v>
       </c>
       <c r="B167" t="str">
         <v>配件</v>
       </c>
       <c r="C167" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D167" t="str">
-        <v>午夜花</v>
+        <v>藏銀樹葉</v>
       </c>
       <c r="E167">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F167">
-        <v>99</v>
-      </c>
-      <c r="G167" t="str">
-        <v>午夜花.png</v>
+        <v>7</v>
+      </c>
+      <c r="G167">
+        <v>69</v>
+      </c>
+      <c r="H167" t="str">
+        <v>藏银树叶.png</v>
+      </c>
+      <c r="I167" t="str">
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>hfj_cysl_6</v>
+        <v>qws_stn_8</v>
       </c>
       <c r="B168" t="str">
         <v>珠子</v>
       </c>
       <c r="C168" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D168" t="str">
-        <v>黑髮晶</v>
+        <v>薔薇石</v>
       </c>
       <c r="E168">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F168">
-        <v>49</v>
-      </c>
-      <c r="G168" t="str">
-        <v>黑发晶.png</v>
+        <v>8</v>
+      </c>
+      <c r="G168">
+        <v>69</v>
+      </c>
+      <c r="H168" t="str">
+        <v>蔷薇石.png</v>
+      </c>
+      <c r="I168" t="str">
+        <v/>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>hfj_cysl_8</v>
+        <v>qws_stn_10</v>
       </c>
       <c r="B169" t="str">
         <v>珠子</v>
       </c>
       <c r="C169" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D169" t="str">
-        <v>黑髮晶</v>
+        <v>薔薇石</v>
       </c>
       <c r="E169">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F169">
-        <v>69</v>
-      </c>
-      <c r="G169" t="str">
-        <v>黑发晶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G169">
+        <v>99</v>
+      </c>
+      <c r="H169" t="str">
+        <v>蔷薇石.png</v>
+      </c>
+      <c r="I169" t="str">
+        <v/>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>hfj_cysl_10</v>
+        <v>jsxz_spc_4</v>
       </c>
       <c r="B170" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C170" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D170" t="str">
-        <v>黑髮晶</v>
+        <v>金色小珠</v>
       </c>
       <c r="E170">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F170">
-        <v>169</v>
-      </c>
-      <c r="G170" t="str">
-        <v>黑发晶.png</v>
+        <v>4</v>
+      </c>
+      <c r="G170">
+        <v>69</v>
+      </c>
+      <c r="H170" t="str">
+        <v>金色小珠.png</v>
+      </c>
+      <c r="I170" t="str">
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>tz_spc_10</v>
+        <v>gtsp_xz_3</v>
       </c>
       <c r="B171" t="str">
         <v>配件</v>
       </c>
       <c r="C171" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D171" t="str">
-        <v>天珠</v>
+        <v>古銅水瓶</v>
       </c>
       <c r="E171">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F171">
-        <v>99</v>
-      </c>
-      <c r="G171" t="str">
-        <v>天珠.png</v>
+        <v>10</v>
+      </c>
+      <c r="G171">
+        <v>39</v>
+      </c>
+      <c r="H171" t="str">
+        <v>古铜水瓶.png</v>
+      </c>
+      <c r="I171" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>ysxz_spc_6</v>
+        <v>gtby_xz_3</v>
       </c>
       <c r="B172" t="str">
         <v>配件</v>
       </c>
       <c r="C172" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D172" t="str">
-        <v>銀色小珠</v>
+        <v>古銅白羊</v>
       </c>
       <c r="E172">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F172">
-        <v>59</v>
-      </c>
-      <c r="G172" t="str">
-        <v>银色小珠.png</v>
+        <v>10</v>
+      </c>
+      <c r="G172">
+        <v>39</v>
+      </c>
+      <c r="H172" t="str">
+        <v>古铜白羊.png</v>
+      </c>
+      <c r="I172" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>jhy_stn_6</v>
+        <v>gszssc_spc_5</v>
       </c>
       <c r="B173" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C173" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D173" t="str">
-        <v>金虎眼</v>
+        <v>鋯石鑽閃雙層</v>
       </c>
       <c r="E173">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F173">
-        <v>49</v>
-      </c>
-      <c r="G173" t="str">
-        <v>金虎眼.png</v>
+        <v>7</v>
+      </c>
+      <c r="G173">
+        <v>159</v>
+      </c>
+      <c r="H173" t="str">
+        <v>锆石钻闪双层.png</v>
+      </c>
+      <c r="I173" t="str">
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>jhy_stn_8</v>
+        <v>gtshz_xz_3</v>
       </c>
       <c r="B174" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C174" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D174" t="str">
-        <v>金虎眼</v>
+        <v>古銅獅子</v>
       </c>
       <c r="E174">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F174">
-        <v>69</v>
-      </c>
-      <c r="G174" t="str">
-        <v>金虎眼.png</v>
+        <v>10</v>
+      </c>
+      <c r="G174">
+        <v>39</v>
+      </c>
+      <c r="H174" t="str">
+        <v>古铜狮子.png</v>
+      </c>
+      <c r="I174" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>jhy_stn_10</v>
+        <v>gttc_xz_3</v>
       </c>
       <c r="B175" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C175" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D175" t="str">
-        <v>金虎眼</v>
+        <v>古銅天秤</v>
       </c>
       <c r="E175">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F175">
-        <v>89</v>
-      </c>
-      <c r="G175" t="str">
-        <v>金虎眼.png</v>
+        <v>10</v>
+      </c>
+      <c r="G175">
+        <v>39</v>
+      </c>
+      <c r="H175" t="str">
+        <v>古铜天秤.png</v>
+      </c>
+      <c r="I175" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>jsmxyl_pnd_2</v>
+        <v>gtcn_xz_3</v>
       </c>
       <c r="B176" t="str">
         <v>配件</v>
       </c>
       <c r="C176" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D176" t="str">
-        <v>滿鑲彩月</v>
+        <v>古銅處女</v>
       </c>
       <c r="E176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F176">
-        <v>99</v>
-      </c>
-      <c r="G176" t="str">
-        <v>满镶彩月.png</v>
+        <v>10</v>
+      </c>
+      <c r="G176">
+        <v>39</v>
+      </c>
+      <c r="H176" t="str">
+        <v>古铜处女.png</v>
+      </c>
+      <c r="I176" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>hbgd_spc_6</v>
+        <v>ygs_stn_6</v>
       </c>
       <c r="B177" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C177" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D177" t="str">
-        <v>花邊軌道</v>
+        <v>月光石</v>
       </c>
       <c r="E177">
         <v>6</v>
       </c>
       <c r="F177">
-        <v>59</v>
-      </c>
-      <c r="G177" t="str">
-        <v>花边轨道.png</v>
+        <v>6</v>
+      </c>
+      <c r="G177">
+        <v>69</v>
+      </c>
+      <c r="H177" t="str">
+        <v>月光石.png</v>
+      </c>
+      <c r="I177" t="str">
+        <v/>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>lcmj_cysl_6</v>
+        <v>ygs_stn_8</v>
       </c>
       <c r="B178" t="str">
         <v>珠子</v>
       </c>
       <c r="C178" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D178" t="str">
-        <v>綠莓晶</v>
+        <v>月光石</v>
       </c>
       <c r="E178">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F178">
-        <v>39</v>
-      </c>
-      <c r="G178" t="str">
-        <v>绿莓晶.png</v>
+        <v>8</v>
+      </c>
+      <c r="G178">
+        <v>89</v>
+      </c>
+      <c r="H178" t="str">
+        <v>月光石.png</v>
+      </c>
+      <c r="I178" t="str">
+        <v/>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>lcmj_cysl_8</v>
+        <v>ygs_stn_10</v>
       </c>
       <c r="B179" t="str">
         <v>珠子</v>
       </c>
       <c r="C179" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D179" t="str">
-        <v>綠莓晶</v>
+        <v>月光石</v>
       </c>
       <c r="E179">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F179">
-        <v>59</v>
-      </c>
-      <c r="G179" t="str">
-        <v>绿莓晶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G179">
+        <v>129</v>
+      </c>
+      <c r="H179" t="str">
+        <v>月光石.png</v>
+      </c>
+      <c r="I179" t="str">
+        <v/>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>lcmj_cysl_10</v>
+        <v>tys_stn_6</v>
       </c>
       <c r="B180" t="str">
         <v>珠子</v>
       </c>
       <c r="C180" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D180" t="str">
-        <v>綠莓晶</v>
+        <v>太陽石</v>
       </c>
       <c r="E180">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F180">
-        <v>89</v>
-      </c>
-      <c r="G180" t="str">
-        <v>绿莓晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G180">
+        <v>49</v>
+      </c>
+      <c r="H180" t="str">
+        <v>太阳石.png</v>
+      </c>
+      <c r="I180" t="str">
+        <v/>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>xy_stn_6</v>
+        <v>tys_stn_8</v>
       </c>
       <c r="B181" t="str">
         <v>珠子</v>
@@ -4550,21 +5630,27 @@
         <v>礦石</v>
       </c>
       <c r="D181" t="str">
-        <v>岫玉</v>
+        <v>太陽石</v>
       </c>
       <c r="E181">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F181">
-        <v>59</v>
-      </c>
-      <c r="G181" t="str">
-        <v>岫玉.png</v>
+        <v>8</v>
+      </c>
+      <c r="G181">
+        <v>69</v>
+      </c>
+      <c r="H181" t="str">
+        <v>太阳石.png</v>
+      </c>
+      <c r="I181" t="str">
+        <v/>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>xy_stn_8</v>
+        <v>tys_stn_10</v>
       </c>
       <c r="B182" t="str">
         <v>珠子</v>
@@ -4573,21 +5659,27 @@
         <v>礦石</v>
       </c>
       <c r="D182" t="str">
-        <v>岫玉</v>
+        <v>太陽石</v>
       </c>
       <c r="E182">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F182">
-        <v>89</v>
-      </c>
-      <c r="G182" t="str">
-        <v>岫玉.png</v>
+        <v>10</v>
+      </c>
+      <c r="G182">
+        <v>169</v>
+      </c>
+      <c r="H182" t="str">
+        <v>太阳石.png</v>
+      </c>
+      <c r="I182" t="str">
+        <v/>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>xy_stn_10</v>
+        <v>shlb_stn_8</v>
       </c>
       <c r="B183" t="str">
         <v>珠子</v>
@@ -4596,44 +5688,56 @@
         <v>礦石</v>
       </c>
       <c r="D183" t="str">
-        <v>岫玉</v>
+        <v>聖海藍寶</v>
       </c>
       <c r="E183">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F183">
-        <v>99</v>
-      </c>
-      <c r="G183" t="str">
-        <v>岫玉.png</v>
+        <v>8</v>
+      </c>
+      <c r="G183">
+        <v>399</v>
+      </c>
+      <c r="H183" t="str">
+        <v>圣海蓝宝.png</v>
+      </c>
+      <c r="I183" t="str">
+        <v/>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>hcw_spc_5</v>
+        <v>shlb_stn_10</v>
       </c>
       <c r="B184" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C184" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D184" t="str">
-        <v>回財紋</v>
+        <v>聖海藍寶</v>
       </c>
       <c r="E184">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F184">
-        <v>59</v>
-      </c>
-      <c r="G184" t="str">
-        <v>回财纹.png</v>
+        <v>10</v>
+      </c>
+      <c r="G184">
+        <v>699</v>
+      </c>
+      <c r="H184" t="str">
+        <v>圣海蓝宝.png</v>
+      </c>
+      <c r="I184" t="str">
+        <v/>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>cyjc_spc_6</v>
+        <v>yslzzy_spc_9</v>
       </c>
       <c r="B185" t="str">
         <v>配件</v>
@@ -4642,21 +5746,27 @@
         <v>隔珠</v>
       </c>
       <c r="D185" t="str">
-        <v>藏銀卷草</v>
+        <v>銀六字箴言</v>
       </c>
       <c r="E185">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F185">
+        <v>7</v>
+      </c>
+      <c r="G185">
         <v>59</v>
       </c>
-      <c r="G185" t="str">
-        <v>藏银卷草.png</v>
+      <c r="H185" t="str">
+        <v>银六字箴言.png</v>
+      </c>
+      <c r="I185" t="str">
+        <v>義烏市亦蝶</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>hx_spc_6</v>
+        <v>ketj_spc_10</v>
       </c>
       <c r="B186" t="str">
         <v>配件</v>
@@ -4665,21 +5775,27 @@
         <v>隔珠</v>
       </c>
       <c r="D186" t="str">
-        <v>花旋</v>
+        <v>凱爾特結</v>
       </c>
       <c r="E186">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F186">
-        <v>59</v>
-      </c>
-      <c r="G186" t="str">
-        <v>花旋.png</v>
+        <v>6</v>
+      </c>
+      <c r="G186">
+        <v>69</v>
+      </c>
+      <c r="H186" t="str">
+        <v>凯尔特结.png</v>
+      </c>
+      <c r="I186" t="str">
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>cyszh_spc_8</v>
+        <v>ysxq_spc_10</v>
       </c>
       <c r="B187" t="str">
         <v>配件</v>
@@ -4688,182 +5804,230 @@
         <v>隔珠</v>
       </c>
       <c r="D187" t="str">
-        <v>藏銀十字花</v>
+        <v>藏銀繡球</v>
       </c>
       <c r="E187">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F187">
-        <v>59</v>
-      </c>
-      <c r="G187" t="str">
-        <v>藏银十字花.png</v>
+        <v>10</v>
+      </c>
+      <c r="G187">
+        <v>69</v>
+      </c>
+      <c r="H187" t="str">
+        <v>藏银绣球.png</v>
+      </c>
+      <c r="I187" t="str">
+        <v>義烏市隱魚</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>cyym_pnd_2</v>
+        <v>gtszz_xz_3</v>
       </c>
       <c r="B188" t="str">
         <v>配件</v>
       </c>
       <c r="C188" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D188" t="str">
-        <v>藏銀羽毛</v>
+        <v>古銅雙子</v>
       </c>
       <c r="E188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F188">
-        <v>99</v>
-      </c>
-      <c r="G188" t="str">
-        <v>藏银羽毛.png</v>
+        <v>10</v>
+      </c>
+      <c r="G188">
+        <v>39</v>
+      </c>
+      <c r="H188" t="str">
+        <v>古铜双子.png</v>
+      </c>
+      <c r="I188" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>lys_stn_6</v>
+        <v>zsj_cysl_6</v>
       </c>
       <c r="B189" t="str">
         <v>珠子</v>
       </c>
       <c r="C189" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D189" t="str">
-        <v>綠螢石</v>
+        <v>紫水晶</v>
       </c>
       <c r="E189">
         <v>6</v>
       </c>
       <c r="F189">
+        <v>6</v>
+      </c>
+      <c r="G189">
         <v>69</v>
       </c>
-      <c r="G189" t="str">
-        <v>绿萤石.png</v>
+      <c r="H189" t="str">
+        <v>紫水晶.png</v>
+      </c>
+      <c r="I189" t="str">
+        <v/>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>lys_stn_8</v>
+        <v>zsj_cysl_8</v>
       </c>
       <c r="B190" t="str">
         <v>珠子</v>
       </c>
       <c r="C190" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D190" t="str">
-        <v>綠螢石</v>
+        <v>紫水晶</v>
       </c>
       <c r="E190">
         <v>8</v>
       </c>
       <c r="F190">
-        <v>99</v>
-      </c>
-      <c r="G190" t="str">
-        <v>绿萤石.png</v>
+        <v>8</v>
+      </c>
+      <c r="G190">
+        <v>89</v>
+      </c>
+      <c r="H190" t="str">
+        <v>紫水晶.png</v>
+      </c>
+      <c r="I190" t="str">
+        <v/>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>cysy_spc_6</v>
+        <v>zsj_cysl_10</v>
       </c>
       <c r="B191" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C191" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D191" t="str">
-        <v>藏銀樹葉</v>
+        <v>紫水晶</v>
       </c>
       <c r="E191">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F191">
-        <v>59</v>
-      </c>
-      <c r="G191" t="str">
-        <v>藏银树叶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G191">
+        <v>99</v>
+      </c>
+      <c r="H191" t="str">
+        <v>紫水晶.png</v>
+      </c>
+      <c r="I191" t="str">
+        <v/>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>qws_stn_8</v>
+        <v>wgzl_pnd_2</v>
       </c>
       <c r="B192" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C192" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D192" t="str">
-        <v>薔薇石</v>
+        <v>國王之淚</v>
       </c>
       <c r="E192">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F192">
-        <v>69</v>
-      </c>
-      <c r="G192" t="str">
-        <v>蔷薇石.png</v>
+        <v>20</v>
+      </c>
+      <c r="G192">
+        <v>99</v>
+      </c>
+      <c r="H192" t="str">
+        <v>国王之泪.png</v>
+      </c>
+      <c r="I192" t="str">
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>qws_stn_10</v>
+        <v>gtsy_xz_3</v>
       </c>
       <c r="B193" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C193" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D193" t="str">
-        <v>薔薇石</v>
+        <v>古銅雙魚</v>
       </c>
       <c r="E193">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F193">
-        <v>99</v>
-      </c>
-      <c r="G193" t="str">
-        <v>蔷薇石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G193">
+        <v>39</v>
+      </c>
+      <c r="H193" t="str">
+        <v>古铜双鱼.png</v>
+      </c>
+      <c r="I193" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>jsxz_spc_6</v>
+        <v>gtmj_xz_3</v>
       </c>
       <c r="B194" t="str">
         <v>配件</v>
       </c>
       <c r="C194" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D194" t="str">
-        <v>金色小珠</v>
+        <v>古銅摩羯</v>
       </c>
       <c r="E194">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F194">
-        <v>59</v>
-      </c>
-      <c r="G194" t="str">
-        <v>金色小珠.png</v>
+        <v>10</v>
+      </c>
+      <c r="G194">
+        <v>39</v>
+      </c>
+      <c r="H194" t="str">
+        <v>古铜摩羯.png</v>
+      </c>
+      <c r="I194" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>gtsp_xz_2</v>
+        <v>gtss_xz_3</v>
       </c>
       <c r="B195" t="str">
         <v>配件</v>
@@ -4872,21 +6036,27 @@
         <v>星座</v>
       </c>
       <c r="D195" t="str">
-        <v>古銅水瓶</v>
+        <v>古銅射手</v>
       </c>
       <c r="E195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F195">
+        <v>10</v>
+      </c>
+      <c r="G195">
         <v>39</v>
       </c>
-      <c r="G195" t="str">
-        <v>古铜水瓶.png</v>
+      <c r="H195" t="str">
+        <v>古铜射手.png</v>
+      </c>
+      <c r="I195" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>gtby_xz_2</v>
+        <v>gtjn_xz_3</v>
       </c>
       <c r="B196" t="str">
         <v>配件</v>
@@ -4895,67 +6065,85 @@
         <v>星座</v>
       </c>
       <c r="D196" t="str">
-        <v>古銅白羊</v>
+        <v>古銅金牛</v>
       </c>
       <c r="E196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F196">
+        <v>10</v>
+      </c>
+      <c r="G196">
         <v>39</v>
       </c>
-      <c r="G196" t="str">
-        <v>古铜白羊.png</v>
+      <c r="H196" t="str">
+        <v>古铜金牛.png</v>
+      </c>
+      <c r="I196" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>gszssc_spc_6</v>
+        <v>zfj_cysl_8</v>
       </c>
       <c r="B197" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C197" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D197" t="str">
-        <v>鋯石鑽閃雙層</v>
+        <v>紫粉晶</v>
       </c>
       <c r="E197">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F197">
-        <v>59</v>
-      </c>
-      <c r="G197" t="str">
-        <v>锆石钻闪双层.png</v>
+        <v>8</v>
+      </c>
+      <c r="G197">
+        <v>69</v>
+      </c>
+      <c r="H197" t="str">
+        <v>紫粉晶.png</v>
+      </c>
+      <c r="I197" t="str">
+        <v/>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>cywp_spc_8</v>
+        <v>zfj_cysl_10</v>
       </c>
       <c r="B198" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C198" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D198" t="str">
-        <v>藏銀瓦片</v>
+        <v>紫粉晶</v>
       </c>
       <c r="E198">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F198">
-        <v>59</v>
-      </c>
-      <c r="G198" t="str">
-        <v>藏银瓦片.png</v>
+        <v>10</v>
+      </c>
+      <c r="G198">
+        <v>99</v>
+      </c>
+      <c r="H198" t="str">
+        <v>紫粉晶.png</v>
+      </c>
+      <c r="I198" t="str">
+        <v/>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>gtshz_xz_2</v>
+        <v>gttx_xz_3</v>
       </c>
       <c r="B199" t="str">
         <v>配件</v>
@@ -4964,1010 +6152,1274 @@
         <v>星座</v>
       </c>
       <c r="D199" t="str">
-        <v>古銅獅子</v>
+        <v>古銅天蠍</v>
       </c>
       <c r="E199">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F199">
+        <v>10</v>
+      </c>
+      <c r="G199">
         <v>39</v>
       </c>
-      <c r="G199" t="str">
-        <v>古铜狮子.png</v>
+      <c r="H199" t="str">
+        <v>古铜天蝎.png</v>
+      </c>
+      <c r="I199" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>syc_pnd_2</v>
+        <v>jslzzy_spc_9</v>
       </c>
       <c r="B200" t="str">
         <v>配件</v>
       </c>
       <c r="C200" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D200" t="str">
-        <v>四葉草</v>
+        <v>金六字箴言</v>
       </c>
       <c r="E200">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F200">
-        <v>99</v>
-      </c>
-      <c r="G200" t="str">
-        <v>四叶草.png</v>
+        <v>7</v>
+      </c>
+      <c r="G200">
+        <v>59</v>
+      </c>
+      <c r="H200" t="str">
+        <v>金六字箴言.png</v>
+      </c>
+      <c r="I200" t="str">
+        <v>義烏市亦蝶</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>gttc_xz_2</v>
+        <v>cmj_cysl_6</v>
       </c>
       <c r="B201" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C201" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D201" t="str">
-        <v>古銅天秤</v>
+        <v>草莓晶</v>
       </c>
       <c r="E201">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F201">
+        <v>6</v>
+      </c>
+      <c r="G201">
         <v>39</v>
       </c>
-      <c r="G201" t="str">
-        <v>古铜天秤.png</v>
+      <c r="H201" t="str">
+        <v>草莓晶.png</v>
+      </c>
+      <c r="I201" t="str">
+        <v/>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>gtcn_xz_2</v>
+        <v>cmj_cysl_8</v>
       </c>
       <c r="B202" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C202" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D202" t="str">
-        <v>古銅處女</v>
+        <v>草莓晶</v>
       </c>
       <c r="E202">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F202">
-        <v>39</v>
-      </c>
-      <c r="G202" t="str">
-        <v>古铜处女.png</v>
+        <v>8</v>
+      </c>
+      <c r="G202">
+        <v>69</v>
+      </c>
+      <c r="H202" t="str">
+        <v>草莓晶.png</v>
+      </c>
+      <c r="I202" t="str">
+        <v/>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>ygs_stn_6</v>
+        <v>cmj_cysl_10</v>
       </c>
       <c r="B203" t="str">
         <v>珠子</v>
       </c>
       <c r="C203" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D203" t="str">
-        <v>月光石</v>
+        <v>草莓晶</v>
       </c>
       <c r="E203">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F203">
-        <v>69</v>
-      </c>
-      <c r="G203" t="str">
-        <v>月光石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G203">
+        <v>99</v>
+      </c>
+      <c r="H203" t="str">
+        <v>草莓晶.png</v>
+      </c>
+      <c r="I203" t="str">
+        <v/>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>ygs_stn_8</v>
+        <v>tg1_sz_7</v>
       </c>
       <c r="B204" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C204" t="str">
-        <v>礦石</v>
+        <v>數字</v>
       </c>
       <c r="D204" t="str">
-        <v>月光石</v>
+        <v>鈦鋼1</v>
       </c>
       <c r="E204">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F204">
-        <v>89</v>
-      </c>
-      <c r="G204" t="str">
-        <v>月光石.png</v>
+        <v>7</v>
+      </c>
+      <c r="G204">
+        <v>59</v>
+      </c>
+      <c r="H204" t="str">
+        <v>钛钢1.png</v>
+      </c>
+      <c r="I204" t="str">
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>ygs_stn_10</v>
+        <v>gtjx_xz_3</v>
       </c>
       <c r="B205" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C205" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D205" t="str">
-        <v>月光石</v>
+        <v>古銅巨蟹</v>
       </c>
       <c r="E205">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F205">
-        <v>129</v>
-      </c>
-      <c r="G205" t="str">
-        <v>月光石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G205">
+        <v>39</v>
+      </c>
+      <c r="H205" t="str">
+        <v>古铜巨蟹.png</v>
+      </c>
+      <c r="I205" t="str">
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>tys_stn_6</v>
+        <v>cyhdls_pnd_2</v>
       </c>
       <c r="B206" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C206" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D206" t="str">
-        <v>太陽石</v>
+        <v>藏銀蝴蝶流蘇</v>
       </c>
       <c r="E206">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F206">
-        <v>49</v>
-      </c>
-      <c r="G206" t="str">
-        <v>太阳石.png</v>
+        <v>58</v>
+      </c>
+      <c r="G206">
+        <v>99</v>
+      </c>
+      <c r="H206" t="str">
+        <v>藏银蝴蝶流苏.png</v>
+      </c>
+      <c r="I206" t="str">
+        <v>中山市凱髮飾品</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>tys_stn_8</v>
+        <v>cyhw_spc_4</v>
       </c>
       <c r="B207" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C207" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D207" t="str">
-        <v>太陽石</v>
+        <v>藏銀回紋</v>
       </c>
       <c r="E207">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F207">
+        <v>10</v>
+      </c>
+      <c r="G207">
         <v>69</v>
       </c>
-      <c r="G207" t="str">
-        <v>太阳石.png</v>
+      <c r="H207" t="str">
+        <v>藏银回纹.png</v>
+      </c>
+      <c r="I207" t="str">
+        <v>中山市凱發</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>tys_stn_10</v>
+        <v>cyszdz_pnd_2</v>
       </c>
       <c r="B208" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C208" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D208" t="str">
-        <v>太陽石</v>
+        <v>藏銀十字</v>
       </c>
       <c r="E208">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F208">
-        <v>169</v>
-      </c>
-      <c r="G208" t="str">
-        <v>太阳石.png</v>
+        <v>8</v>
+      </c>
+      <c r="G208">
+        <v>99</v>
+      </c>
+      <c r="H208" t="str">
+        <v>藏银十字.png</v>
+      </c>
+      <c r="I208" t="str">
+        <v>汕頭市澄海區漁米</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>shlb_stn_8</v>
+        <v>cydhlf_spc_8</v>
       </c>
       <c r="B209" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C209" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D209" t="str">
-        <v>聖海藍寶</v>
+        <v>藏銀立方</v>
       </c>
       <c r="E209">
         <v>8</v>
       </c>
       <c r="F209">
-        <v>399</v>
-      </c>
-      <c r="G209" t="str">
-        <v>圣海蓝宝.png</v>
+        <v>8</v>
+      </c>
+      <c r="G209">
+        <v>69</v>
+      </c>
+      <c r="H209" t="str">
+        <v>藏银立方.png</v>
+      </c>
+      <c r="I209" t="str">
+        <v>義烏市鑫澗</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>shlb_stn_10</v>
+        <v>jtlfq_spc_11</v>
       </c>
       <c r="B210" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C210" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D210" t="str">
-        <v>聖海藍寶</v>
+        <v>景泰藍</v>
       </c>
       <c r="E210">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F210">
-        <v>699</v>
-      </c>
-      <c r="G210" t="str">
-        <v>圣海蓝宝.png</v>
+        <v>11</v>
+      </c>
+      <c r="G210">
+        <v>99</v>
+      </c>
+      <c r="H210" t="str">
+        <v>景泰蓝.png</v>
+      </c>
+      <c r="I210" t="str">
+        <v>義烏市璇霽</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>yslzzy_spc_8</v>
+        <v>hjc_cysl_6</v>
       </c>
       <c r="B211" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C211" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D211" t="str">
-        <v>銀六字箴言</v>
+        <v>黑金超</v>
       </c>
       <c r="E211">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F211">
-        <v>59</v>
-      </c>
-      <c r="G211" t="str">
-        <v>银六字箴言.png</v>
+        <v>6</v>
+      </c>
+      <c r="G211">
+        <v>49</v>
+      </c>
+      <c r="H211" t="str">
+        <v>黑金超.png</v>
+      </c>
+      <c r="I211" t="str">
+        <v/>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>ketj_spc_6</v>
+        <v>hjc_cysl_8</v>
       </c>
       <c r="B212" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C212" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D212" t="str">
-        <v>凱爾特結</v>
+        <v>黑金超</v>
       </c>
       <c r="E212">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F212">
-        <v>59</v>
-      </c>
-      <c r="G212" t="str">
-        <v>凯尔特结.png</v>
+        <v>8</v>
+      </c>
+      <c r="G212">
+        <v>69</v>
+      </c>
+      <c r="H212" t="str">
+        <v>黑金超.png</v>
+      </c>
+      <c r="I212" t="str">
+        <v/>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>ysxq_spc_8</v>
+        <v>hjc_cysl_10</v>
       </c>
       <c r="B213" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C213" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D213" t="str">
-        <v>藏銀繡球</v>
+        <v>黑金超</v>
       </c>
       <c r="E213">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F213">
-        <v>59</v>
-      </c>
-      <c r="G213" t="str">
-        <v>藏银绣球.png</v>
+        <v>10</v>
+      </c>
+      <c r="G213">
+        <v>99</v>
+      </c>
+      <c r="H213" t="str">
+        <v>黑金超.png</v>
+      </c>
+      <c r="I213" t="str">
+        <v/>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>gtszz_xz_2</v>
+        <v>nh_agt_6</v>
       </c>
       <c r="B214" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C214" t="str">
-        <v>星座</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D214" t="str">
-        <v>古銅雙子</v>
+        <v>南紅</v>
       </c>
       <c r="E214">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F214">
+        <v>6</v>
+      </c>
+      <c r="G214">
         <v>39</v>
       </c>
-      <c r="G214" t="str">
-        <v>古铜双子.png</v>
+      <c r="H214" t="str">
+        <v>南红.png</v>
+      </c>
+      <c r="I214" t="str">
+        <v/>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>zsj_cysl_6</v>
+        <v>nh_agt_8</v>
       </c>
       <c r="B215" t="str">
         <v>珠子</v>
       </c>
       <c r="C215" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D215" t="str">
-        <v>紫水晶</v>
+        <v>南紅</v>
       </c>
       <c r="E215">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F215">
+        <v>8</v>
+      </c>
+      <c r="G215">
         <v>69</v>
       </c>
-      <c r="G215" t="str">
-        <v>紫水晶.png</v>
+      <c r="H215" t="str">
+        <v>南红.png</v>
+      </c>
+      <c r="I215" t="str">
+        <v/>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>zsj_cysl_8</v>
+        <v>nh_agt_10</v>
       </c>
       <c r="B216" t="str">
         <v>珠子</v>
       </c>
       <c r="C216" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D216" t="str">
-        <v>紫水晶</v>
+        <v>南紅</v>
       </c>
       <c r="E216">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F216">
-        <v>89</v>
-      </c>
-      <c r="G216" t="str">
-        <v>紫水晶.png</v>
+        <v>10</v>
+      </c>
+      <c r="G216">
+        <v>129</v>
+      </c>
+      <c r="H216" t="str">
+        <v>南红.png</v>
+      </c>
+      <c r="I216" t="str">
+        <v/>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>zsj_cysl_10</v>
+        <v>hyes_stn_6</v>
       </c>
       <c r="B217" t="str">
         <v>珠子</v>
       </c>
       <c r="C217" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D217" t="str">
-        <v>紫水晶</v>
+        <v>虎眼石</v>
       </c>
       <c r="E217">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F217">
-        <v>99</v>
-      </c>
-      <c r="G217" t="str">
-        <v>紫水晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G217">
+        <v>39</v>
+      </c>
+      <c r="H217" t="str">
+        <v>虎眼石.png</v>
+      </c>
+      <c r="I217" t="str">
+        <v/>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>wgzl_pnd_2</v>
+        <v>hyes_stn_8</v>
       </c>
       <c r="B218" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C218" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D218" t="str">
-        <v>國王之淚</v>
+        <v>虎眼石</v>
       </c>
       <c r="E218">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F218">
-        <v>99</v>
-      </c>
-      <c r="G218" t="str">
-        <v>国王之泪.png</v>
+        <v>8</v>
+      </c>
+      <c r="G218">
+        <v>59</v>
+      </c>
+      <c r="H218" t="str">
+        <v>虎眼石.png</v>
+      </c>
+      <c r="I218" t="str">
+        <v/>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>gtsy_xz_2</v>
+        <v>hyes_stn_10</v>
       </c>
       <c r="B219" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C219" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D219" t="str">
-        <v>古銅雙魚</v>
+        <v>虎眼石</v>
       </c>
       <c r="E219">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F219">
-        <v>39</v>
-      </c>
-      <c r="G219" t="str">
-        <v>古铜双鱼.png</v>
+        <v>10</v>
+      </c>
+      <c r="G219">
+        <v>89</v>
+      </c>
+      <c r="H219" t="str">
+        <v>虎眼石.png</v>
+      </c>
+      <c r="I219" t="str">
+        <v/>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>gtmj_xz_2</v>
+        <v>gqys_agt_6</v>
       </c>
       <c r="B220" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C220" t="str">
-        <v>星座</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D220" t="str">
-        <v>古銅摩羯</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E220">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F220">
-        <v>39</v>
-      </c>
-      <c r="G220" t="str">
-        <v>古铜摩羯.png</v>
+        <v>6</v>
+      </c>
+      <c r="G220">
+        <v>59</v>
+      </c>
+      <c r="H220" t="str">
+        <v>干青玉髓.png</v>
+      </c>
+      <c r="I220" t="str">
+        <v/>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>gtss_xz_2</v>
+        <v>gqys_agt_8</v>
       </c>
       <c r="B221" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C221" t="str">
-        <v>星座</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D221" t="str">
-        <v>古銅射手</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E221">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F221">
-        <v>39</v>
-      </c>
-      <c r="G221" t="str">
-        <v>古铜射手.png</v>
+        <v>8</v>
+      </c>
+      <c r="G221">
+        <v>69</v>
+      </c>
+      <c r="H221" t="str">
+        <v>干青玉髓.png</v>
+      </c>
+      <c r="I221" t="str">
+        <v/>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>gtjn_xz_2</v>
+        <v>gqys_agt_10</v>
       </c>
       <c r="B222" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C222" t="str">
-        <v>星座</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D222" t="str">
-        <v>古銅金牛</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E222">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F222">
-        <v>39</v>
-      </c>
-      <c r="G222" t="str">
-        <v>古铜金牛.png</v>
+        <v>10</v>
+      </c>
+      <c r="G222">
+        <v>89</v>
+      </c>
+      <c r="H222" t="str">
+        <v>干青玉髓.png</v>
+      </c>
+      <c r="I222" t="str">
+        <v/>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>zfj_cysl_8</v>
+        <v>yys_stn_6</v>
       </c>
       <c r="B223" t="str">
         <v>珠子</v>
       </c>
       <c r="C223" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D223" t="str">
-        <v>紫粉晶</v>
+        <v>銀曜石</v>
       </c>
       <c r="E223">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F223">
-        <v>69</v>
-      </c>
-      <c r="G223" t="str">
-        <v>紫粉晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G223">
+        <v>39</v>
+      </c>
+      <c r="H223" t="str">
+        <v>银曜石.png</v>
+      </c>
+      <c r="I223" t="str">
+        <v/>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>zfj_cysl_10</v>
+        <v>yys_stn_8</v>
       </c>
       <c r="B224" t="str">
         <v>珠子</v>
       </c>
       <c r="C224" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D224" t="str">
-        <v>紫粉晶</v>
+        <v>銀曜石</v>
       </c>
       <c r="E224">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F224">
-        <v>99</v>
-      </c>
-      <c r="G224" t="str">
-        <v>紫粉晶.png</v>
+        <v>8</v>
+      </c>
+      <c r="G224">
+        <v>69</v>
+      </c>
+      <c r="H224" t="str">
+        <v>银曜石.png</v>
+      </c>
+      <c r="I224" t="str">
+        <v/>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>gttx_xz_2</v>
+        <v>yys_stn_10</v>
       </c>
       <c r="B225" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C225" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D225" t="str">
-        <v>古銅天蠍</v>
+        <v>銀曜石</v>
       </c>
       <c r="E225">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F225">
-        <v>39</v>
-      </c>
-      <c r="G225" t="str">
-        <v>古铜天蝎.png</v>
+        <v>10</v>
+      </c>
+      <c r="G225">
+        <v>99</v>
+      </c>
+      <c r="H225" t="str">
+        <v>银曜石.png</v>
+      </c>
+      <c r="I225" t="str">
+        <v/>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>jslzzy_spc_8</v>
+        <v>bmw_pnd_2</v>
       </c>
       <c r="B226" t="str">
         <v>配件</v>
       </c>
       <c r="C226" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D226" t="str">
-        <v>金六字箴言</v>
+        <v>捕夢網</v>
       </c>
       <c r="E226">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F226">
-        <v>59</v>
-      </c>
-      <c r="G226" t="str">
-        <v>金六字箴言.png</v>
+        <v>30</v>
+      </c>
+      <c r="G226">
+        <v>69</v>
+      </c>
+      <c r="H226" t="str">
+        <v>捕梦网.png</v>
+      </c>
+      <c r="I226" t="str">
+        <v>東海縣祥慕戀</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>cmj_cysl_6</v>
+        <v>zs_stn_6</v>
       </c>
       <c r="B227" t="str">
         <v>珠子</v>
       </c>
       <c r="C227" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D227" t="str">
-        <v>草莓晶</v>
+        <v>硃砂</v>
       </c>
       <c r="E227">
         <v>6</v>
       </c>
       <c r="F227">
-        <v>39</v>
-      </c>
-      <c r="G227" t="str">
-        <v>草莓晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G227">
+        <v>99</v>
+      </c>
+      <c r="H227" t="str">
+        <v>朱砂.png</v>
+      </c>
+      <c r="I227" t="str">
+        <v/>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>cmj_cysl_8</v>
+        <v>ljs_stn_6</v>
       </c>
       <c r="B228" t="str">
         <v>珠子</v>
       </c>
       <c r="C228" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D228" t="str">
-        <v>草莓晶</v>
+        <v>藍晶石</v>
       </c>
       <c r="E228">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F228">
-        <v>69</v>
-      </c>
-      <c r="G228" t="str">
-        <v>草莓晶.png</v>
+        <v>6</v>
+      </c>
+      <c r="G228">
+        <v>99</v>
+      </c>
+      <c r="H228" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+      <c r="I228" t="str">
+        <v/>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>cmj_cysl_10</v>
+        <v>ljs_stn_8</v>
       </c>
       <c r="B229" t="str">
         <v>珠子</v>
       </c>
       <c r="C229" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D229" t="str">
-        <v>草莓晶</v>
+        <v>藍晶石</v>
       </c>
       <c r="E229">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F229">
-        <v>99</v>
-      </c>
-      <c r="G229" t="str">
-        <v>草莓晶.png</v>
+        <v>8</v>
+      </c>
+      <c r="G229">
+        <v>139</v>
+      </c>
+      <c r="H229" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+      <c r="I229" t="str">
+        <v/>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>tg1_sz_7</v>
+        <v>ljs_stn_10</v>
       </c>
       <c r="B230" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C230" t="str">
-        <v>數字</v>
+        <v>礦石</v>
       </c>
       <c r="D230" t="str">
-        <v>鈦鋼1</v>
+        <v>藍晶石</v>
       </c>
       <c r="E230">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F230">
-        <v>39</v>
-      </c>
-      <c r="G230" t="str">
-        <v>钛钢1.png</v>
+        <v>10</v>
+      </c>
+      <c r="G230">
+        <v>199</v>
+      </c>
+      <c r="H230" t="str">
+        <v>蓝晶石.png</v>
+      </c>
+      <c r="I230" t="str">
+        <v/>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>gtjx_xz_2</v>
+        <v>hmn_agt_6</v>
       </c>
       <c r="B231" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C231" t="str">
-        <v>星座</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D231" t="str">
-        <v>古銅巨蟹</v>
+        <v>紅瑪瑙</v>
       </c>
       <c r="E231">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F231">
+        <v>6</v>
+      </c>
+      <c r="G231">
         <v>39</v>
       </c>
-      <c r="G231" t="str">
-        <v>古铜巨蟹.png</v>
+      <c r="H231" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+      <c r="I231" t="str">
+        <v/>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>cyhdls_pnd_2</v>
+        <v>hmn_agt_8</v>
       </c>
       <c r="B232" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C232" t="str">
-        <v>吊墜</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D232" t="str">
-        <v>藏銀蝴蝶流蘇</v>
+        <v>紅瑪瑙</v>
       </c>
       <c r="E232">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F232">
-        <v>99</v>
-      </c>
-      <c r="G232" t="str">
-        <v>藏银蝴蝶流苏.png</v>
+        <v>8</v>
+      </c>
+      <c r="G232">
+        <v>59</v>
+      </c>
+      <c r="H232" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+      <c r="I232" t="str">
+        <v/>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>mghh_spc_6</v>
+        <v>hmn_agt_10</v>
       </c>
       <c r="B233" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C233" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D233" t="str">
-        <v>玫瑰花環</v>
+        <v>紅瑪瑙</v>
       </c>
       <c r="E233">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F233">
-        <v>59</v>
-      </c>
-      <c r="G233" t="str">
-        <v>玫瑰花环.png</v>
+        <v>10</v>
+      </c>
+      <c r="G233">
+        <v>89</v>
+      </c>
+      <c r="H233" t="str">
+        <v>红玛瑙.png</v>
+      </c>
+      <c r="I233" t="str">
+        <v/>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>bmnmh_spc_8</v>
+        <v>csj_cysl_6</v>
       </c>
       <c r="B234" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C234" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D234" t="str">
-        <v>白瑪瑙魔盒</v>
+        <v>茶水晶</v>
       </c>
       <c r="E234">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F234">
-        <v>59</v>
-      </c>
-      <c r="G234" t="str">
-        <v>白玛瑙魔盒.png</v>
+        <v>6</v>
+      </c>
+      <c r="G234">
+        <v>39</v>
+      </c>
+      <c r="H234" t="str">
+        <v>茶水晶.png</v>
+      </c>
+      <c r="I234" t="str">
+        <v/>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>cyhw_spc_5</v>
+        <v>csj_cysl_8</v>
       </c>
       <c r="B235" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C235" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D235" t="str">
-        <v>藏銀回紋</v>
+        <v>茶水晶</v>
       </c>
       <c r="E235">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F235">
+        <v>8</v>
+      </c>
+      <c r="G235">
         <v>59</v>
       </c>
-      <c r="G235" t="str">
-        <v>藏银回纹.png</v>
+      <c r="H235" t="str">
+        <v>茶水晶.png</v>
+      </c>
+      <c r="I235" t="str">
+        <v/>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>zsmh_spc_8</v>
+        <v>csj_cysl_10</v>
       </c>
       <c r="B236" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C236" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D236" t="str">
-        <v>硃砂魔盒</v>
+        <v>茶水晶</v>
       </c>
       <c r="E236">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F236">
-        <v>59</v>
-      </c>
-      <c r="G236" t="str">
-        <v>朱砂魔盒.png</v>
+        <v>10</v>
+      </c>
+      <c r="G236">
+        <v>89</v>
+      </c>
+      <c r="H236" t="str">
+        <v>茶水晶.png</v>
+      </c>
+      <c r="I236" t="str">
+        <v/>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>cyszdz_pnd_2</v>
+        <v>kqs_stn_6</v>
       </c>
       <c r="B237" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C237" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D237" t="str">
-        <v>藏銀十字</v>
+        <v>孔雀石</v>
       </c>
       <c r="E237">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F237">
-        <v>99</v>
-      </c>
-      <c r="G237" t="str">
-        <v>藏银十字.png</v>
+        <v>6</v>
+      </c>
+      <c r="G237">
+        <v>69</v>
+      </c>
+      <c r="H237" t="str">
+        <v>孔雀石.png</v>
+      </c>
+      <c r="I237" t="str">
+        <v/>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>cyyc_pnd_2</v>
+        <v>kqs_stn_8</v>
       </c>
       <c r="B238" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C238" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D238" t="str">
-        <v>藏銀葉叢</v>
+        <v>孔雀石</v>
       </c>
       <c r="E238">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F238">
-        <v>99</v>
-      </c>
-      <c r="G238" t="str">
-        <v>藏银叶丛.png</v>
+        <v>8</v>
+      </c>
+      <c r="G238">
+        <v>89</v>
+      </c>
+      <c r="H238" t="str">
+        <v>孔雀石.png</v>
+      </c>
+      <c r="I238" t="str">
+        <v/>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>cydhlf_spc_8</v>
+        <v>kqs_stn_10</v>
       </c>
       <c r="B239" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C239" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D239" t="str">
-        <v>藏銀立方</v>
+        <v>孔雀石</v>
       </c>
       <c r="E239">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F239">
-        <v>59</v>
-      </c>
-      <c r="G239" t="str">
-        <v>藏银立方.png</v>
+        <v>10</v>
+      </c>
+      <c r="G239">
+        <v>199</v>
+      </c>
+      <c r="H239" t="str">
+        <v>孔雀石.png</v>
+      </c>
+      <c r="I239" t="str">
+        <v/>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>jtlfq_spc_8</v>
+        <v>qjs_stn_6</v>
       </c>
       <c r="B240" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C240" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D240" t="str">
-        <v>景泰藍</v>
+        <v>青金石</v>
       </c>
       <c r="E240">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F240">
-        <v>59</v>
-      </c>
-      <c r="G240" t="str">
-        <v>景泰蓝.png</v>
+        <v>6</v>
+      </c>
+      <c r="G240">
+        <v>69</v>
+      </c>
+      <c r="H240" t="str">
+        <v>青金石.png</v>
+      </c>
+      <c r="I240" t="str">
+        <v/>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>hjc_cysl_6</v>
+        <v>qjs_stn_8</v>
       </c>
       <c r="B241" t="str">
         <v>珠子</v>
       </c>
       <c r="C241" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D241" t="str">
-        <v>黑金超</v>
+        <v>青金石</v>
       </c>
       <c r="E241">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F241">
-        <v>49</v>
-      </c>
-      <c r="G241" t="str">
-        <v>黑金超.png</v>
+        <v>8</v>
+      </c>
+      <c r="G241">
+        <v>89</v>
+      </c>
+      <c r="H241" t="str">
+        <v>青金石.png</v>
+      </c>
+      <c r="I241" t="str">
+        <v/>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>hjc_cysl_8</v>
+        <v>qjs_stn_10</v>
       </c>
       <c r="B242" t="str">
         <v>珠子</v>
       </c>
       <c r="C242" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D242" t="str">
-        <v>黑金超</v>
+        <v>青金石</v>
       </c>
       <c r="E242">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F242">
-        <v>69</v>
-      </c>
-      <c r="G242" t="str">
-        <v>黑金超.png</v>
+        <v>10</v>
+      </c>
+      <c r="G242">
+        <v>99</v>
+      </c>
+      <c r="H242" t="str">
+        <v>青金石.png</v>
+      </c>
+      <c r="I242" t="str">
+        <v/>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>hjc_cysl_10</v>
+        <v>wlg_cysl_6</v>
       </c>
       <c r="B243" t="str">
         <v>珠子</v>
@@ -5976,159 +7428,201 @@
         <v>水晶</v>
       </c>
       <c r="D243" t="str">
-        <v>黑金超</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E243">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F243">
-        <v>99</v>
-      </c>
-      <c r="G243" t="str">
-        <v>黑金超.png</v>
+        <v>6</v>
+      </c>
+      <c r="G243">
+        <v>69</v>
+      </c>
+      <c r="H243" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+      <c r="I243" t="str">
+        <v/>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>nh_agt_6</v>
+        <v>wlg_cysl_8</v>
       </c>
       <c r="B244" t="str">
         <v>珠子</v>
       </c>
       <c r="C244" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D244" t="str">
-        <v>南紅</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E244">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F244">
-        <v>39</v>
-      </c>
-      <c r="G244" t="str">
-        <v>南红.png</v>
+        <v>8</v>
+      </c>
+      <c r="G244">
+        <v>99</v>
+      </c>
+      <c r="H244" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+      <c r="I244" t="str">
+        <v/>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>nh_agt_8</v>
+        <v>wlg_cysl_10</v>
       </c>
       <c r="B245" t="str">
         <v>珠子</v>
       </c>
       <c r="C245" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D245" t="str">
-        <v>南紅</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E245">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F245">
-        <v>69</v>
-      </c>
-      <c r="G245" t="str">
-        <v>南红.png</v>
+        <v>10</v>
+      </c>
+      <c r="G245">
+        <v>169</v>
+      </c>
+      <c r="H245" t="str">
+        <v>乌拉圭.png</v>
+      </c>
+      <c r="I245" t="str">
+        <v/>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>nh_agt_10</v>
+        <v>zyl_cysl_6</v>
       </c>
       <c r="B246" t="str">
         <v>珠子</v>
       </c>
       <c r="C246" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D246" t="str">
-        <v>南紅</v>
+        <v>紫幽靈</v>
       </c>
       <c r="E246">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F246">
-        <v>129</v>
-      </c>
-      <c r="G246" t="str">
-        <v>南红.png</v>
+        <v>6</v>
+      </c>
+      <c r="G246">
+        <v>39</v>
+      </c>
+      <c r="H246" t="str">
+        <v>紫幽灵.png</v>
+      </c>
+      <c r="I246" t="str">
+        <v/>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>hyes_stn_6</v>
+        <v>zyl_cysl_8</v>
       </c>
       <c r="B247" t="str">
         <v>珠子</v>
       </c>
       <c r="C247" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D247" t="str">
-        <v>虎眼石</v>
+        <v>紫幽靈</v>
       </c>
       <c r="E247">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F247">
-        <v>39</v>
-      </c>
-      <c r="G247" t="str">
-        <v>虎眼石.png</v>
+        <v>8</v>
+      </c>
+      <c r="G247">
+        <v>59</v>
+      </c>
+      <c r="H247" t="str">
+        <v>紫幽灵.png</v>
+      </c>
+      <c r="I247" t="str">
+        <v/>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>hyes_stn_8</v>
+        <v>he_agt_6</v>
       </c>
       <c r="B248" t="str">
         <v>珠子</v>
       </c>
       <c r="C248" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D248" t="str">
-        <v>虎眼石</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E248">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F248">
-        <v>59</v>
-      </c>
-      <c r="G248" t="str">
-        <v>虎眼石.png</v>
+        <v>6</v>
+      </c>
+      <c r="G248">
+        <v>39</v>
+      </c>
+      <c r="H248" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+      <c r="I248" t="str">
+        <v/>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>hyes_stn_10</v>
+        <v>he_agt_8</v>
       </c>
       <c r="B249" t="str">
         <v>珠子</v>
       </c>
       <c r="C249" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D249" t="str">
-        <v>虎眼石</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E249">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F249">
-        <v>89</v>
-      </c>
-      <c r="G249" t="str">
-        <v>虎眼石.png</v>
+        <v>8</v>
+      </c>
+      <c r="G249">
+        <v>59</v>
+      </c>
+      <c r="H249" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+      <c r="I249" t="str">
+        <v/>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>gqys_agt_6</v>
+        <v>he_agt_10</v>
       </c>
       <c r="B250" t="str">
         <v>珠子</v>
@@ -6137,67 +7631,85 @@
         <v>瑪瑙</v>
       </c>
       <c r="D250" t="str">
-        <v>乾青玉髓</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E250">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F250">
-        <v>59</v>
-      </c>
-      <c r="G250" t="str">
-        <v>干青玉髓.png</v>
+        <v>10</v>
+      </c>
+      <c r="G250">
+        <v>89</v>
+      </c>
+      <c r="H250" t="str">
+        <v>黑玛瑙.png</v>
+      </c>
+      <c r="I250" t="str">
+        <v/>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>gqys_agt_8</v>
+        <v>zjs_stn_6</v>
       </c>
       <c r="B251" t="str">
         <v>珠子</v>
       </c>
       <c r="C251" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D251" t="str">
-        <v>乾青玉髓</v>
+        <v>紫金砂</v>
       </c>
       <c r="E251">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F251">
+        <v>6</v>
+      </c>
+      <c r="G251">
         <v>69</v>
       </c>
-      <c r="G251" t="str">
-        <v>干青玉髓.png</v>
+      <c r="H251" t="str">
+        <v>紫金砂.png</v>
+      </c>
+      <c r="I251" t="str">
+        <v/>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>gqys_agt_10</v>
+        <v>zjs_stn_8</v>
       </c>
       <c r="B252" t="str">
         <v>珠子</v>
       </c>
       <c r="C252" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D252" t="str">
-        <v>乾青玉髓</v>
+        <v>紫金砂</v>
       </c>
       <c r="E252">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F252">
-        <v>89</v>
-      </c>
-      <c r="G252" t="str">
-        <v>干青玉髓.png</v>
+        <v>8</v>
+      </c>
+      <c r="G252">
+        <v>99</v>
+      </c>
+      <c r="H252" t="str">
+        <v>紫金砂.png</v>
+      </c>
+      <c r="I252" t="str">
+        <v/>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>yys_stn_6</v>
+        <v>zjs_stn_10</v>
       </c>
       <c r="B253" t="str">
         <v>珠子</v>
@@ -6206,21 +7718,27 @@
         <v>礦石</v>
       </c>
       <c r="D253" t="str">
-        <v>銀曜石</v>
+        <v>紫金砂</v>
       </c>
       <c r="E253">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F253">
-        <v>39</v>
-      </c>
-      <c r="G253" t="str">
-        <v>银曜石.png</v>
+        <v>10</v>
+      </c>
+      <c r="G253">
+        <v>129</v>
+      </c>
+      <c r="H253" t="str">
+        <v>紫金砂.png</v>
+      </c>
+      <c r="I253" t="str">
+        <v/>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>yys_stn_8</v>
+        <v>jys_stn_6</v>
       </c>
       <c r="B254" t="str">
         <v>珠子</v>
@@ -6229,21 +7747,27 @@
         <v>礦石</v>
       </c>
       <c r="D254" t="str">
-        <v>銀曜石</v>
+        <v>金曜石</v>
       </c>
       <c r="E254">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F254">
-        <v>69</v>
-      </c>
-      <c r="G254" t="str">
-        <v>银曜石.png</v>
+        <v>6</v>
+      </c>
+      <c r="G254">
+        <v>39</v>
+      </c>
+      <c r="H254" t="str">
+        <v>金曜石.png</v>
+      </c>
+      <c r="I254" t="str">
+        <v/>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>yys_stn_10</v>
+        <v>jys_stn_8</v>
       </c>
       <c r="B255" t="str">
         <v>珠子</v>
@@ -6252,44 +7776,56 @@
         <v>礦石</v>
       </c>
       <c r="D255" t="str">
-        <v>銀曜石</v>
+        <v>金曜石</v>
       </c>
       <c r="E255">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F255">
-        <v>99</v>
-      </c>
-      <c r="G255" t="str">
-        <v>银曜石.png</v>
+        <v>8</v>
+      </c>
+      <c r="G255">
+        <v>69</v>
+      </c>
+      <c r="H255" t="str">
+        <v>金曜石.png</v>
+      </c>
+      <c r="I255" t="str">
+        <v/>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>bmw_pnd_2</v>
+        <v>jys_stn_10</v>
       </c>
       <c r="B256" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C256" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D256" t="str">
-        <v>捕夢網</v>
+        <v>金曜石</v>
       </c>
       <c r="E256">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F256">
+        <v>10</v>
+      </c>
+      <c r="G256">
         <v>99</v>
       </c>
-      <c r="G256" t="str">
-        <v>捕梦网.png</v>
+      <c r="H256" t="str">
+        <v>金曜石.png</v>
+      </c>
+      <c r="I256" t="str">
+        <v/>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>zs_stn_6</v>
+        <v>hys_stn_6</v>
       </c>
       <c r="B257" t="str">
         <v>珠子</v>
@@ -6298,21 +7834,27 @@
         <v>礦石</v>
       </c>
       <c r="D257" t="str">
-        <v>硃砂</v>
+        <v>黑曜石</v>
       </c>
       <c r="E257">
         <v>6</v>
       </c>
       <c r="F257">
-        <v>99</v>
-      </c>
-      <c r="G257" t="str">
-        <v>朱砂.png</v>
+        <v>6</v>
+      </c>
+      <c r="G257">
+        <v>39</v>
+      </c>
+      <c r="H257" t="str">
+        <v>黑曜石.png</v>
+      </c>
+      <c r="I257" t="str">
+        <v/>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>ljs_stn_6</v>
+        <v>hys_stn_8</v>
       </c>
       <c r="B258" t="str">
         <v>珠子</v>
@@ -6321,21 +7863,27 @@
         <v>礦石</v>
       </c>
       <c r="D258" t="str">
-        <v>藍晶石</v>
+        <v>黑曜石</v>
       </c>
       <c r="E258">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F258">
-        <v>99</v>
-      </c>
-      <c r="G258" t="str">
-        <v>蓝晶石.png</v>
+        <v>8</v>
+      </c>
+      <c r="G258">
+        <v>69</v>
+      </c>
+      <c r="H258" t="str">
+        <v>黑曜石.png</v>
+      </c>
+      <c r="I258" t="str">
+        <v/>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>ljs_stn_8</v>
+        <v>hys_stn_10</v>
       </c>
       <c r="B259" t="str">
         <v>珠子</v>
@@ -6344,711 +7892,27 @@
         <v>礦石</v>
       </c>
       <c r="D259" t="str">
-        <v>藍晶石</v>
+        <v>黑曜石</v>
       </c>
       <c r="E259">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F259">
-        <v>139</v>
-      </c>
-      <c r="G259" t="str">
-        <v>蓝晶石.png</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="str">
-        <v>ljs_stn_10</v>
-      </c>
-      <c r="B260" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C260" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D260" t="str">
-        <v>藍晶石</v>
-      </c>
-      <c r="E260">
-        <v>10</v>
-      </c>
-      <c r="F260">
-        <v>199</v>
-      </c>
-      <c r="G260" t="str">
-        <v>蓝晶石.png</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="str">
-        <v>hmn_agt_6</v>
-      </c>
-      <c r="B261" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C261" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D261" t="str">
-        <v>紅瑪瑙</v>
-      </c>
-      <c r="E261">
-        <v>6</v>
-      </c>
-      <c r="F261">
-        <v>39</v>
-      </c>
-      <c r="G261" t="str">
-        <v>红玛瑙.png</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="str">
-        <v>hmn_agt_8</v>
-      </c>
-      <c r="B262" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C262" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D262" t="str">
-        <v>紅瑪瑙</v>
-      </c>
-      <c r="E262">
-        <v>8</v>
-      </c>
-      <c r="F262">
-        <v>59</v>
-      </c>
-      <c r="G262" t="str">
-        <v>红玛瑙.png</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="str">
-        <v>hmn_agt_10</v>
-      </c>
-      <c r="B263" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C263" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D263" t="str">
-        <v>紅瑪瑙</v>
-      </c>
-      <c r="E263">
-        <v>10</v>
-      </c>
-      <c r="F263">
-        <v>89</v>
-      </c>
-      <c r="G263" t="str">
-        <v>红玛瑙.png</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="str">
-        <v>csj_cysl_6</v>
-      </c>
-      <c r="B264" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C264" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D264" t="str">
-        <v>茶水晶</v>
-      </c>
-      <c r="E264">
-        <v>6</v>
-      </c>
-      <c r="F264">
-        <v>39</v>
-      </c>
-      <c r="G264" t="str">
-        <v>茶水晶.png</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="str">
-        <v>csj_cysl_8</v>
-      </c>
-      <c r="B265" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C265" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D265" t="str">
-        <v>茶水晶</v>
-      </c>
-      <c r="E265">
-        <v>8</v>
-      </c>
-      <c r="F265">
-        <v>59</v>
-      </c>
-      <c r="G265" t="str">
-        <v>茶水晶.png</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="str">
-        <v>csj_cysl_10</v>
-      </c>
-      <c r="B266" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C266" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D266" t="str">
-        <v>茶水晶</v>
-      </c>
-      <c r="E266">
-        <v>10</v>
-      </c>
-      <c r="F266">
-        <v>89</v>
-      </c>
-      <c r="G266" t="str">
-        <v>茶水晶.png</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="str">
-        <v>kqs_stn_6</v>
-      </c>
-      <c r="B267" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C267" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D267" t="str">
-        <v>孔雀石</v>
-      </c>
-      <c r="E267">
-        <v>6</v>
-      </c>
-      <c r="F267">
-        <v>69</v>
-      </c>
-      <c r="G267" t="str">
-        <v>孔雀石.png</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="str">
-        <v>kqs_stn_8</v>
-      </c>
-      <c r="B268" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C268" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D268" t="str">
-        <v>孔雀石</v>
-      </c>
-      <c r="E268">
-        <v>8</v>
-      </c>
-      <c r="F268">
-        <v>89</v>
-      </c>
-      <c r="G268" t="str">
-        <v>孔雀石.png</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>kqs_stn_10</v>
-      </c>
-      <c r="B269" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C269" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D269" t="str">
-        <v>孔雀石</v>
-      </c>
-      <c r="E269">
-        <v>10</v>
-      </c>
-      <c r="F269">
-        <v>199</v>
-      </c>
-      <c r="G269" t="str">
-        <v>孔雀石.png</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="str">
-        <v>qjs_stn_6</v>
-      </c>
-      <c r="B270" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C270" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D270" t="str">
-        <v>青金石</v>
-      </c>
-      <c r="E270">
-        <v>6</v>
-      </c>
-      <c r="F270">
-        <v>69</v>
-      </c>
-      <c r="G270" t="str">
-        <v>青金石.png</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="str">
-        <v>qjs_stn_8</v>
-      </c>
-      <c r="B271" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C271" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D271" t="str">
-        <v>青金石</v>
-      </c>
-      <c r="E271">
-        <v>8</v>
-      </c>
-      <c r="F271">
-        <v>89</v>
-      </c>
-      <c r="G271" t="str">
-        <v>青金石.png</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="str">
-        <v>qjs_stn_10</v>
-      </c>
-      <c r="B272" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C272" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D272" t="str">
-        <v>青金石</v>
-      </c>
-      <c r="E272">
-        <v>10</v>
-      </c>
-      <c r="F272">
+        <v>10</v>
+      </c>
+      <c r="G259">
         <v>99</v>
       </c>
-      <c r="G272" t="str">
-        <v>青金石.png</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="str">
-        <v>wlg_cysl_6</v>
-      </c>
-      <c r="B273" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C273" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D273" t="str">
-        <v>烏拉圭</v>
-      </c>
-      <c r="E273">
-        <v>6</v>
-      </c>
-      <c r="F273">
-        <v>69</v>
-      </c>
-      <c r="G273" t="str">
-        <v>乌拉圭.png</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="str">
-        <v>wlg_cysl_8</v>
-      </c>
-      <c r="B274" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C274" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D274" t="str">
-        <v>烏拉圭</v>
-      </c>
-      <c r="E274">
-        <v>8</v>
-      </c>
-      <c r="F274">
-        <v>99</v>
-      </c>
-      <c r="G274" t="str">
-        <v>乌拉圭.png</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="str">
-        <v>wlg_cysl_10</v>
-      </c>
-      <c r="B275" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C275" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D275" t="str">
-        <v>烏拉圭</v>
-      </c>
-      <c r="E275">
-        <v>10</v>
-      </c>
-      <c r="F275">
-        <v>169</v>
-      </c>
-      <c r="G275" t="str">
-        <v>乌拉圭.png</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="str">
-        <v>zyl_cysl_6</v>
-      </c>
-      <c r="B276" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C276" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D276" t="str">
-        <v>紫幽靈</v>
-      </c>
-      <c r="E276">
-        <v>6</v>
-      </c>
-      <c r="F276">
-        <v>39</v>
-      </c>
-      <c r="G276" t="str">
-        <v>紫幽灵.png</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="str">
-        <v>zyl_cysl_8</v>
-      </c>
-      <c r="B277" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C277" t="str">
-        <v>水晶</v>
-      </c>
-      <c r="D277" t="str">
-        <v>紫幽靈</v>
-      </c>
-      <c r="E277">
-        <v>8</v>
-      </c>
-      <c r="F277">
-        <v>59</v>
-      </c>
-      <c r="G277" t="str">
-        <v>紫幽灵.png</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="str">
-        <v>he_agt_6</v>
-      </c>
-      <c r="B278" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C278" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D278" t="str">
-        <v>黑瑪瑙</v>
-      </c>
-      <c r="E278">
-        <v>6</v>
-      </c>
-      <c r="F278">
-        <v>39</v>
-      </c>
-      <c r="G278" t="str">
-        <v>黑玛瑙.png</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="str">
-        <v>he_agt_8</v>
-      </c>
-      <c r="B279" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C279" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D279" t="str">
-        <v>黑瑪瑙</v>
-      </c>
-      <c r="E279">
-        <v>8</v>
-      </c>
-      <c r="F279">
-        <v>59</v>
-      </c>
-      <c r="G279" t="str">
-        <v>黑玛瑙.png</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="str">
-        <v>he_agt_10</v>
-      </c>
-      <c r="B280" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C280" t="str">
-        <v>瑪瑙</v>
-      </c>
-      <c r="D280" t="str">
-        <v>黑瑪瑙</v>
-      </c>
-      <c r="E280">
-        <v>10</v>
-      </c>
-      <c r="F280">
-        <v>89</v>
-      </c>
-      <c r="G280" t="str">
-        <v>黑玛瑙.png</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="str">
-        <v>zjs_stn_6</v>
-      </c>
-      <c r="B281" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C281" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D281" t="str">
-        <v>紫金砂</v>
-      </c>
-      <c r="E281">
-        <v>6</v>
-      </c>
-      <c r="F281">
-        <v>69</v>
-      </c>
-      <c r="G281" t="str">
-        <v>紫金砂.png</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="str">
-        <v>zjs_stn_8</v>
-      </c>
-      <c r="B282" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C282" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D282" t="str">
-        <v>紫金砂</v>
-      </c>
-      <c r="E282">
-        <v>8</v>
-      </c>
-      <c r="F282">
-        <v>99</v>
-      </c>
-      <c r="G282" t="str">
-        <v>紫金砂.png</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="str">
-        <v>zjs_stn_10</v>
-      </c>
-      <c r="B283" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C283" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D283" t="str">
-        <v>紫金砂</v>
-      </c>
-      <c r="E283">
-        <v>10</v>
-      </c>
-      <c r="F283">
-        <v>129</v>
-      </c>
-      <c r="G283" t="str">
-        <v>紫金砂.png</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="str">
-        <v>jys_stn_6</v>
-      </c>
-      <c r="B284" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C284" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D284" t="str">
-        <v>金曜石</v>
-      </c>
-      <c r="E284">
-        <v>6</v>
-      </c>
-      <c r="F284">
-        <v>39</v>
-      </c>
-      <c r="G284" t="str">
-        <v>金曜石.png</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="str">
-        <v>jys_stn_8</v>
-      </c>
-      <c r="B285" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C285" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D285" t="str">
-        <v>金曜石</v>
-      </c>
-      <c r="E285">
-        <v>8</v>
-      </c>
-      <c r="F285">
-        <v>69</v>
-      </c>
-      <c r="G285" t="str">
-        <v>金曜石.png</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="str">
-        <v>jys_stn_10</v>
-      </c>
-      <c r="B286" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C286" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D286" t="str">
-        <v>金曜石</v>
-      </c>
-      <c r="E286">
-        <v>10</v>
-      </c>
-      <c r="F286">
-        <v>99</v>
-      </c>
-      <c r="G286" t="str">
-        <v>金曜石.png</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="str">
-        <v>hys_stn_6</v>
-      </c>
-      <c r="B287" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C287" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D287" t="str">
-        <v>黑曜石</v>
-      </c>
-      <c r="E287">
-        <v>6</v>
-      </c>
-      <c r="F287">
-        <v>39</v>
-      </c>
-      <c r="G287" t="str">
+      <c r="H259" t="str">
         <v>黑曜石.png</v>
       </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="str">
-        <v>hys_stn_8</v>
-      </c>
-      <c r="B288" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C288" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D288" t="str">
-        <v>黑曜石</v>
-      </c>
-      <c r="E288">
-        <v>8</v>
-      </c>
-      <c r="F288">
-        <v>69</v>
-      </c>
-      <c r="G288" t="str">
-        <v>黑曜石.png</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="str">
-        <v>hys_stn_10</v>
-      </c>
-      <c r="B289" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C289" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D289" t="str">
-        <v>黑曜石</v>
-      </c>
-      <c r="E289">
-        <v>10</v>
-      </c>
-      <c r="F289">
-        <v>99</v>
-      </c>
-      <c r="G289" t="str">
-        <v>黑曜石.png</v>
+      <c r="I259" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G289"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I259"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -517,36 +517,36 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>xhyl_cysl_6</v>
+        <v>tg1_sz_7</v>
       </c>
       <c r="B5" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C5" t="str">
-        <v>水晶</v>
+        <v>數字</v>
       </c>
       <c r="D5" t="str">
-        <v>雪花幽靈</v>
+        <v>鈦鋼1</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>59</v>
       </c>
       <c r="H5" t="str">
-        <v>雪花幽灵.png</v>
+        <v>钛钢1.png</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>xhyl_cysl_8</v>
+        <v>xhyl_cysl_6</v>
       </c>
       <c r="B6" t="str">
         <v>珠子</v>
@@ -558,13 +558,13 @@
         <v>雪花幽靈</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H6" t="str">
         <v>雪花幽灵.png</v>
@@ -575,7 +575,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>xhyl_cysl_10</v>
+        <v>xhyl_cysl_8</v>
       </c>
       <c r="B7" t="str">
         <v>珠子</v>
@@ -587,13 +587,13 @@
         <v>雪花幽靈</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="H7" t="str">
         <v>雪花幽灵.png</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>byl_cysl_8</v>
+        <v>xhyl_cysl_10</v>
       </c>
       <c r="B8" t="str">
         <v>珠子</v>
@@ -613,19 +613,19 @@
         <v>水晶</v>
       </c>
       <c r="D8" t="str">
-        <v>白幽靈</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="H8" t="str">
-        <v>白幽灵.png</v>
+        <v>雪花幽灵.png</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -633,28 +633,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>dszzhu_prl_6</v>
+        <v>byl_cysl_8</v>
       </c>
       <c r="B9" t="str">
         <v>珠子</v>
       </c>
       <c r="C9" t="str">
-        <v>珍珠</v>
+        <v>水晶</v>
       </c>
       <c r="D9" t="str">
-        <v>淡水珍珠</v>
+        <v>白幽靈</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H9" t="str">
-        <v>淡水珍珠.png</v>
+        <v>白幽灵.png</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -662,7 +662,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>dszzhu_prl_8</v>
+        <v>dszzhu_prl_6</v>
       </c>
       <c r="B10" t="str">
         <v>珠子</v>
@@ -674,13 +674,13 @@
         <v>淡水珍珠</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="H10" t="str">
         <v>淡水珍珠.png</v>
@@ -691,7 +691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>dszzhu_prl_10</v>
+        <v>dszzhu_prl_8</v>
       </c>
       <c r="B11" t="str">
         <v>珠子</v>
@@ -703,13 +703,13 @@
         <v>淡水珍珠</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G11">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="H11" t="str">
         <v>淡水珍珠.png</v>
@@ -720,28 +720,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>nbj_cysl_8</v>
+        <v>dszzhu_prl_10</v>
       </c>
       <c r="B12" t="str">
         <v>珠子</v>
       </c>
       <c r="C12" t="str">
-        <v>水晶</v>
+        <v>珍珠</v>
       </c>
       <c r="D12" t="str">
-        <v>奶白晶</v>
+        <v>淡水珍珠</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="H12" t="str">
-        <v>奶白晶.png</v>
+        <v>淡水珍珠.png</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -749,7 +749,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>nbj_cysl_10</v>
+        <v>nbj_cysl_8</v>
       </c>
       <c r="B13" t="str">
         <v>珠子</v>
@@ -761,13 +761,13 @@
         <v>奶白晶</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G13">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H13" t="str">
         <v>奶白晶.png</v>
@@ -778,28 +778,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>pts_stn_6</v>
+        <v>nbj_cysl_10</v>
       </c>
       <c r="B14" t="str">
         <v>珠子</v>
       </c>
       <c r="C14" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D14" t="str">
-        <v>葡萄石</v>
+        <v>奶白晶</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H14" t="str">
-        <v>葡萄石.png</v>
+        <v>奶白晶.png</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -807,7 +807,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>pts_stn_10</v>
+        <v>pts_stn_6</v>
       </c>
       <c r="B15" t="str">
         <v>珠子</v>
@@ -819,13 +819,13 @@
         <v>葡萄石</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="H15" t="str">
         <v>葡萄石.png</v>
@@ -836,36 +836,36 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mxxx_pnd_2</v>
+        <v>pts_stn_10</v>
       </c>
       <c r="B16" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C16" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D16" t="str">
-        <v>滿鑲星星</v>
+        <v>葡萄石</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H16" t="str">
-        <v>满镶星星.png</v>
+        <v>葡萄石.png</v>
       </c>
       <c r="I16" t="str">
-        <v>廣州市嘉鈺</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>pl_pnd_5</v>
+        <v>mxxx_pnd_2</v>
       </c>
       <c r="B17" t="str">
         <v>配件</v>
@@ -874,27 +874,27 @@
         <v>吊墜</v>
       </c>
       <c r="D17" t="str">
-        <v>霹靂</v>
+        <v>滿鑲星星</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>20</v>
       </c>
       <c r="G17">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H17" t="str">
-        <v>霹雳.png</v>
+        <v>满镶星星.png</v>
       </c>
       <c r="I17" t="str">
-        <v>義烏市眾帆</v>
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>axqbz_pnd_2</v>
+        <v>pl_pnd_5</v>
       </c>
       <c r="B18" t="str">
         <v>配件</v>
@@ -903,56 +903,56 @@
         <v>吊墜</v>
       </c>
       <c r="D18" t="str">
-        <v>愛心曲別針</v>
+        <v>霹靂</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G18">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H18" t="str">
-        <v>爱心曲别针.png</v>
+        <v>霹雳.png</v>
       </c>
       <c r="I18" t="str">
-        <v>義烏市爆財</v>
+        <v>義烏市眾帆</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>xgfj_cysl_6</v>
+        <v>axqbz_pnd_2</v>
       </c>
       <c r="B19" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C19" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D19" t="str">
-        <v>星光粉晶</v>
+        <v>愛心曲別針</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H19" t="str">
-        <v>星光粉晶.png</v>
+        <v>爱心曲别针.png</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>義烏市爆財</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>xgfj_cysl_8</v>
+        <v>xgfj_cysl_6</v>
       </c>
       <c r="B20" t="str">
         <v>珠子</v>
@@ -964,13 +964,13 @@
         <v>星光粉晶</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H20" t="str">
         <v>星光粉晶.png</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>xgfj_cysl_10</v>
+        <v>xgfj_cysl_8</v>
       </c>
       <c r="B21" t="str">
         <v>珠子</v>
@@ -993,13 +993,13 @@
         <v>星光粉晶</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G21">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H21" t="str">
         <v>星光粉晶.png</v>
@@ -1010,28 +1010,28 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>by_agt_6</v>
+        <v>xgfj_cysl_10</v>
       </c>
       <c r="B22" t="str">
         <v>珠子</v>
       </c>
       <c r="C22" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D22" t="str">
-        <v>白玉髓</v>
+        <v>星光粉晶</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="H22" t="str">
-        <v>白玉髓.png</v>
+        <v>星光粉晶.png</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>by_agt_8</v>
+        <v>by_agt_6</v>
       </c>
       <c r="B23" t="str">
         <v>珠子</v>
@@ -1051,13 +1051,13 @@
         <v>白玉髓</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H23" t="str">
         <v>白玉髓.png</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>by_agt_10</v>
+        <v>by_agt_8</v>
       </c>
       <c r="B24" t="str">
         <v>珠子</v>
@@ -1080,13 +1080,13 @@
         <v>白玉髓</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G24">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H24" t="str">
         <v>白玉髓.png</v>
@@ -1097,28 +1097,28 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>zlh_cysl_6</v>
+        <v>by_agt_10</v>
       </c>
       <c r="B25" t="str">
         <v>珠子</v>
       </c>
       <c r="C25" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D25" t="str">
-        <v>紫鋰輝</v>
+        <v>白玉髓</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>89</v>
       </c>
       <c r="H25" t="str">
-        <v>紫锂辉.png</v>
+        <v>白玉髓.png</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>zlh_cysl_8</v>
+        <v>zlh_cysl_6</v>
       </c>
       <c r="B26" t="str">
         <v>珠子</v>
@@ -1138,13 +1138,13 @@
         <v>紫鋰輝</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="H26" t="str">
         <v>紫锂辉.png</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>zlh_cysl_10</v>
+        <v>zlh_cysl_8</v>
       </c>
       <c r="B27" t="str">
         <v>珠子</v>
@@ -1167,13 +1167,13 @@
         <v>紫鋰輝</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G27">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="H27" t="str">
         <v>紫锂辉.png</v>
@@ -1184,65 +1184,65 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lglf_spc_8</v>
+        <v>zlh_cysl_10</v>
       </c>
       <c r="B28" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C28" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D28" t="str">
-        <v>菱格立方</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="H28" t="str">
-        <v>菱格立方.png</v>
+        <v>紫锂辉.png</v>
       </c>
       <c r="I28" t="str">
-        <v>廣州市荔灣區金嶠旭</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>fsj_cysl_6</v>
+        <v>lglf_spc_8</v>
       </c>
       <c r="B29" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C29" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D29" t="str">
-        <v>粉水晶</v>
+        <v>菱格立方</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G29">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="H29" t="str">
-        <v>粉水晶.png</v>
+        <v>菱格立方.png</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>廣州市荔灣區金嶠旭</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>fsj_cysl_8</v>
+        <v>fsj_cysl_6</v>
       </c>
       <c r="B30" t="str">
         <v>珠子</v>
@@ -1254,13 +1254,13 @@
         <v>粉水晶</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G30">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H30" t="str">
         <v>粉水晶.png</v>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>fsj_cysl_10</v>
+        <v>fsj_cysl_8</v>
       </c>
       <c r="B31" t="str">
         <v>珠子</v>
@@ -1283,13 +1283,13 @@
         <v>粉水晶</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G31">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="H31" t="str">
         <v>粉水晶.png</v>
@@ -1300,36 +1300,36 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ysmxyl_pnd_2</v>
+        <v>fsj_cysl_10</v>
       </c>
       <c r="B32" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C32" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D32" t="str">
-        <v>滿鑲月亮</v>
+        <v>粉水晶</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>10</v>
       </c>
       <c r="G32">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H32" t="str">
-        <v>满镶月亮.png</v>
+        <v>粉水晶.png</v>
       </c>
       <c r="I32" t="str">
-        <v>廣州銅品彙</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lkjf_pnd_2</v>
+        <v>ysmxyl_pnd_2</v>
       </c>
       <c r="B33" t="str">
         <v>配件</v>
@@ -1338,56 +1338,56 @@
         <v>吊墜</v>
       </c>
       <c r="D33" t="str">
-        <v>鏤空金福</v>
+        <v>滿鑲月亮</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>599</v>
+        <v>69</v>
       </c>
       <c r="H33" t="str">
-        <v>镂空金福.png</v>
+        <v>满镶月亮.png</v>
       </c>
       <c r="I33" t="str">
-        <v>廣州市荔灣區嘉明銀飾</v>
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>bas_cysl_8</v>
+        <v>lkjf_pnd_2</v>
       </c>
       <c r="B34" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C34" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D34" t="str">
-        <v>白阿塞</v>
+        <v>鏤空金福</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G34">
-        <v>69</v>
+        <v>599</v>
       </c>
       <c r="H34" t="str">
-        <v>白阿塞.png</v>
+        <v>镂空金福.png</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>廣州市荔灣區嘉明銀飾</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>bas_cysl_10</v>
+        <v>bas_cysl_8</v>
       </c>
       <c r="B35" t="str">
         <v>珠子</v>
@@ -1399,13 +1399,13 @@
         <v>白阿塞</v>
       </c>
       <c r="E35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G35">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H35" t="str">
         <v>白阿塞.png</v>
@@ -1416,28 +1416,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>nyhlb_stn_6</v>
+        <v>bas_cysl_10</v>
       </c>
       <c r="B36" t="str">
         <v>珠子</v>
       </c>
       <c r="C36" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D36" t="str">
-        <v>奶油海藍寶</v>
+        <v>白阿塞</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H36" t="str">
-        <v>奶油海蓝宝.png</v>
+        <v>白阿塞.png</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>nyhlb_stn_8</v>
+        <v>nyhlb_stn_6</v>
       </c>
       <c r="B37" t="str">
         <v>珠子</v>
@@ -1457,13 +1457,13 @@
         <v>奶油海藍寶</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G37">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H37" t="str">
         <v>奶油海蓝宝.png</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>nyhlb_stn_10</v>
+        <v>nyhlb_stn_8</v>
       </c>
       <c r="B38" t="str">
         <v>珠子</v>
@@ -1486,13 +1486,13 @@
         <v>奶油海藍寶</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G38">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="H38" t="str">
         <v>奶油海蓝宝.png</v>
@@ -1503,28 +1503,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>zys_agt_6</v>
+        <v>nyhlb_stn_10</v>
       </c>
       <c r="B39" t="str">
         <v>珠子</v>
       </c>
       <c r="C39" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D39" t="str">
-        <v>紫玉髓</v>
+        <v>奶油海藍寶</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G39">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="H39" t="str">
-        <v>紫玉髓.png</v>
+        <v>奶油海蓝宝.png</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>zys_agt_8</v>
+        <v>zys_agt_6</v>
       </c>
       <c r="B40" t="str">
         <v>珠子</v>
@@ -1544,13 +1544,13 @@
         <v>紫玉髓</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G40">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H40" t="str">
         <v>紫玉髓.png</v>
@@ -1561,28 +1561,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>hws_stn_6</v>
+        <v>zys_agt_8</v>
       </c>
       <c r="B41" t="str">
         <v>珠子</v>
       </c>
       <c r="C41" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D41" t="str">
-        <v>海紋石</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G41">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H41" t="str">
-        <v>海纹石.png</v>
+        <v>紫玉髓.png</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>hws_stn_8</v>
+        <v>hws_stn_6</v>
       </c>
       <c r="B42" t="str">
         <v>珠子</v>
@@ -1602,13 +1602,13 @@
         <v>海紋石</v>
       </c>
       <c r="E42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G42">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H42" t="str">
         <v>海纹石.png</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>hws_stn_10</v>
+        <v>hws_stn_8</v>
       </c>
       <c r="B43" t="str">
         <v>珠子</v>
@@ -1631,13 +1631,13 @@
         <v>海紋石</v>
       </c>
       <c r="E43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G43">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="H43" t="str">
         <v>海纹石.png</v>
@@ -1648,28 +1648,28 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>jfj_cysl_6</v>
+        <v>hws_stn_10</v>
       </c>
       <c r="B44" t="str">
         <v>珠子</v>
       </c>
       <c r="C44" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D44" t="str">
-        <v>金髮晶</v>
+        <v>海紋石</v>
       </c>
       <c r="E44">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G44">
-        <v>49</v>
+        <v>169</v>
       </c>
       <c r="H44" t="str">
-        <v>金发晶.png</v>
+        <v>海纹石.png</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>jfj_cysl_8</v>
+        <v>jfj_cysl_6</v>
       </c>
       <c r="B45" t="str">
         <v>珠子</v>
@@ -1689,13 +1689,13 @@
         <v>金髮晶</v>
       </c>
       <c r="E45">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F45">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G45">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H45" t="str">
         <v>金发晶.png</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>jfj_cysl_10</v>
+        <v>jfj_cysl_8</v>
       </c>
       <c r="B46" t="str">
         <v>珠子</v>
@@ -1718,13 +1718,13 @@
         <v>金髮晶</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G46">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H46" t="str">
         <v>金发晶.png</v>
@@ -1735,94 +1735,94 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>bsyw_pnd_2</v>
+        <v>jfj_cysl_10</v>
       </c>
       <c r="B47" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C47" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D47" t="str">
-        <v>白水魚尾</v>
+        <v>金髮晶</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F47">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G47">
-        <v>699</v>
+        <v>99</v>
       </c>
       <c r="H47" t="str">
-        <v>白水鱼尾.png</v>
+        <v>金发晶.png</v>
       </c>
       <c r="I47" t="str">
-        <v>廣州市荔灣區嘉明</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>zyb_spc_6</v>
+        <v>bsyw_pnd_2</v>
       </c>
       <c r="B48" t="str">
         <v>配件</v>
       </c>
       <c r="C48" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D48" t="str">
-        <v>轉運柄</v>
+        <v>白水魚尾</v>
       </c>
       <c r="E48">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G48">
-        <v>399</v>
+        <v>699</v>
       </c>
       <c r="H48" t="str">
-        <v>转运柄.png</v>
+        <v>白水鱼尾.png</v>
       </c>
       <c r="I48" t="str">
-        <v>莆田市秀嶼區東嶠寶鑫格</v>
+        <v>廣州市荔灣區嘉明</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lwmn_agt_6</v>
+        <v>zyb_spc_6</v>
       </c>
       <c r="B49" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C49" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D49" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>轉運柄</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G49">
-        <v>69</v>
+        <v>399</v>
       </c>
       <c r="H49" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>转运柄.png</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>莆田市秀嶼區東嶠寶鑫格</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lwmn_agt_8</v>
+        <v>lwmn_agt_6</v>
       </c>
       <c r="B50" t="str">
         <v>珠子</v>
@@ -1834,13 +1834,13 @@
         <v>藍紋瑪瑙</v>
       </c>
       <c r="E50">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F50">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H50" t="str">
         <v>蓝纹玛瑙.png</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lwmn_agt_10</v>
+        <v>lwmn_agt_8</v>
       </c>
       <c r="B51" t="str">
         <v>珠子</v>
@@ -1863,13 +1863,13 @@
         <v>藍紋瑪瑙</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G51">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="H51" t="str">
         <v>蓝纹玛瑙.png</v>
@@ -1880,28 +1880,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>xyc_cysl_8</v>
+        <v>lwmn_agt_10</v>
       </c>
       <c r="B52" t="str">
         <v>珠子</v>
       </c>
       <c r="C52" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D52" t="str">
-        <v>薰衣草</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G52">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="H52" t="str">
-        <v>薰衣草.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>xyc_cysl_10</v>
+        <v>xyc_cysl_8</v>
       </c>
       <c r="B53" t="str">
         <v>珠子</v>
@@ -1921,13 +1921,13 @@
         <v>薰衣草</v>
       </c>
       <c r="E53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G53">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="H53" t="str">
         <v>薰衣草.png</v>
@@ -1938,36 +1938,36 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>fyh_spc_12</v>
+        <v>xyc_cysl_10</v>
       </c>
       <c r="B54" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C54" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D54" t="str">
-        <v>粉櫻花</v>
+        <v>薰衣草</v>
       </c>
       <c r="E54">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F54">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G54">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="H54" t="str">
-        <v>粉樱花.png</v>
+        <v>薰衣草.png</v>
       </c>
       <c r="I54" t="str">
-        <v>義烏市聚飾優</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>gshxz_spc_10</v>
+        <v>fyh_spc_12</v>
       </c>
       <c r="B55" t="str">
         <v>配件</v>
@@ -1976,27 +1976,27 @@
         <v>隔珠</v>
       </c>
       <c r="D55" t="str">
-        <v>鋯石花形鑽</v>
+        <v>粉櫻花</v>
       </c>
       <c r="E55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G55">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H55" t="str">
-        <v>锆石花形钻.png</v>
+        <v>粉樱花.png</v>
       </c>
       <c r="I55" t="str">
-        <v>義烏市闊乘</v>
+        <v>義烏市聚飾優</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>gsqg_spc_5</v>
+        <v>gshxz_spc_10</v>
       </c>
       <c r="B56" t="str">
         <v>配件</v>
@@ -2005,56 +2005,56 @@
         <v>隔珠</v>
       </c>
       <c r="D56" t="str">
-        <v>鋯石切割</v>
+        <v>鋯石花形鑽</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F56">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G56">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="H56" t="str">
-        <v>锆石切割.png</v>
+        <v>锆石花形钻.png</v>
       </c>
       <c r="I56" t="str">
-        <v>義烏市硯鈺</v>
+        <v>義烏市闊乘</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>hsj_cysl_6</v>
+        <v>gsqg_spc_5</v>
       </c>
       <c r="B57" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C57" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D57" t="str">
-        <v>黃水晶</v>
+        <v>鋯石切割</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F57">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G57">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="H57" t="str">
-        <v>黄水晶.png</v>
+        <v>锆石切割.png</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>hsj_cysl_8</v>
+        <v>hsj_cysl_6</v>
       </c>
       <c r="B58" t="str">
         <v>珠子</v>
@@ -2066,13 +2066,13 @@
         <v>黃水晶</v>
       </c>
       <c r="E58">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F58">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G58">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H58" t="str">
         <v>黄水晶.png</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>hsj_cysl_10</v>
+        <v>hsj_cysl_8</v>
       </c>
       <c r="B59" t="str">
         <v>珠子</v>
@@ -2095,13 +2095,13 @@
         <v>黃水晶</v>
       </c>
       <c r="E59">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F59">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G59">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H59" t="str">
         <v>黄水晶.png</v>
@@ -2112,123 +2112,123 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>jzj_spc_4</v>
+        <v>hsj_cysl_10</v>
       </c>
       <c r="B60" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C60" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D60" t="str">
-        <v>交織戒</v>
+        <v>黃水晶</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F60">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G60">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H60" t="str">
-        <v>交织戒.png</v>
+        <v>黄水晶.png</v>
       </c>
       <c r="I60" t="str">
-        <v>廣州市弘達</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>gscx_pnd_2</v>
+        <v>jzj_spc_4</v>
       </c>
       <c r="B61" t="str">
         <v>配件</v>
       </c>
       <c r="C61" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D61" t="str">
-        <v>鋯石晨星</v>
+        <v>交織戒</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G61">
         <v>69</v>
       </c>
       <c r="H61" t="str">
-        <v>锆石晨星.png</v>
+        <v>交织戒.png</v>
       </c>
       <c r="I61" t="str">
-        <v>義烏市適旗</v>
+        <v>廣州市弘達</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>tg4_sz_7</v>
+        <v>gscx_pnd_2</v>
       </c>
       <c r="B62" t="str">
         <v>配件</v>
       </c>
       <c r="C62" t="str">
-        <v>數字</v>
+        <v>吊墜</v>
       </c>
       <c r="D62" t="str">
-        <v>鈦鋼4</v>
+        <v>鋯石晨星</v>
       </c>
       <c r="E62">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G62">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H62" t="str">
-        <v>钛钢4.png</v>
+        <v>锆石晨星.png</v>
       </c>
       <c r="I62" t="str">
-        <v>東莞晞亞</v>
+        <v>義烏市適旗</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>cyszj_spc_13</v>
+        <v>tg4_sz_7</v>
       </c>
       <c r="B63" t="str">
         <v>配件</v>
       </c>
       <c r="C63" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D63" t="str">
-        <v>藏銀十字架</v>
+        <v>鈦鋼4</v>
       </c>
       <c r="E63">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G63">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H63" t="str">
-        <v>藏银十字架.png</v>
+        <v>钛钢4.png</v>
       </c>
       <c r="I63" t="str">
-        <v>義烏市尋意</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ysxh_spc_2</v>
+        <v>cyszj_spc_13</v>
       </c>
       <c r="B64" t="str">
         <v>配件</v>
@@ -2237,94 +2237,94 @@
         <v>隔珠</v>
       </c>
       <c r="D64" t="str">
-        <v>銀色小環</v>
+        <v>藏銀十字架</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G64">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H64" t="str">
-        <v>银色小环.png</v>
+        <v>藏银十字架.png</v>
       </c>
       <c r="I64" t="str">
-        <v>廣州鑫鈺</v>
+        <v>義烏市尋意</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>tg9_sz_7</v>
+        <v>ysxh_spc_2</v>
       </c>
       <c r="B65" t="str">
         <v>配件</v>
       </c>
       <c r="C65" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D65" t="str">
-        <v>鈦鋼9</v>
+        <v>銀色小環</v>
       </c>
       <c r="E65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G65">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H65" t="str">
-        <v>钛钢9.png</v>
+        <v>银色小环.png</v>
       </c>
       <c r="I65" t="str">
-        <v>東莞晞亞</v>
+        <v>廣州鑫鈺</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>gh_spc_6</v>
+        <v>tg9_sz_7</v>
       </c>
       <c r="B66" t="str">
         <v>配件</v>
       </c>
       <c r="C66" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D66" t="str">
-        <v>桂花</v>
+        <v>鈦鋼9</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G66">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H66" t="str">
-        <v>桂花.png</v>
+        <v>钛钢9.png</v>
       </c>
       <c r="I66" t="str">
-        <v>廣州嘉鈺</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>hm_agt_6</v>
+        <v>gh_spc_6</v>
       </c>
       <c r="B67" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C67" t="str">
-        <v>瑪瑙</v>
+        <v>隔珠</v>
       </c>
       <c r="D67" t="str">
-        <v>黃瑪瑙</v>
+        <v>桂花</v>
       </c>
       <c r="E67">
         <v>6</v>
@@ -2333,18 +2333,18 @@
         <v>6</v>
       </c>
       <c r="G67">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H67" t="str">
-        <v>黄玛瑙.png</v>
+        <v>桂花.png</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>廣州嘉鈺</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>hm_agt_8</v>
+        <v>hm_agt_6</v>
       </c>
       <c r="B68" t="str">
         <v>珠子</v>
@@ -2356,13 +2356,13 @@
         <v>黃瑪瑙</v>
       </c>
       <c r="E68">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F68">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G68">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H68" t="str">
         <v>黄玛瑙.png</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>hm_agt_10</v>
+        <v>hm_agt_8</v>
       </c>
       <c r="B69" t="str">
         <v>珠子</v>
@@ -2385,13 +2385,13 @@
         <v>黃瑪瑙</v>
       </c>
       <c r="E69">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G69">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H69" t="str">
         <v>黄玛瑙.png</v>
@@ -2402,28 +2402,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ml_stn_6</v>
+        <v>hm_agt_10</v>
       </c>
       <c r="B70" t="str">
         <v>珠子</v>
       </c>
       <c r="C70" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D70" t="str">
-        <v>蜜蠟</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E70">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F70">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G70">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H70" t="str">
-        <v>蜜蜡.png</v>
+        <v>黄玛瑙.png</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ml_stn_8</v>
+        <v>ml_stn_6</v>
       </c>
       <c r="B71" t="str">
         <v>珠子</v>
@@ -2443,13 +2443,13 @@
         <v>蜜蠟</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F71">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G71">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H71" t="str">
         <v>蜜蜡.png</v>
@@ -2460,297 +2460,297 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ysr_zm_4</v>
+        <v>ml_stn_8</v>
       </c>
       <c r="B72" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C72" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D72" t="str">
-        <v>銀飾R</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F72">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G72">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="H72" t="str">
-        <v>银饰R.png</v>
+        <v>蜜蜡.png</v>
       </c>
       <c r="I72" t="str">
-        <v>廣州市德潤</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>jd_pnd_2</v>
+        <v>ysr_zm_4</v>
       </c>
       <c r="B73" t="str">
         <v>配件</v>
       </c>
       <c r="C73" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D73" t="str">
-        <v>晶蝶</v>
+        <v>銀飾R</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F73">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G73">
-        <v>69</v>
+        <v>399</v>
       </c>
       <c r="H73" t="str">
-        <v>晶蝶.png</v>
+        <v>银饰R.png</v>
       </c>
       <c r="I73" t="str">
-        <v>廣州市嘉鈺</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>tg7_sz_7</v>
+        <v>jd_pnd_2</v>
       </c>
       <c r="B74" t="str">
         <v>配件</v>
       </c>
       <c r="C74" t="str">
-        <v>數字</v>
+        <v>吊墜</v>
       </c>
       <c r="D74" t="str">
-        <v>鈦鋼7</v>
+        <v>晶蝶</v>
       </c>
       <c r="E74">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G74">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H74" t="str">
-        <v>钛钢7.png</v>
+        <v>晶蝶.png</v>
       </c>
       <c r="I74" t="str">
-        <v>東莞晞亞</v>
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>jpts_stn_8</v>
+        <v>tg7_sz_7</v>
       </c>
       <c r="B75" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C75" t="str">
-        <v>礦石</v>
+        <v>數字</v>
       </c>
       <c r="D75" t="str">
-        <v>金葡萄石</v>
+        <v>鈦鋼7</v>
       </c>
       <c r="E75">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F75">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G75">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H75" t="str">
-        <v>金葡萄石.png</v>
+        <v>钛钢7.png</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>gymj_xz_3</v>
+        <v>jpts_stn_8</v>
       </c>
       <c r="B76" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C76" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D76" t="str">
-        <v>古銀摩羯</v>
+        <v>金葡萄石</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F76">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G76">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H76" t="str">
-        <v>古银摩羯.png</v>
+        <v>金葡萄石.png</v>
       </c>
       <c r="I76" t="str">
-        <v>義烏市唐人印象</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>tg0_sz_7</v>
+        <v>gymj_xz_3</v>
       </c>
       <c r="B77" t="str">
         <v>配件</v>
       </c>
       <c r="C77" t="str">
-        <v>數字</v>
+        <v>星座</v>
       </c>
       <c r="D77" t="str">
-        <v>鈦鋼0</v>
+        <v>古銀摩羯</v>
       </c>
       <c r="E77">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F77">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G77">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H77" t="str">
-        <v>钛钢0.png</v>
+        <v>古银摩羯.png</v>
       </c>
       <c r="I77" t="str">
-        <v>東莞晞亞</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>jf_pnd_2</v>
+        <v>tg0_sz_7</v>
       </c>
       <c r="B78" t="str">
         <v>配件</v>
       </c>
       <c r="C78" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D78" t="str">
-        <v>金福</v>
+        <v>鈦鋼0</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F78">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G78">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H78" t="str">
-        <v>金福.png</v>
+        <v>钛钢0.png</v>
       </c>
       <c r="I78" t="str">
-        <v>義烏市曉磊</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ysj_zm_4</v>
+        <v>jf_pnd_2</v>
       </c>
       <c r="B79" t="str">
         <v>配件</v>
       </c>
       <c r="C79" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D79" t="str">
-        <v>銀飾J</v>
+        <v>金福</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79">
         <v>10</v>
       </c>
       <c r="G79">
-        <v>399</v>
+        <v>49</v>
       </c>
       <c r="H79" t="str">
-        <v>银饰J.png</v>
+        <v>金福.png</v>
       </c>
       <c r="I79" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市曉磊</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>tg6_sz_7</v>
+        <v>ysj_zm_4</v>
       </c>
       <c r="B80" t="str">
         <v>配件</v>
       </c>
       <c r="C80" t="str">
-        <v>數字</v>
+        <v>字母</v>
       </c>
       <c r="D80" t="str">
-        <v>鈦鋼6</v>
+        <v>銀飾J</v>
       </c>
       <c r="E80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F80">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G80">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="H80" t="str">
-        <v>钛钢6.png</v>
+        <v>银饰J.png</v>
       </c>
       <c r="I80" t="str">
-        <v>東莞晞亞</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>xxy_spc_2</v>
+        <v>tg6_sz_7</v>
       </c>
       <c r="B81" t="str">
         <v>配件</v>
       </c>
       <c r="C81" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D81" t="str">
-        <v>小祥雲</v>
+        <v>鈦鋼6</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F81">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G81">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H81" t="str">
-        <v>小祥云.png</v>
+        <v>钛钢6.png</v>
       </c>
       <c r="I81" t="str">
-        <v>廣州璐悠</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>dxy_spc_3</v>
+        <v>xxy_spc_2</v>
       </c>
       <c r="B82" t="str">
         <v>配件</v>
@@ -2759,19 +2759,19 @@
         <v>隔珠</v>
       </c>
       <c r="D82" t="str">
-        <v>大祥雲</v>
+        <v>小祥雲</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G82">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H82" t="str">
-        <v>大祥云.png</v>
+        <v>小祥云.png</v>
       </c>
       <c r="I82" t="str">
         <v>廣州璐悠</v>
@@ -2779,36 +2779,36 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ysi_zm_4</v>
+        <v>dxy_spc_3</v>
       </c>
       <c r="B83" t="str">
         <v>配件</v>
       </c>
       <c r="C83" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D83" t="str">
-        <v>銀飾I</v>
+        <v>大祥雲</v>
       </c>
       <c r="E83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F83">
         <v>10</v>
       </c>
       <c r="G83">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="H83" t="str">
-        <v>银饰I.png</v>
+        <v>大祥云.png</v>
       </c>
       <c r="I83" t="str">
-        <v>廣州市德潤</v>
+        <v>廣州璐悠</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ysu_zm_4</v>
+        <v>ysi_zm_4</v>
       </c>
       <c r="B84" t="str">
         <v>配件</v>
@@ -2817,7 +2817,7 @@
         <v>字母</v>
       </c>
       <c r="D84" t="str">
-        <v>銀飾U</v>
+        <v>銀飾I</v>
       </c>
       <c r="E84">
         <v>4</v>
@@ -2829,7 +2829,7 @@
         <v>399</v>
       </c>
       <c r="H84" t="str">
-        <v>银饰U.png</v>
+        <v>银饰I.png</v>
       </c>
       <c r="I84" t="str">
         <v>廣州市德潤</v>
@@ -2837,36 +2837,36 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>tg3_sz_7</v>
+        <v>ysu_zm_4</v>
       </c>
       <c r="B85" t="str">
         <v>配件</v>
       </c>
       <c r="C85" t="str">
-        <v>數字</v>
+        <v>字母</v>
       </c>
       <c r="D85" t="str">
-        <v>鈦鋼3</v>
+        <v>銀飾U</v>
       </c>
       <c r="E85">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F85">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G85">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="H85" t="str">
-        <v>钛钢3.png</v>
+        <v>银饰U.png</v>
       </c>
       <c r="I85" t="str">
-        <v>東莞晞亞</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>tg2_sz_7</v>
+        <v>tg3_sz_7</v>
       </c>
       <c r="B86" t="str">
         <v>配件</v>
@@ -2875,7 +2875,7 @@
         <v>數字</v>
       </c>
       <c r="D86" t="str">
-        <v>鈦鋼2</v>
+        <v>鈦鋼3</v>
       </c>
       <c r="E86">
         <v>7</v>
@@ -2887,7 +2887,7 @@
         <v>59</v>
       </c>
       <c r="H86" t="str">
-        <v>钛钢2.png</v>
+        <v>钛钢3.png</v>
       </c>
       <c r="I86" t="str">
         <v>東莞晞亞</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>tg8_sz_7</v>
+        <v>tg2_sz_7</v>
       </c>
       <c r="B87" t="str">
         <v>配件</v>
@@ -2904,7 +2904,7 @@
         <v>數字</v>
       </c>
       <c r="D87" t="str">
-        <v>鈦鋼8</v>
+        <v>鈦鋼2</v>
       </c>
       <c r="E87">
         <v>7</v>
@@ -2916,7 +2916,7 @@
         <v>59</v>
       </c>
       <c r="H87" t="str">
-        <v>钛钢8.png</v>
+        <v>钛钢2.png</v>
       </c>
       <c r="I87" t="str">
         <v>東莞晞亞</v>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>tg5_sz_7</v>
+        <v>tg8_sz_7</v>
       </c>
       <c r="B88" t="str">
         <v>配件</v>
@@ -2933,7 +2933,7 @@
         <v>數字</v>
       </c>
       <c r="D88" t="str">
-        <v>鈦鋼5</v>
+        <v>鈦鋼8</v>
       </c>
       <c r="E88">
         <v>7</v>
@@ -2945,7 +2945,7 @@
         <v>59</v>
       </c>
       <c r="H88" t="str">
-        <v>钛钢5.png</v>
+        <v>钛钢8.png</v>
       </c>
       <c r="I88" t="str">
         <v>東莞晞亞</v>
@@ -2953,123 +2953,123 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>gycn_xz_3</v>
+        <v>tg5_sz_7</v>
       </c>
       <c r="B89" t="str">
         <v>配件</v>
       </c>
       <c r="C89" t="str">
-        <v>星座</v>
+        <v>數字</v>
       </c>
       <c r="D89" t="str">
-        <v>古銀處女</v>
+        <v>鈦鋼5</v>
       </c>
       <c r="E89">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F89">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G89">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H89" t="str">
-        <v>古银处女.png</v>
+        <v>钛钢5.png</v>
       </c>
       <c r="I89" t="str">
-        <v>義烏市唐人印象</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ysp_zm_4</v>
+        <v>gycn_xz_3</v>
       </c>
       <c r="B90" t="str">
         <v>配件</v>
       </c>
       <c r="C90" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D90" t="str">
-        <v>銀飾P</v>
+        <v>古銀處女</v>
       </c>
       <c r="E90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F90">
         <v>10</v>
       </c>
       <c r="G90">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H90" t="str">
-        <v>银饰P.png</v>
+        <v>古银处女.png</v>
       </c>
       <c r="I90" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>gyby_xz_3</v>
+        <v>ysp_zm_4</v>
       </c>
       <c r="B91" t="str">
         <v>配件</v>
       </c>
       <c r="C91" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D91" t="str">
-        <v>古銀白羊</v>
+        <v>銀飾P</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91">
         <v>10</v>
       </c>
       <c r="G91">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H91" t="str">
-        <v>古银白羊.png</v>
+        <v>银饰P.png</v>
       </c>
       <c r="I91" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>lfj_cysl_8</v>
+        <v>gyby_xz_3</v>
       </c>
       <c r="B92" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C92" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D92" t="str">
-        <v>綠髮晶</v>
+        <v>古銀白羊</v>
       </c>
       <c r="E92">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F92">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G92">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H92" t="str">
-        <v>绿发晶.png</v>
+        <v>古银白羊.png</v>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>lfj_cysl_10</v>
+        <v>lfj_cysl_8</v>
       </c>
       <c r="B93" t="str">
         <v>珠子</v>
@@ -3081,13 +3081,13 @@
         <v>綠髮晶</v>
       </c>
       <c r="E93">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F93">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G93">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="H93" t="str">
         <v>绿发晶.png</v>
@@ -3098,36 +3098,36 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ysc_zm_4</v>
+        <v>lfj_cysl_10</v>
       </c>
       <c r="B94" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C94" t="str">
-        <v>字母</v>
+        <v>水晶</v>
       </c>
       <c r="D94" t="str">
-        <v>銀飾C</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E94">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F94">
         <v>10</v>
       </c>
       <c r="G94">
-        <v>399</v>
+        <v>139</v>
       </c>
       <c r="H94" t="str">
-        <v>银饰C.png</v>
+        <v>绿发晶.png</v>
       </c>
       <c r="I94" t="str">
-        <v>廣州市德潤</v>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ysb_zm_4</v>
+        <v>ysc_zm_4</v>
       </c>
       <c r="B95" t="str">
         <v>配件</v>
@@ -3136,7 +3136,7 @@
         <v>字母</v>
       </c>
       <c r="D95" t="str">
-        <v>銀飾B</v>
+        <v>銀飾C</v>
       </c>
       <c r="E95">
         <v>4</v>
@@ -3148,7 +3148,7 @@
         <v>399</v>
       </c>
       <c r="H95" t="str">
-        <v>银饰B.png</v>
+        <v>银饰C.png</v>
       </c>
       <c r="I95" t="str">
         <v>廣州市德潤</v>
@@ -3156,65 +3156,65 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>gysp_xz_3</v>
+        <v>ysb_zm_4</v>
       </c>
       <c r="B96" t="str">
         <v>配件</v>
       </c>
       <c r="C96" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D96" t="str">
-        <v>古銀水瓶</v>
+        <v>銀飾B</v>
       </c>
       <c r="E96">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F96">
         <v>10</v>
       </c>
       <c r="G96">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H96" t="str">
-        <v>古银水瓶.png</v>
+        <v>银饰B.png</v>
       </c>
       <c r="I96" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>yso_zm_4</v>
+        <v>gysp_xz_3</v>
       </c>
       <c r="B97" t="str">
         <v>配件</v>
       </c>
       <c r="C97" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D97" t="str">
-        <v>銀飾O</v>
+        <v>古銀水瓶</v>
       </c>
       <c r="E97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F97">
         <v>10</v>
       </c>
       <c r="G97">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H97" t="str">
-        <v>银饰O.png</v>
+        <v>古银水瓶.png</v>
       </c>
       <c r="I97" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ysw_zm_4</v>
+        <v>yso_zm_4</v>
       </c>
       <c r="B98" t="str">
         <v>配件</v>
@@ -3223,7 +3223,7 @@
         <v>字母</v>
       </c>
       <c r="D98" t="str">
-        <v>銀飾W</v>
+        <v>銀飾O</v>
       </c>
       <c r="E98">
         <v>4</v>
@@ -3235,7 +3235,7 @@
         <v>399</v>
       </c>
       <c r="H98" t="str">
-        <v>银饰W.png</v>
+        <v>银饰O.png</v>
       </c>
       <c r="I98" t="str">
         <v>廣州市德潤</v>
@@ -3243,36 +3243,36 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>zyd_pnd_2</v>
+        <v>ysw_zm_4</v>
       </c>
       <c r="B99" t="str">
         <v>配件</v>
       </c>
       <c r="C99" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D99" t="str">
-        <v>珠遇蝶</v>
+        <v>銀飾W</v>
       </c>
       <c r="E99">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G99">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="H99" t="str">
-        <v>珠遇蝶.png</v>
+        <v>银饰W.png</v>
       </c>
       <c r="I99" t="str">
-        <v>廣州瑤心飾品</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>xfp_pnd_2</v>
+        <v>zyd_pnd_2</v>
       </c>
       <c r="B100" t="str">
         <v>配件</v>
@@ -3281,259 +3281,259 @@
         <v>吊墜</v>
       </c>
       <c r="D100" t="str">
-        <v>招財</v>
+        <v>珠遇蝶</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G100">
         <v>59</v>
       </c>
       <c r="H100" t="str">
-        <v>招财.png</v>
+        <v>珠遇蝶.png</v>
       </c>
       <c r="I100" t="str">
-        <v>義烏市歌爾</v>
+        <v>廣州瑤心飾品</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>ysq_zm_4</v>
+        <v>xfp_pnd_2</v>
       </c>
       <c r="B101" t="str">
         <v>配件</v>
       </c>
       <c r="C101" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D101" t="str">
-        <v>銀飾Q</v>
+        <v>招財</v>
       </c>
       <c r="E101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F101">
         <v>10</v>
       </c>
       <c r="G101">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="H101" t="str">
-        <v>银饰Q.png</v>
+        <v>招财.png</v>
       </c>
       <c r="I101" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市歌爾</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ymys_stn_10</v>
+        <v>ysq_zm_4</v>
       </c>
       <c r="B102" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C102" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D102" t="str">
-        <v>羽毛螢石</v>
+        <v>銀飾Q</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F102">
         <v>10</v>
       </c>
       <c r="G102">
-        <v>139</v>
+        <v>399</v>
       </c>
       <c r="H102" t="str">
-        <v>羽毛萤石.png</v>
+        <v>银饰Q.png</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>gyjx_xz_3</v>
+        <v>ymys_stn_10</v>
       </c>
       <c r="B103" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C103" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D103" t="str">
-        <v>古銀巨蟹</v>
+        <v>羽毛螢石</v>
       </c>
       <c r="E103">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F103">
         <v>10</v>
       </c>
       <c r="G103">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="H103" t="str">
-        <v>古银巨蟹.png</v>
+        <v>羽毛萤石.png</v>
       </c>
       <c r="I103" t="str">
-        <v>義烏市唐人印象</v>
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ysf_zm_4</v>
+        <v>gyjx_xz_3</v>
       </c>
       <c r="B104" t="str">
         <v>配件</v>
       </c>
       <c r="C104" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D104" t="str">
-        <v>銀飾F</v>
+        <v>古銀巨蟹</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F104">
         <v>10</v>
       </c>
       <c r="G104">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H104" t="str">
-        <v>银饰F.png</v>
+        <v>古银巨蟹.png</v>
       </c>
       <c r="I104" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>gyss_xz_3</v>
+        <v>ysf_zm_4</v>
       </c>
       <c r="B105" t="str">
         <v>配件</v>
       </c>
       <c r="C105" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D105" t="str">
-        <v>古銀射手</v>
+        <v>銀飾F</v>
       </c>
       <c r="E105">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F105">
         <v>10</v>
       </c>
       <c r="G105">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H105" t="str">
-        <v>古银射手.png</v>
+        <v>银饰F.png</v>
       </c>
       <c r="I105" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>hlcs_pnd_3</v>
+        <v>gyss_xz_3</v>
       </c>
       <c r="B106" t="str">
         <v>配件</v>
       </c>
       <c r="C106" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D106" t="str">
-        <v>葫蘆成雙</v>
+        <v>古銀射手</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G106">
-        <v>299</v>
+        <v>39</v>
       </c>
       <c r="H106" t="str">
-        <v>葫芦成双.png</v>
+        <v>古银射手.png</v>
       </c>
       <c r="I106" t="str">
-        <v>東海縣花眠</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>gyszz_xz_3</v>
+        <v>hlcs_pnd_3</v>
       </c>
       <c r="B107" t="str">
         <v>配件</v>
       </c>
       <c r="C107" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D107" t="str">
-        <v>古銀雙子</v>
+        <v>葫蘆成雙</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G107">
-        <v>39</v>
+        <v>299</v>
       </c>
       <c r="H107" t="str">
-        <v>古银双子.png</v>
+        <v>葫芦成双.png</v>
       </c>
       <c r="I107" t="str">
-        <v>義烏市唐人印象</v>
+        <v>東海縣花眠</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ysn_zm_4</v>
+        <v>gyszz_xz_3</v>
       </c>
       <c r="B108" t="str">
         <v>配件</v>
       </c>
       <c r="C108" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D108" t="str">
-        <v>銀飾N</v>
+        <v>古銀雙子</v>
       </c>
       <c r="E108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F108">
         <v>10</v>
       </c>
       <c r="G108">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H108" t="str">
-        <v>银饰N.png</v>
+        <v>古银双子.png</v>
       </c>
       <c r="I108" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ysm_zm_4</v>
+        <v>ysn_zm_4</v>
       </c>
       <c r="B109" t="str">
         <v>配件</v>
@@ -3542,7 +3542,7 @@
         <v>字母</v>
       </c>
       <c r="D109" t="str">
-        <v>銀飾M</v>
+        <v>銀飾N</v>
       </c>
       <c r="E109">
         <v>4</v>
@@ -3554,7 +3554,7 @@
         <v>399</v>
       </c>
       <c r="H109" t="str">
-        <v>银饰M.png</v>
+        <v>银饰N.png</v>
       </c>
       <c r="I109" t="str">
         <v>廣州市德潤</v>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ysh_zm_4</v>
+        <v>ysm_zm_4</v>
       </c>
       <c r="B110" t="str">
         <v>配件</v>
@@ -3571,7 +3571,7 @@
         <v>字母</v>
       </c>
       <c r="D110" t="str">
-        <v>銀飾H</v>
+        <v>銀飾M</v>
       </c>
       <c r="E110">
         <v>4</v>
@@ -3583,7 +3583,7 @@
         <v>399</v>
       </c>
       <c r="H110" t="str">
-        <v>银饰H.png</v>
+        <v>银饰M.png</v>
       </c>
       <c r="I110" t="str">
         <v>廣州市德潤</v>
@@ -3591,123 +3591,123 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>gytx_xz_3</v>
+        <v>ysh_zm_4</v>
       </c>
       <c r="B111" t="str">
         <v>配件</v>
       </c>
       <c r="C111" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D111" t="str">
-        <v>古銀天蠍</v>
+        <v>銀飾H</v>
       </c>
       <c r="E111">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F111">
         <v>10</v>
       </c>
       <c r="G111">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H111" t="str">
-        <v>古银天蝎.png</v>
+        <v>银饰H.png</v>
       </c>
       <c r="I111" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ysg_zm_4</v>
+        <v>gytx_xz_3</v>
       </c>
       <c r="B112" t="str">
         <v>配件</v>
       </c>
       <c r="C112" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D112" t="str">
-        <v>銀飾G</v>
+        <v>古銀天蠍</v>
       </c>
       <c r="E112">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F112">
         <v>10</v>
       </c>
       <c r="G112">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H112" t="str">
-        <v>银饰G.png</v>
+        <v>古银天蝎.png</v>
       </c>
       <c r="I112" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>gytc_xz_3</v>
+        <v>ysg_zm_4</v>
       </c>
       <c r="B113" t="str">
         <v>配件</v>
       </c>
       <c r="C113" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D113" t="str">
-        <v>古銀天秤</v>
+        <v>銀飾G</v>
       </c>
       <c r="E113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F113">
         <v>10</v>
       </c>
       <c r="G113">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H113" t="str">
-        <v>古银天秤.png</v>
+        <v>银饰G.png</v>
       </c>
       <c r="I113" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>yst_zm_4</v>
+        <v>gytc_xz_3</v>
       </c>
       <c r="B114" t="str">
         <v>配件</v>
       </c>
       <c r="C114" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D114" t="str">
-        <v>銀飾T</v>
+        <v>古銀天秤</v>
       </c>
       <c r="E114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114">
         <v>10</v>
       </c>
       <c r="G114">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H114" t="str">
-        <v>银饰T.png</v>
+        <v>古银天秤.png</v>
       </c>
       <c r="I114" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>yse_zm_4</v>
+        <v>yst_zm_4</v>
       </c>
       <c r="B115" t="str">
         <v>配件</v>
@@ -3716,7 +3716,7 @@
         <v>字母</v>
       </c>
       <c r="D115" t="str">
-        <v>銀飾E</v>
+        <v>銀飾T</v>
       </c>
       <c r="E115">
         <v>4</v>
@@ -3728,7 +3728,7 @@
         <v>399</v>
       </c>
       <c r="H115" t="str">
-        <v>银饰E.png</v>
+        <v>银饰T.png</v>
       </c>
       <c r="I115" t="str">
         <v>廣州市德潤</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ysk_zm_4</v>
+        <v>yse_zm_4</v>
       </c>
       <c r="B116" t="str">
         <v>配件</v>
@@ -3745,7 +3745,7 @@
         <v>字母</v>
       </c>
       <c r="D116" t="str">
-        <v>銀飾K</v>
+        <v>銀飾E</v>
       </c>
       <c r="E116">
         <v>4</v>
@@ -3757,7 +3757,7 @@
         <v>399</v>
       </c>
       <c r="H116" t="str">
-        <v>银饰K.png</v>
+        <v>银饰E.png</v>
       </c>
       <c r="I116" t="str">
         <v>廣州市德潤</v>
@@ -3765,123 +3765,123 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>syyl_pnd_2</v>
+        <v>ysk_zm_4</v>
       </c>
       <c r="B117" t="str">
         <v>配件</v>
       </c>
       <c r="C117" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D117" t="str">
-        <v>閃躍月亮</v>
+        <v>銀飾K</v>
       </c>
       <c r="E117">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F117">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G117">
-        <v>69</v>
+        <v>399</v>
       </c>
       <c r="H117" t="str">
-        <v>闪跃月亮.png</v>
+        <v>银饰K.png</v>
       </c>
       <c r="I117" t="str">
-        <v>廣州銅品彙</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ysv_zm_4</v>
+        <v>syyl_pnd_2</v>
       </c>
       <c r="B118" t="str">
         <v>配件</v>
       </c>
       <c r="C118" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D118" t="str">
-        <v>銀飾V</v>
+        <v>閃躍月亮</v>
       </c>
       <c r="E118">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F118">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G118">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="H118" t="str">
-        <v>银饰V.png</v>
+        <v>闪跃月亮.png</v>
       </c>
       <c r="I118" t="str">
-        <v>廣州市德潤</v>
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>gszs_spc_3</v>
+        <v>ysv_zm_4</v>
       </c>
       <c r="B119" t="str">
         <v>配件</v>
       </c>
       <c r="C119" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D119" t="str">
-        <v>藏銀繡球鋯石細閃</v>
+        <v>銀飾V</v>
       </c>
       <c r="E119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G119">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="H119" t="str">
-        <v>藏银绣球锆石细闪.png</v>
+        <v>银饰V.png</v>
       </c>
       <c r="I119" t="str">
-        <v>義烏市硯鈺</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ysl_zm_4</v>
+        <v>gszs_spc_3</v>
       </c>
       <c r="B120" t="str">
         <v>配件</v>
       </c>
       <c r="C120" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D120" t="str">
-        <v>銀飾L</v>
+        <v>藏銀繡球鋯石細閃</v>
       </c>
       <c r="E120">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F120">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G120">
-        <v>399</v>
+        <v>129</v>
       </c>
       <c r="H120" t="str">
-        <v>银饰L.png</v>
+        <v>藏银绣球锆石细闪.png</v>
       </c>
       <c r="I120" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>ysa_zm_4</v>
+        <v>ysl_zm_4</v>
       </c>
       <c r="B121" t="str">
         <v>配件</v>
@@ -3890,7 +3890,7 @@
         <v>字母</v>
       </c>
       <c r="D121" t="str">
-        <v>銀飾A</v>
+        <v>銀飾L</v>
       </c>
       <c r="E121">
         <v>4</v>
@@ -3902,7 +3902,7 @@
         <v>399</v>
       </c>
       <c r="H121" t="str">
-        <v>银饰A.png</v>
+        <v>银饰L.png</v>
       </c>
       <c r="I121" t="str">
         <v>廣州市德潤</v>
@@ -3910,210 +3910,210 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>gyjn_xz_3</v>
+        <v>ysa_zm_4</v>
       </c>
       <c r="B122" t="str">
         <v>配件</v>
       </c>
       <c r="C122" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D122" t="str">
-        <v>古銀金牛</v>
+        <v>銀飾A</v>
       </c>
       <c r="E122">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F122">
         <v>10</v>
       </c>
       <c r="G122">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H122" t="str">
-        <v>古银金牛.png</v>
+        <v>银饰A.png</v>
       </c>
       <c r="I122" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>ysy_zm_4</v>
+        <v>gyjn_xz_3</v>
       </c>
       <c r="B123" t="str">
         <v>配件</v>
       </c>
       <c r="C123" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D123" t="str">
-        <v>銀飾Y</v>
+        <v>古銀金牛</v>
       </c>
       <c r="E123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F123">
         <v>10</v>
       </c>
       <c r="G123">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H123" t="str">
-        <v>银饰Y.png</v>
+        <v>古银金牛.png</v>
       </c>
       <c r="I123" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>jsxh_spc_2</v>
+        <v>ysy_zm_4</v>
       </c>
       <c r="B124" t="str">
         <v>配件</v>
       </c>
       <c r="C124" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D124" t="str">
-        <v>金色小環</v>
+        <v>銀飾Y</v>
       </c>
       <c r="E124">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F124">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G124">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H124" t="str">
-        <v>金色小环.png</v>
+        <v>银饰Y.png</v>
       </c>
       <c r="I124" t="str">
-        <v>廣州鑫鈺</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>gyshz_xz_3</v>
+        <v>jsxh_spc_2</v>
       </c>
       <c r="B125" t="str">
         <v>配件</v>
       </c>
       <c r="C125" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D125" t="str">
-        <v>古銀獅子</v>
+        <v>金色小環</v>
       </c>
       <c r="E125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F125">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G125">
         <v>39</v>
       </c>
       <c r="H125" t="str">
-        <v>古银狮子.png</v>
+        <v>金色小环.png</v>
       </c>
       <c r="I125" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州鑫鈺</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>bjx_pnd_2</v>
+        <v>gyshz_xz_3</v>
       </c>
       <c r="B126" t="str">
         <v>配件</v>
       </c>
       <c r="C126" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D126" t="str">
-        <v>北極星</v>
+        <v>古銀獅子</v>
       </c>
       <c r="E126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G126">
-        <v>299</v>
+        <v>39</v>
       </c>
       <c r="H126" t="str">
-        <v>北极星.png</v>
+        <v>古银狮子.png</v>
       </c>
       <c r="I126" t="str">
-        <v>海豐縣梅隴鎮創藝祺</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ysx_zm_4</v>
+        <v>bjx_pnd_2</v>
       </c>
       <c r="B127" t="str">
         <v>配件</v>
       </c>
       <c r="C127" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D127" t="str">
-        <v>銀飾X</v>
+        <v>北極星</v>
       </c>
       <c r="E127">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F127">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G127">
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="H127" t="str">
-        <v>银饰X.png</v>
+        <v>北极星.png</v>
       </c>
       <c r="I127" t="str">
-        <v>廣州市德潤</v>
+        <v>海豐縣梅隴鎮創藝祺</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>hps_stn_6</v>
+        <v>ysx_zm_4</v>
       </c>
       <c r="B128" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C128" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D128" t="str">
-        <v>琥珀石</v>
+        <v>銀飾X</v>
       </c>
       <c r="E128">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F128">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G128">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="H128" t="str">
-        <v>琥珀石.png</v>
+        <v>银饰X.png</v>
       </c>
       <c r="I128" t="str">
-        <v/>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>hps_stn_8</v>
+        <v>hps_stn_6</v>
       </c>
       <c r="B129" t="str">
         <v>珠子</v>
@@ -4125,13 +4125,13 @@
         <v>琥珀石</v>
       </c>
       <c r="E129">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F129">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G129">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H129" t="str">
         <v>琥珀石.png</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>hps_stn_10</v>
+        <v>hps_stn_8</v>
       </c>
       <c r="B130" t="str">
         <v>珠子</v>
@@ -4154,13 +4154,13 @@
         <v>琥珀石</v>
       </c>
       <c r="E130">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F130">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G130">
-        <v>199</v>
+        <v>89</v>
       </c>
       <c r="H130" t="str">
         <v>琥珀石.png</v>
@@ -4171,77 +4171,77 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>gysy_xz_3</v>
+        <v>hps_stn_10</v>
       </c>
       <c r="B131" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C131" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D131" t="str">
-        <v>古銀雙魚</v>
+        <v>琥珀石</v>
       </c>
       <c r="E131">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F131">
         <v>10</v>
       </c>
       <c r="G131">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="H131" t="str">
-        <v>古银双鱼.png</v>
+        <v>琥珀石.png</v>
       </c>
       <c r="I131" t="str">
-        <v>義烏市唐人印象</v>
+        <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>xs_spc_10</v>
+        <v>gysy_xz_3</v>
       </c>
       <c r="B132" t="str">
         <v>配件</v>
       </c>
       <c r="C132" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D132" t="str">
-        <v>醒獅</v>
+        <v>古銀雙魚</v>
       </c>
       <c r="E132">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F132">
         <v>10</v>
       </c>
       <c r="G132">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H132" t="str">
-        <v>醒狮.png</v>
+        <v>古银双鱼.png</v>
       </c>
       <c r="I132" t="str">
-        <v>連雲港趣界</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>ysz_zm_4</v>
+        <v>xs_spc_10</v>
       </c>
       <c r="B133" t="str">
         <v>配件</v>
       </c>
       <c r="C133" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D133" t="str">
-        <v>銀飾Z</v>
+        <v>醒獅</v>
       </c>
       <c r="E133">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F133">
         <v>10</v>
@@ -4250,44 +4250,44 @@
         <v>399</v>
       </c>
       <c r="H133" t="str">
-        <v>银饰Z.png</v>
+        <v>醒狮.png</v>
       </c>
       <c r="I133" t="str">
-        <v>廣州市德潤</v>
+        <v>連雲港趣界</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ths_stn_6</v>
+        <v>ysz_zm_4</v>
       </c>
       <c r="B134" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C134" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D134" t="str">
-        <v>天河石</v>
+        <v>銀飾Z</v>
       </c>
       <c r="E134">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F134">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G134">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="H134" t="str">
-        <v>天河石.png</v>
+        <v>银饰Z.png</v>
       </c>
       <c r="I134" t="str">
-        <v/>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ths_stn_8</v>
+        <v>ths_stn_6</v>
       </c>
       <c r="B135" t="str">
         <v>珠子</v>
@@ -4299,13 +4299,13 @@
         <v>天河石</v>
       </c>
       <c r="E135">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F135">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G135">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="H135" t="str">
         <v>天河石.png</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ths_stn_10</v>
+        <v>ths_stn_8</v>
       </c>
       <c r="B136" t="str">
         <v>珠子</v>
@@ -4328,13 +4328,13 @@
         <v>天河石</v>
       </c>
       <c r="E136">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F136">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G136">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="H136" t="str">
         <v>天河石.png</v>
@@ -4345,65 +4345,65 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>ysd_zm_4</v>
+        <v>ths_stn_10</v>
       </c>
       <c r="B137" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C137" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D137" t="str">
-        <v>銀飾D</v>
+        <v>天河石</v>
       </c>
       <c r="E137">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F137">
         <v>10</v>
       </c>
       <c r="G137">
-        <v>399</v>
+        <v>139</v>
       </c>
       <c r="H137" t="str">
-        <v>银饰D.png</v>
+        <v>天河石.png</v>
       </c>
       <c r="I137" t="str">
-        <v>廣州市德潤</v>
+        <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>hlb_stn_6</v>
+        <v>ysd_zm_4</v>
       </c>
       <c r="B138" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C138" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D138" t="str">
-        <v>海藍寶</v>
+        <v>銀飾D</v>
       </c>
       <c r="E138">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F138">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G138">
-        <v>89</v>
+        <v>399</v>
       </c>
       <c r="H138" t="str">
-        <v>海蓝宝.png</v>
+        <v>银饰D.png</v>
       </c>
       <c r="I138" t="str">
-        <v/>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>hlb_stn_8</v>
+        <v>hlb_stn_6</v>
       </c>
       <c r="B139" t="str">
         <v>珠子</v>
@@ -4415,13 +4415,13 @@
         <v>海藍寶</v>
       </c>
       <c r="E139">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F139">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G139">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H139" t="str">
         <v>海蓝宝.png</v>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>hlb_stn_10</v>
+        <v>hlb_stn_8</v>
       </c>
       <c r="B140" t="str">
         <v>珠子</v>
@@ -4444,13 +4444,13 @@
         <v>海藍寶</v>
       </c>
       <c r="E140">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F140">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G140">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="H140" t="str">
         <v>海蓝宝.png</v>
@@ -4461,103 +4461,103 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>yss_zm_4</v>
+        <v>hlb_stn_10</v>
       </c>
       <c r="B141" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C141" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D141" t="str">
-        <v>銀飾S</v>
+        <v>海藍寶</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F141">
         <v>10</v>
       </c>
       <c r="G141">
-        <v>399</v>
+        <v>169</v>
       </c>
       <c r="H141" t="str">
-        <v>银饰S.png</v>
+        <v>海蓝宝.png</v>
       </c>
       <c r="I141" t="str">
-        <v>廣州市德潤</v>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>gsch_pnd_2</v>
+        <v>yss_zm_4</v>
       </c>
       <c r="B142" t="str">
         <v>配件</v>
       </c>
       <c r="C142" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D142" t="str">
-        <v>鋯石彩虹</v>
+        <v>銀飾S</v>
       </c>
       <c r="E142">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F142">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G142">
-        <v>199</v>
+        <v>399</v>
       </c>
       <c r="H142" t="str">
-        <v>锆石彩虹.png</v>
+        <v>银饰S.png</v>
       </c>
       <c r="I142" t="str">
-        <v>東海縣慕戀夢</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>xgszs_spc_6</v>
+        <v>gsch_pnd_2</v>
       </c>
       <c r="B143" t="str">
         <v>配件</v>
       </c>
       <c r="C143" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D143" t="str">
-        <v>小鋯石鑽閃</v>
+        <v>鋯石彩虹</v>
       </c>
       <c r="E143">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F143">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G143">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="H143" t="str">
-        <v>小锆石钻闪.png</v>
+        <v>锆石彩虹.png</v>
       </c>
       <c r="I143" t="str">
-        <v>廣州戴芙妮</v>
+        <v>東海縣慕戀夢</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>htj_cysl_6</v>
+        <v>xgszs_spc_6</v>
       </c>
       <c r="B144" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C144" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D144" t="str">
-        <v>黃塔晶</v>
+        <v>小鋯石鑽閃</v>
       </c>
       <c r="E144">
         <v>6</v>
@@ -4566,18 +4566,18 @@
         <v>6</v>
       </c>
       <c r="G144">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H144" t="str">
-        <v>黄塔晶.png</v>
+        <v>小锆石钻闪.png</v>
       </c>
       <c r="I144" t="str">
-        <v/>
+        <v>廣州戴芙妮</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>htj_cysl_8</v>
+        <v>htj_cysl_6</v>
       </c>
       <c r="B145" t="str">
         <v>珠子</v>
@@ -4589,13 +4589,13 @@
         <v>黃塔晶</v>
       </c>
       <c r="E145">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F145">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G145">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H145" t="str">
         <v>黄塔晶.png</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>htj_cysl_10</v>
+        <v>htj_cysl_8</v>
       </c>
       <c r="B146" t="str">
         <v>珠子</v>
@@ -4618,13 +4618,13 @@
         <v>黃塔晶</v>
       </c>
       <c r="E146">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F146">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G146">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="H146" t="str">
         <v>黄塔晶.png</v>
@@ -4635,65 +4635,65 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>wyh_pnd_2</v>
+        <v>htj_cysl_10</v>
       </c>
       <c r="B147" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C147" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D147" t="str">
-        <v>午夜花</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F147">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G147">
         <v>99</v>
       </c>
       <c r="H147" t="str">
-        <v>午夜花.png</v>
+        <v>黄塔晶.png</v>
       </c>
       <c r="I147" t="str">
-        <v>義烏市亮飛</v>
+        <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>hfj_cysl_6</v>
+        <v>wyh_pnd_2</v>
       </c>
       <c r="B148" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C148" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D148" t="str">
-        <v>黑髮晶</v>
+        <v>午夜花</v>
       </c>
       <c r="E148">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F148">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G148">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="H148" t="str">
-        <v>黑发晶.png</v>
+        <v>午夜花.png</v>
       </c>
       <c r="I148" t="str">
-        <v/>
+        <v>義烏市亮飛</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>hfj_cysl_8</v>
+        <v>hfj_cysl_6</v>
       </c>
       <c r="B149" t="str">
         <v>珠子</v>
@@ -4705,13 +4705,13 @@
         <v>黑髮晶</v>
       </c>
       <c r="E149">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F149">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G149">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H149" t="str">
         <v>黑发晶.png</v>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>hfj_cysl_10</v>
+        <v>hfj_cysl_8</v>
       </c>
       <c r="B150" t="str">
         <v>珠子</v>
@@ -4734,13 +4734,13 @@
         <v>黑髮晶</v>
       </c>
       <c r="E150">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F150">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G150">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="H150" t="str">
         <v>黑发晶.png</v>
@@ -4751,36 +4751,36 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>tz_spc_19</v>
+        <v>hfj_cysl_10</v>
       </c>
       <c r="B151" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C151" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D151" t="str">
-        <v>天珠</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E151">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F151">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G151">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="H151" t="str">
-        <v>天珠.png</v>
+        <v>黑发晶.png</v>
       </c>
       <c r="I151" t="str">
-        <v>義烏市楊航</v>
+        <v/>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ysxz_spc_4</v>
+        <v>tz_spc_19</v>
       </c>
       <c r="B152" t="str">
         <v>配件</v>
@@ -4789,56 +4789,56 @@
         <v>隔珠</v>
       </c>
       <c r="D152" t="str">
-        <v>銀色小珠</v>
+        <v>天珠</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F152">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G152">
         <v>69</v>
       </c>
       <c r="H152" t="str">
-        <v>银色小珠.png</v>
+        <v>天珠.png</v>
       </c>
       <c r="I152" t="str">
-        <v>義烏市硯鈺</v>
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>jhy_stn_6</v>
+        <v>ysxz_spc_4</v>
       </c>
       <c r="B153" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C153" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D153" t="str">
-        <v>金虎眼</v>
+        <v>銀色小珠</v>
       </c>
       <c r="E153">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F153">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G153">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H153" t="str">
-        <v>金虎眼.png</v>
+        <v>银色小珠.png</v>
       </c>
       <c r="I153" t="str">
-        <v/>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>jhy_stn_8</v>
+        <v>jhy_stn_6</v>
       </c>
       <c r="B154" t="str">
         <v>珠子</v>
@@ -4850,13 +4850,13 @@
         <v>金虎眼</v>
       </c>
       <c r="E154">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F154">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G154">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H154" t="str">
         <v>金虎眼.png</v>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>jhy_stn_10</v>
+        <v>jhy_stn_8</v>
       </c>
       <c r="B155" t="str">
         <v>珠子</v>
@@ -4879,13 +4879,13 @@
         <v>金虎眼</v>
       </c>
       <c r="E155">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F155">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G155">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H155" t="str">
         <v>金虎眼.png</v>
@@ -4896,65 +4896,65 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>jsmxyl_pnd_2</v>
+        <v>jhy_stn_10</v>
       </c>
       <c r="B156" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C156" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D156" t="str">
-        <v>滿鑲彩月</v>
+        <v>金虎眼</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F156">
         <v>10</v>
       </c>
       <c r="G156">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H156" t="str">
-        <v>满镶彩月.png</v>
+        <v>金虎眼.png</v>
       </c>
       <c r="I156" t="str">
-        <v>廣州銅品彙</v>
+        <v/>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>lcmj_cysl_6</v>
+        <v>jsmxyl_pnd_2</v>
       </c>
       <c r="B157" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C157" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D157" t="str">
-        <v>綠莓晶</v>
+        <v>滿鑲彩月</v>
       </c>
       <c r="E157">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F157">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G157">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H157" t="str">
-        <v>绿莓晶.png</v>
+        <v>满镶彩月.png</v>
       </c>
       <c r="I157" t="str">
-        <v/>
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>lcmj_cysl_8</v>
+        <v>lcmj_cysl_6</v>
       </c>
       <c r="B158" t="str">
         <v>珠子</v>
@@ -4966,13 +4966,13 @@
         <v>綠莓晶</v>
       </c>
       <c r="E158">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F158">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G158">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H158" t="str">
         <v>绿莓晶.png</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>lcmj_cysl_10</v>
+        <v>lcmj_cysl_8</v>
       </c>
       <c r="B159" t="str">
         <v>珠子</v>
@@ -4995,13 +4995,13 @@
         <v>綠莓晶</v>
       </c>
       <c r="E159">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F159">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G159">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H159" t="str">
         <v>绿莓晶.png</v>
@@ -5012,28 +5012,28 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>xy_stn_6</v>
+        <v>lcmj_cysl_10</v>
       </c>
       <c r="B160" t="str">
         <v>珠子</v>
       </c>
       <c r="C160" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D160" t="str">
-        <v>岫玉</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E160">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F160">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G160">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H160" t="str">
-        <v>岫玉.png</v>
+        <v>绿莓晶.png</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>xy_stn_8</v>
+        <v>xy_stn_6</v>
       </c>
       <c r="B161" t="str">
         <v>珠子</v>
@@ -5053,13 +5053,13 @@
         <v>岫玉</v>
       </c>
       <c r="E161">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F161">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G161">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H161" t="str">
         <v>岫玉.png</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>xy_stn_10</v>
+        <v>xy_stn_8</v>
       </c>
       <c r="B162" t="str">
         <v>珠子</v>
@@ -5082,13 +5082,13 @@
         <v>岫玉</v>
       </c>
       <c r="E162">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F162">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G162">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H162" t="str">
         <v>岫玉.png</v>
@@ -5099,16 +5099,16 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>cyszh_spc_10</v>
+        <v>xy_stn_10</v>
       </c>
       <c r="B163" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C163" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D163" t="str">
-        <v>藏銀十字花</v>
+        <v>岫玉</v>
       </c>
       <c r="E163">
         <v>10</v>
@@ -5117,76 +5117,76 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H163" t="str">
-        <v>藏银十字花.png</v>
+        <v>岫玉.png</v>
       </c>
       <c r="I163" t="str">
-        <v>義烏市楓瑢</v>
+        <v/>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>cyym_pnd_2</v>
+        <v>cyszh_spc_10</v>
       </c>
       <c r="B164" t="str">
         <v>配件</v>
       </c>
       <c r="C164" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D164" t="str">
-        <v>藏銀羽毛</v>
+        <v>藏銀十字花</v>
       </c>
       <c r="E164">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F164">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G164">
-        <v>599</v>
+        <v>69</v>
       </c>
       <c r="H164" t="str">
-        <v>藏银羽毛.png</v>
+        <v>藏银十字花.png</v>
       </c>
       <c r="I164" t="str">
-        <v>廣州市無風帶</v>
+        <v>義烏市楓瑢</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>lys_stn_6</v>
+        <v>cyym_pnd_2</v>
       </c>
       <c r="B165" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C165" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D165" t="str">
-        <v>綠螢石</v>
+        <v>藏銀羽毛</v>
       </c>
       <c r="E165">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F165">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G165">
-        <v>69</v>
+        <v>599</v>
       </c>
       <c r="H165" t="str">
-        <v>绿萤石.png</v>
+        <v>藏银羽毛.png</v>
       </c>
       <c r="I165" t="str">
-        <v/>
+        <v>廣州市無風帶</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>lys_stn_8</v>
+        <v>lys_stn_6</v>
       </c>
       <c r="B166" t="str">
         <v>珠子</v>
@@ -5198,13 +5198,13 @@
         <v>綠螢石</v>
       </c>
       <c r="E166">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F166">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G166">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H166" t="str">
         <v>绿萤石.png</v>
@@ -5215,65 +5215,65 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>cysy_spc_4</v>
+        <v>lys_stn_8</v>
       </c>
       <c r="B167" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C167" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D167" t="str">
-        <v>藏銀樹葉</v>
+        <v>綠螢石</v>
       </c>
       <c r="E167">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F167">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G167">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H167" t="str">
-        <v>藏银树叶.png</v>
+        <v>绿萤石.png</v>
       </c>
       <c r="I167" t="str">
-        <v>義烏市楊航</v>
+        <v/>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>qws_stn_8</v>
+        <v>cysy_spc_4</v>
       </c>
       <c r="B168" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C168" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D168" t="str">
-        <v>薔薇石</v>
+        <v>藏銀樹葉</v>
       </c>
       <c r="E168">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F168">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G168">
         <v>69</v>
       </c>
       <c r="H168" t="str">
-        <v>蔷薇石.png</v>
+        <v>藏银树叶.png</v>
       </c>
       <c r="I168" t="str">
-        <v/>
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>qws_stn_10</v>
+        <v>qws_stn_8</v>
       </c>
       <c r="B169" t="str">
         <v>珠子</v>
@@ -5285,13 +5285,13 @@
         <v>薔薇石</v>
       </c>
       <c r="E169">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F169">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G169">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H169" t="str">
         <v>蔷薇石.png</v>
@@ -5302,65 +5302,65 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>jsxz_spc_4</v>
+        <v>qws_stn_10</v>
       </c>
       <c r="B170" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C170" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D170" t="str">
-        <v>金色小珠</v>
+        <v>薔薇石</v>
       </c>
       <c r="E170">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F170">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G170">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H170" t="str">
-        <v>金色小珠.png</v>
+        <v>蔷薇石.png</v>
       </c>
       <c r="I170" t="str">
-        <v>義烏市硯鈺</v>
+        <v/>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>gtsp_xz_3</v>
+        <v>jsxz_spc_4</v>
       </c>
       <c r="B171" t="str">
         <v>配件</v>
       </c>
       <c r="C171" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D171" t="str">
-        <v>古銅水瓶</v>
+        <v>金色小珠</v>
       </c>
       <c r="E171">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F171">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G171">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H171" t="str">
-        <v>古铜水瓶.png</v>
+        <v>金色小珠.png</v>
       </c>
       <c r="I171" t="str">
-        <v>義烏市唐人印象</v>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>gtby_xz_3</v>
+        <v>gtsp_xz_3</v>
       </c>
       <c r="B172" t="str">
         <v>配件</v>
@@ -5369,7 +5369,7 @@
         <v>星座</v>
       </c>
       <c r="D172" t="str">
-        <v>古銅白羊</v>
+        <v>古銅水瓶</v>
       </c>
       <c r="E172">
         <v>3</v>
@@ -5381,7 +5381,7 @@
         <v>39</v>
       </c>
       <c r="H172" t="str">
-        <v>古铜白羊.png</v>
+        <v>古铜水瓶.png</v>
       </c>
       <c r="I172" t="str">
         <v>義烏市唐人印象</v>
@@ -5389,65 +5389,65 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>gszssc_spc_5</v>
+        <v>gtby_xz_3</v>
       </c>
       <c r="B173" t="str">
         <v>配件</v>
       </c>
       <c r="C173" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D173" t="str">
-        <v>鋯石鑽閃雙層</v>
+        <v>古銅白羊</v>
       </c>
       <c r="E173">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F173">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G173">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="H173" t="str">
-        <v>锆石钻闪双层.png</v>
+        <v>古铜白羊.png</v>
       </c>
       <c r="I173" t="str">
-        <v>義烏市硯鈺</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>gtshz_xz_3</v>
+        <v>gszssc_spc_5</v>
       </c>
       <c r="B174" t="str">
         <v>配件</v>
       </c>
       <c r="C174" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D174" t="str">
-        <v>古銅獅子</v>
+        <v>鋯石鑽閃雙層</v>
       </c>
       <c r="E174">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F174">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G174">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="H174" t="str">
-        <v>古铜狮子.png</v>
+        <v>锆石钻闪双层.png</v>
       </c>
       <c r="I174" t="str">
-        <v>義烏市唐人印象</v>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gttc_xz_3</v>
+        <v>gtshz_xz_3</v>
       </c>
       <c r="B175" t="str">
         <v>配件</v>
@@ -5456,7 +5456,7 @@
         <v>星座</v>
       </c>
       <c r="D175" t="str">
-        <v>古銅天秤</v>
+        <v>古銅獅子</v>
       </c>
       <c r="E175">
         <v>3</v>
@@ -5468,7 +5468,7 @@
         <v>39</v>
       </c>
       <c r="H175" t="str">
-        <v>古铜天秤.png</v>
+        <v>古铜狮子.png</v>
       </c>
       <c r="I175" t="str">
         <v>義烏市唐人印象</v>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>gtcn_xz_3</v>
+        <v>gttc_xz_3</v>
       </c>
       <c r="B176" t="str">
         <v>配件</v>
@@ -5485,7 +5485,7 @@
         <v>星座</v>
       </c>
       <c r="D176" t="str">
-        <v>古銅處女</v>
+        <v>古銅天秤</v>
       </c>
       <c r="E176">
         <v>3</v>
@@ -5497,7 +5497,7 @@
         <v>39</v>
       </c>
       <c r="H176" t="str">
-        <v>古铜处女.png</v>
+        <v>古铜天秤.png</v>
       </c>
       <c r="I176" t="str">
         <v>義烏市唐人印象</v>
@@ -5505,36 +5505,36 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>ygs_stn_6</v>
+        <v>gtcn_xz_3</v>
       </c>
       <c r="B177" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C177" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D177" t="str">
-        <v>月光石</v>
+        <v>古銅處女</v>
       </c>
       <c r="E177">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F177">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G177">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H177" t="str">
-        <v>月光石.png</v>
+        <v>古铜处女.png</v>
       </c>
       <c r="I177" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>ygs_stn_8</v>
+        <v>ygs_stn_6</v>
       </c>
       <c r="B178" t="str">
         <v>珠子</v>
@@ -5546,13 +5546,13 @@
         <v>月光石</v>
       </c>
       <c r="E178">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F178">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G178">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H178" t="str">
         <v>月光石.png</v>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>ygs_stn_10</v>
+        <v>ygs_stn_8</v>
       </c>
       <c r="B179" t="str">
         <v>珠子</v>
@@ -5575,13 +5575,13 @@
         <v>月光石</v>
       </c>
       <c r="E179">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F179">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G179">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="H179" t="str">
         <v>月光石.png</v>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>tys_stn_6</v>
+        <v>ygs_stn_10</v>
       </c>
       <c r="B180" t="str">
         <v>珠子</v>
@@ -5601,19 +5601,19 @@
         <v>礦石</v>
       </c>
       <c r="D180" t="str">
-        <v>太陽石</v>
+        <v>月光石</v>
       </c>
       <c r="E180">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F180">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G180">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="H180" t="str">
-        <v>太阳石.png</v>
+        <v>月光石.png</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>tys_stn_8</v>
+        <v>tys_stn_6</v>
       </c>
       <c r="B181" t="str">
         <v>珠子</v>
@@ -5633,13 +5633,13 @@
         <v>太陽石</v>
       </c>
       <c r="E181">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F181">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G181">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H181" t="str">
         <v>太阳石.png</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>tys_stn_10</v>
+        <v>tys_stn_8</v>
       </c>
       <c r="B182" t="str">
         <v>珠子</v>
@@ -5662,13 +5662,13 @@
         <v>太陽石</v>
       </c>
       <c r="E182">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F182">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G182">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="H182" t="str">
         <v>太阳石.png</v>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>shlb_stn_8</v>
+        <v>tys_stn_10</v>
       </c>
       <c r="B183" t="str">
         <v>珠子</v>
@@ -5688,19 +5688,19 @@
         <v>礦石</v>
       </c>
       <c r="D183" t="str">
-        <v>聖海藍寶</v>
+        <v>太陽石</v>
       </c>
       <c r="E183">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F183">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G183">
-        <v>399</v>
+        <v>169</v>
       </c>
       <c r="H183" t="str">
-        <v>圣海蓝宝.png</v>
+        <v>太阳石.png</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>shlb_stn_10</v>
+        <v>shlb_stn_8</v>
       </c>
       <c r="B184" t="str">
         <v>珠子</v>
@@ -5720,13 +5720,13 @@
         <v>聖海藍寶</v>
       </c>
       <c r="E184">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F184">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G184">
-        <v>699</v>
+        <v>399</v>
       </c>
       <c r="H184" t="str">
         <v>圣海蓝宝.png</v>
@@ -5737,36 +5737,36 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>yslzzy_spc_9</v>
+        <v>shlb_stn_10</v>
       </c>
       <c r="B185" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C185" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D185" t="str">
-        <v>銀六字箴言</v>
+        <v>聖海藍寶</v>
       </c>
       <c r="E185">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F185">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G185">
-        <v>59</v>
+        <v>699</v>
       </c>
       <c r="H185" t="str">
-        <v>银六字箴言.png</v>
+        <v>圣海蓝宝.png</v>
       </c>
       <c r="I185" t="str">
-        <v>義烏市亦蝶</v>
+        <v/>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>ketj_spc_10</v>
+        <v>yslzzy_spc_9</v>
       </c>
       <c r="B186" t="str">
         <v>配件</v>
@@ -5775,27 +5775,27 @@
         <v>隔珠</v>
       </c>
       <c r="D186" t="str">
-        <v>凱爾特結</v>
+        <v>銀六字箴言</v>
       </c>
       <c r="E186">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F186">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G186">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H186" t="str">
-        <v>凯尔特结.png</v>
+        <v>银六字箴言.png</v>
       </c>
       <c r="I186" t="str">
-        <v>義烏市楊航</v>
+        <v>義烏市亦蝶</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ysxq_spc_10</v>
+        <v>ketj_spc_10</v>
       </c>
       <c r="B187" t="str">
         <v>配件</v>
@@ -5804,85 +5804,85 @@
         <v>隔珠</v>
       </c>
       <c r="D187" t="str">
-        <v>藏銀繡球</v>
+        <v>凱爾特結</v>
       </c>
       <c r="E187">
         <v>10</v>
       </c>
       <c r="F187">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G187">
         <v>69</v>
       </c>
       <c r="H187" t="str">
-        <v>藏银绣球.png</v>
+        <v>凯尔特结.png</v>
       </c>
       <c r="I187" t="str">
-        <v>義烏市隱魚</v>
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>gtszz_xz_3</v>
+        <v>ysxq_spc_10</v>
       </c>
       <c r="B188" t="str">
         <v>配件</v>
       </c>
       <c r="C188" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D188" t="str">
-        <v>古銅雙子</v>
+        <v>藏銀繡球</v>
       </c>
       <c r="E188">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F188">
         <v>10</v>
       </c>
       <c r="G188">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H188" t="str">
-        <v>古铜双子.png</v>
+        <v>藏银绣球.png</v>
       </c>
       <c r="I188" t="str">
-        <v>義烏市唐人印象</v>
+        <v>義烏市隱魚</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>zsj_cysl_6</v>
+        <v>gtszz_xz_3</v>
       </c>
       <c r="B189" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C189" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D189" t="str">
-        <v>紫水晶</v>
+        <v>古銅雙子</v>
       </c>
       <c r="E189">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F189">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G189">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H189" t="str">
-        <v>紫水晶.png</v>
+        <v>古铜双子.png</v>
       </c>
       <c r="I189" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>zsj_cysl_8</v>
+        <v>zsj_cysl_6</v>
       </c>
       <c r="B190" t="str">
         <v>珠子</v>
@@ -5894,13 +5894,13 @@
         <v>紫水晶</v>
       </c>
       <c r="E190">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F190">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G190">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H190" t="str">
         <v>紫水晶.png</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>zsj_cysl_10</v>
+        <v>zsj_cysl_8</v>
       </c>
       <c r="B191" t="str">
         <v>珠子</v>
@@ -5923,13 +5923,13 @@
         <v>紫水晶</v>
       </c>
       <c r="E191">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F191">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G191">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H191" t="str">
         <v>紫水晶.png</v>
@@ -5940,65 +5940,65 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>wgzl_pnd_2</v>
+        <v>zsj_cysl_10</v>
       </c>
       <c r="B192" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C192" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D192" t="str">
-        <v>國王之淚</v>
+        <v>紫水晶</v>
       </c>
       <c r="E192">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F192">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G192">
         <v>99</v>
       </c>
       <c r="H192" t="str">
-        <v>国王之泪.png</v>
+        <v>紫水晶.png</v>
       </c>
       <c r="I192" t="str">
-        <v>廣州市嘉鈺</v>
+        <v/>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>gtsy_xz_3</v>
+        <v>wgzl_pnd_2</v>
       </c>
       <c r="B193" t="str">
         <v>配件</v>
       </c>
       <c r="C193" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D193" t="str">
-        <v>古銅雙魚</v>
+        <v>國王之淚</v>
       </c>
       <c r="E193">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F193">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G193">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="H193" t="str">
-        <v>古铜双鱼.png</v>
+        <v>国王之泪.png</v>
       </c>
       <c r="I193" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>gtmj_xz_3</v>
+        <v>gtsy_xz_3</v>
       </c>
       <c r="B194" t="str">
         <v>配件</v>
@@ -6007,7 +6007,7 @@
         <v>星座</v>
       </c>
       <c r="D194" t="str">
-        <v>古銅摩羯</v>
+        <v>古銅雙魚</v>
       </c>
       <c r="E194">
         <v>3</v>
@@ -6019,7 +6019,7 @@
         <v>39</v>
       </c>
       <c r="H194" t="str">
-        <v>古铜摩羯.png</v>
+        <v>古铜双鱼.png</v>
       </c>
       <c r="I194" t="str">
         <v>義烏市唐人印象</v>
@@ -6027,7 +6027,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>gtss_xz_3</v>
+        <v>gtmj_xz_3</v>
       </c>
       <c r="B195" t="str">
         <v>配件</v>
@@ -6036,7 +6036,7 @@
         <v>星座</v>
       </c>
       <c r="D195" t="str">
-        <v>古銅射手</v>
+        <v>古銅摩羯</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -6048,7 +6048,7 @@
         <v>39</v>
       </c>
       <c r="H195" t="str">
-        <v>古铜射手.png</v>
+        <v>古铜摩羯.png</v>
       </c>
       <c r="I195" t="str">
         <v>義烏市唐人印象</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>gtjn_xz_3</v>
+        <v>gtss_xz_3</v>
       </c>
       <c r="B196" t="str">
         <v>配件</v>
@@ -6065,7 +6065,7 @@
         <v>星座</v>
       </c>
       <c r="D196" t="str">
-        <v>古銅金牛</v>
+        <v>古銅射手</v>
       </c>
       <c r="E196">
         <v>3</v>
@@ -6077,7 +6077,7 @@
         <v>39</v>
       </c>
       <c r="H196" t="str">
-        <v>古铜金牛.png</v>
+        <v>古铜射手.png</v>
       </c>
       <c r="I196" t="str">
         <v>義烏市唐人印象</v>
@@ -6085,36 +6085,36 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>zfj_cysl_8</v>
+        <v>gtjn_xz_3</v>
       </c>
       <c r="B197" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C197" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D197" t="str">
-        <v>紫粉晶</v>
+        <v>古銅金牛</v>
       </c>
       <c r="E197">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F197">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G197">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H197" t="str">
-        <v>紫粉晶.png</v>
+        <v>古铜金牛.png</v>
       </c>
       <c r="I197" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>zfj_cysl_10</v>
+        <v>zfj_cysl_8</v>
       </c>
       <c r="B198" t="str">
         <v>珠子</v>
@@ -6126,13 +6126,13 @@
         <v>紫粉晶</v>
       </c>
       <c r="E198">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F198">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G198">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H198" t="str">
         <v>紫粉晶.png</v>
@@ -6143,94 +6143,94 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>gttx_xz_3</v>
+        <v>zfj_cysl_10</v>
       </c>
       <c r="B199" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C199" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D199" t="str">
-        <v>古銅天蠍</v>
+        <v>紫粉晶</v>
       </c>
       <c r="E199">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F199">
         <v>10</v>
       </c>
       <c r="G199">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="H199" t="str">
-        <v>古铜天蝎.png</v>
+        <v>紫粉晶.png</v>
       </c>
       <c r="I199" t="str">
-        <v>義烏市唐人印象</v>
+        <v/>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>jslzzy_spc_9</v>
+        <v>gttx_xz_3</v>
       </c>
       <c r="B200" t="str">
         <v>配件</v>
       </c>
       <c r="C200" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D200" t="str">
-        <v>金六字箴言</v>
+        <v>古銅天蠍</v>
       </c>
       <c r="E200">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F200">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G200">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H200" t="str">
-        <v>金六字箴言.png</v>
+        <v>古铜天蝎.png</v>
       </c>
       <c r="I200" t="str">
-        <v>義烏市亦蝶</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>cmj_cysl_6</v>
+        <v>jslzzy_spc_9</v>
       </c>
       <c r="B201" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C201" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D201" t="str">
-        <v>草莓晶</v>
+        <v>金六字箴言</v>
       </c>
       <c r="E201">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F201">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G201">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H201" t="str">
-        <v>草莓晶.png</v>
+        <v>金六字箴言.png</v>
       </c>
       <c r="I201" t="str">
-        <v/>
+        <v>義烏市亦蝶</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>cmj_cysl_8</v>
+        <v>cmj_cysl_6</v>
       </c>
       <c r="B202" t="str">
         <v>珠子</v>
@@ -6242,13 +6242,13 @@
         <v>草莓晶</v>
       </c>
       <c r="E202">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F202">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G202">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H202" t="str">
         <v>草莓晶.png</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>cmj_cysl_10</v>
+        <v>cmj_cysl_8</v>
       </c>
       <c r="B203" t="str">
         <v>珠子</v>
@@ -6271,13 +6271,13 @@
         <v>草莓晶</v>
       </c>
       <c r="E203">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F203">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G203">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H203" t="str">
         <v>草莓晶.png</v>
@@ -6288,31 +6288,31 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>tg1_sz_7</v>
+        <v>cmj_cysl_10</v>
       </c>
       <c r="B204" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C204" t="str">
-        <v>數字</v>
+        <v>水晶</v>
       </c>
       <c r="D204" t="str">
-        <v>鈦鋼1</v>
+        <v>草莓晶</v>
       </c>
       <c r="E204">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F204">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G204">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H204" t="str">
-        <v>钛钢1.png</v>
+        <v>草莓晶.png</v>
       </c>
       <c r="I204" t="str">
-        <v>東莞晞亞</v>
+        <v/>
       </c>
     </row>
     <row r="205">

--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -3861,7 +3861,7 @@
         <v>隔珠</v>
       </c>
       <c r="D120" t="str">
-        <v>藏銀繡球鋯石細閃</v>
+        <v>鋯石細閃</v>
       </c>
       <c r="E120">
         <v>3</v>
@@ -3873,7 +3873,7 @@
         <v>129</v>
       </c>
       <c r="H120" t="str">
-        <v>藏银绣球锆石细闪.png</v>
+        <v>锆石细闪.png</v>
       </c>
       <c r="I120" t="str">
         <v>義烏市硯鈺</v>

--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I259"/>
+  <dimension ref="A1:I258"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,36 +517,36 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>tg1_sz_7</v>
+        <v>xhyl_cysl_6</v>
       </c>
       <c r="B5" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C5" t="str">
-        <v>數字</v>
+        <v>水晶</v>
       </c>
       <c r="D5" t="str">
-        <v>鈦鋼1</v>
+        <v>雪花幽靈</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>59</v>
       </c>
       <c r="H5" t="str">
-        <v>钛钢1.png</v>
+        <v>雪花幽灵.png</v>
       </c>
       <c r="I5" t="str">
-        <v>東莞晞亞</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>xhyl_cysl_6</v>
+        <v>xhyl_cysl_8</v>
       </c>
       <c r="B6" t="str">
         <v>珠子</v>
@@ -558,13 +558,13 @@
         <v>雪花幽靈</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H6" t="str">
         <v>雪花幽灵.png</v>
@@ -575,7 +575,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>xhyl_cysl_8</v>
+        <v>xhyl_cysl_10</v>
       </c>
       <c r="B7" t="str">
         <v>珠子</v>
@@ -587,13 +587,13 @@
         <v>雪花幽靈</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="H7" t="str">
         <v>雪花幽灵.png</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>xhyl_cysl_10</v>
+        <v>byl_cysl_8</v>
       </c>
       <c r="B8" t="str">
         <v>珠子</v>
@@ -613,19 +613,19 @@
         <v>水晶</v>
       </c>
       <c r="D8" t="str">
-        <v>雪花幽靈</v>
+        <v>白幽靈</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="H8" t="str">
-        <v>雪花幽灵.png</v>
+        <v>白幽灵.png</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -633,28 +633,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>byl_cysl_8</v>
+        <v>dszzhu_prl_6</v>
       </c>
       <c r="B9" t="str">
         <v>珠子</v>
       </c>
       <c r="C9" t="str">
-        <v>水晶</v>
+        <v>珍珠</v>
       </c>
       <c r="D9" t="str">
-        <v>白幽靈</v>
+        <v>淡水珍珠</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H9" t="str">
-        <v>白幽灵.png</v>
+        <v>淡水珍珠.png</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -662,7 +662,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>dszzhu_prl_6</v>
+        <v>dszzhu_prl_8</v>
       </c>
       <c r="B10" t="str">
         <v>珠子</v>
@@ -674,13 +674,13 @@
         <v>淡水珍珠</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="H10" t="str">
         <v>淡水珍珠.png</v>
@@ -691,7 +691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>dszzhu_prl_8</v>
+        <v>dszzhu_prl_10</v>
       </c>
       <c r="B11" t="str">
         <v>珠子</v>
@@ -703,13 +703,13 @@
         <v>淡水珍珠</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="H11" t="str">
         <v>淡水珍珠.png</v>
@@ -720,28 +720,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>dszzhu_prl_10</v>
+        <v>nbj_cysl_8</v>
       </c>
       <c r="B12" t="str">
         <v>珠子</v>
       </c>
       <c r="C12" t="str">
-        <v>珍珠</v>
+        <v>水晶</v>
       </c>
       <c r="D12" t="str">
-        <v>淡水珍珠</v>
+        <v>奶白晶</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G12">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="H12" t="str">
-        <v>淡水珍珠.png</v>
+        <v>奶白晶.png</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -749,7 +749,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>nbj_cysl_8</v>
+        <v>nbj_cysl_10</v>
       </c>
       <c r="B13" t="str">
         <v>珠子</v>
@@ -761,13 +761,13 @@
         <v>奶白晶</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H13" t="str">
         <v>奶白晶.png</v>
@@ -778,28 +778,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>nbj_cysl_10</v>
+        <v>pts_stn_6</v>
       </c>
       <c r="B14" t="str">
         <v>珠子</v>
       </c>
       <c r="C14" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D14" t="str">
-        <v>奶白晶</v>
+        <v>葡萄石</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="H14" t="str">
-        <v>奶白晶.png</v>
+        <v>葡萄石.png</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -807,7 +807,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>pts_stn_6</v>
+        <v>pts_stn_10</v>
       </c>
       <c r="B15" t="str">
         <v>珠子</v>
@@ -819,13 +819,13 @@
         <v>葡萄石</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H15" t="str">
         <v>葡萄石.png</v>
@@ -836,36 +836,36 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>pts_stn_10</v>
+        <v>mxxx_pnd_2</v>
       </c>
       <c r="B16" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C16" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D16" t="str">
-        <v>葡萄石</v>
+        <v>滿鑲星星</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G16">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H16" t="str">
-        <v>葡萄石.png</v>
+        <v>满镶星星.png</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mxxx_pnd_2</v>
+        <v>pl_pnd_5</v>
       </c>
       <c r="B17" t="str">
         <v>配件</v>
@@ -874,27 +874,27 @@
         <v>吊墜</v>
       </c>
       <c r="D17" t="str">
-        <v>滿鑲星星</v>
+        <v>霹靂</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>20</v>
       </c>
       <c r="G17">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H17" t="str">
-        <v>满镶星星.png</v>
+        <v>霹雳.png</v>
       </c>
       <c r="I17" t="str">
-        <v>廣州市嘉鈺</v>
+        <v>義烏市眾帆</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>pl_pnd_5</v>
+        <v>axqbz_pnd_2</v>
       </c>
       <c r="B18" t="str">
         <v>配件</v>
@@ -903,56 +903,56 @@
         <v>吊墜</v>
       </c>
       <c r="D18" t="str">
-        <v>霹靂</v>
+        <v>愛心曲別針</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G18">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H18" t="str">
-        <v>霹雳.png</v>
+        <v>爱心曲别针.png</v>
       </c>
       <c r="I18" t="str">
-        <v>義烏市眾帆</v>
+        <v>義烏市爆財</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>axqbz_pnd_2</v>
+        <v>xgfj_cysl_6</v>
       </c>
       <c r="B19" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C19" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D19" t="str">
-        <v>愛心曲別針</v>
+        <v>星光粉晶</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H19" t="str">
-        <v>爱心曲别针.png</v>
+        <v>星光粉晶.png</v>
       </c>
       <c r="I19" t="str">
-        <v>義烏市爆財</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>xgfj_cysl_6</v>
+        <v>xgfj_cysl_8</v>
       </c>
       <c r="B20" t="str">
         <v>珠子</v>
@@ -964,13 +964,13 @@
         <v>星光粉晶</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G20">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H20" t="str">
         <v>星光粉晶.png</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>xgfj_cysl_8</v>
+        <v>xgfj_cysl_10</v>
       </c>
       <c r="B21" t="str">
         <v>珠子</v>
@@ -993,13 +993,13 @@
         <v>星光粉晶</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H21" t="str">
         <v>星光粉晶.png</v>
@@ -1010,28 +1010,28 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>xgfj_cysl_10</v>
+        <v>by_agt_6</v>
       </c>
       <c r="B22" t="str">
         <v>珠子</v>
       </c>
       <c r="C22" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D22" t="str">
-        <v>星光粉晶</v>
+        <v>白玉髓</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H22" t="str">
-        <v>星光粉晶.png</v>
+        <v>白玉髓.png</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>by_agt_6</v>
+        <v>by_agt_8</v>
       </c>
       <c r="B23" t="str">
         <v>珠子</v>
@@ -1051,13 +1051,13 @@
         <v>白玉髓</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G23">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H23" t="str">
         <v>白玉髓.png</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>by_agt_8</v>
+        <v>by_agt_10</v>
       </c>
       <c r="B24" t="str">
         <v>珠子</v>
@@ -1080,13 +1080,13 @@
         <v>白玉髓</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H24" t="str">
         <v>白玉髓.png</v>
@@ -1097,28 +1097,28 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>by_agt_10</v>
+        <v>zlh_cysl_6</v>
       </c>
       <c r="B25" t="str">
         <v>珠子</v>
       </c>
       <c r="C25" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D25" t="str">
-        <v>白玉髓</v>
+        <v>紫鋰輝</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>89</v>
       </c>
       <c r="H25" t="str">
-        <v>白玉髓.png</v>
+        <v>紫锂辉.png</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>zlh_cysl_6</v>
+        <v>zlh_cysl_8</v>
       </c>
       <c r="B26" t="str">
         <v>珠子</v>
@@ -1138,13 +1138,13 @@
         <v>紫鋰輝</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="H26" t="str">
         <v>紫锂辉.png</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>zlh_cysl_8</v>
+        <v>zlh_cysl_10</v>
       </c>
       <c r="B27" t="str">
         <v>珠子</v>
@@ -1167,13 +1167,13 @@
         <v>紫鋰輝</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="H27" t="str">
         <v>紫锂辉.png</v>
@@ -1184,65 +1184,65 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>zlh_cysl_10</v>
+        <v>lglf_spc_8</v>
       </c>
       <c r="B28" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C28" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D28" t="str">
-        <v>紫鋰輝</v>
+        <v>菱格立方</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G28">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="H28" t="str">
-        <v>紫锂辉.png</v>
+        <v>菱格立方.png</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>廣州市荔灣區金嶠旭</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lglf_spc_8</v>
+        <v>fsj_cysl_6</v>
       </c>
       <c r="B29" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C29" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D29" t="str">
-        <v>菱格立方</v>
+        <v>粉水晶</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H29" t="str">
-        <v>菱格立方.png</v>
+        <v>粉水晶.png</v>
       </c>
       <c r="I29" t="str">
-        <v>廣州市荔灣區金嶠旭</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>fsj_cysl_6</v>
+        <v>fsj_cysl_8</v>
       </c>
       <c r="B30" t="str">
         <v>珠子</v>
@@ -1254,13 +1254,13 @@
         <v>粉水晶</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G30">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H30" t="str">
         <v>粉水晶.png</v>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>fsj_cysl_8</v>
+        <v>fsj_cysl_10</v>
       </c>
       <c r="B31" t="str">
         <v>珠子</v>
@@ -1283,13 +1283,13 @@
         <v>粉水晶</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H31" t="str">
         <v>粉水晶.png</v>
@@ -1300,36 +1300,36 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>fsj_cysl_10</v>
+        <v>ysmxyl_pnd_2</v>
       </c>
       <c r="B32" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C32" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D32" t="str">
-        <v>粉水晶</v>
+        <v>滿鑲月亮</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F32">
         <v>10</v>
       </c>
       <c r="G32">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H32" t="str">
-        <v>粉水晶.png</v>
+        <v>满镶月亮.png</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ysmxyl_pnd_2</v>
+        <v>lkjf_pnd_2</v>
       </c>
       <c r="B33" t="str">
         <v>配件</v>
@@ -1338,56 +1338,56 @@
         <v>吊墜</v>
       </c>
       <c r="D33" t="str">
-        <v>滿鑲月亮</v>
+        <v>鏤空金福</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G33">
-        <v>69</v>
+        <v>599</v>
       </c>
       <c r="H33" t="str">
-        <v>满镶月亮.png</v>
+        <v>镂空金福.png</v>
       </c>
       <c r="I33" t="str">
-        <v>廣州銅品彙</v>
+        <v>廣州市荔灣區嘉明銀飾</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lkjf_pnd_2</v>
+        <v>bas_cysl_8</v>
       </c>
       <c r="B34" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C34" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D34" t="str">
-        <v>鏤空金福</v>
+        <v>白阿塞</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G34">
-        <v>599</v>
+        <v>69</v>
       </c>
       <c r="H34" t="str">
-        <v>镂空金福.png</v>
+        <v>白阿塞.png</v>
       </c>
       <c r="I34" t="str">
-        <v>廣州市荔灣區嘉明銀飾</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>bas_cysl_8</v>
+        <v>bas_cysl_10</v>
       </c>
       <c r="B35" t="str">
         <v>珠子</v>
@@ -1399,13 +1399,13 @@
         <v>白阿塞</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G35">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H35" t="str">
         <v>白阿塞.png</v>
@@ -1416,28 +1416,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>bas_cysl_10</v>
+        <v>nyhlb_stn_6</v>
       </c>
       <c r="B36" t="str">
         <v>珠子</v>
       </c>
       <c r="C36" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D36" t="str">
-        <v>白阿塞</v>
+        <v>奶油海藍寶</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G36">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H36" t="str">
-        <v>白阿塞.png</v>
+        <v>奶油海蓝宝.png</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>nyhlb_stn_6</v>
+        <v>nyhlb_stn_8</v>
       </c>
       <c r="B37" t="str">
         <v>珠子</v>
@@ -1457,13 +1457,13 @@
         <v>奶油海藍寶</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G37">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H37" t="str">
         <v>奶油海蓝宝.png</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>nyhlb_stn_8</v>
+        <v>nyhlb_stn_10</v>
       </c>
       <c r="B38" t="str">
         <v>珠子</v>
@@ -1486,13 +1486,13 @@
         <v>奶油海藍寶</v>
       </c>
       <c r="E38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G38">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="H38" t="str">
         <v>奶油海蓝宝.png</v>
@@ -1503,28 +1503,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>nyhlb_stn_10</v>
+        <v>zys_agt_6</v>
       </c>
       <c r="B39" t="str">
         <v>珠子</v>
       </c>
       <c r="C39" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D39" t="str">
-        <v>奶油海藍寶</v>
+        <v>紫玉髓</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G39">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="H39" t="str">
-        <v>奶油海蓝宝.png</v>
+        <v>紫玉髓.png</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>zys_agt_6</v>
+        <v>zys_agt_8</v>
       </c>
       <c r="B40" t="str">
         <v>珠子</v>
@@ -1544,13 +1544,13 @@
         <v>紫玉髓</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G40">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H40" t="str">
         <v>紫玉髓.png</v>
@@ -1561,28 +1561,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>zys_agt_8</v>
+        <v>hws_stn_6</v>
       </c>
       <c r="B41" t="str">
         <v>珠子</v>
       </c>
       <c r="C41" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D41" t="str">
-        <v>紫玉髓</v>
+        <v>海紋石</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H41" t="str">
-        <v>紫玉髓.png</v>
+        <v>海纹石.png</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>hws_stn_6</v>
+        <v>hws_stn_8</v>
       </c>
       <c r="B42" t="str">
         <v>珠子</v>
@@ -1602,13 +1602,13 @@
         <v>海紋石</v>
       </c>
       <c r="E42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G42">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H42" t="str">
         <v>海纹石.png</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>hws_stn_8</v>
+        <v>hws_stn_10</v>
       </c>
       <c r="B43" t="str">
         <v>珠子</v>
@@ -1631,13 +1631,13 @@
         <v>海紋石</v>
       </c>
       <c r="E43">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F43">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G43">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="H43" t="str">
         <v>海纹石.png</v>
@@ -1648,28 +1648,28 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>hws_stn_10</v>
+        <v>jfj_cysl_6</v>
       </c>
       <c r="B44" t="str">
         <v>珠子</v>
       </c>
       <c r="C44" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D44" t="str">
-        <v>海紋石</v>
+        <v>金髮晶</v>
       </c>
       <c r="E44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="H44" t="str">
-        <v>海纹石.png</v>
+        <v>金发晶.png</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>jfj_cysl_6</v>
+        <v>jfj_cysl_8</v>
       </c>
       <c r="B45" t="str">
         <v>珠子</v>
@@ -1689,13 +1689,13 @@
         <v>金髮晶</v>
       </c>
       <c r="E45">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G45">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H45" t="str">
         <v>金发晶.png</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>jfj_cysl_8</v>
+        <v>jfj_cysl_10</v>
       </c>
       <c r="B46" t="str">
         <v>珠子</v>
@@ -1718,13 +1718,13 @@
         <v>金髮晶</v>
       </c>
       <c r="E46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G46">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H46" t="str">
         <v>金发晶.png</v>
@@ -1735,94 +1735,94 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>jfj_cysl_10</v>
+        <v>bsyw_pnd_2</v>
       </c>
       <c r="B47" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C47" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D47" t="str">
-        <v>金髮晶</v>
+        <v>白水魚尾</v>
       </c>
       <c r="E47">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F47">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G47">
-        <v>99</v>
+        <v>699</v>
       </c>
       <c r="H47" t="str">
-        <v>金发晶.png</v>
+        <v>白水鱼尾.png</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>廣州市荔灣區嘉明</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>bsyw_pnd_2</v>
+        <v>zyb_spc_6</v>
       </c>
       <c r="B48" t="str">
         <v>配件</v>
       </c>
       <c r="C48" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D48" t="str">
-        <v>白水魚尾</v>
+        <v>轉運柄</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F48">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G48">
-        <v>699</v>
+        <v>399</v>
       </c>
       <c r="H48" t="str">
-        <v>白水鱼尾.png</v>
+        <v>转运柄.png</v>
       </c>
       <c r="I48" t="str">
-        <v>廣州市荔灣區嘉明</v>
+        <v>莆田市秀嶼區東嶠寶鑫格</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>zyb_spc_6</v>
+        <v>lwmn_agt_6</v>
       </c>
       <c r="B49" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C49" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D49" t="str">
-        <v>轉運柄</v>
+        <v>藍紋瑪瑙</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
       <c r="F49">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="H49" t="str">
-        <v>转运柄.png</v>
+        <v>蓝纹玛瑙.png</v>
       </c>
       <c r="I49" t="str">
-        <v>莆田市秀嶼區東嶠寶鑫格</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>lwmn_agt_6</v>
+        <v>lwmn_agt_8</v>
       </c>
       <c r="B50" t="str">
         <v>珠子</v>
@@ -1834,13 +1834,13 @@
         <v>藍紋瑪瑙</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G50">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H50" t="str">
         <v>蓝纹玛瑙.png</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>lwmn_agt_8</v>
+        <v>lwmn_agt_10</v>
       </c>
       <c r="B51" t="str">
         <v>珠子</v>
@@ -1863,13 +1863,13 @@
         <v>藍紋瑪瑙</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G51">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="H51" t="str">
         <v>蓝纹玛瑙.png</v>
@@ -1880,28 +1880,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>lwmn_agt_10</v>
+        <v>xyc_cysl_8</v>
       </c>
       <c r="B52" t="str">
         <v>珠子</v>
       </c>
       <c r="C52" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D52" t="str">
-        <v>藍紋瑪瑙</v>
+        <v>薰衣草</v>
       </c>
       <c r="E52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F52">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G52">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="H52" t="str">
-        <v>蓝纹玛瑙.png</v>
+        <v>薰衣草.png</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>xyc_cysl_8</v>
+        <v>xyc_cysl_10</v>
       </c>
       <c r="B53" t="str">
         <v>珠子</v>
@@ -1921,13 +1921,13 @@
         <v>薰衣草</v>
       </c>
       <c r="E53">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F53">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G53">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="H53" t="str">
         <v>薰衣草.png</v>
@@ -1938,36 +1938,36 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>xyc_cysl_10</v>
+        <v>fyh_spc_12</v>
       </c>
       <c r="B54" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C54" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D54" t="str">
-        <v>薰衣草</v>
+        <v>粉櫻花</v>
       </c>
       <c r="E54">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F54">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G54">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="H54" t="str">
-        <v>薰衣草.png</v>
+        <v>粉樱花.png</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>義烏市聚飾優</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>fyh_spc_12</v>
+        <v>gshxz_spc_10</v>
       </c>
       <c r="B55" t="str">
         <v>配件</v>
@@ -1976,27 +1976,27 @@
         <v>隔珠</v>
       </c>
       <c r="D55" t="str">
-        <v>粉櫻花</v>
+        <v>鋯石花形鑽</v>
       </c>
       <c r="E55">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F55">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G55">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H55" t="str">
-        <v>粉樱花.png</v>
+        <v>锆石花形钻.png</v>
       </c>
       <c r="I55" t="str">
-        <v>義烏市聚飾優</v>
+        <v>義烏市闊乘</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>gshxz_spc_10</v>
+        <v>gsqg_spc_5</v>
       </c>
       <c r="B56" t="str">
         <v>配件</v>
@@ -2005,56 +2005,56 @@
         <v>隔珠</v>
       </c>
       <c r="D56" t="str">
-        <v>鋯石花形鑽</v>
+        <v>鋯石切割</v>
       </c>
       <c r="E56">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F56">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G56">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="H56" t="str">
-        <v>锆石花形钻.png</v>
+        <v>锆石切割.png</v>
       </c>
       <c r="I56" t="str">
-        <v>義烏市闊乘</v>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>gsqg_spc_5</v>
+        <v>hsj_cysl_6</v>
       </c>
       <c r="B57" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C57" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D57" t="str">
-        <v>鋯石切割</v>
+        <v>黃水晶</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G57">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="H57" t="str">
-        <v>锆石切割.png</v>
+        <v>黄水晶.png</v>
       </c>
       <c r="I57" t="str">
-        <v>義烏市硯鈺</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>hsj_cysl_6</v>
+        <v>hsj_cysl_8</v>
       </c>
       <c r="B58" t="str">
         <v>珠子</v>
@@ -2066,13 +2066,13 @@
         <v>黃水晶</v>
       </c>
       <c r="E58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G58">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H58" t="str">
         <v>黄水晶.png</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>hsj_cysl_8</v>
+        <v>hsj_cysl_10</v>
       </c>
       <c r="B59" t="str">
         <v>珠子</v>
@@ -2095,13 +2095,13 @@
         <v>黃水晶</v>
       </c>
       <c r="E59">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F59">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G59">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H59" t="str">
         <v>黄水晶.png</v>
@@ -2112,123 +2112,123 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>hsj_cysl_10</v>
+        <v>jzj_spc_4</v>
       </c>
       <c r="B60" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C60" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D60" t="str">
-        <v>黃水晶</v>
+        <v>交織戒</v>
       </c>
       <c r="E60">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G60">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H60" t="str">
-        <v>黄水晶.png</v>
+        <v>交织戒.png</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>廣州市弘達</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>jzj_spc_4</v>
+        <v>gscx_pnd_2</v>
       </c>
       <c r="B61" t="str">
         <v>配件</v>
       </c>
       <c r="C61" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D61" t="str">
-        <v>交織戒</v>
+        <v>鋯石晨星</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G61">
         <v>69</v>
       </c>
       <c r="H61" t="str">
-        <v>交织戒.png</v>
+        <v>锆石晨星.png</v>
       </c>
       <c r="I61" t="str">
-        <v>廣州市弘達</v>
+        <v>義烏市適旗</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>gscx_pnd_2</v>
+        <v>tg4_sz_7</v>
       </c>
       <c r="B62" t="str">
         <v>配件</v>
       </c>
       <c r="C62" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D62" t="str">
-        <v>鋯石晨星</v>
+        <v>鈦鋼4</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F62">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G62">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H62" t="str">
-        <v>锆石晨星.png</v>
+        <v>钛钢4.png</v>
       </c>
       <c r="I62" t="str">
-        <v>義烏市適旗</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>tg4_sz_7</v>
+        <v>cyszj_spc_13</v>
       </c>
       <c r="B63" t="str">
         <v>配件</v>
       </c>
       <c r="C63" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D63" t="str">
-        <v>鈦鋼4</v>
+        <v>藏銀十字架</v>
       </c>
       <c r="E63">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G63">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H63" t="str">
-        <v>钛钢4.png</v>
+        <v>藏银十字架.png</v>
       </c>
       <c r="I63" t="str">
-        <v>東莞晞亞</v>
+        <v>義烏市尋意</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>cyszj_spc_13</v>
+        <v>ysxh_spc_2</v>
       </c>
       <c r="B64" t="str">
         <v>配件</v>
@@ -2237,94 +2237,94 @@
         <v>隔珠</v>
       </c>
       <c r="D64" t="str">
-        <v>藏銀十字架</v>
+        <v>銀色小環</v>
       </c>
       <c r="E64">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H64" t="str">
-        <v>藏银十字架.png</v>
+        <v>银色小环.png</v>
       </c>
       <c r="I64" t="str">
-        <v>義烏市尋意</v>
+        <v>廣州鑫鈺</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ysxh_spc_2</v>
+        <v>tg9_sz_7</v>
       </c>
       <c r="B65" t="str">
         <v>配件</v>
       </c>
       <c r="C65" t="str">
-        <v>隔珠</v>
+        <v>數字</v>
       </c>
       <c r="D65" t="str">
-        <v>銀色小環</v>
+        <v>鈦鋼9</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G65">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H65" t="str">
-        <v>银色小环.png</v>
+        <v>钛钢9.png</v>
       </c>
       <c r="I65" t="str">
-        <v>廣州鑫鈺</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>tg9_sz_7</v>
+        <v>gh_spc_6</v>
       </c>
       <c r="B66" t="str">
         <v>配件</v>
       </c>
       <c r="C66" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D66" t="str">
-        <v>鈦鋼9</v>
+        <v>桂花</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G66">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H66" t="str">
-        <v>钛钢9.png</v>
+        <v>桂花.png</v>
       </c>
       <c r="I66" t="str">
-        <v>東莞晞亞</v>
+        <v>廣州嘉鈺</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>gh_spc_6</v>
+        <v>hm_agt_6</v>
       </c>
       <c r="B67" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C67" t="str">
-        <v>隔珠</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D67" t="str">
-        <v>桂花</v>
+        <v>黃瑪瑙</v>
       </c>
       <c r="E67">
         <v>6</v>
@@ -2333,18 +2333,18 @@
         <v>6</v>
       </c>
       <c r="G67">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H67" t="str">
-        <v>桂花.png</v>
+        <v>黄玛瑙.png</v>
       </c>
       <c r="I67" t="str">
-        <v>廣州嘉鈺</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>hm_agt_6</v>
+        <v>hm_agt_8</v>
       </c>
       <c r="B68" t="str">
         <v>珠子</v>
@@ -2356,13 +2356,13 @@
         <v>黃瑪瑙</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G68">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H68" t="str">
         <v>黄玛瑙.png</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>hm_agt_8</v>
+        <v>hm_agt_10</v>
       </c>
       <c r="B69" t="str">
         <v>珠子</v>
@@ -2385,13 +2385,13 @@
         <v>黃瑪瑙</v>
       </c>
       <c r="E69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F69">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G69">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H69" t="str">
         <v>黄玛瑙.png</v>
@@ -2402,28 +2402,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>hm_agt_10</v>
+        <v>ml_stn_6</v>
       </c>
       <c r="B70" t="str">
         <v>珠子</v>
       </c>
       <c r="C70" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D70" t="str">
-        <v>黃瑪瑙</v>
+        <v>蜜蠟</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F70">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G70">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H70" t="str">
-        <v>黄玛瑙.png</v>
+        <v>蜜蜡.png</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ml_stn_6</v>
+        <v>ml_stn_8</v>
       </c>
       <c r="B71" t="str">
         <v>珠子</v>
@@ -2443,13 +2443,13 @@
         <v>蜜蠟</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F71">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G71">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H71" t="str">
         <v>蜜蜡.png</v>
@@ -2460,297 +2460,297 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ml_stn_8</v>
+        <v>ysr_zm_4</v>
       </c>
       <c r="B72" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C72" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D72" t="str">
-        <v>蜜蠟</v>
+        <v>銀飾R</v>
       </c>
       <c r="E72">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F72">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G72">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="H72" t="str">
-        <v>蜜蜡.png</v>
+        <v>银饰R.png</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ysr_zm_4</v>
+        <v>jd_pnd_2</v>
       </c>
       <c r="B73" t="str">
         <v>配件</v>
       </c>
       <c r="C73" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D73" t="str">
-        <v>銀飾R</v>
+        <v>晶蝶</v>
       </c>
       <c r="E73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G73">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="H73" t="str">
-        <v>银饰R.png</v>
+        <v>晶蝶.png</v>
       </c>
       <c r="I73" t="str">
-        <v>廣州市德潤</v>
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>jd_pnd_2</v>
+        <v>tg7_sz_7</v>
       </c>
       <c r="B74" t="str">
         <v>配件</v>
       </c>
       <c r="C74" t="str">
-        <v>吊墜</v>
+        <v>數字</v>
       </c>
       <c r="D74" t="str">
-        <v>晶蝶</v>
+        <v>鈦鋼7</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F74">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G74">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H74" t="str">
-        <v>晶蝶.png</v>
+        <v>钛钢7.png</v>
       </c>
       <c r="I74" t="str">
-        <v>廣州市嘉鈺</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>tg7_sz_7</v>
+        <v>jpts_stn_8</v>
       </c>
       <c r="B75" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C75" t="str">
-        <v>數字</v>
+        <v>礦石</v>
       </c>
       <c r="D75" t="str">
-        <v>鈦鋼7</v>
+        <v>金葡萄石</v>
       </c>
       <c r="E75">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F75">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G75">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H75" t="str">
-        <v>钛钢7.png</v>
+        <v>金葡萄石.png</v>
       </c>
       <c r="I75" t="str">
-        <v>東莞晞亞</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>jpts_stn_8</v>
+        <v>gymj_xz_3</v>
       </c>
       <c r="B76" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C76" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D76" t="str">
-        <v>金葡萄石</v>
+        <v>古銀摩羯</v>
       </c>
       <c r="E76">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G76">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H76" t="str">
-        <v>金葡萄石.png</v>
+        <v>古银摩羯.png</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>gymj_xz_3</v>
+        <v>tg0_sz_7</v>
       </c>
       <c r="B77" t="str">
         <v>配件</v>
       </c>
       <c r="C77" t="str">
-        <v>星座</v>
+        <v>數字</v>
       </c>
       <c r="D77" t="str">
-        <v>古銀摩羯</v>
+        <v>鈦鋼0</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F77">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G77">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H77" t="str">
-        <v>古银摩羯.png</v>
+        <v>钛钢0.png</v>
       </c>
       <c r="I77" t="str">
-        <v>義烏市唐人印象</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>tg0_sz_7</v>
+        <v>jf_pnd_2</v>
       </c>
       <c r="B78" t="str">
         <v>配件</v>
       </c>
       <c r="C78" t="str">
-        <v>數字</v>
+        <v>吊墜</v>
       </c>
       <c r="D78" t="str">
-        <v>鈦鋼0</v>
+        <v>金福</v>
       </c>
       <c r="E78">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G78">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H78" t="str">
-        <v>钛钢0.png</v>
+        <v>金福.png</v>
       </c>
       <c r="I78" t="str">
-        <v>東莞晞亞</v>
+        <v>義烏市曉磊</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>jf_pnd_2</v>
+        <v>ysj_zm_4</v>
       </c>
       <c r="B79" t="str">
         <v>配件</v>
       </c>
       <c r="C79" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D79" t="str">
-        <v>金福</v>
+        <v>銀飾J</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F79">
         <v>10</v>
       </c>
       <c r="G79">
-        <v>49</v>
+        <v>399</v>
       </c>
       <c r="H79" t="str">
-        <v>金福.png</v>
+        <v>银饰J.png</v>
       </c>
       <c r="I79" t="str">
-        <v>義烏市曉磊</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>ysj_zm_4</v>
+        <v>tg6_sz_7</v>
       </c>
       <c r="B80" t="str">
         <v>配件</v>
       </c>
       <c r="C80" t="str">
-        <v>字母</v>
+        <v>數字</v>
       </c>
       <c r="D80" t="str">
-        <v>銀飾J</v>
+        <v>鈦鋼6</v>
       </c>
       <c r="E80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F80">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G80">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="H80" t="str">
-        <v>银饰J.png</v>
+        <v>钛钢6.png</v>
       </c>
       <c r="I80" t="str">
-        <v>廣州市德潤</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>tg6_sz_7</v>
+        <v>xxy_spc_2</v>
       </c>
       <c r="B81" t="str">
         <v>配件</v>
       </c>
       <c r="C81" t="str">
-        <v>數字</v>
+        <v>隔珠</v>
       </c>
       <c r="D81" t="str">
-        <v>鈦鋼6</v>
+        <v>小祥雲</v>
       </c>
       <c r="E81">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F81">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G81">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H81" t="str">
-        <v>钛钢6.png</v>
+        <v>小祥云.png</v>
       </c>
       <c r="I81" t="str">
-        <v>東莞晞亞</v>
+        <v>廣州璐悠</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>xxy_spc_2</v>
+        <v>dxy_spc_3</v>
       </c>
       <c r="B82" t="str">
         <v>配件</v>
@@ -2759,19 +2759,19 @@
         <v>隔珠</v>
       </c>
       <c r="D82" t="str">
-        <v>小祥雲</v>
+        <v>大祥雲</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G82">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H82" t="str">
-        <v>小祥云.png</v>
+        <v>大祥云.png</v>
       </c>
       <c r="I82" t="str">
         <v>廣州璐悠</v>
@@ -2779,36 +2779,36 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>dxy_spc_3</v>
+        <v>ysi_zm_4</v>
       </c>
       <c r="B83" t="str">
         <v>配件</v>
       </c>
       <c r="C83" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D83" t="str">
-        <v>大祥雲</v>
+        <v>銀飾I</v>
       </c>
       <c r="E83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F83">
         <v>10</v>
       </c>
       <c r="G83">
-        <v>99</v>
+        <v>399</v>
       </c>
       <c r="H83" t="str">
-        <v>大祥云.png</v>
+        <v>银饰I.png</v>
       </c>
       <c r="I83" t="str">
-        <v>廣州璐悠</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ysi_zm_4</v>
+        <v>ysu_zm_4</v>
       </c>
       <c r="B84" t="str">
         <v>配件</v>
@@ -2817,7 +2817,7 @@
         <v>字母</v>
       </c>
       <c r="D84" t="str">
-        <v>銀飾I</v>
+        <v>銀飾U</v>
       </c>
       <c r="E84">
         <v>4</v>
@@ -2829,7 +2829,7 @@
         <v>399</v>
       </c>
       <c r="H84" t="str">
-        <v>银饰I.png</v>
+        <v>银饰U.png</v>
       </c>
       <c r="I84" t="str">
         <v>廣州市德潤</v>
@@ -2837,36 +2837,36 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ysu_zm_4</v>
+        <v>tg3_sz_7</v>
       </c>
       <c r="B85" t="str">
         <v>配件</v>
       </c>
       <c r="C85" t="str">
-        <v>字母</v>
+        <v>數字</v>
       </c>
       <c r="D85" t="str">
-        <v>銀飾U</v>
+        <v>鈦鋼3</v>
       </c>
       <c r="E85">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F85">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G85">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="H85" t="str">
-        <v>银饰U.png</v>
+        <v>钛钢3.png</v>
       </c>
       <c r="I85" t="str">
-        <v>廣州市德潤</v>
+        <v>東莞晞亞</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>tg3_sz_7</v>
+        <v>tg2_sz_7</v>
       </c>
       <c r="B86" t="str">
         <v>配件</v>
@@ -2875,7 +2875,7 @@
         <v>數字</v>
       </c>
       <c r="D86" t="str">
-        <v>鈦鋼3</v>
+        <v>鈦鋼2</v>
       </c>
       <c r="E86">
         <v>7</v>
@@ -2887,7 +2887,7 @@
         <v>59</v>
       </c>
       <c r="H86" t="str">
-        <v>钛钢3.png</v>
+        <v>钛钢2.png</v>
       </c>
       <c r="I86" t="str">
         <v>東莞晞亞</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>tg2_sz_7</v>
+        <v>tg8_sz_7</v>
       </c>
       <c r="B87" t="str">
         <v>配件</v>
@@ -2904,7 +2904,7 @@
         <v>數字</v>
       </c>
       <c r="D87" t="str">
-        <v>鈦鋼2</v>
+        <v>鈦鋼8</v>
       </c>
       <c r="E87">
         <v>7</v>
@@ -2916,7 +2916,7 @@
         <v>59</v>
       </c>
       <c r="H87" t="str">
-        <v>钛钢2.png</v>
+        <v>钛钢8.png</v>
       </c>
       <c r="I87" t="str">
         <v>東莞晞亞</v>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>tg8_sz_7</v>
+        <v>tg5_sz_7</v>
       </c>
       <c r="B88" t="str">
         <v>配件</v>
@@ -2933,7 +2933,7 @@
         <v>數字</v>
       </c>
       <c r="D88" t="str">
-        <v>鈦鋼8</v>
+        <v>鈦鋼5</v>
       </c>
       <c r="E88">
         <v>7</v>
@@ -2945,7 +2945,7 @@
         <v>59</v>
       </c>
       <c r="H88" t="str">
-        <v>钛钢8.png</v>
+        <v>钛钢5.png</v>
       </c>
       <c r="I88" t="str">
         <v>東莞晞亞</v>
@@ -2953,123 +2953,123 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>tg5_sz_7</v>
+        <v>gycn_xz_3</v>
       </c>
       <c r="B89" t="str">
         <v>配件</v>
       </c>
       <c r="C89" t="str">
-        <v>數字</v>
+        <v>星座</v>
       </c>
       <c r="D89" t="str">
-        <v>鈦鋼5</v>
+        <v>古銀處女</v>
       </c>
       <c r="E89">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F89">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G89">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H89" t="str">
-        <v>钛钢5.png</v>
+        <v>古银处女.png</v>
       </c>
       <c r="I89" t="str">
-        <v>東莞晞亞</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>gycn_xz_3</v>
+        <v>ysp_zm_4</v>
       </c>
       <c r="B90" t="str">
         <v>配件</v>
       </c>
       <c r="C90" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D90" t="str">
-        <v>古銀處女</v>
+        <v>銀飾P</v>
       </c>
       <c r="E90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F90">
         <v>10</v>
       </c>
       <c r="G90">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H90" t="str">
-        <v>古银处女.png</v>
+        <v>银饰P.png</v>
       </c>
       <c r="I90" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ysp_zm_4</v>
+        <v>gyby_xz_3</v>
       </c>
       <c r="B91" t="str">
         <v>配件</v>
       </c>
       <c r="C91" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D91" t="str">
-        <v>銀飾P</v>
+        <v>古銀白羊</v>
       </c>
       <c r="E91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F91">
         <v>10</v>
       </c>
       <c r="G91">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H91" t="str">
-        <v>银饰P.png</v>
+        <v>古银白羊.png</v>
       </c>
       <c r="I91" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>gyby_xz_3</v>
+        <v>lfj_cysl_8</v>
       </c>
       <c r="B92" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C92" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D92" t="str">
-        <v>古銀白羊</v>
+        <v>綠髮晶</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F92">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G92">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="H92" t="str">
-        <v>古银白羊.png</v>
+        <v>绿发晶.png</v>
       </c>
       <c r="I92" t="str">
-        <v>義烏市唐人印象</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>lfj_cysl_8</v>
+        <v>lfj_cysl_10</v>
       </c>
       <c r="B93" t="str">
         <v>珠子</v>
@@ -3081,13 +3081,13 @@
         <v>綠髮晶</v>
       </c>
       <c r="E93">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F93">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G93">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="H93" t="str">
         <v>绿发晶.png</v>
@@ -3098,36 +3098,36 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>lfj_cysl_10</v>
+        <v>ysc_zm_4</v>
       </c>
       <c r="B94" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C94" t="str">
-        <v>水晶</v>
+        <v>字母</v>
       </c>
       <c r="D94" t="str">
-        <v>綠髮晶</v>
+        <v>銀飾C</v>
       </c>
       <c r="E94">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F94">
         <v>10</v>
       </c>
       <c r="G94">
-        <v>139</v>
+        <v>399</v>
       </c>
       <c r="H94" t="str">
-        <v>绿发晶.png</v>
+        <v>银饰C.png</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ysc_zm_4</v>
+        <v>ysb_zm_4</v>
       </c>
       <c r="B95" t="str">
         <v>配件</v>
@@ -3136,7 +3136,7 @@
         <v>字母</v>
       </c>
       <c r="D95" t="str">
-        <v>銀飾C</v>
+        <v>銀飾B</v>
       </c>
       <c r="E95">
         <v>4</v>
@@ -3148,7 +3148,7 @@
         <v>399</v>
       </c>
       <c r="H95" t="str">
-        <v>银饰C.png</v>
+        <v>银饰B.png</v>
       </c>
       <c r="I95" t="str">
         <v>廣州市德潤</v>
@@ -3156,65 +3156,65 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>ysb_zm_4</v>
+        <v>gysp_xz_3</v>
       </c>
       <c r="B96" t="str">
         <v>配件</v>
       </c>
       <c r="C96" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D96" t="str">
-        <v>銀飾B</v>
+        <v>古銀水瓶</v>
       </c>
       <c r="E96">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F96">
         <v>10</v>
       </c>
       <c r="G96">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H96" t="str">
-        <v>银饰B.png</v>
+        <v>古银水瓶.png</v>
       </c>
       <c r="I96" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>gysp_xz_3</v>
+        <v>yso_zm_4</v>
       </c>
       <c r="B97" t="str">
         <v>配件</v>
       </c>
       <c r="C97" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D97" t="str">
-        <v>古銀水瓶</v>
+        <v>銀飾O</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97">
         <v>10</v>
       </c>
       <c r="G97">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H97" t="str">
-        <v>古银水瓶.png</v>
+        <v>银饰O.png</v>
       </c>
       <c r="I97" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>yso_zm_4</v>
+        <v>ysw_zm_4</v>
       </c>
       <c r="B98" t="str">
         <v>配件</v>
@@ -3223,7 +3223,7 @@
         <v>字母</v>
       </c>
       <c r="D98" t="str">
-        <v>銀飾O</v>
+        <v>銀飾W</v>
       </c>
       <c r="E98">
         <v>4</v>
@@ -3235,7 +3235,7 @@
         <v>399</v>
       </c>
       <c r="H98" t="str">
-        <v>银饰O.png</v>
+        <v>银饰W.png</v>
       </c>
       <c r="I98" t="str">
         <v>廣州市德潤</v>
@@ -3243,36 +3243,36 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>ysw_zm_4</v>
+        <v>zyd_pnd_2</v>
       </c>
       <c r="B99" t="str">
         <v>配件</v>
       </c>
       <c r="C99" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D99" t="str">
-        <v>銀飾W</v>
+        <v>珠遇蝶</v>
       </c>
       <c r="E99">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F99">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G99">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="H99" t="str">
-        <v>银饰W.png</v>
+        <v>珠遇蝶.png</v>
       </c>
       <c r="I99" t="str">
-        <v>廣州市德潤</v>
+        <v>廣州瑤心飾品</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>zyd_pnd_2</v>
+        <v>xfp_pnd_2</v>
       </c>
       <c r="B100" t="str">
         <v>配件</v>
@@ -3281,259 +3281,259 @@
         <v>吊墜</v>
       </c>
       <c r="D100" t="str">
-        <v>珠遇蝶</v>
+        <v>招財</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G100">
         <v>59</v>
       </c>
       <c r="H100" t="str">
-        <v>珠遇蝶.png</v>
+        <v>招财.png</v>
       </c>
       <c r="I100" t="str">
-        <v>廣州瑤心飾品</v>
+        <v>義烏市歌爾</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>xfp_pnd_2</v>
+        <v>ysq_zm_4</v>
       </c>
       <c r="B101" t="str">
         <v>配件</v>
       </c>
       <c r="C101" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D101" t="str">
-        <v>招財</v>
+        <v>銀飾Q</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F101">
         <v>10</v>
       </c>
       <c r="G101">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="H101" t="str">
-        <v>招财.png</v>
+        <v>银饰Q.png</v>
       </c>
       <c r="I101" t="str">
-        <v>義烏市歌爾</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ysq_zm_4</v>
+        <v>ymys_stn_10</v>
       </c>
       <c r="B102" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C102" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D102" t="str">
-        <v>銀飾Q</v>
+        <v>羽毛螢石</v>
       </c>
       <c r="E102">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F102">
         <v>10</v>
       </c>
       <c r="G102">
-        <v>399</v>
+        <v>139</v>
       </c>
       <c r="H102" t="str">
-        <v>银饰Q.png</v>
+        <v>羽毛萤石.png</v>
       </c>
       <c r="I102" t="str">
-        <v>廣州市德潤</v>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ymys_stn_10</v>
+        <v>gyjx_xz_3</v>
       </c>
       <c r="B103" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C103" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D103" t="str">
-        <v>羽毛螢石</v>
+        <v>古銀巨蟹</v>
       </c>
       <c r="E103">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F103">
         <v>10</v>
       </c>
       <c r="G103">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="H103" t="str">
-        <v>羽毛萤石.png</v>
+        <v>古银巨蟹.png</v>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>gyjx_xz_3</v>
+        <v>ysf_zm_4</v>
       </c>
       <c r="B104" t="str">
         <v>配件</v>
       </c>
       <c r="C104" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D104" t="str">
-        <v>古銀巨蟹</v>
+        <v>銀飾F</v>
       </c>
       <c r="E104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F104">
         <v>10</v>
       </c>
       <c r="G104">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H104" t="str">
-        <v>古银巨蟹.png</v>
+        <v>银饰F.png</v>
       </c>
       <c r="I104" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ysf_zm_4</v>
+        <v>gyss_xz_3</v>
       </c>
       <c r="B105" t="str">
         <v>配件</v>
       </c>
       <c r="C105" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D105" t="str">
-        <v>銀飾F</v>
+        <v>古銀射手</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F105">
         <v>10</v>
       </c>
       <c r="G105">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H105" t="str">
-        <v>银饰F.png</v>
+        <v>古银射手.png</v>
       </c>
       <c r="I105" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>gyss_xz_3</v>
+        <v>hlcs_pnd_3</v>
       </c>
       <c r="B106" t="str">
         <v>配件</v>
       </c>
       <c r="C106" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D106" t="str">
-        <v>古銀射手</v>
+        <v>葫蘆成雙</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G106">
-        <v>39</v>
+        <v>299</v>
       </c>
       <c r="H106" t="str">
-        <v>古银射手.png</v>
+        <v>葫芦成双.png</v>
       </c>
       <c r="I106" t="str">
-        <v>義烏市唐人印象</v>
+        <v>東海縣花眠</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>hlcs_pnd_3</v>
+        <v>gyszz_xz_3</v>
       </c>
       <c r="B107" t="str">
         <v>配件</v>
       </c>
       <c r="C107" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D107" t="str">
-        <v>葫蘆成雙</v>
+        <v>古銀雙子</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G107">
-        <v>299</v>
+        <v>39</v>
       </c>
       <c r="H107" t="str">
-        <v>葫芦成双.png</v>
+        <v>古银双子.png</v>
       </c>
       <c r="I107" t="str">
-        <v>東海縣花眠</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>gyszz_xz_3</v>
+        <v>ysn_zm_4</v>
       </c>
       <c r="B108" t="str">
         <v>配件</v>
       </c>
       <c r="C108" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D108" t="str">
-        <v>古銀雙子</v>
+        <v>銀飾N</v>
       </c>
       <c r="E108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F108">
         <v>10</v>
       </c>
       <c r="G108">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H108" t="str">
-        <v>古银双子.png</v>
+        <v>银饰N.png</v>
       </c>
       <c r="I108" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ysn_zm_4</v>
+        <v>ysm_zm_4</v>
       </c>
       <c r="B109" t="str">
         <v>配件</v>
@@ -3542,7 +3542,7 @@
         <v>字母</v>
       </c>
       <c r="D109" t="str">
-        <v>銀飾N</v>
+        <v>銀飾M</v>
       </c>
       <c r="E109">
         <v>4</v>
@@ -3554,7 +3554,7 @@
         <v>399</v>
       </c>
       <c r="H109" t="str">
-        <v>银饰N.png</v>
+        <v>银饰M.png</v>
       </c>
       <c r="I109" t="str">
         <v>廣州市德潤</v>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ysm_zm_4</v>
+        <v>ysh_zm_4</v>
       </c>
       <c r="B110" t="str">
         <v>配件</v>
@@ -3571,7 +3571,7 @@
         <v>字母</v>
       </c>
       <c r="D110" t="str">
-        <v>銀飾M</v>
+        <v>銀飾H</v>
       </c>
       <c r="E110">
         <v>4</v>
@@ -3583,7 +3583,7 @@
         <v>399</v>
       </c>
       <c r="H110" t="str">
-        <v>银饰M.png</v>
+        <v>银饰H.png</v>
       </c>
       <c r="I110" t="str">
         <v>廣州市德潤</v>
@@ -3591,123 +3591,123 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ysh_zm_4</v>
+        <v>gytx_xz_3</v>
       </c>
       <c r="B111" t="str">
         <v>配件</v>
       </c>
       <c r="C111" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D111" t="str">
-        <v>銀飾H</v>
+        <v>古銀天蠍</v>
       </c>
       <c r="E111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F111">
         <v>10</v>
       </c>
       <c r="G111">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H111" t="str">
-        <v>银饰H.png</v>
+        <v>古银天蝎.png</v>
       </c>
       <c r="I111" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>gytx_xz_3</v>
+        <v>ysg_zm_4</v>
       </c>
       <c r="B112" t="str">
         <v>配件</v>
       </c>
       <c r="C112" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D112" t="str">
-        <v>古銀天蠍</v>
+        <v>銀飾G</v>
       </c>
       <c r="E112">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F112">
         <v>10</v>
       </c>
       <c r="G112">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H112" t="str">
-        <v>古银天蝎.png</v>
+        <v>银饰G.png</v>
       </c>
       <c r="I112" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ysg_zm_4</v>
+        <v>gytc_xz_3</v>
       </c>
       <c r="B113" t="str">
         <v>配件</v>
       </c>
       <c r="C113" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D113" t="str">
-        <v>銀飾G</v>
+        <v>古銀天秤</v>
       </c>
       <c r="E113">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F113">
         <v>10</v>
       </c>
       <c r="G113">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H113" t="str">
-        <v>银饰G.png</v>
+        <v>古银天秤.png</v>
       </c>
       <c r="I113" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>gytc_xz_3</v>
+        <v>yst_zm_4</v>
       </c>
       <c r="B114" t="str">
         <v>配件</v>
       </c>
       <c r="C114" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D114" t="str">
-        <v>古銀天秤</v>
+        <v>銀飾T</v>
       </c>
       <c r="E114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114">
         <v>10</v>
       </c>
       <c r="G114">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H114" t="str">
-        <v>古银天秤.png</v>
+        <v>银饰T.png</v>
       </c>
       <c r="I114" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>yst_zm_4</v>
+        <v>yse_zm_4</v>
       </c>
       <c r="B115" t="str">
         <v>配件</v>
@@ -3716,7 +3716,7 @@
         <v>字母</v>
       </c>
       <c r="D115" t="str">
-        <v>銀飾T</v>
+        <v>銀飾E</v>
       </c>
       <c r="E115">
         <v>4</v>
@@ -3728,7 +3728,7 @@
         <v>399</v>
       </c>
       <c r="H115" t="str">
-        <v>银饰T.png</v>
+        <v>银饰E.png</v>
       </c>
       <c r="I115" t="str">
         <v>廣州市德潤</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>yse_zm_4</v>
+        <v>ysk_zm_4</v>
       </c>
       <c r="B116" t="str">
         <v>配件</v>
@@ -3745,7 +3745,7 @@
         <v>字母</v>
       </c>
       <c r="D116" t="str">
-        <v>銀飾E</v>
+        <v>銀飾K</v>
       </c>
       <c r="E116">
         <v>4</v>
@@ -3757,7 +3757,7 @@
         <v>399</v>
       </c>
       <c r="H116" t="str">
-        <v>银饰E.png</v>
+        <v>银饰K.png</v>
       </c>
       <c r="I116" t="str">
         <v>廣州市德潤</v>
@@ -3765,123 +3765,123 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ysk_zm_4</v>
+        <v>syyl_pnd_2</v>
       </c>
       <c r="B117" t="str">
         <v>配件</v>
       </c>
       <c r="C117" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D117" t="str">
-        <v>銀飾K</v>
+        <v>閃躍月亮</v>
       </c>
       <c r="E117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F117">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G117">
-        <v>399</v>
+        <v>69</v>
       </c>
       <c r="H117" t="str">
-        <v>银饰K.png</v>
+        <v>闪跃月亮.png</v>
       </c>
       <c r="I117" t="str">
-        <v>廣州市德潤</v>
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>syyl_pnd_2</v>
+        <v>ysv_zm_4</v>
       </c>
       <c r="B118" t="str">
         <v>配件</v>
       </c>
       <c r="C118" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D118" t="str">
-        <v>閃躍月亮</v>
+        <v>銀飾V</v>
       </c>
       <c r="E118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F118">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G118">
-        <v>69</v>
+        <v>399</v>
       </c>
       <c r="H118" t="str">
-        <v>闪跃月亮.png</v>
+        <v>银饰V.png</v>
       </c>
       <c r="I118" t="str">
-        <v>廣州銅品彙</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ysv_zm_4</v>
+        <v>gszs_spc_3</v>
       </c>
       <c r="B119" t="str">
         <v>配件</v>
       </c>
       <c r="C119" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D119" t="str">
-        <v>銀飾V</v>
+        <v>鋯石細閃</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F119">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G119">
-        <v>399</v>
+        <v>129</v>
       </c>
       <c r="H119" t="str">
-        <v>银饰V.png</v>
+        <v>锆石细闪.png</v>
       </c>
       <c r="I119" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>gszs_spc_3</v>
+        <v>ysl_zm_4</v>
       </c>
       <c r="B120" t="str">
         <v>配件</v>
       </c>
       <c r="C120" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D120" t="str">
-        <v>鋯石細閃</v>
+        <v>銀飾L</v>
       </c>
       <c r="E120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F120">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G120">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="H120" t="str">
-        <v>锆石细闪.png</v>
+        <v>银饰L.png</v>
       </c>
       <c r="I120" t="str">
-        <v>義烏市硯鈺</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>ysl_zm_4</v>
+        <v>ysa_zm_4</v>
       </c>
       <c r="B121" t="str">
         <v>配件</v>
@@ -3890,7 +3890,7 @@
         <v>字母</v>
       </c>
       <c r="D121" t="str">
-        <v>銀飾L</v>
+        <v>銀飾A</v>
       </c>
       <c r="E121">
         <v>4</v>
@@ -3902,7 +3902,7 @@
         <v>399</v>
       </c>
       <c r="H121" t="str">
-        <v>银饰L.png</v>
+        <v>银饰A.png</v>
       </c>
       <c r="I121" t="str">
         <v>廣州市德潤</v>
@@ -3910,210 +3910,210 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ysa_zm_4</v>
+        <v>gyjn_xz_3</v>
       </c>
       <c r="B122" t="str">
         <v>配件</v>
       </c>
       <c r="C122" t="str">
-        <v>字母</v>
+        <v>星座</v>
       </c>
       <c r="D122" t="str">
-        <v>銀飾A</v>
+        <v>古銀金牛</v>
       </c>
       <c r="E122">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F122">
         <v>10</v>
       </c>
       <c r="G122">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H122" t="str">
-        <v>银饰A.png</v>
+        <v>古银金牛.png</v>
       </c>
       <c r="I122" t="str">
-        <v>廣州市德潤</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>gyjn_xz_3</v>
+        <v>ysy_zm_4</v>
       </c>
       <c r="B123" t="str">
         <v>配件</v>
       </c>
       <c r="C123" t="str">
-        <v>星座</v>
+        <v>字母</v>
       </c>
       <c r="D123" t="str">
-        <v>古銀金牛</v>
+        <v>銀飾Y</v>
       </c>
       <c r="E123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F123">
         <v>10</v>
       </c>
       <c r="G123">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H123" t="str">
-        <v>古银金牛.png</v>
+        <v>银饰Y.png</v>
       </c>
       <c r="I123" t="str">
-        <v>義烏市唐人印象</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ysy_zm_4</v>
+        <v>jsxh_spc_2</v>
       </c>
       <c r="B124" t="str">
         <v>配件</v>
       </c>
       <c r="C124" t="str">
-        <v>字母</v>
+        <v>隔珠</v>
       </c>
       <c r="D124" t="str">
-        <v>銀飾Y</v>
+        <v>金色小環</v>
       </c>
       <c r="E124">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F124">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G124">
-        <v>399</v>
+        <v>39</v>
       </c>
       <c r="H124" t="str">
-        <v>银饰Y.png</v>
+        <v>金色小环.png</v>
       </c>
       <c r="I124" t="str">
-        <v>廣州市德潤</v>
+        <v>廣州鑫鈺</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>jsxh_spc_2</v>
+        <v>gyshz_xz_3</v>
       </c>
       <c r="B125" t="str">
         <v>配件</v>
       </c>
       <c r="C125" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D125" t="str">
-        <v>金色小環</v>
+        <v>古銀獅子</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G125">
         <v>39</v>
       </c>
       <c r="H125" t="str">
-        <v>金色小环.png</v>
+        <v>古银狮子.png</v>
       </c>
       <c r="I125" t="str">
-        <v>廣州鑫鈺</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>gyshz_xz_3</v>
+        <v>bjx_pnd_2</v>
       </c>
       <c r="B126" t="str">
         <v>配件</v>
       </c>
       <c r="C126" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D126" t="str">
-        <v>古銀獅子</v>
+        <v>北極星</v>
       </c>
       <c r="E126">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F126">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G126">
-        <v>39</v>
+        <v>299</v>
       </c>
       <c r="H126" t="str">
-        <v>古银狮子.png</v>
+        <v>北极星.png</v>
       </c>
       <c r="I126" t="str">
-        <v>義烏市唐人印象</v>
+        <v>海豐縣梅隴鎮創藝祺</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>bjx_pnd_2</v>
+        <v>ysx_zm_4</v>
       </c>
       <c r="B127" t="str">
         <v>配件</v>
       </c>
       <c r="C127" t="str">
-        <v>吊墜</v>
+        <v>字母</v>
       </c>
       <c r="D127" t="str">
-        <v>北極星</v>
+        <v>銀飾X</v>
       </c>
       <c r="E127">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F127">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G127">
-        <v>299</v>
+        <v>399</v>
       </c>
       <c r="H127" t="str">
-        <v>北极星.png</v>
+        <v>银饰X.png</v>
       </c>
       <c r="I127" t="str">
-        <v>海豐縣梅隴鎮創藝祺</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ysx_zm_4</v>
+        <v>hps_stn_6</v>
       </c>
       <c r="B128" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C128" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D128" t="str">
-        <v>銀飾X</v>
+        <v>琥珀石</v>
       </c>
       <c r="E128">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F128">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G128">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="H128" t="str">
-        <v>银饰X.png</v>
+        <v>琥珀石.png</v>
       </c>
       <c r="I128" t="str">
-        <v>廣州市德潤</v>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>hps_stn_6</v>
+        <v>hps_stn_8</v>
       </c>
       <c r="B129" t="str">
         <v>珠子</v>
@@ -4125,13 +4125,13 @@
         <v>琥珀石</v>
       </c>
       <c r="E129">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F129">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G129">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H129" t="str">
         <v>琥珀石.png</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>hps_stn_8</v>
+        <v>hps_stn_10</v>
       </c>
       <c r="B130" t="str">
         <v>珠子</v>
@@ -4154,13 +4154,13 @@
         <v>琥珀石</v>
       </c>
       <c r="E130">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F130">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G130">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="H130" t="str">
         <v>琥珀石.png</v>
@@ -4171,77 +4171,77 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>hps_stn_10</v>
+        <v>gysy_xz_3</v>
       </c>
       <c r="B131" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C131" t="str">
-        <v>礦石</v>
+        <v>星座</v>
       </c>
       <c r="D131" t="str">
-        <v>琥珀石</v>
+        <v>古銀雙魚</v>
       </c>
       <c r="E131">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F131">
         <v>10</v>
       </c>
       <c r="G131">
-        <v>199</v>
+        <v>39</v>
       </c>
       <c r="H131" t="str">
-        <v>琥珀石.png</v>
+        <v>古银双鱼.png</v>
       </c>
       <c r="I131" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>gysy_xz_3</v>
+        <v>xs_spc_10</v>
       </c>
       <c r="B132" t="str">
         <v>配件</v>
       </c>
       <c r="C132" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D132" t="str">
-        <v>古銀雙魚</v>
+        <v>醒獅</v>
       </c>
       <c r="E132">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F132">
         <v>10</v>
       </c>
       <c r="G132">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="H132" t="str">
-        <v>古银双鱼.png</v>
+        <v>醒狮.png</v>
       </c>
       <c r="I132" t="str">
-        <v>義烏市唐人印象</v>
+        <v>連雲港趣界</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>xs_spc_10</v>
+        <v>ysz_zm_4</v>
       </c>
       <c r="B133" t="str">
         <v>配件</v>
       </c>
       <c r="C133" t="str">
-        <v>隔珠</v>
+        <v>字母</v>
       </c>
       <c r="D133" t="str">
-        <v>醒獅</v>
+        <v>銀飾Z</v>
       </c>
       <c r="E133">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F133">
         <v>10</v>
@@ -4250,44 +4250,44 @@
         <v>399</v>
       </c>
       <c r="H133" t="str">
-        <v>醒狮.png</v>
+        <v>银饰Z.png</v>
       </c>
       <c r="I133" t="str">
-        <v>連雲港趣界</v>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ysz_zm_4</v>
+        <v>ths_stn_6</v>
       </c>
       <c r="B134" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C134" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D134" t="str">
-        <v>銀飾Z</v>
+        <v>天河石</v>
       </c>
       <c r="E134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F134">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G134">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="H134" t="str">
-        <v>银饰Z.png</v>
+        <v>天河石.png</v>
       </c>
       <c r="I134" t="str">
-        <v>廣州市德潤</v>
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ths_stn_6</v>
+        <v>ths_stn_8</v>
       </c>
       <c r="B135" t="str">
         <v>珠子</v>
@@ -4299,13 +4299,13 @@
         <v>天河石</v>
       </c>
       <c r="E135">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F135">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G135">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H135" t="str">
         <v>天河石.png</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ths_stn_8</v>
+        <v>ths_stn_10</v>
       </c>
       <c r="B136" t="str">
         <v>珠子</v>
@@ -4328,13 +4328,13 @@
         <v>天河石</v>
       </c>
       <c r="E136">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F136">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G136">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="H136" t="str">
         <v>天河石.png</v>
@@ -4345,65 +4345,65 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>ths_stn_10</v>
+        <v>ysd_zm_4</v>
       </c>
       <c r="B137" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C137" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D137" t="str">
-        <v>天河石</v>
+        <v>銀飾D</v>
       </c>
       <c r="E137">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F137">
         <v>10</v>
       </c>
       <c r="G137">
-        <v>139</v>
+        <v>399</v>
       </c>
       <c r="H137" t="str">
-        <v>天河石.png</v>
+        <v>银饰D.png</v>
       </c>
       <c r="I137" t="str">
-        <v/>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>ysd_zm_4</v>
+        <v>hlb_stn_6</v>
       </c>
       <c r="B138" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C138" t="str">
-        <v>字母</v>
+        <v>礦石</v>
       </c>
       <c r="D138" t="str">
-        <v>銀飾D</v>
+        <v>海藍寶</v>
       </c>
       <c r="E138">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F138">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G138">
-        <v>399</v>
+        <v>89</v>
       </c>
       <c r="H138" t="str">
-        <v>银饰D.png</v>
+        <v>海蓝宝.png</v>
       </c>
       <c r="I138" t="str">
-        <v>廣州市德潤</v>
+        <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>hlb_stn_6</v>
+        <v>hlb_stn_8</v>
       </c>
       <c r="B139" t="str">
         <v>珠子</v>
@@ -4415,13 +4415,13 @@
         <v>海藍寶</v>
       </c>
       <c r="E139">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F139">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G139">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H139" t="str">
         <v>海蓝宝.png</v>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>hlb_stn_8</v>
+        <v>hlb_stn_10</v>
       </c>
       <c r="B140" t="str">
         <v>珠子</v>
@@ -4444,13 +4444,13 @@
         <v>海藍寶</v>
       </c>
       <c r="E140">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F140">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G140">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="H140" t="str">
         <v>海蓝宝.png</v>
@@ -4461,103 +4461,103 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>hlb_stn_10</v>
+        <v>yss_zm_4</v>
       </c>
       <c r="B141" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C141" t="str">
-        <v>礦石</v>
+        <v>字母</v>
       </c>
       <c r="D141" t="str">
-        <v>海藍寶</v>
+        <v>銀飾S</v>
       </c>
       <c r="E141">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F141">
         <v>10</v>
       </c>
       <c r="G141">
-        <v>169</v>
+        <v>399</v>
       </c>
       <c r="H141" t="str">
-        <v>海蓝宝.png</v>
+        <v>银饰S.png</v>
       </c>
       <c r="I141" t="str">
-        <v/>
+        <v>廣州市德潤</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>yss_zm_4</v>
+        <v>gsch_pnd_2</v>
       </c>
       <c r="B142" t="str">
         <v>配件</v>
       </c>
       <c r="C142" t="str">
-        <v>字母</v>
+        <v>吊墜</v>
       </c>
       <c r="D142" t="str">
-        <v>銀飾S</v>
+        <v>鋯石彩虹</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F142">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G142">
-        <v>399</v>
+        <v>199</v>
       </c>
       <c r="H142" t="str">
-        <v>银饰S.png</v>
+        <v>锆石彩虹.png</v>
       </c>
       <c r="I142" t="str">
-        <v>廣州市德潤</v>
+        <v>東海縣慕戀夢</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>gsch_pnd_2</v>
+        <v>xgszs_spc_6</v>
       </c>
       <c r="B143" t="str">
         <v>配件</v>
       </c>
       <c r="C143" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D143" t="str">
-        <v>鋯石彩虹</v>
+        <v>小鋯石鑽閃</v>
       </c>
       <c r="E143">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F143">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G143">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="H143" t="str">
-        <v>锆石彩虹.png</v>
+        <v>小锆石钻闪.png</v>
       </c>
       <c r="I143" t="str">
-        <v>東海縣慕戀夢</v>
+        <v>廣州戴芙妮</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>xgszs_spc_6</v>
+        <v>htj_cysl_6</v>
       </c>
       <c r="B144" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C144" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D144" t="str">
-        <v>小鋯石鑽閃</v>
+        <v>黃塔晶</v>
       </c>
       <c r="E144">
         <v>6</v>
@@ -4566,18 +4566,18 @@
         <v>6</v>
       </c>
       <c r="G144">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H144" t="str">
-        <v>小锆石钻闪.png</v>
+        <v>黄塔晶.png</v>
       </c>
       <c r="I144" t="str">
-        <v>廣州戴芙妮</v>
+        <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>htj_cysl_6</v>
+        <v>htj_cysl_8</v>
       </c>
       <c r="B145" t="str">
         <v>珠子</v>
@@ -4589,13 +4589,13 @@
         <v>黃塔晶</v>
       </c>
       <c r="E145">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F145">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G145">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H145" t="str">
         <v>黄塔晶.png</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>htj_cysl_8</v>
+        <v>htj_cysl_10</v>
       </c>
       <c r="B146" t="str">
         <v>珠子</v>
@@ -4618,13 +4618,13 @@
         <v>黃塔晶</v>
       </c>
       <c r="E146">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F146">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G146">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H146" t="str">
         <v>黄塔晶.png</v>
@@ -4635,65 +4635,65 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>htj_cysl_10</v>
+        <v>wyh_pnd_2</v>
       </c>
       <c r="B147" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C147" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D147" t="str">
-        <v>黃塔晶</v>
+        <v>午夜花</v>
       </c>
       <c r="E147">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F147">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G147">
         <v>99</v>
       </c>
       <c r="H147" t="str">
-        <v>黄塔晶.png</v>
+        <v>午夜花.png</v>
       </c>
       <c r="I147" t="str">
-        <v/>
+        <v>義烏市亮飛</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>wyh_pnd_2</v>
+        <v>hfj_cysl_6</v>
       </c>
       <c r="B148" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C148" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D148" t="str">
-        <v>午夜花</v>
+        <v>黑髮晶</v>
       </c>
       <c r="E148">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F148">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G148">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="H148" t="str">
-        <v>午夜花.png</v>
+        <v>黑发晶.png</v>
       </c>
       <c r="I148" t="str">
-        <v>義烏市亮飛</v>
+        <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>hfj_cysl_6</v>
+        <v>hfj_cysl_8</v>
       </c>
       <c r="B149" t="str">
         <v>珠子</v>
@@ -4705,13 +4705,13 @@
         <v>黑髮晶</v>
       </c>
       <c r="E149">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F149">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G149">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H149" t="str">
         <v>黑发晶.png</v>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>hfj_cysl_8</v>
+        <v>hfj_cysl_10</v>
       </c>
       <c r="B150" t="str">
         <v>珠子</v>
@@ -4734,13 +4734,13 @@
         <v>黑髮晶</v>
       </c>
       <c r="E150">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F150">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G150">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="H150" t="str">
         <v>黑发晶.png</v>
@@ -4751,36 +4751,36 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>hfj_cysl_10</v>
+        <v>tz_spc_19</v>
       </c>
       <c r="B151" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C151" t="str">
-        <v>水晶</v>
+        <v>隔珠</v>
       </c>
       <c r="D151" t="str">
-        <v>黑髮晶</v>
+        <v>天珠</v>
       </c>
       <c r="E151">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F151">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G151">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="H151" t="str">
-        <v>黑发晶.png</v>
+        <v>天珠.png</v>
       </c>
       <c r="I151" t="str">
-        <v/>
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>tz_spc_19</v>
+        <v>ysxz_spc_4</v>
       </c>
       <c r="B152" t="str">
         <v>配件</v>
@@ -4789,56 +4789,56 @@
         <v>隔珠</v>
       </c>
       <c r="D152" t="str">
-        <v>天珠</v>
+        <v>銀色小珠</v>
       </c>
       <c r="E152">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F152">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G152">
         <v>69</v>
       </c>
       <c r="H152" t="str">
-        <v>天珠.png</v>
+        <v>银色小珠.png</v>
       </c>
       <c r="I152" t="str">
-        <v>義烏市楊航</v>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ysxz_spc_4</v>
+        <v>jhy_stn_6</v>
       </c>
       <c r="B153" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C153" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D153" t="str">
-        <v>銀色小珠</v>
+        <v>金虎眼</v>
       </c>
       <c r="E153">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F153">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G153">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H153" t="str">
-        <v>银色小珠.png</v>
+        <v>金虎眼.png</v>
       </c>
       <c r="I153" t="str">
-        <v>義烏市硯鈺</v>
+        <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>jhy_stn_6</v>
+        <v>jhy_stn_8</v>
       </c>
       <c r="B154" t="str">
         <v>珠子</v>
@@ -4850,13 +4850,13 @@
         <v>金虎眼</v>
       </c>
       <c r="E154">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F154">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G154">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H154" t="str">
         <v>金虎眼.png</v>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>jhy_stn_8</v>
+        <v>jhy_stn_10</v>
       </c>
       <c r="B155" t="str">
         <v>珠子</v>
@@ -4879,13 +4879,13 @@
         <v>金虎眼</v>
       </c>
       <c r="E155">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F155">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G155">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H155" t="str">
         <v>金虎眼.png</v>
@@ -4896,65 +4896,65 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>jhy_stn_10</v>
+        <v>jsmxyl_pnd_2</v>
       </c>
       <c r="B156" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C156" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D156" t="str">
-        <v>金虎眼</v>
+        <v>滿鑲彩月</v>
       </c>
       <c r="E156">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F156">
         <v>10</v>
       </c>
       <c r="G156">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H156" t="str">
-        <v>金虎眼.png</v>
+        <v>满镶彩月.png</v>
       </c>
       <c r="I156" t="str">
-        <v/>
+        <v>廣州銅品彙</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>jsmxyl_pnd_2</v>
+        <v>lcmj_cysl_6</v>
       </c>
       <c r="B157" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C157" t="str">
-        <v>吊墜</v>
+        <v>水晶</v>
       </c>
       <c r="D157" t="str">
-        <v>滿鑲彩月</v>
+        <v>綠莓晶</v>
       </c>
       <c r="E157">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F157">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G157">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H157" t="str">
-        <v>满镶彩月.png</v>
+        <v>绿莓晶.png</v>
       </c>
       <c r="I157" t="str">
-        <v>廣州銅品彙</v>
+        <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>lcmj_cysl_6</v>
+        <v>lcmj_cysl_8</v>
       </c>
       <c r="B158" t="str">
         <v>珠子</v>
@@ -4966,13 +4966,13 @@
         <v>綠莓晶</v>
       </c>
       <c r="E158">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F158">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G158">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H158" t="str">
         <v>绿莓晶.png</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>lcmj_cysl_8</v>
+        <v>lcmj_cysl_10</v>
       </c>
       <c r="B159" t="str">
         <v>珠子</v>
@@ -4995,13 +4995,13 @@
         <v>綠莓晶</v>
       </c>
       <c r="E159">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F159">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G159">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H159" t="str">
         <v>绿莓晶.png</v>
@@ -5012,28 +5012,28 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>lcmj_cysl_10</v>
+        <v>xy_stn_6</v>
       </c>
       <c r="B160" t="str">
         <v>珠子</v>
       </c>
       <c r="C160" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D160" t="str">
-        <v>綠莓晶</v>
+        <v>岫玉</v>
       </c>
       <c r="E160">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F160">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G160">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H160" t="str">
-        <v>绿莓晶.png</v>
+        <v>岫玉.png</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>xy_stn_6</v>
+        <v>xy_stn_8</v>
       </c>
       <c r="B161" t="str">
         <v>珠子</v>
@@ -5053,13 +5053,13 @@
         <v>岫玉</v>
       </c>
       <c r="E161">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F161">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G161">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H161" t="str">
         <v>岫玉.png</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>xy_stn_8</v>
+        <v>xy_stn_10</v>
       </c>
       <c r="B162" t="str">
         <v>珠子</v>
@@ -5082,13 +5082,13 @@
         <v>岫玉</v>
       </c>
       <c r="E162">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F162">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G162">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H162" t="str">
         <v>岫玉.png</v>
@@ -5099,16 +5099,16 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>xy_stn_10</v>
+        <v>cyszh_spc_10</v>
       </c>
       <c r="B163" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C163" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D163" t="str">
-        <v>岫玉</v>
+        <v>藏銀十字花</v>
       </c>
       <c r="E163">
         <v>10</v>
@@ -5117,76 +5117,76 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H163" t="str">
-        <v>岫玉.png</v>
+        <v>藏银十字花.png</v>
       </c>
       <c r="I163" t="str">
-        <v/>
+        <v>義烏市楓瑢</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>cyszh_spc_10</v>
+        <v>cyym_pnd_2</v>
       </c>
       <c r="B164" t="str">
         <v>配件</v>
       </c>
       <c r="C164" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D164" t="str">
-        <v>藏銀十字花</v>
+        <v>藏銀羽毛</v>
       </c>
       <c r="E164">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F164">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G164">
-        <v>69</v>
+        <v>599</v>
       </c>
       <c r="H164" t="str">
-        <v>藏银十字花.png</v>
+        <v>藏银羽毛.png</v>
       </c>
       <c r="I164" t="str">
-        <v>義烏市楓瑢</v>
+        <v>廣州市無風帶</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>cyym_pnd_2</v>
+        <v>lys_stn_6</v>
       </c>
       <c r="B165" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C165" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D165" t="str">
-        <v>藏銀羽毛</v>
+        <v>綠螢石</v>
       </c>
       <c r="E165">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F165">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G165">
-        <v>599</v>
+        <v>69</v>
       </c>
       <c r="H165" t="str">
-        <v>藏银羽毛.png</v>
+        <v>绿萤石.png</v>
       </c>
       <c r="I165" t="str">
-        <v>廣州市無風帶</v>
+        <v/>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>lys_stn_6</v>
+        <v>lys_stn_8</v>
       </c>
       <c r="B166" t="str">
         <v>珠子</v>
@@ -5198,13 +5198,13 @@
         <v>綠螢石</v>
       </c>
       <c r="E166">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F166">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G166">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H166" t="str">
         <v>绿萤石.png</v>
@@ -5215,65 +5215,65 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>lys_stn_8</v>
+        <v>cysy_spc_4</v>
       </c>
       <c r="B167" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C167" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D167" t="str">
-        <v>綠螢石</v>
+        <v>藏銀樹葉</v>
       </c>
       <c r="E167">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F167">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G167">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H167" t="str">
-        <v>绿萤石.png</v>
+        <v>藏银树叶.png</v>
       </c>
       <c r="I167" t="str">
-        <v/>
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>cysy_spc_4</v>
+        <v>qws_stn_8</v>
       </c>
       <c r="B168" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C168" t="str">
-        <v>隔珠</v>
+        <v>礦石</v>
       </c>
       <c r="D168" t="str">
-        <v>藏銀樹葉</v>
+        <v>薔薇石</v>
       </c>
       <c r="E168">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F168">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G168">
         <v>69</v>
       </c>
       <c r="H168" t="str">
-        <v>藏银树叶.png</v>
+        <v>蔷薇石.png</v>
       </c>
       <c r="I168" t="str">
-        <v>義烏市楊航</v>
+        <v/>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>qws_stn_8</v>
+        <v>qws_stn_10</v>
       </c>
       <c r="B169" t="str">
         <v>珠子</v>
@@ -5285,13 +5285,13 @@
         <v>薔薇石</v>
       </c>
       <c r="E169">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F169">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G169">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H169" t="str">
         <v>蔷薇石.png</v>
@@ -5302,65 +5302,65 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>qws_stn_10</v>
+        <v>jsxz_spc_4</v>
       </c>
       <c r="B170" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C170" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D170" t="str">
-        <v>薔薇石</v>
+        <v>金色小珠</v>
       </c>
       <c r="E170">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F170">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G170">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H170" t="str">
-        <v>蔷薇石.png</v>
+        <v>金色小珠.png</v>
       </c>
       <c r="I170" t="str">
-        <v/>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>jsxz_spc_4</v>
+        <v>gtsp_xz_3</v>
       </c>
       <c r="B171" t="str">
         <v>配件</v>
       </c>
       <c r="C171" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D171" t="str">
-        <v>金色小珠</v>
+        <v>古銅水瓶</v>
       </c>
       <c r="E171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F171">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G171">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H171" t="str">
-        <v>金色小珠.png</v>
+        <v>古铜水瓶.png</v>
       </c>
       <c r="I171" t="str">
-        <v>義烏市硯鈺</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>gtsp_xz_3</v>
+        <v>gtby_xz_3</v>
       </c>
       <c r="B172" t="str">
         <v>配件</v>
@@ -5369,7 +5369,7 @@
         <v>星座</v>
       </c>
       <c r="D172" t="str">
-        <v>古銅水瓶</v>
+        <v>古銅白羊</v>
       </c>
       <c r="E172">
         <v>3</v>
@@ -5381,7 +5381,7 @@
         <v>39</v>
       </c>
       <c r="H172" t="str">
-        <v>古铜水瓶.png</v>
+        <v>古铜白羊.png</v>
       </c>
       <c r="I172" t="str">
         <v>義烏市唐人印象</v>
@@ -5389,65 +5389,65 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>gtby_xz_3</v>
+        <v>gszssc_spc_5</v>
       </c>
       <c r="B173" t="str">
         <v>配件</v>
       </c>
       <c r="C173" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D173" t="str">
-        <v>古銅白羊</v>
+        <v>鋯石鑽閃雙層</v>
       </c>
       <c r="E173">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F173">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G173">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="H173" t="str">
-        <v>古铜白羊.png</v>
+        <v>锆石钻闪双层.png</v>
       </c>
       <c r="I173" t="str">
-        <v>義烏市唐人印象</v>
+        <v>義烏市硯鈺</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>gszssc_spc_5</v>
+        <v>gtshz_xz_3</v>
       </c>
       <c r="B174" t="str">
         <v>配件</v>
       </c>
       <c r="C174" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D174" t="str">
-        <v>鋯石鑽閃雙層</v>
+        <v>古銅獅子</v>
       </c>
       <c r="E174">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F174">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G174">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="H174" t="str">
-        <v>锆石钻闪双层.png</v>
+        <v>古铜狮子.png</v>
       </c>
       <c r="I174" t="str">
-        <v>義烏市硯鈺</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gtshz_xz_3</v>
+        <v>gttc_xz_3</v>
       </c>
       <c r="B175" t="str">
         <v>配件</v>
@@ -5456,7 +5456,7 @@
         <v>星座</v>
       </c>
       <c r="D175" t="str">
-        <v>古銅獅子</v>
+        <v>古銅天秤</v>
       </c>
       <c r="E175">
         <v>3</v>
@@ -5468,7 +5468,7 @@
         <v>39</v>
       </c>
       <c r="H175" t="str">
-        <v>古铜狮子.png</v>
+        <v>古铜天秤.png</v>
       </c>
       <c r="I175" t="str">
         <v>義烏市唐人印象</v>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>gttc_xz_3</v>
+        <v>gtcn_xz_3</v>
       </c>
       <c r="B176" t="str">
         <v>配件</v>
@@ -5485,7 +5485,7 @@
         <v>星座</v>
       </c>
       <c r="D176" t="str">
-        <v>古銅天秤</v>
+        <v>古銅處女</v>
       </c>
       <c r="E176">
         <v>3</v>
@@ -5497,7 +5497,7 @@
         <v>39</v>
       </c>
       <c r="H176" t="str">
-        <v>古铜天秤.png</v>
+        <v>古铜处女.png</v>
       </c>
       <c r="I176" t="str">
         <v>義烏市唐人印象</v>
@@ -5505,36 +5505,36 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>gtcn_xz_3</v>
+        <v>ygs_stn_6</v>
       </c>
       <c r="B177" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C177" t="str">
-        <v>星座</v>
+        <v>礦石</v>
       </c>
       <c r="D177" t="str">
-        <v>古銅處女</v>
+        <v>月光石</v>
       </c>
       <c r="E177">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F177">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G177">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H177" t="str">
-        <v>古铜处女.png</v>
+        <v>月光石.png</v>
       </c>
       <c r="I177" t="str">
-        <v>義烏市唐人印象</v>
+        <v/>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>ygs_stn_6</v>
+        <v>ygs_stn_8</v>
       </c>
       <c r="B178" t="str">
         <v>珠子</v>
@@ -5546,13 +5546,13 @@
         <v>月光石</v>
       </c>
       <c r="E178">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F178">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G178">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H178" t="str">
         <v>月光石.png</v>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>ygs_stn_8</v>
+        <v>ygs_stn_10</v>
       </c>
       <c r="B179" t="str">
         <v>珠子</v>
@@ -5575,13 +5575,13 @@
         <v>月光石</v>
       </c>
       <c r="E179">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F179">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G179">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="H179" t="str">
         <v>月光石.png</v>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>ygs_stn_10</v>
+        <v>tys_stn_6</v>
       </c>
       <c r="B180" t="str">
         <v>珠子</v>
@@ -5601,19 +5601,19 @@
         <v>礦石</v>
       </c>
       <c r="D180" t="str">
-        <v>月光石</v>
+        <v>太陽石</v>
       </c>
       <c r="E180">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F180">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G180">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="H180" t="str">
-        <v>月光石.png</v>
+        <v>太阳石.png</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>tys_stn_6</v>
+        <v>tys_stn_8</v>
       </c>
       <c r="B181" t="str">
         <v>珠子</v>
@@ -5633,13 +5633,13 @@
         <v>太陽石</v>
       </c>
       <c r="E181">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F181">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G181">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H181" t="str">
         <v>太阳石.png</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>tys_stn_8</v>
+        <v>tys_stn_10</v>
       </c>
       <c r="B182" t="str">
         <v>珠子</v>
@@ -5662,13 +5662,13 @@
         <v>太陽石</v>
       </c>
       <c r="E182">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F182">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G182">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="H182" t="str">
         <v>太阳石.png</v>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>tys_stn_10</v>
+        <v>shlb_stn_8</v>
       </c>
       <c r="B183" t="str">
         <v>珠子</v>
@@ -5688,19 +5688,19 @@
         <v>礦石</v>
       </c>
       <c r="D183" t="str">
-        <v>太陽石</v>
+        <v>聖海藍寶</v>
       </c>
       <c r="E183">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F183">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G183">
-        <v>169</v>
+        <v>399</v>
       </c>
       <c r="H183" t="str">
-        <v>太阳石.png</v>
+        <v>圣海蓝宝.png</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>shlb_stn_8</v>
+        <v>shlb_stn_10</v>
       </c>
       <c r="B184" t="str">
         <v>珠子</v>
@@ -5720,13 +5720,13 @@
         <v>聖海藍寶</v>
       </c>
       <c r="E184">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F184">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G184">
-        <v>399</v>
+        <v>699</v>
       </c>
       <c r="H184" t="str">
         <v>圣海蓝宝.png</v>
@@ -5737,36 +5737,36 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>shlb_stn_10</v>
+        <v>yslzzy_spc_9</v>
       </c>
       <c r="B185" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C185" t="str">
-        <v>礦石</v>
+        <v>隔珠</v>
       </c>
       <c r="D185" t="str">
-        <v>聖海藍寶</v>
+        <v>銀六字箴言</v>
       </c>
       <c r="E185">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F185">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G185">
-        <v>699</v>
+        <v>59</v>
       </c>
       <c r="H185" t="str">
-        <v>圣海蓝宝.png</v>
+        <v>银六字箴言.png</v>
       </c>
       <c r="I185" t="str">
-        <v/>
+        <v>義烏市亦蝶</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>yslzzy_spc_9</v>
+        <v>ketj_spc_10</v>
       </c>
       <c r="B186" t="str">
         <v>配件</v>
@@ -5775,27 +5775,27 @@
         <v>隔珠</v>
       </c>
       <c r="D186" t="str">
-        <v>銀六字箴言</v>
+        <v>凱爾特結</v>
       </c>
       <c r="E186">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F186">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G186">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H186" t="str">
-        <v>银六字箴言.png</v>
+        <v>凯尔特结.png</v>
       </c>
       <c r="I186" t="str">
-        <v>義烏市亦蝶</v>
+        <v>義烏市楊航</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>ketj_spc_10</v>
+        <v>ysxq_spc_10</v>
       </c>
       <c r="B187" t="str">
         <v>配件</v>
@@ -5804,85 +5804,85 @@
         <v>隔珠</v>
       </c>
       <c r="D187" t="str">
-        <v>凱爾特結</v>
+        <v>藏銀繡球</v>
       </c>
       <c r="E187">
         <v>10</v>
       </c>
       <c r="F187">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G187">
         <v>69</v>
       </c>
       <c r="H187" t="str">
-        <v>凯尔特结.png</v>
+        <v>藏银绣球.png</v>
       </c>
       <c r="I187" t="str">
-        <v>義烏市楊航</v>
+        <v>義烏市隱魚</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>ysxq_spc_10</v>
+        <v>gtszz_xz_3</v>
       </c>
       <c r="B188" t="str">
         <v>配件</v>
       </c>
       <c r="C188" t="str">
-        <v>隔珠</v>
+        <v>星座</v>
       </c>
       <c r="D188" t="str">
-        <v>藏銀繡球</v>
+        <v>古銅雙子</v>
       </c>
       <c r="E188">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F188">
         <v>10</v>
       </c>
       <c r="G188">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H188" t="str">
-        <v>藏银绣球.png</v>
+        <v>古铜双子.png</v>
       </c>
       <c r="I188" t="str">
-        <v>義烏市隱魚</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>gtszz_xz_3</v>
+        <v>zsj_cysl_6</v>
       </c>
       <c r="B189" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C189" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D189" t="str">
-        <v>古銅雙子</v>
+        <v>紫水晶</v>
       </c>
       <c r="E189">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F189">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G189">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H189" t="str">
-        <v>古铜双子.png</v>
+        <v>紫水晶.png</v>
       </c>
       <c r="I189" t="str">
-        <v>義烏市唐人印象</v>
+        <v/>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>zsj_cysl_6</v>
+        <v>zsj_cysl_8</v>
       </c>
       <c r="B190" t="str">
         <v>珠子</v>
@@ -5894,13 +5894,13 @@
         <v>紫水晶</v>
       </c>
       <c r="E190">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F190">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G190">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H190" t="str">
         <v>紫水晶.png</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>zsj_cysl_8</v>
+        <v>zsj_cysl_10</v>
       </c>
       <c r="B191" t="str">
         <v>珠子</v>
@@ -5923,13 +5923,13 @@
         <v>紫水晶</v>
       </c>
       <c r="E191">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F191">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G191">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H191" t="str">
         <v>紫水晶.png</v>
@@ -5940,65 +5940,65 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>zsj_cysl_10</v>
+        <v>wgzl_pnd_2</v>
       </c>
       <c r="B192" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C192" t="str">
-        <v>水晶</v>
+        <v>吊墜</v>
       </c>
       <c r="D192" t="str">
-        <v>紫水晶</v>
+        <v>國王之淚</v>
       </c>
       <c r="E192">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F192">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G192">
         <v>99</v>
       </c>
       <c r="H192" t="str">
-        <v>紫水晶.png</v>
+        <v>国王之泪.png</v>
       </c>
       <c r="I192" t="str">
-        <v/>
+        <v>廣州市嘉鈺</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>wgzl_pnd_2</v>
+        <v>gtsy_xz_3</v>
       </c>
       <c r="B193" t="str">
         <v>配件</v>
       </c>
       <c r="C193" t="str">
-        <v>吊墜</v>
+        <v>星座</v>
       </c>
       <c r="D193" t="str">
-        <v>國王之淚</v>
+        <v>古銅雙魚</v>
       </c>
       <c r="E193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F193">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G193">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H193" t="str">
-        <v>国王之泪.png</v>
+        <v>古铜双鱼.png</v>
       </c>
       <c r="I193" t="str">
-        <v>廣州市嘉鈺</v>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>gtsy_xz_3</v>
+        <v>gtmj_xz_3</v>
       </c>
       <c r="B194" t="str">
         <v>配件</v>
@@ -6007,7 +6007,7 @@
         <v>星座</v>
       </c>
       <c r="D194" t="str">
-        <v>古銅雙魚</v>
+        <v>古銅摩羯</v>
       </c>
       <c r="E194">
         <v>3</v>
@@ -6019,7 +6019,7 @@
         <v>39</v>
       </c>
       <c r="H194" t="str">
-        <v>古铜双鱼.png</v>
+        <v>古铜摩羯.png</v>
       </c>
       <c r="I194" t="str">
         <v>義烏市唐人印象</v>
@@ -6027,7 +6027,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>gtmj_xz_3</v>
+        <v>gtss_xz_3</v>
       </c>
       <c r="B195" t="str">
         <v>配件</v>
@@ -6036,7 +6036,7 @@
         <v>星座</v>
       </c>
       <c r="D195" t="str">
-        <v>古銅摩羯</v>
+        <v>古銅射手</v>
       </c>
       <c r="E195">
         <v>3</v>
@@ -6048,7 +6048,7 @@
         <v>39</v>
       </c>
       <c r="H195" t="str">
-        <v>古铜摩羯.png</v>
+        <v>古铜射手.png</v>
       </c>
       <c r="I195" t="str">
         <v>義烏市唐人印象</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>gtss_xz_3</v>
+        <v>gtjn_xz_3</v>
       </c>
       <c r="B196" t="str">
         <v>配件</v>
@@ -6065,7 +6065,7 @@
         <v>星座</v>
       </c>
       <c r="D196" t="str">
-        <v>古銅射手</v>
+        <v>古銅金牛</v>
       </c>
       <c r="E196">
         <v>3</v>
@@ -6077,7 +6077,7 @@
         <v>39</v>
       </c>
       <c r="H196" t="str">
-        <v>古铜射手.png</v>
+        <v>古铜金牛.png</v>
       </c>
       <c r="I196" t="str">
         <v>義烏市唐人印象</v>
@@ -6085,36 +6085,36 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>gtjn_xz_3</v>
+        <v>zfj_cysl_8</v>
       </c>
       <c r="B197" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C197" t="str">
-        <v>星座</v>
+        <v>水晶</v>
       </c>
       <c r="D197" t="str">
-        <v>古銅金牛</v>
+        <v>紫粉晶</v>
       </c>
       <c r="E197">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F197">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G197">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H197" t="str">
-        <v>古铜金牛.png</v>
+        <v>紫粉晶.png</v>
       </c>
       <c r="I197" t="str">
-        <v>義烏市唐人印象</v>
+        <v/>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>zfj_cysl_8</v>
+        <v>zfj_cysl_10</v>
       </c>
       <c r="B198" t="str">
         <v>珠子</v>
@@ -6126,13 +6126,13 @@
         <v>紫粉晶</v>
       </c>
       <c r="E198">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F198">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G198">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H198" t="str">
         <v>紫粉晶.png</v>
@@ -6143,94 +6143,94 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>zfj_cysl_10</v>
+        <v>gttx_xz_3</v>
       </c>
       <c r="B199" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C199" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D199" t="str">
-        <v>紫粉晶</v>
+        <v>古銅天蠍</v>
       </c>
       <c r="E199">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F199">
         <v>10</v>
       </c>
       <c r="G199">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H199" t="str">
-        <v>紫粉晶.png</v>
+        <v>古铜天蝎.png</v>
       </c>
       <c r="I199" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>gttx_xz_3</v>
+        <v>jslzzy_spc_9</v>
       </c>
       <c r="B200" t="str">
         <v>配件</v>
       </c>
       <c r="C200" t="str">
-        <v>星座</v>
+        <v>隔珠</v>
       </c>
       <c r="D200" t="str">
-        <v>古銅天蠍</v>
+        <v>金六字箴言</v>
       </c>
       <c r="E200">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F200">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G200">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H200" t="str">
-        <v>古铜天蝎.png</v>
+        <v>金六字箴言.png</v>
       </c>
       <c r="I200" t="str">
-        <v>義烏市唐人印象</v>
+        <v>義烏市亦蝶</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>jslzzy_spc_9</v>
+        <v>cmj_cysl_6</v>
       </c>
       <c r="B201" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C201" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D201" t="str">
-        <v>金六字箴言</v>
+        <v>草莓晶</v>
       </c>
       <c r="E201">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F201">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G201">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H201" t="str">
-        <v>金六字箴言.png</v>
+        <v>草莓晶.png</v>
       </c>
       <c r="I201" t="str">
-        <v>義烏市亦蝶</v>
+        <v/>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>cmj_cysl_6</v>
+        <v>cmj_cysl_8</v>
       </c>
       <c r="B202" t="str">
         <v>珠子</v>
@@ -6242,13 +6242,13 @@
         <v>草莓晶</v>
       </c>
       <c r="E202">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F202">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G202">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H202" t="str">
         <v>草莓晶.png</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>cmj_cysl_8</v>
+        <v>cmj_cysl_10</v>
       </c>
       <c r="B203" t="str">
         <v>珠子</v>
@@ -6271,13 +6271,13 @@
         <v>草莓晶</v>
       </c>
       <c r="E203">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F203">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G203">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H203" t="str">
         <v>草莓晶.png</v>
@@ -6288,152 +6288,152 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>cmj_cysl_10</v>
+        <v>gtjx_xz_3</v>
       </c>
       <c r="B204" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C204" t="str">
-        <v>水晶</v>
+        <v>星座</v>
       </c>
       <c r="D204" t="str">
-        <v>草莓晶</v>
+        <v>古銅巨蟹</v>
       </c>
       <c r="E204">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F204">
         <v>10</v>
       </c>
       <c r="G204">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H204" t="str">
-        <v>草莓晶.png</v>
+        <v>古铜巨蟹.png</v>
       </c>
       <c r="I204" t="str">
-        <v/>
+        <v>義烏市唐人印象</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>gtjx_xz_3</v>
+        <v>cyhdls_pnd_2</v>
       </c>
       <c r="B205" t="str">
         <v>配件</v>
       </c>
       <c r="C205" t="str">
-        <v>星座</v>
+        <v>吊墜</v>
       </c>
       <c r="D205" t="str">
-        <v>古銅巨蟹</v>
+        <v>藏銀蝴蝶流蘇</v>
       </c>
       <c r="E205">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F205">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="G205">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="H205" t="str">
-        <v>古铜巨蟹.png</v>
+        <v>藏银蝴蝶流苏.png</v>
       </c>
       <c r="I205" t="str">
-        <v>義烏市唐人印象</v>
+        <v>中山市凱髮飾品</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>cyhdls_pnd_2</v>
+        <v>cyhw_spc_4</v>
       </c>
       <c r="B206" t="str">
         <v>配件</v>
       </c>
       <c r="C206" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D206" t="str">
-        <v>藏銀蝴蝶流蘇</v>
+        <v>藏銀回紋</v>
       </c>
       <c r="E206">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F206">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="G206">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H206" t="str">
-        <v>藏银蝴蝶流苏.png</v>
+        <v>藏银回纹.png</v>
       </c>
       <c r="I206" t="str">
-        <v>中山市凱髮飾品</v>
+        <v>中山市凱發</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>cyhw_spc_4</v>
+        <v>cyszdz_pnd_2</v>
       </c>
       <c r="B207" t="str">
         <v>配件</v>
       </c>
       <c r="C207" t="str">
-        <v>隔珠</v>
+        <v>吊墜</v>
       </c>
       <c r="D207" t="str">
-        <v>藏銀回紋</v>
+        <v>藏銀十字</v>
       </c>
       <c r="E207">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F207">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G207">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H207" t="str">
-        <v>藏银回纹.png</v>
+        <v>藏银十字.png</v>
       </c>
       <c r="I207" t="str">
-        <v>中山市凱發</v>
+        <v>汕頭市澄海區漁米</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>cyszdz_pnd_2</v>
+        <v>cydhlf_spc_8</v>
       </c>
       <c r="B208" t="str">
         <v>配件</v>
       </c>
       <c r="C208" t="str">
-        <v>吊墜</v>
+        <v>隔珠</v>
       </c>
       <c r="D208" t="str">
-        <v>藏銀十字</v>
+        <v>藏銀立方</v>
       </c>
       <c r="E208">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F208">
         <v>8</v>
       </c>
       <c r="G208">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H208" t="str">
-        <v>藏银十字.png</v>
+        <v>藏银立方.png</v>
       </c>
       <c r="I208" t="str">
-        <v>汕頭市澄海區漁米</v>
+        <v>義烏市鑫澗</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>cydhlf_spc_8</v>
+        <v>jtlfq_spc_11</v>
       </c>
       <c r="B209" t="str">
         <v>配件</v>
@@ -6442,56 +6442,56 @@
         <v>隔珠</v>
       </c>
       <c r="D209" t="str">
-        <v>藏銀立方</v>
+        <v>景泰藍</v>
       </c>
       <c r="E209">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F209">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G209">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H209" t="str">
-        <v>藏银立方.png</v>
+        <v>景泰蓝.png</v>
       </c>
       <c r="I209" t="str">
-        <v>義烏市鑫澗</v>
+        <v>義烏市璇霽</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>jtlfq_spc_11</v>
+        <v>hjc_cysl_6</v>
       </c>
       <c r="B210" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C210" t="str">
-        <v>隔珠</v>
+        <v>水晶</v>
       </c>
       <c r="D210" t="str">
-        <v>景泰藍</v>
+        <v>黑金超</v>
       </c>
       <c r="E210">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F210">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G210">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="H210" t="str">
-        <v>景泰蓝.png</v>
+        <v>黑金超.png</v>
       </c>
       <c r="I210" t="str">
-        <v>義烏市璇霽</v>
+        <v/>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>hjc_cysl_6</v>
+        <v>hjc_cysl_8</v>
       </c>
       <c r="B211" t="str">
         <v>珠子</v>
@@ -6503,13 +6503,13 @@
         <v>黑金超</v>
       </c>
       <c r="E211">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F211">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G211">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H211" t="str">
         <v>黑金超.png</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>hjc_cysl_8</v>
+        <v>hjc_cysl_10</v>
       </c>
       <c r="B212" t="str">
         <v>珠子</v>
@@ -6532,13 +6532,13 @@
         <v>黑金超</v>
       </c>
       <c r="E212">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F212">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G212">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H212" t="str">
         <v>黑金超.png</v>
@@ -6549,28 +6549,28 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>hjc_cysl_10</v>
+        <v>nh_agt_6</v>
       </c>
       <c r="B213" t="str">
         <v>珠子</v>
       </c>
       <c r="C213" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D213" t="str">
-        <v>黑金超</v>
+        <v>南紅</v>
       </c>
       <c r="E213">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F213">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G213">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H213" t="str">
-        <v>黑金超.png</v>
+        <v>南红.png</v>
       </c>
       <c r="I213" t="str">
         <v/>
@@ -6578,7 +6578,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>nh_agt_6</v>
+        <v>nh_agt_8</v>
       </c>
       <c r="B214" t="str">
         <v>珠子</v>
@@ -6590,13 +6590,13 @@
         <v>南紅</v>
       </c>
       <c r="E214">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F214">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G214">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H214" t="str">
         <v>南红.png</v>
@@ -6607,7 +6607,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>nh_agt_8</v>
+        <v>nh_agt_10</v>
       </c>
       <c r="B215" t="str">
         <v>珠子</v>
@@ -6619,13 +6619,13 @@
         <v>南紅</v>
       </c>
       <c r="E215">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F215">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G215">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="H215" t="str">
         <v>南红.png</v>
@@ -6636,28 +6636,28 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>nh_agt_10</v>
+        <v>hyes_stn_6</v>
       </c>
       <c r="B216" t="str">
         <v>珠子</v>
       </c>
       <c r="C216" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D216" t="str">
-        <v>南紅</v>
+        <v>虎眼石</v>
       </c>
       <c r="E216">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F216">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G216">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="H216" t="str">
-        <v>南红.png</v>
+        <v>虎眼石.png</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>hyes_stn_6</v>
+        <v>hyes_stn_8</v>
       </c>
       <c r="B217" t="str">
         <v>珠子</v>
@@ -6677,13 +6677,13 @@
         <v>虎眼石</v>
       </c>
       <c r="E217">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F217">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G217">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H217" t="str">
         <v>虎眼石.png</v>
@@ -6694,7 +6694,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>hyes_stn_8</v>
+        <v>hyes_stn_10</v>
       </c>
       <c r="B218" t="str">
         <v>珠子</v>
@@ -6706,13 +6706,13 @@
         <v>虎眼石</v>
       </c>
       <c r="E218">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F218">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G218">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H218" t="str">
         <v>虎眼石.png</v>
@@ -6723,28 +6723,28 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>hyes_stn_10</v>
+        <v>gqys_agt_6</v>
       </c>
       <c r="B219" t="str">
         <v>珠子</v>
       </c>
       <c r="C219" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D219" t="str">
-        <v>虎眼石</v>
+        <v>乾青玉髓</v>
       </c>
       <c r="E219">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F219">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G219">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H219" t="str">
-        <v>虎眼石.png</v>
+        <v>干青玉髓.png</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -6752,7 +6752,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>gqys_agt_6</v>
+        <v>gqys_agt_8</v>
       </c>
       <c r="B220" t="str">
         <v>珠子</v>
@@ -6764,13 +6764,13 @@
         <v>乾青玉髓</v>
       </c>
       <c r="E220">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F220">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G220">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H220" t="str">
         <v>干青玉髓.png</v>
@@ -6781,7 +6781,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>gqys_agt_8</v>
+        <v>gqys_agt_10</v>
       </c>
       <c r="B221" t="str">
         <v>珠子</v>
@@ -6793,13 +6793,13 @@
         <v>乾青玉髓</v>
       </c>
       <c r="E221">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F221">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G221">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H221" t="str">
         <v>干青玉髓.png</v>
@@ -6810,28 +6810,28 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>gqys_agt_10</v>
+        <v>yys_stn_6</v>
       </c>
       <c r="B222" t="str">
         <v>珠子</v>
       </c>
       <c r="C222" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D222" t="str">
-        <v>乾青玉髓</v>
+        <v>銀曜石</v>
       </c>
       <c r="E222">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F222">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G222">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H222" t="str">
-        <v>干青玉髓.png</v>
+        <v>银曜石.png</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>yys_stn_6</v>
+        <v>yys_stn_8</v>
       </c>
       <c r="B223" t="str">
         <v>珠子</v>
@@ -6851,13 +6851,13 @@
         <v>銀曜石</v>
       </c>
       <c r="E223">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F223">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G223">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H223" t="str">
         <v>银曜石.png</v>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>yys_stn_8</v>
+        <v>yys_stn_10</v>
       </c>
       <c r="B224" t="str">
         <v>珠子</v>
@@ -6880,13 +6880,13 @@
         <v>銀曜石</v>
       </c>
       <c r="E224">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F224">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G224">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H224" t="str">
         <v>银曜石.png</v>
@@ -6897,65 +6897,65 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>yys_stn_10</v>
+        <v>bmw_pnd_2</v>
       </c>
       <c r="B225" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C225" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
       <c r="D225" t="str">
-        <v>銀曜石</v>
+        <v>捕夢網</v>
       </c>
       <c r="E225">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F225">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G225">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H225" t="str">
-        <v>银曜石.png</v>
+        <v>捕梦网.png</v>
       </c>
       <c r="I225" t="str">
-        <v/>
+        <v>東海縣祥慕戀</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>bmw_pnd_2</v>
+        <v>zs_stn_6</v>
       </c>
       <c r="B226" t="str">
-        <v>配件</v>
+        <v>珠子</v>
       </c>
       <c r="C226" t="str">
-        <v>吊墜</v>
+        <v>礦石</v>
       </c>
       <c r="D226" t="str">
-        <v>捕夢網</v>
+        <v>硃砂</v>
       </c>
       <c r="E226">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F226">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G226">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H226" t="str">
-        <v>捕梦网.png</v>
+        <v>朱砂.png</v>
       </c>
       <c r="I226" t="str">
-        <v>東海縣祥慕戀</v>
+        <v/>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>zs_stn_6</v>
+        <v>ljs_stn_6</v>
       </c>
       <c r="B227" t="str">
         <v>珠子</v>
@@ -6964,7 +6964,7 @@
         <v>礦石</v>
       </c>
       <c r="D227" t="str">
-        <v>硃砂</v>
+        <v>藍晶石</v>
       </c>
       <c r="E227">
         <v>6</v>
@@ -6976,7 +6976,7 @@
         <v>99</v>
       </c>
       <c r="H227" t="str">
-        <v>朱砂.png</v>
+        <v>蓝晶石.png</v>
       </c>
       <c r="I227" t="str">
         <v/>
@@ -6984,7 +6984,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>ljs_stn_6</v>
+        <v>ljs_stn_8</v>
       </c>
       <c r="B228" t="str">
         <v>珠子</v>
@@ -6996,13 +6996,13 @@
         <v>藍晶石</v>
       </c>
       <c r="E228">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F228">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G228">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="H228" t="str">
         <v>蓝晶石.png</v>
@@ -7013,7 +7013,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>ljs_stn_8</v>
+        <v>ljs_stn_10</v>
       </c>
       <c r="B229" t="str">
         <v>珠子</v>
@@ -7025,13 +7025,13 @@
         <v>藍晶石</v>
       </c>
       <c r="E229">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F229">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G229">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="H229" t="str">
         <v>蓝晶石.png</v>
@@ -7042,28 +7042,28 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>ljs_stn_10</v>
+        <v>hmn_agt_6</v>
       </c>
       <c r="B230" t="str">
         <v>珠子</v>
       </c>
       <c r="C230" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D230" t="str">
-        <v>藍晶石</v>
+        <v>紅瑪瑙</v>
       </c>
       <c r="E230">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F230">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G230">
-        <v>199</v>
+        <v>39</v>
       </c>
       <c r="H230" t="str">
-        <v>蓝晶石.png</v>
+        <v>红玛瑙.png</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>hmn_agt_6</v>
+        <v>hmn_agt_8</v>
       </c>
       <c r="B231" t="str">
         <v>珠子</v>
@@ -7083,13 +7083,13 @@
         <v>紅瑪瑙</v>
       </c>
       <c r="E231">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F231">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G231">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H231" t="str">
         <v>红玛瑙.png</v>
@@ -7100,7 +7100,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>hmn_agt_8</v>
+        <v>hmn_agt_10</v>
       </c>
       <c r="B232" t="str">
         <v>珠子</v>
@@ -7112,13 +7112,13 @@
         <v>紅瑪瑙</v>
       </c>
       <c r="E232">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F232">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G232">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H232" t="str">
         <v>红玛瑙.png</v>
@@ -7129,28 +7129,28 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>hmn_agt_10</v>
+        <v>csj_cysl_6</v>
       </c>
       <c r="B233" t="str">
         <v>珠子</v>
       </c>
       <c r="C233" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D233" t="str">
-        <v>紅瑪瑙</v>
+        <v>茶水晶</v>
       </c>
       <c r="E233">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F233">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G233">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H233" t="str">
-        <v>红玛瑙.png</v>
+        <v>茶水晶.png</v>
       </c>
       <c r="I233" t="str">
         <v/>
@@ -7158,7 +7158,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>csj_cysl_6</v>
+        <v>csj_cysl_8</v>
       </c>
       <c r="B234" t="str">
         <v>珠子</v>
@@ -7170,13 +7170,13 @@
         <v>茶水晶</v>
       </c>
       <c r="E234">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F234">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G234">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H234" t="str">
         <v>茶水晶.png</v>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>csj_cysl_8</v>
+        <v>csj_cysl_10</v>
       </c>
       <c r="B235" t="str">
         <v>珠子</v>
@@ -7199,13 +7199,13 @@
         <v>茶水晶</v>
       </c>
       <c r="E235">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F235">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G235">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H235" t="str">
         <v>茶水晶.png</v>
@@ -7216,28 +7216,28 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>csj_cysl_10</v>
+        <v>kqs_stn_6</v>
       </c>
       <c r="B236" t="str">
         <v>珠子</v>
       </c>
       <c r="C236" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D236" t="str">
-        <v>茶水晶</v>
+        <v>孔雀石</v>
       </c>
       <c r="E236">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F236">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G236">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H236" t="str">
-        <v>茶水晶.png</v>
+        <v>孔雀石.png</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>kqs_stn_6</v>
+        <v>kqs_stn_8</v>
       </c>
       <c r="B237" t="str">
         <v>珠子</v>
@@ -7257,13 +7257,13 @@
         <v>孔雀石</v>
       </c>
       <c r="E237">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F237">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G237">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H237" t="str">
         <v>孔雀石.png</v>
@@ -7274,7 +7274,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>kqs_stn_8</v>
+        <v>kqs_stn_10</v>
       </c>
       <c r="B238" t="str">
         <v>珠子</v>
@@ -7286,13 +7286,13 @@
         <v>孔雀石</v>
       </c>
       <c r="E238">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F238">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G238">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="H238" t="str">
         <v>孔雀石.png</v>
@@ -7303,7 +7303,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>kqs_stn_10</v>
+        <v>qjs_stn_6</v>
       </c>
       <c r="B239" t="str">
         <v>珠子</v>
@@ -7312,19 +7312,19 @@
         <v>礦石</v>
       </c>
       <c r="D239" t="str">
-        <v>孔雀石</v>
+        <v>青金石</v>
       </c>
       <c r="E239">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F239">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G239">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="H239" t="str">
-        <v>孔雀石.png</v>
+        <v>青金石.png</v>
       </c>
       <c r="I239" t="str">
         <v/>
@@ -7332,7 +7332,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>qjs_stn_6</v>
+        <v>qjs_stn_8</v>
       </c>
       <c r="B240" t="str">
         <v>珠子</v>
@@ -7344,13 +7344,13 @@
         <v>青金石</v>
       </c>
       <c r="E240">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F240">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G240">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H240" t="str">
         <v>青金石.png</v>
@@ -7361,7 +7361,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>qjs_stn_8</v>
+        <v>qjs_stn_10</v>
       </c>
       <c r="B241" t="str">
         <v>珠子</v>
@@ -7373,13 +7373,13 @@
         <v>青金石</v>
       </c>
       <c r="E241">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F241">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G241">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H241" t="str">
         <v>青金石.png</v>
@@ -7390,28 +7390,28 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>qjs_stn_10</v>
+        <v>wlg_cysl_6</v>
       </c>
       <c r="B242" t="str">
         <v>珠子</v>
       </c>
       <c r="C242" t="str">
-        <v>礦石</v>
+        <v>水晶</v>
       </c>
       <c r="D242" t="str">
-        <v>青金石</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E242">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F242">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G242">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H242" t="str">
-        <v>青金石.png</v>
+        <v>乌拉圭.png</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -7419,7 +7419,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>wlg_cysl_6</v>
+        <v>wlg_cysl_8</v>
       </c>
       <c r="B243" t="str">
         <v>珠子</v>
@@ -7431,13 +7431,13 @@
         <v>烏拉圭</v>
       </c>
       <c r="E243">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F243">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G243">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H243" t="str">
         <v>乌拉圭.png</v>
@@ -7448,7 +7448,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>wlg_cysl_8</v>
+        <v>wlg_cysl_10</v>
       </c>
       <c r="B244" t="str">
         <v>珠子</v>
@@ -7460,13 +7460,13 @@
         <v>烏拉圭</v>
       </c>
       <c r="E244">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F244">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G244">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="H244" t="str">
         <v>乌拉圭.png</v>
@@ -7477,7 +7477,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>wlg_cysl_10</v>
+        <v>zyl_cysl_6</v>
       </c>
       <c r="B245" t="str">
         <v>珠子</v>
@@ -7486,19 +7486,19 @@
         <v>水晶</v>
       </c>
       <c r="D245" t="str">
-        <v>烏拉圭</v>
+        <v>紫幽靈</v>
       </c>
       <c r="E245">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F245">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G245">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="H245" t="str">
-        <v>乌拉圭.png</v>
+        <v>紫幽灵.png</v>
       </c>
       <c r="I245" t="str">
         <v/>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>zyl_cysl_6</v>
+        <v>zyl_cysl_8</v>
       </c>
       <c r="B246" t="str">
         <v>珠子</v>
@@ -7518,13 +7518,13 @@
         <v>紫幽靈</v>
       </c>
       <c r="E246">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F246">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G246">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H246" t="str">
         <v>紫幽灵.png</v>
@@ -7535,28 +7535,28 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>zyl_cysl_8</v>
+        <v>he_agt_6</v>
       </c>
       <c r="B247" t="str">
         <v>珠子</v>
       </c>
       <c r="C247" t="str">
-        <v>水晶</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D247" t="str">
-        <v>紫幽靈</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E247">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F247">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G247">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H247" t="str">
-        <v>紫幽灵.png</v>
+        <v>黑玛瑙.png</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -7564,7 +7564,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>he_agt_6</v>
+        <v>he_agt_8</v>
       </c>
       <c r="B248" t="str">
         <v>珠子</v>
@@ -7576,13 +7576,13 @@
         <v>黑瑪瑙</v>
       </c>
       <c r="E248">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F248">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G248">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H248" t="str">
         <v>黑玛瑙.png</v>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>he_agt_8</v>
+        <v>he_agt_10</v>
       </c>
       <c r="B249" t="str">
         <v>珠子</v>
@@ -7605,13 +7605,13 @@
         <v>黑瑪瑙</v>
       </c>
       <c r="E249">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F249">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G249">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H249" t="str">
         <v>黑玛瑙.png</v>
@@ -7622,28 +7622,28 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>he_agt_10</v>
+        <v>zjs_stn_6</v>
       </c>
       <c r="B250" t="str">
         <v>珠子</v>
       </c>
       <c r="C250" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
       <c r="D250" t="str">
-        <v>黑瑪瑙</v>
+        <v>紫金砂</v>
       </c>
       <c r="E250">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F250">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G250">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H250" t="str">
-        <v>黑玛瑙.png</v>
+        <v>紫金砂.png</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>zjs_stn_6</v>
+        <v>zjs_stn_8</v>
       </c>
       <c r="B251" t="str">
         <v>珠子</v>
@@ -7663,13 +7663,13 @@
         <v>紫金砂</v>
       </c>
       <c r="E251">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F251">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G251">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H251" t="str">
         <v>紫金砂.png</v>
@@ -7680,7 +7680,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>zjs_stn_8</v>
+        <v>zjs_stn_10</v>
       </c>
       <c r="B252" t="str">
         <v>珠子</v>
@@ -7692,13 +7692,13 @@
         <v>紫金砂</v>
       </c>
       <c r="E252">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F252">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G252">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="H252" t="str">
         <v>紫金砂.png</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>zjs_stn_10</v>
+        <v>jys_stn_6</v>
       </c>
       <c r="B253" t="str">
         <v>珠子</v>
@@ -7718,19 +7718,19 @@
         <v>礦石</v>
       </c>
       <c r="D253" t="str">
-        <v>紫金砂</v>
+        <v>金曜石</v>
       </c>
       <c r="E253">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F253">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G253">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="H253" t="str">
-        <v>紫金砂.png</v>
+        <v>金曜石.png</v>
       </c>
       <c r="I253" t="str">
         <v/>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>jys_stn_6</v>
+        <v>jys_stn_8</v>
       </c>
       <c r="B254" t="str">
         <v>珠子</v>
@@ -7750,13 +7750,13 @@
         <v>金曜石</v>
       </c>
       <c r="E254">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F254">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G254">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H254" t="str">
         <v>金曜石.png</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>jys_stn_8</v>
+        <v>jys_stn_10</v>
       </c>
       <c r="B255" t="str">
         <v>珠子</v>
@@ -7779,13 +7779,13 @@
         <v>金曜石</v>
       </c>
       <c r="E255">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F255">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G255">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H255" t="str">
         <v>金曜石.png</v>
@@ -7796,7 +7796,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>jys_stn_10</v>
+        <v>hys_stn_6</v>
       </c>
       <c r="B256" t="str">
         <v>珠子</v>
@@ -7805,19 +7805,19 @@
         <v>礦石</v>
       </c>
       <c r="D256" t="str">
-        <v>金曜石</v>
+        <v>黑曜石</v>
       </c>
       <c r="E256">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F256">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G256">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="H256" t="str">
-        <v>金曜石.png</v>
+        <v>黑曜石.png</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>hys_stn_6</v>
+        <v>hys_stn_8</v>
       </c>
       <c r="B257" t="str">
         <v>珠子</v>
@@ -7837,13 +7837,13 @@
         <v>黑曜石</v>
       </c>
       <c r="E257">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F257">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G257">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H257" t="str">
         <v>黑曜石.png</v>
@@ -7854,7 +7854,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>hys_stn_8</v>
+        <v>hys_stn_10</v>
       </c>
       <c r="B258" t="str">
         <v>珠子</v>
@@ -7866,13 +7866,13 @@
         <v>黑曜石</v>
       </c>
       <c r="E258">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F258">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G258">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H258" t="str">
         <v>黑曜石.png</v>
@@ -7881,38 +7881,9 @@
         <v/>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="str">
-        <v>hys_stn_10</v>
-      </c>
-      <c r="B259" t="str">
-        <v>珠子</v>
-      </c>
-      <c r="C259" t="str">
-        <v>礦石</v>
-      </c>
-      <c r="D259" t="str">
-        <v>黑曜石</v>
-      </c>
-      <c r="E259">
-        <v>10</v>
-      </c>
-      <c r="F259">
-        <v>10</v>
-      </c>
-      <c r="G259">
-        <v>99</v>
-      </c>
-      <c r="H259" t="str">
-        <v>黑曜石.png</v>
-      </c>
-      <c r="I259" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I259"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I258"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -2214,7 +2214,7 @@
         <v>13</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G63">
         <v>69</v>

--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -564,7 +564,7 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H6" t="str">
         <v>雪花幽灵.png</v>
@@ -593,7 +593,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="H7" t="str">
         <v>雪花幽灵.png</v>
@@ -622,7 +622,7 @@
         <v>8</v>
       </c>
       <c r="G8">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H8" t="str">
         <v>白幽灵.png</v>
@@ -651,7 +651,7 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H9" t="str">
         <v>淡水珍珠.png</v>
@@ -680,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="H10" t="str">
         <v>淡水珍珠.png</v>
@@ -709,7 +709,7 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="H11" t="str">
         <v>淡水珍珠.png</v>
@@ -738,7 +738,7 @@
         <v>8</v>
       </c>
       <c r="G12">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H12" t="str">
         <v>奶白晶.png</v>
@@ -767,7 +767,7 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H13" t="str">
         <v>奶白晶.png</v>
@@ -851,7 +851,7 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>69</v>
@@ -880,7 +880,7 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>49</v>
@@ -909,7 +909,7 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>59</v>
@@ -970,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="G20">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H20" t="str">
         <v>星光粉晶.png</v>
@@ -1115,7 +1115,7 @@
         <v>6</v>
       </c>
       <c r="G25">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H25" t="str">
         <v>紫锂辉.png</v>
@@ -1144,7 +1144,7 @@
         <v>8</v>
       </c>
       <c r="G26">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="H26" t="str">
         <v>紫锂辉.png</v>
@@ -1173,7 +1173,7 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="H27" t="str">
         <v>紫锂辉.png</v>
@@ -1202,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="G28">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H28" t="str">
         <v>菱格立方.png</v>
@@ -1289,7 +1289,7 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H31" t="str">
         <v>粉水晶.png</v>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
       <c r="G33">
-        <v>599</v>
+        <v>399</v>
       </c>
       <c r="H33" t="str">
         <v>镂空金福.png</v>
@@ -1376,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="G34">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H34" t="str">
         <v>白阿塞.png</v>
@@ -1434,7 +1434,7 @@
         <v>6</v>
       </c>
       <c r="G36">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H36" t="str">
         <v>奶油海蓝宝.png</v>
@@ -1463,7 +1463,7 @@
         <v>8</v>
       </c>
       <c r="G37">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H37" t="str">
         <v>奶油海蓝宝.png</v>
@@ -1492,7 +1492,7 @@
         <v>10</v>
       </c>
       <c r="G38">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H38" t="str">
         <v>奶油海蓝宝.png</v>
@@ -1579,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="G41">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H41" t="str">
         <v>海纹石.png</v>
@@ -1608,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="G42">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H42" t="str">
         <v>海纹石.png</v>
@@ -1637,7 +1637,7 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="H43" t="str">
         <v>海纹石.png</v>
@@ -1695,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="G45">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H45" t="str">
         <v>金发晶.png</v>
@@ -1724,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="G46">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H46" t="str">
         <v>金发晶.png</v>
@@ -1753,7 +1753,7 @@
         <v>14</v>
       </c>
       <c r="G47">
-        <v>699</v>
+        <v>499</v>
       </c>
       <c r="H47" t="str">
         <v>白水鱼尾.png</v>
@@ -1782,7 +1782,7 @@
         <v>10</v>
       </c>
       <c r="G48">
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="H48" t="str">
         <v>转运柄.png</v>
@@ -1898,7 +1898,7 @@
         <v>8</v>
       </c>
       <c r="G52">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H52" t="str">
         <v>薰衣草.png</v>
@@ -1950,13 +1950,13 @@
         <v>粉櫻花</v>
       </c>
       <c r="E54">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F54">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G54">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H54" t="str">
         <v>粉樱花.png</v>
@@ -1985,7 +1985,7 @@
         <v>10</v>
       </c>
       <c r="G55">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H55" t="str">
         <v>锆石花形钻.png</v>
@@ -2072,7 +2072,7 @@
         <v>8</v>
       </c>
       <c r="G58">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H58" t="str">
         <v>黄水晶.png</v>
@@ -2101,7 +2101,7 @@
         <v>10</v>
       </c>
       <c r="G59">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H59" t="str">
         <v>黄水晶.png</v>
@@ -2188,7 +2188,7 @@
         <v>7</v>
       </c>
       <c r="G62">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H62" t="str">
         <v>钛钢4.png</v>
@@ -2275,7 +2275,7 @@
         <v>7</v>
       </c>
       <c r="G65">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H65" t="str">
         <v>钛钢9.png</v>
@@ -2304,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="G66">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H66" t="str">
         <v>桂花.png</v>
@@ -2420,7 +2420,7 @@
         <v>6</v>
       </c>
       <c r="G70">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H70" t="str">
         <v>蜜蜡.png</v>
@@ -2449,7 +2449,7 @@
         <v>8</v>
       </c>
       <c r="G71">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H71" t="str">
         <v>蜜蜡.png</v>
@@ -2478,7 +2478,7 @@
         <v>10</v>
       </c>
       <c r="G72">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H72" t="str">
         <v>银饰R.png</v>
@@ -2536,7 +2536,7 @@
         <v>7</v>
       </c>
       <c r="G74">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H74" t="str">
         <v>钛钢7.png</v>
@@ -2623,7 +2623,7 @@
         <v>7</v>
       </c>
       <c r="G77">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H77" t="str">
         <v>钛钢0.png</v>
@@ -2681,7 +2681,7 @@
         <v>10</v>
       </c>
       <c r="G79">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H79" t="str">
         <v>银饰J.png</v>
@@ -2710,7 +2710,7 @@
         <v>7</v>
       </c>
       <c r="G80">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H80" t="str">
         <v>钛钢6.png</v>
@@ -2797,7 +2797,7 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H83" t="str">
         <v>银饰I.png</v>
@@ -2826,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="G84">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H84" t="str">
         <v>银饰U.png</v>
@@ -2855,7 +2855,7 @@
         <v>7</v>
       </c>
       <c r="G85">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H85" t="str">
         <v>钛钢3.png</v>
@@ -2884,7 +2884,7 @@
         <v>7</v>
       </c>
       <c r="G86">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H86" t="str">
         <v>钛钢2.png</v>
@@ -2913,7 +2913,7 @@
         <v>7</v>
       </c>
       <c r="G87">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H87" t="str">
         <v>钛钢8.png</v>
@@ -2942,7 +2942,7 @@
         <v>7</v>
       </c>
       <c r="G88">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H88" t="str">
         <v>钛钢5.png</v>
@@ -3000,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="G90">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H90" t="str">
         <v>银饰P.png</v>
@@ -3058,7 +3058,7 @@
         <v>8</v>
       </c>
       <c r="G92">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H92" t="str">
         <v>绿发晶.png</v>
@@ -3116,7 +3116,7 @@
         <v>10</v>
       </c>
       <c r="G94">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H94" t="str">
         <v>银饰C.png</v>
@@ -3145,7 +3145,7 @@
         <v>10</v>
       </c>
       <c r="G95">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H95" t="str">
         <v>银饰B.png</v>
@@ -3203,7 +3203,7 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H97" t="str">
         <v>银饰O.png</v>
@@ -3232,7 +3232,7 @@
         <v>10</v>
       </c>
       <c r="G98">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H98" t="str">
         <v>银饰W.png</v>
@@ -3258,7 +3258,7 @@
         <v>2</v>
       </c>
       <c r="F99">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G99">
         <v>59</v>
@@ -3319,7 +3319,7 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H101" t="str">
         <v>银饰Q.png</v>
@@ -3348,7 +3348,7 @@
         <v>10</v>
       </c>
       <c r="G102">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H102" t="str">
         <v>羽毛萤石.png</v>
@@ -3406,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="G104">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H104" t="str">
         <v>银饰F.png</v>
@@ -3461,7 +3461,7 @@
         <v>3</v>
       </c>
       <c r="F106">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G106">
         <v>299</v>
@@ -3522,7 +3522,7 @@
         <v>10</v>
       </c>
       <c r="G108">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H108" t="str">
         <v>银饰N.png</v>
@@ -3551,7 +3551,7 @@
         <v>10</v>
       </c>
       <c r="G109">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H109" t="str">
         <v>银饰M.png</v>
@@ -3580,7 +3580,7 @@
         <v>10</v>
       </c>
       <c r="G110">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H110" t="str">
         <v>银饰H.png</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="G112">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H112" t="str">
         <v>银饰G.png</v>
@@ -3696,7 +3696,7 @@
         <v>10</v>
       </c>
       <c r="G114">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H114" t="str">
         <v>银饰T.png</v>
@@ -3725,7 +3725,7 @@
         <v>10</v>
       </c>
       <c r="G115">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H115" t="str">
         <v>银饰E.png</v>
@@ -3754,7 +3754,7 @@
         <v>10</v>
       </c>
       <c r="G116">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H116" t="str">
         <v>银饰K.png</v>
@@ -3812,7 +3812,7 @@
         <v>10</v>
       </c>
       <c r="G118">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H118" t="str">
         <v>银饰V.png</v>
@@ -3870,7 +3870,7 @@
         <v>10</v>
       </c>
       <c r="G120">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H120" t="str">
         <v>银饰L.png</v>
@@ -3899,7 +3899,7 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H121" t="str">
         <v>银饰A.png</v>
@@ -3957,7 +3957,7 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H123" t="str">
         <v>银饰Y.png</v>
@@ -4073,7 +4073,7 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H127" t="str">
         <v>银饰X.png</v>
@@ -4160,7 +4160,7 @@
         <v>10</v>
       </c>
       <c r="G130">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="H130" t="str">
         <v>琥珀石.png</v>
@@ -4247,7 +4247,7 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H133" t="str">
         <v>银饰Z.png</v>
@@ -4363,7 +4363,7 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H137" t="str">
         <v>银饰D.png</v>
@@ -4450,7 +4450,7 @@
         <v>10</v>
       </c>
       <c r="G140">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="H140" t="str">
         <v>海蓝宝.png</v>
@@ -4479,7 +4479,7 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="H141" t="str">
         <v>银饰S.png</v>
@@ -4566,7 +4566,7 @@
         <v>6</v>
       </c>
       <c r="G144">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H144" t="str">
         <v>黄塔晶.png</v>
@@ -4595,7 +4595,7 @@
         <v>8</v>
       </c>
       <c r="G145">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H145" t="str">
         <v>黄塔晶.png</v>
@@ -4624,7 +4624,7 @@
         <v>10</v>
       </c>
       <c r="G146">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="H146" t="str">
         <v>黄塔晶.png</v>
@@ -4711,7 +4711,7 @@
         <v>8</v>
       </c>
       <c r="G149">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H149" t="str">
         <v>黑发晶.png</v>
@@ -4769,7 +4769,7 @@
         <v>7</v>
       </c>
       <c r="G151">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H151" t="str">
         <v>天珠.png</v>
@@ -4798,7 +4798,7 @@
         <v>4</v>
       </c>
       <c r="G152">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H152" t="str">
         <v>银色小珠.png</v>
@@ -5143,10 +5143,10 @@
         <v>2</v>
       </c>
       <c r="F164">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G164">
-        <v>599</v>
+        <v>399</v>
       </c>
       <c r="H164" t="str">
         <v>藏银羽毛.png</v>
@@ -5175,7 +5175,7 @@
         <v>6</v>
       </c>
       <c r="G165">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H165" t="str">
         <v>绿萤石.png</v>
@@ -5204,7 +5204,7 @@
         <v>8</v>
       </c>
       <c r="G166">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H166" t="str">
         <v>绿萤石.png</v>
@@ -5262,7 +5262,7 @@
         <v>8</v>
       </c>
       <c r="G168">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H168" t="str">
         <v>蔷薇石.png</v>
@@ -5291,7 +5291,7 @@
         <v>10</v>
       </c>
       <c r="G169">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H169" t="str">
         <v>蔷薇石.png</v>
@@ -5320,7 +5320,7 @@
         <v>4</v>
       </c>
       <c r="G170">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H170" t="str">
         <v>金色小珠.png</v>
@@ -5407,7 +5407,7 @@
         <v>7</v>
       </c>
       <c r="G173">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="H173" t="str">
         <v>锆石钻闪双层.png</v>
@@ -5523,7 +5523,7 @@
         <v>6</v>
       </c>
       <c r="G177">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H177" t="str">
         <v>月光石.png</v>
@@ -5639,7 +5639,7 @@
         <v>8</v>
       </c>
       <c r="G181">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H181" t="str">
         <v>太阳石.png</v>
@@ -5668,7 +5668,7 @@
         <v>10</v>
       </c>
       <c r="G182">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="H182" t="str">
         <v>太阳石.png</v>
@@ -5726,7 +5726,7 @@
         <v>10</v>
       </c>
       <c r="G184">
-        <v>699</v>
+        <v>599</v>
       </c>
       <c r="H184" t="str">
         <v>圣海蓝宝.png</v>
@@ -5871,7 +5871,7 @@
         <v>6</v>
       </c>
       <c r="G189">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H189" t="str">
         <v>紫水晶.png</v>
@@ -5929,7 +5929,7 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H191" t="str">
         <v>紫水晶.png</v>
@@ -5955,10 +5955,10 @@
         <v>2</v>
       </c>
       <c r="F192">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G192">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H192" t="str">
         <v>国王之泪.png</v>
@@ -6103,7 +6103,7 @@
         <v>8</v>
       </c>
       <c r="G197">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H197" t="str">
         <v>紫粉晶.png</v>
@@ -6132,7 +6132,7 @@
         <v>10</v>
       </c>
       <c r="G198">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H198" t="str">
         <v>紫粉晶.png</v>
@@ -6219,7 +6219,7 @@
         <v>6</v>
       </c>
       <c r="G201">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H201" t="str">
         <v>草莓晶.png</v>
@@ -6248,7 +6248,7 @@
         <v>8</v>
       </c>
       <c r="G202">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H202" t="str">
         <v>草莓晶.png</v>
@@ -6277,7 +6277,7 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H203" t="str">
         <v>草莓晶.png</v>
@@ -6332,10 +6332,10 @@
         <v>2</v>
       </c>
       <c r="F205">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G205">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H205" t="str">
         <v>藏银蝴蝶流苏.png</v>
@@ -6393,7 +6393,7 @@
         <v>8</v>
       </c>
       <c r="G207">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H207" t="str">
         <v>藏银十字.png</v>
@@ -6451,7 +6451,7 @@
         <v>11</v>
       </c>
       <c r="G209">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H209" t="str">
         <v>景泰蓝.png</v>
@@ -6509,7 +6509,7 @@
         <v>8</v>
       </c>
       <c r="G211">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H211" t="str">
         <v>黑金超.png</v>
@@ -6538,7 +6538,7 @@
         <v>10</v>
       </c>
       <c r="G212">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H212" t="str">
         <v>黑金超.png</v>
@@ -6857,7 +6857,7 @@
         <v>8</v>
       </c>
       <c r="G223">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H223" t="str">
         <v>银曜石.png</v>
@@ -6886,7 +6886,7 @@
         <v>10</v>
       </c>
       <c r="G224">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H224" t="str">
         <v>银曜石.png</v>
@@ -6912,7 +6912,7 @@
         <v>2</v>
       </c>
       <c r="F225">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G225">
         <v>69</v>
@@ -6944,7 +6944,7 @@
         <v>6</v>
       </c>
       <c r="G226">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="H226" t="str">
         <v>朱砂.png</v>
@@ -6973,7 +6973,7 @@
         <v>6</v>
       </c>
       <c r="G227">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H227" t="str">
         <v>蓝晶石.png</v>
@@ -7031,7 +7031,7 @@
         <v>10</v>
       </c>
       <c r="G229">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="H229" t="str">
         <v>蓝晶石.png</v>
@@ -7234,7 +7234,7 @@
         <v>6</v>
       </c>
       <c r="G236">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H236" t="str">
         <v>孔雀石.png</v>
@@ -7292,7 +7292,7 @@
         <v>10</v>
       </c>
       <c r="G238">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="H238" t="str">
         <v>孔雀石.png</v>
@@ -7321,7 +7321,7 @@
         <v>6</v>
       </c>
       <c r="G239">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H239" t="str">
         <v>青金石.png</v>
@@ -7408,7 +7408,7 @@
         <v>6</v>
       </c>
       <c r="G242">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H242" t="str">
         <v>乌拉圭.png</v>
@@ -7437,7 +7437,7 @@
         <v>8</v>
       </c>
       <c r="G243">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H243" t="str">
         <v>乌拉圭.png</v>
@@ -7466,7 +7466,7 @@
         <v>10</v>
       </c>
       <c r="G244">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="H244" t="str">
         <v>乌拉圭.png</v>
@@ -7495,7 +7495,7 @@
         <v>6</v>
       </c>
       <c r="G245">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H245" t="str">
         <v>紫幽灵.png</v>
@@ -7640,7 +7640,7 @@
         <v>6</v>
       </c>
       <c r="G250">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H250" t="str">
         <v>紫金砂.png</v>
@@ -7669,7 +7669,7 @@
         <v>8</v>
       </c>
       <c r="G251">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H251" t="str">
         <v>紫金砂.png</v>
@@ -7698,7 +7698,7 @@
         <v>10</v>
       </c>
       <c r="G252">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="H252" t="str">
         <v>紫金砂.png</v>
@@ -7756,7 +7756,7 @@
         <v>8</v>
       </c>
       <c r="G254">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H254" t="str">
         <v>金曜石.png</v>
@@ -7785,7 +7785,7 @@
         <v>10</v>
       </c>
       <c r="G255">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H255" t="str">
         <v>金曜石.png</v>
@@ -7843,7 +7843,7 @@
         <v>8</v>
       </c>
       <c r="G257">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H257" t="str">
         <v>黑曜石.png</v>
@@ -7872,7 +7872,7 @@
         <v>10</v>
       </c>
       <c r="G258">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H258" t="str">
         <v>黑曜石.png</v>

--- a/data/commodity_idx.xlsx
+++ b/data/commodity_idx.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I258"/>
+  <dimension ref="A1:I260"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7216,36 +7216,36 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>kqs_stn_6</v>
+        <v>slft_ft_8</v>
       </c>
       <c r="B236" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C236" t="str">
-        <v>礦石</v>
+        <v>方糖</v>
       </c>
       <c r="D236" t="str">
-        <v>孔雀石</v>
+        <v>聖藍方糖</v>
       </c>
       <c r="E236">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F236">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G236">
         <v>59</v>
       </c>
       <c r="H236" t="str">
-        <v>孔雀石.png</v>
+        <v>圣蓝方糖.png</v>
       </c>
       <c r="I236" t="str">
-        <v/>
+        <v>龍海市上全</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>kqs_stn_8</v>
+        <v>kqs_stn_6</v>
       </c>
       <c r="B237" t="str">
         <v>珠子</v>
@@ -7257,13 +7257,13 @@
         <v>孔雀石</v>
       </c>
       <c r="E237">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F237">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G237">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H237" t="str">
         <v>孔雀石.png</v>
@@ -7274,7 +7274,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>kqs_stn_10</v>
+        <v>kqs_stn_8</v>
       </c>
       <c r="B238" t="str">
         <v>珠子</v>
@@ -7286,13 +7286,13 @@
         <v>孔雀石</v>
       </c>
       <c r="E238">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F238">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G238">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="H238" t="str">
         <v>孔雀石.png</v>
@@ -7303,7 +7303,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>qjs_stn_6</v>
+        <v>kqs_stn_10</v>
       </c>
       <c r="B239" t="str">
         <v>珠子</v>
@@ -7312,19 +7312,19 @@
         <v>礦石</v>
       </c>
       <c r="D239" t="str">
-        <v>青金石</v>
+        <v>孔雀石</v>
       </c>
       <c r="E239">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F239">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G239">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="H239" t="str">
-        <v>青金石.png</v>
+        <v>孔雀石.png</v>
       </c>
       <c r="I239" t="str">
         <v/>
@@ -7332,7 +7332,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>qjs_stn_8</v>
+        <v>qjs_stn_6</v>
       </c>
       <c r="B240" t="str">
         <v>珠子</v>
@@ -7344,13 +7344,13 @@
         <v>青金石</v>
       </c>
       <c r="E240">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F240">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G240">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H240" t="str">
         <v>青金石.png</v>
@@ -7361,7 +7361,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>qjs_stn_10</v>
+        <v>qjs_stn_8</v>
       </c>
       <c r="B241" t="str">
         <v>珠子</v>
@@ -7373,13 +7373,13 @@
         <v>青金石</v>
       </c>
       <c r="E241">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F241">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G241">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H241" t="str">
         <v>青金石.png</v>
@@ -7390,28 +7390,28 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>wlg_cysl_6</v>
+        <v>qjs_stn_10</v>
       </c>
       <c r="B242" t="str">
         <v>珠子</v>
       </c>
       <c r="C242" t="str">
-        <v>水晶</v>
+        <v>礦石</v>
       </c>
       <c r="D242" t="str">
-        <v>烏拉圭</v>
+        <v>青金石</v>
       </c>
       <c r="E242">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F242">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G242">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H242" t="str">
-        <v>乌拉圭.png</v>
+        <v>青金石.png</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -7419,7 +7419,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>wlg_cysl_8</v>
+        <v>wlg_cysl_6</v>
       </c>
       <c r="B243" t="str">
         <v>珠子</v>
@@ -7431,13 +7431,13 @@
         <v>烏拉圭</v>
       </c>
       <c r="E243">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F243">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G243">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H243" t="str">
         <v>乌拉圭.png</v>
@@ -7448,7 +7448,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>wlg_cysl_10</v>
+        <v>wlg_cysl_8</v>
       </c>
       <c r="B244" t="str">
         <v>珠子</v>
@@ -7460,13 +7460,13 @@
         <v>烏拉圭</v>
       </c>
       <c r="E244">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F244">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G244">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="H244" t="str">
         <v>乌拉圭.png</v>
@@ -7477,7 +7477,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>zyl_cysl_6</v>
+        <v>wlg_cysl_10</v>
       </c>
       <c r="B245" t="str">
         <v>珠子</v>
@@ -7486,19 +7486,19 @@
         <v>水晶</v>
       </c>
       <c r="D245" t="str">
-        <v>紫幽靈</v>
+        <v>烏拉圭</v>
       </c>
       <c r="E245">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F245">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G245">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="H245" t="str">
-        <v>紫幽灵.png</v>
+        <v>乌拉圭.png</v>
       </c>
       <c r="I245" t="str">
         <v/>
@@ -7506,45 +7506,45 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>zyl_cysl_8</v>
+        <v>qjsph_ph_4</v>
       </c>
       <c r="B246" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="C246" t="str">
-        <v>水晶</v>
+        <v>跑環</v>
       </c>
       <c r="D246" t="str">
-        <v>紫幽靈</v>
+        <v>青金石跑環</v>
       </c>
       <c r="E246">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F246">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G246">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H246" t="str">
-        <v>紫幽灵.png</v>
+        <v>青金石跑环.png</v>
       </c>
       <c r="I246" t="str">
-        <v/>
+        <v>義烏晶德</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>he_agt_6</v>
+        <v>zyl_cysl_6</v>
       </c>
       <c r="B247" t="str">
         <v>珠子</v>
       </c>
       <c r="C247" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D247" t="str">
-        <v>黑瑪瑙</v>
+        <v>紫幽靈</v>
       </c>
       <c r="E247">
         <v>6</v>
@@ -7553,10 +7553,10 @@
         <v>6</v>
       </c>
       <c r="G247">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H247" t="str">
-        <v>黑玛瑙.png</v>
+        <v>紫幽灵.png</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -7564,16 +7564,16 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>he_agt_8</v>
+        <v>zyl_cysl_8</v>
       </c>
       <c r="B248" t="str">
         <v>珠子</v>
       </c>
       <c r="C248" t="str">
-        <v>瑪瑙</v>
+        <v>水晶</v>
       </c>
       <c r="D248" t="str">
-        <v>黑瑪瑙</v>
+        <v>紫幽靈</v>
       </c>
       <c r="E248">
         <v>8</v>
@@ -7585,7 +7585,7 @@
         <v>59</v>
       </c>
       <c r="H248" t="str">
-        <v>黑玛瑙.png</v>
+        <v>紫幽灵.png</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>he_agt_10</v>
+        <v>he_agt_6</v>
       </c>
       <c r="B249" t="str">
         <v>珠子</v>
@@ -7605,13 +7605,13 @@
         <v>黑瑪瑙</v>
       </c>
       <c r="E249">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F249">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G249">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H249" t="str">
         <v>黑玛瑙.png</v>
@@ -7622,28 +7622,28 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>zjs_stn_6</v>
+        <v>he_agt_8</v>
       </c>
       <c r="B250" t="str">
         <v>珠子</v>
       </c>
       <c r="C250" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D250" t="str">
-        <v>紫金砂</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E250">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F250">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G250">
         <v>59</v>
       </c>
       <c r="H250" t="str">
-        <v>紫金砂.png</v>
+        <v>黑玛瑙.png</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -7651,28 +7651,28 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>zjs_stn_8</v>
+        <v>he_agt_10</v>
       </c>
       <c r="B251" t="str">
         <v>珠子</v>
       </c>
       <c r="C251" t="str">
-        <v>礦石</v>
+        <v>瑪瑙</v>
       </c>
       <c r="D251" t="str">
-        <v>紫金砂</v>
+        <v>黑瑪瑙</v>
       </c>
       <c r="E251">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F251">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G251">
         <v>89</v>
       </c>
       <c r="H251" t="str">
-        <v>紫金砂.png</v>
+        <v>黑玛瑙.png</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -7680,7 +7680,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>zjs_stn_10</v>
+        <v>zjs_stn_6</v>
       </c>
       <c r="B252" t="str">
         <v>珠子</v>
@@ -7692,13 +7692,13 @@
         <v>紫金砂</v>
       </c>
       <c r="E252">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F252">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G252">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="H252" t="str">
         <v>紫金砂.png</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>jys_stn_6</v>
+        <v>zjs_stn_8</v>
       </c>
       <c r="B253" t="str">
         <v>珠子</v>
@@ -7718,19 +7718,19 @@
         <v>礦石</v>
       </c>
       <c r="D253" t="str">
-        <v>金曜石</v>
+        <v>紫金砂</v>
       </c>
       <c r="E253">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F253">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G253">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H253" t="str">
-        <v>金曜石.png</v>
+        <v>紫金砂.png</v>
       </c>
       <c r="I253" t="str">
         <v/>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>jys_stn_8</v>
+        <v>zjs_stn_10</v>
       </c>
       <c r="B254" t="str">
         <v>珠子</v>
@@ -7747,19 +7747,19 @@
         <v>礦石</v>
       </c>
       <c r="D254" t="str">
-        <v>金曜石</v>
+        <v>紫金砂</v>
       </c>
       <c r="E254">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F254">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G254">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H254" t="str">
-        <v>金曜石.png</v>
+        <v>紫金砂.png</v>
       </c>
       <c r="I254" t="str">
         <v/>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>jys_stn_10</v>
+        <v>jys_stn_6</v>
       </c>
       <c r="B255" t="str">
         <v>珠子</v>
@@ -7779,13 +7779,13 @@
         <v>金曜石</v>
       </c>
       <c r="E255">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F255">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G255">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H255" t="str">
         <v>金曜石.png</v>
@@ -7796,7 +7796,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>hys_stn_6</v>
+        <v>jys_stn_8</v>
       </c>
       <c r="B256" t="str">
         <v>珠子</v>
@@ -7805,19 +7805,19 @@
         <v>礦石</v>
       </c>
       <c r="D256" t="str">
-        <v>黑曜石</v>
+        <v>金曜石</v>
       </c>
       <c r="E256">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F256">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G256">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H256" t="str">
-        <v>黑曜石.png</v>
+        <v>金曜石.png</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>hys_stn_8</v>
+        <v>jys_stn_10</v>
       </c>
       <c r="B257" t="str">
         <v>珠子</v>
@@ -7834,19 +7834,19 @@
         <v>礦石</v>
       </c>
       <c r="D257" t="str">
-        <v>黑曜石</v>
+        <v>金曜石</v>
       </c>
       <c r="E257">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F257">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G257">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="H257" t="str">
-        <v>黑曜石.png</v>
+        <v>金曜石.png</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -7854,7 +7854,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>hys_stn_10</v>
+        <v>hys_stn_6</v>
       </c>
       <c r="B258" t="str">
         <v>珠子</v>
@@ -7866,13 +7866,13 @@
         <v>黑曜石</v>
       </c>
       <c r="E258">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F258">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G258">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H258" t="str">
         <v>黑曜石.png</v>
@@ -7881,9 +7881,67 @@
         <v/>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>hys_stn_8</v>
+      </c>
+      <c r="B259" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C259" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D259" t="str">
+        <v>黑曜石</v>
+      </c>
+      <c r="E259">
+        <v>8</v>
+      </c>
+      <c r="F259">
+        <v>8</v>
+      </c>
+      <c r="G259">
+        <v>59</v>
+      </c>
+      <c r="H259" t="str">
+        <v>黑曜石.png</v>
+      </c>
+      <c r="I259" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>hys_stn_10</v>
+      </c>
+      <c r="B260" t="str">
+        <v>珠子</v>
+      </c>
+      <c r="C260" t="str">
+        <v>礦石</v>
+      </c>
+      <c r="D260" t="str">
+        <v>黑曜石</v>
+      </c>
+      <c r="E260">
+        <v>10</v>
+      </c>
+      <c r="F260">
+        <v>10</v>
+      </c>
+      <c r="G260">
+        <v>89</v>
+      </c>
+      <c r="H260" t="str">
+        <v>黑曜石.png</v>
+      </c>
+      <c r="I260" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I258"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I260"/>
   </ignoredErrors>
 </worksheet>
 </file>